--- a/database/event/7908/event_7908_evp_summary.xlsx
+++ b/database/event/7908/event_7908_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -508,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.3945</v>
+        <v>9.0244</v>
       </c>
       <c r="C2" t="n">
-        <v>9.115600000000001</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>6.938505474037123</v>
+        <v>3.2243</v>
       </c>
       <c r="E2" t="n">
-        <v>86.4718</v>
+        <v>9.0244</v>
       </c>
       <c r="F2" t="n">
-        <v>10.2785369869153</v>
+        <v>4.4</v>
       </c>
       <c r="G2" t="n">
-        <v>76.19326319630194</v>
+        <v>4.6243</v>
       </c>
       <c r="H2" t="n">
-        <v>10.2785369869153</v>
+        <v>5.1419</v>
       </c>
       <c r="I2" t="n">
-        <v>8.286287553312224</v>
+        <v>4.1677</v>
       </c>
       <c r="J2" t="n">
-        <v>76.19326319630194</v>
+        <v>4.6243</v>
       </c>
       <c r="K2" t="n">
         <v>97</v>
@@ -541,7 +529,7 @@
         <v>156</v>
       </c>
       <c r="M2" t="n">
-        <v>84.4796</v>
+        <v>8.792</v>
       </c>
       <c r="N2" t="n">
         <v>253</v>
@@ -550,47 +538,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.5641</v>
+        <v>6.7257</v>
       </c>
       <c r="C3" t="n">
-        <v>7.65128</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.691270679765893</v>
+        <v>2.2957</v>
       </c>
       <c r="E3" t="n">
-        <v>58.4654</v>
+        <v>6.7257</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.347595183788953</v>
+        <v>3.8343</v>
       </c>
       <c r="G3" t="n">
-        <v>61.81301289427897</v>
+        <v>2.8914</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.347595183788953</v>
+        <v>3.8343</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.698743638347616</v>
+        <v>3.1078</v>
       </c>
       <c r="J3" t="n">
-        <v>61.81301289427897</v>
+        <v>2.8914</v>
       </c>
       <c r="K3" t="n">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="L3" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="M3" t="n">
-        <v>59.1143</v>
+        <v>5.9992</v>
       </c>
       <c r="N3" t="n">
-        <v>253</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4">
@@ -600,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.5594</v>
+        <v>6.4669</v>
       </c>
       <c r="C4" t="n">
-        <v>6.84752</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3.741013276962943</v>
+        <v>2.1911</v>
       </c>
       <c r="E4" t="n">
-        <v>46.6227</v>
+        <v>6.4669</v>
       </c>
       <c r="F4" t="n">
-        <v>4.210934571769144</v>
+        <v>2.9425</v>
       </c>
       <c r="G4" t="n">
-        <v>42.4118077145579</v>
+        <v>3.5244</v>
       </c>
       <c r="H4" t="n">
-        <v>4.210934571769144</v>
+        <v>2.9425</v>
       </c>
       <c r="I4" t="n">
-        <v>3.990007599120027</v>
+        <v>2.385</v>
       </c>
       <c r="J4" t="n">
-        <v>42.4118077145579</v>
+        <v>3.5244</v>
       </c>
       <c r="K4" t="n">
         <v>134</v>
@@ -633,7 +621,7 @@
         <v>151</v>
       </c>
       <c r="M4" t="n">
-        <v>46.4018</v>
+        <v>5.9094</v>
       </c>
       <c r="N4" t="n">
         <v>285</v>
@@ -642,47 +630,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.1825</v>
+        <v>5.7281</v>
       </c>
       <c r="C5" t="n">
-        <v>5.746</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2.691057481233205</v>
+        <v>1.8927</v>
       </c>
       <c r="E5" t="n">
-        <v>33.5376</v>
+        <v>5.7281</v>
       </c>
       <c r="F5" t="n">
-        <v>5.73946948545959</v>
+        <v>4.428</v>
       </c>
       <c r="G5" t="n">
-        <v>27.79809644563051</v>
+        <v>1.3001</v>
       </c>
       <c r="H5" t="n">
-        <v>5.73946948545959</v>
+        <v>5.2543</v>
       </c>
       <c r="I5" t="n">
-        <v>5.438347823172199</v>
+        <v>4.2587</v>
       </c>
       <c r="J5" t="n">
-        <v>27.79809644563051</v>
+        <v>1.3001</v>
       </c>
       <c r="K5" t="n">
-        <v>134</v>
+        <v>215</v>
       </c>
       <c r="L5" t="n">
-        <v>151</v>
+        <v>49</v>
       </c>
       <c r="M5" t="n">
-        <v>33.2364</v>
+        <v>5.5588</v>
       </c>
       <c r="N5" t="n">
-        <v>285</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6">
@@ -692,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.8778</v>
+        <v>5.2476</v>
       </c>
       <c r="C6" t="n">
-        <v>5.50224</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2.492117005096805</v>
+        <v>1.6986</v>
       </c>
       <c r="E6" t="n">
-        <v>31.0583</v>
+        <v>5.2476</v>
       </c>
       <c r="F6" t="n">
-        <v>5.774620826414676</v>
+        <v>3.3636</v>
       </c>
       <c r="G6" t="n">
-        <v>25.28363004681591</v>
+        <v>1.884</v>
       </c>
       <c r="H6" t="n">
-        <v>5.774620826414676</v>
+        <v>3.3636</v>
       </c>
       <c r="I6" t="n">
-        <v>5.471654946600413</v>
+        <v>2.7263</v>
       </c>
       <c r="J6" t="n">
-        <v>25.28363004681591</v>
+        <v>1.884</v>
       </c>
       <c r="K6" t="n">
         <v>134</v>
@@ -725,7 +713,7 @@
         <v>151</v>
       </c>
       <c r="M6" t="n">
-        <v>30.7553</v>
+        <v>4.610300000000001</v>
       </c>
       <c r="N6" t="n">
         <v>285</v>
@@ -738,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.4527</v>
+        <v>4.9586</v>
       </c>
       <c r="C7" t="n">
-        <v>4.36216</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1.695007475038313</v>
+        <v>1.5818</v>
       </c>
       <c r="E7" t="n">
-        <v>21.1242</v>
+        <v>4.9586</v>
       </c>
       <c r="F7" t="n">
-        <v>3.747482469542665</v>
+        <v>3.2657</v>
       </c>
       <c r="G7" t="n">
-        <v>17.37671325805566</v>
+        <v>1.6929</v>
       </c>
       <c r="H7" t="n">
-        <v>3.747482469542665</v>
+        <v>3.2657</v>
       </c>
       <c r="I7" t="n">
-        <v>4.142945443715509</v>
+        <v>2.647</v>
       </c>
       <c r="J7" t="n">
-        <v>17.37671325805566</v>
+        <v>1.6929</v>
       </c>
       <c r="K7" t="n">
         <v>165</v>
@@ -771,7 +759,7 @@
         <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>21.5197</v>
+        <v>4.3399</v>
       </c>
       <c r="N7" t="n">
         <v>209</v>
@@ -780,507 +768,507 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.4217</v>
+        <v>3.2238</v>
       </c>
       <c r="C8" t="n">
-        <v>4.33736</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1.67984157466164</v>
+        <v>0.881</v>
       </c>
       <c r="E8" t="n">
-        <v>20.9352</v>
+        <v>3.2238</v>
       </c>
       <c r="F8" t="n">
-        <v>7.592585870721864</v>
+        <v>3.3595</v>
       </c>
       <c r="G8" t="n">
-        <v>13.34260334648637</v>
+        <v>-0.1357</v>
       </c>
       <c r="H8" t="n">
-        <v>7.592585870721864</v>
+        <v>3.3595</v>
       </c>
       <c r="I8" t="n">
-        <v>10.93739338160939</v>
+        <v>2.723</v>
       </c>
       <c r="J8" t="n">
-        <v>13.34260334648637</v>
+        <v>-0.1357</v>
       </c>
       <c r="K8" t="n">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="L8" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M8" t="n">
-        <v>24.28</v>
+        <v>2.5873</v>
       </c>
       <c r="N8" t="n">
-        <v>264</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.0744</v>
+        <v>3.0029</v>
       </c>
       <c r="C9" t="n">
-        <v>4.05952</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1.51586228997652</v>
+        <v>0.7917</v>
       </c>
       <c r="E9" t="n">
-        <v>18.8916</v>
+        <v>3.0029</v>
       </c>
       <c r="F9" t="n">
-        <v>2.553988938807821</v>
+        <v>3.0029</v>
       </c>
       <c r="G9" t="n">
-        <v>16.33759247373174</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.553988938807821</v>
+        <v>3.0029</v>
       </c>
       <c r="I9" t="n">
-        <v>2.419993733037363</v>
+        <v>3.0029</v>
       </c>
       <c r="J9" t="n">
-        <v>16.33759247373174</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="L9" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>18.7576</v>
+        <v>3.0029</v>
       </c>
       <c r="N9" t="n">
-        <v>285</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3417</v>
+        <v>2.9487</v>
       </c>
       <c r="C10" t="n">
-        <v>2.67336</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.836000661696103</v>
+        <v>0.7698</v>
       </c>
       <c r="E10" t="n">
-        <v>10.4187</v>
+        <v>2.9487</v>
       </c>
       <c r="F10" t="n">
-        <v>10.41873966111625</v>
+        <v>2.9487</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>10.41873966111625</v>
+        <v>2.9487</v>
       </c>
       <c r="I10" t="n">
-        <v>12.5653141641603</v>
+        <v>2.9487</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>180</v>
+        <v>121</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>12.5653</v>
+        <v>2.9487</v>
       </c>
       <c r="N10" t="n">
-        <v>180</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8839</v>
+        <v>2.7605</v>
       </c>
       <c r="C11" t="n">
-        <v>2.30712</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.689361642553323</v>
+        <v>0.6938</v>
       </c>
       <c r="E11" t="n">
-        <v>8.591200000000001</v>
+        <v>2.7605</v>
       </c>
       <c r="F11" t="n">
-        <v>2.780571680624665</v>
+        <v>3.7605</v>
       </c>
       <c r="G11" t="n">
-        <v>5.810664923842765</v>
+        <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>2.780571680624665</v>
+        <v>3.7605</v>
       </c>
       <c r="I11" t="n">
-        <v>4.005513643780924</v>
+        <v>3.048</v>
       </c>
       <c r="J11" t="n">
-        <v>5.810664923842765</v>
+        <v>-1</v>
       </c>
       <c r="K11" t="n">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="L11" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M11" t="n">
-        <v>9.8162</v>
+        <v>2.048</v>
       </c>
       <c r="N11" t="n">
-        <v>264</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7557</v>
+        <v>2.4159</v>
       </c>
       <c r="C12" t="n">
-        <v>2.20456</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6504454768154384</v>
+        <v>0.5546</v>
       </c>
       <c r="E12" t="n">
-        <v>8.106199999999999</v>
+        <v>2.4159</v>
       </c>
       <c r="F12" t="n">
-        <v>8.10624009907081</v>
+        <v>3.2278</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.8119</v>
       </c>
       <c r="H12" t="n">
-        <v>8.10624009907081</v>
+        <v>3.2278</v>
       </c>
       <c r="I12" t="n">
-        <v>7.298859071391837</v>
+        <v>2.6162</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.8119</v>
       </c>
       <c r="K12" t="n">
-        <v>121</v>
+        <v>215</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M12" t="n">
-        <v>7.2989</v>
+        <v>1.8043</v>
       </c>
       <c r="N12" t="n">
-        <v>121</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5986</v>
+        <v>2.2413</v>
       </c>
       <c r="C13" t="n">
-        <v>2.07888</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6039449704054174</v>
+        <v>0.4841</v>
       </c>
       <c r="E13" t="n">
-        <v>7.5267</v>
+        <v>2.2413</v>
       </c>
       <c r="F13" t="n">
-        <v>5.067193506827592</v>
+        <v>2.2413</v>
       </c>
       <c r="G13" t="n">
-        <v>2.459529502611787</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.067193506827592</v>
+        <v>2.2413</v>
       </c>
       <c r="I13" t="n">
-        <v>5.601922469859649</v>
+        <v>2.2413</v>
       </c>
       <c r="J13" t="n">
-        <v>2.459529502611787</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="L13" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>8.061500000000001</v>
+        <v>2.2413</v>
       </c>
       <c r="N13" t="n">
-        <v>209</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9962</v>
+        <v>2.0494</v>
       </c>
       <c r="C14" t="n">
-        <v>1.59696</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4375492981000612</v>
+        <v>0.4065</v>
       </c>
       <c r="E14" t="n">
-        <v>5.453</v>
+        <v>2.0494</v>
       </c>
       <c r="F14" t="n">
-        <v>5.453000738731276</v>
+        <v>1.0559</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.9935</v>
       </c>
       <c r="H14" t="n">
-        <v>5.453000738731276</v>
+        <v>1.0559</v>
       </c>
       <c r="I14" t="n">
-        <v>6.576483302992494</v>
+        <v>0.8558</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.9935</v>
       </c>
       <c r="K14" t="n">
-        <v>180</v>
+        <v>134</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M14" t="n">
-        <v>6.5765</v>
+        <v>1.8493</v>
       </c>
       <c r="N14" t="n">
-        <v>180</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9125</v>
+        <v>2.0431</v>
       </c>
       <c r="C15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.415836720703204</v>
+        <v>0.404</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1824</v>
+        <v>2.0431</v>
       </c>
       <c r="F15" t="n">
-        <v>5.18240562842271</v>
+        <v>3.008</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.9649</v>
       </c>
       <c r="H15" t="n">
-        <v>5.18240562842271</v>
+        <v>3.008</v>
       </c>
       <c r="I15" t="n">
-        <v>4.666238338657282</v>
+        <v>2.4381</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.9649</v>
       </c>
       <c r="K15" t="n">
-        <v>121</v>
+        <v>215</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6662</v>
+        <v>1.4732</v>
       </c>
       <c r="N15" t="n">
-        <v>121</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8433</v>
+        <v>1.8709</v>
       </c>
       <c r="C16" t="n">
-        <v>1.47464</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3981505508195917</v>
+        <v>0.3344</v>
       </c>
       <c r="E16" t="n">
-        <v>4.962</v>
+        <v>1.8709</v>
       </c>
       <c r="F16" t="n">
-        <v>4.961990013863525</v>
+        <v>1.4933</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.3776</v>
       </c>
       <c r="H16" t="n">
-        <v>4.961990013863525</v>
+        <v>1.4933</v>
       </c>
       <c r="I16" t="n">
-        <v>5.38587860801267</v>
+        <v>1.2104</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.3776</v>
       </c>
       <c r="K16" t="n">
-        <v>162</v>
+        <v>215</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M16" t="n">
-        <v>5.3859</v>
+        <v>1.588</v>
       </c>
       <c r="N16" t="n">
-        <v>162</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>kyousuke</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6806</v>
+        <v>1.6669</v>
       </c>
       <c r="C17" t="n">
-        <v>1.34448</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3573904776921675</v>
+        <v>0.252</v>
       </c>
       <c r="E17" t="n">
-        <v>4.454</v>
+        <v>1.6669</v>
       </c>
       <c r="F17" t="n">
-        <v>4.454013633054074</v>
+        <v>1.7033</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.0364</v>
       </c>
       <c r="H17" t="n">
-        <v>4.454013633054074</v>
+        <v>1.7033</v>
       </c>
       <c r="I17" t="n">
-        <v>3.99378788408455</v>
+        <v>1.3806</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.0364</v>
       </c>
       <c r="K17" t="n">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9938</v>
+        <v>1.3442</v>
       </c>
       <c r="N17" t="n">
-        <v>120</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5426</v>
+        <v>1.6126</v>
       </c>
       <c r="C18" t="n">
-        <v>1.23408</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3237495014169</v>
+        <v>0.2301</v>
       </c>
       <c r="E18" t="n">
-        <v>4.0348</v>
+        <v>1.6126</v>
       </c>
       <c r="F18" t="n">
-        <v>5.164223312808135</v>
+        <v>1.6126</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.129463622743415</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>5.164223312808135</v>
+        <v>1.6126</v>
       </c>
       <c r="I18" t="n">
-        <v>7.439249663341702</v>
+        <v>1.6126</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.129463622743415</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="L18" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>6.3098</v>
+        <v>1.6126</v>
       </c>
       <c r="N18" t="n">
-        <v>264</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19">
@@ -1290,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4515</v>
+        <v>1.3642</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1612</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3020053144232095</v>
+        <v>0.1297</v>
       </c>
       <c r="E19" t="n">
-        <v>3.7638</v>
+        <v>1.3642</v>
       </c>
       <c r="F19" t="n">
-        <v>3.763770642077287</v>
+        <v>1.3642</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.763770642077287</v>
+        <v>1.3642</v>
       </c>
       <c r="I19" t="n">
-        <v>3.374866542223469</v>
+        <v>1.3642</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1323,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3749</v>
+        <v>1.3642</v>
       </c>
       <c r="N19" t="n">
         <v>120</v>
@@ -1332,219 +1320,219 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kvem</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.439</v>
+        <v>1.0816</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1512</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2990585513570827</v>
+        <v>0.0156</v>
       </c>
       <c r="E20" t="n">
-        <v>3.727</v>
+        <v>1.0816</v>
       </c>
       <c r="F20" t="n">
-        <v>3.727046320392325</v>
+        <v>1.0816</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3.727046320392325</v>
+        <v>1.0816</v>
       </c>
       <c r="I20" t="n">
-        <v>4.045437212084131</v>
+        <v>1.0816</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.0454</v>
+        <v>1.0816</v>
       </c>
       <c r="N20" t="n">
-        <v>162</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4134</v>
+        <v>1.0439</v>
       </c>
       <c r="C21" t="n">
-        <v>1.13072</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2930100658729521</v>
+        <v>0.0004</v>
       </c>
       <c r="E21" t="n">
-        <v>3.6517</v>
+        <v>1.0439</v>
       </c>
       <c r="F21" t="n">
-        <v>3.65166648100877</v>
+        <v>-3.1518</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>4.1957</v>
       </c>
       <c r="H21" t="n">
-        <v>3.65166648100877</v>
+        <v>-3.1518</v>
       </c>
       <c r="I21" t="n">
-        <v>3.963617888934142</v>
+        <v>-2.5546</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>4.1957</v>
       </c>
       <c r="K21" t="n">
-        <v>162</v>
+        <v>97</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9636</v>
+        <v>1.6411</v>
       </c>
       <c r="N21" t="n">
-        <v>162</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2741</v>
+        <v>0.9709</v>
       </c>
       <c r="C22" t="n">
-        <v>1.01928</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2606754085242923</v>
+        <v>-0.0291</v>
       </c>
       <c r="E22" t="n">
-        <v>3.2487</v>
+        <v>0.9709</v>
       </c>
       <c r="F22" t="n">
-        <v>3.24869266485939</v>
+        <v>0.9709</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.24869266485939</v>
+        <v>0.9709</v>
       </c>
       <c r="I22" t="n">
-        <v>3.918021304353033</v>
+        <v>0.9709</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>180</v>
+        <v>121</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.918</v>
+        <v>0.9709</v>
       </c>
       <c r="N22" t="n">
-        <v>180</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>Kvem</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0166</v>
+        <v>0.803</v>
       </c>
       <c r="C23" t="n">
-        <v>0.81328</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2030278416772985</v>
+        <v>-0.097</v>
       </c>
       <c r="E23" t="n">
-        <v>2.5303</v>
+        <v>0.803</v>
       </c>
       <c r="F23" t="n">
-        <v>2.530254248964982</v>
+        <v>0.803</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.530254248964982</v>
+        <v>0.803</v>
       </c>
       <c r="I23" t="n">
-        <v>2.278241077525291</v>
+        <v>0.803</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.2782</v>
+        <v>0.803</v>
       </c>
       <c r="N23" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8365</v>
+        <v>0.7015</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6692</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1642759497343972</v>
+        <v>-0.138</v>
       </c>
       <c r="E24" t="n">
-        <v>2.0473</v>
+        <v>0.7015</v>
       </c>
       <c r="F24" t="n">
-        <v>5.376093194375893</v>
+        <v>1.7015</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.32878817263959</v>
+        <v>-1</v>
       </c>
       <c r="H24" t="n">
-        <v>5.376093194375893</v>
+        <v>1.7015</v>
       </c>
       <c r="I24" t="n">
-        <v>5.943419611872846</v>
+        <v>1.3791</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.32878817263959</v>
+        <v>-1</v>
       </c>
       <c r="K24" t="n">
         <v>165</v>
@@ -1553,7 +1541,7 @@
         <v>44</v>
       </c>
       <c r="M24" t="n">
-        <v>2.6146</v>
+        <v>0.3791</v>
       </c>
       <c r="N24" t="n">
         <v>209</v>
@@ -1562,32 +1550,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7811</v>
+        <v>0.6704</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6248800000000001</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1525889028056178</v>
+        <v>-0.1505</v>
       </c>
       <c r="E25" t="n">
-        <v>1.9017</v>
+        <v>0.6704</v>
       </c>
       <c r="F25" t="n">
-        <v>1.901654061232084</v>
+        <v>0.6704</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.901654061232084</v>
+        <v>0.6704</v>
       </c>
       <c r="I25" t="n">
-        <v>1.705159340579116</v>
+        <v>0.6704</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1599,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.7052</v>
+        <v>0.6704</v>
       </c>
       <c r="N25" t="n">
         <v>120</v>
@@ -1608,633 +1596,633 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7595</v>
+        <v>0.3872</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6076</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1480830408537995</v>
+        <v>-0.2649</v>
       </c>
       <c r="E26" t="n">
-        <v>1.8455</v>
+        <v>0.3872</v>
       </c>
       <c r="F26" t="n">
-        <v>1.845499317849848</v>
+        <v>2.0732</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-1.686</v>
       </c>
       <c r="H26" t="n">
-        <v>1.845499317849848</v>
+        <v>2.0732</v>
       </c>
       <c r="I26" t="n">
-        <v>2.003155038470187</v>
+        <v>1.6804</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-1.686</v>
       </c>
       <c r="K26" t="n">
-        <v>162</v>
+        <v>97</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M26" t="n">
-        <v>2.0032</v>
+        <v>-0.005600000000000049</v>
       </c>
       <c r="N26" t="n">
-        <v>162</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.3015</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5584800000000001</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1353438857801477</v>
+        <v>-0.2996</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6867</v>
+        <v>0.3015</v>
       </c>
       <c r="F27" t="n">
-        <v>4.548689958601412</v>
+        <v>0.3015</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.86195360147182</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>4.548689958601412</v>
+        <v>0.3015</v>
       </c>
       <c r="I27" t="n">
-        <v>6.552551699157814</v>
+        <v>0.3015</v>
       </c>
       <c r="J27" t="n">
-        <v>-2.86195360147182</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>215</v>
+        <v>121</v>
       </c>
       <c r="L27" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6906</v>
+        <v>0.3015</v>
       </c>
       <c r="N27" t="n">
-        <v>264</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2099</v>
+        <v>0.1261</v>
       </c>
       <c r="C28" t="n">
-        <v>0.16792</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0388955117750107</v>
+        <v>-0.3704</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4847</v>
+        <v>0.1261</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4847391033728978</v>
+        <v>0.1261</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4847391033728978</v>
+        <v>0.1261</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4346518258555999</v>
+        <v>0.1261</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4347</v>
+        <v>0.1261</v>
       </c>
       <c r="N28" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1384</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>0.11072</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02547627691077413</v>
+        <v>-0.3947</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3175</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3175005820322546</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3175005820322546</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2858775431045947</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2859</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kyousuke</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1103</v>
+        <v>0.0565</v>
       </c>
       <c r="C30" t="n">
-        <v>0.08824</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.02026396172474065</v>
+        <v>-0.3985</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2525</v>
+        <v>0.0565</v>
       </c>
       <c r="F30" t="n">
-        <v>4.162295349548404</v>
+        <v>0.0565</v>
       </c>
       <c r="G30" t="n">
-        <v>-3.909753753128419</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>4.162295349548404</v>
+        <v>0.0565</v>
       </c>
       <c r="I30" t="n">
-        <v>3.355533593163934</v>
+        <v>0.0565</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.909753753128419</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="L30" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5542</v>
+        <v>0.0565</v>
       </c>
       <c r="N30" t="n">
-        <v>253</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0512</v>
+        <v>-0.0285</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.04096</v>
+        <v>-0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.009344898188007494</v>
+        <v>-0.4329</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1165</v>
+        <v>-0.0285</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1164617037299421</v>
+        <v>0.9715</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1164617037299421</v>
+        <v>0.9715</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1044279114605126</v>
+        <v>0.7874</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K31" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1044</v>
+        <v>-0.2126</v>
       </c>
       <c r="N31" t="n">
-        <v>120</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4462</v>
+        <v>-1.1574</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.35696</v>
+        <v>-0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.08451008246879446</v>
+        <v>-0.8889</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.0532</v>
+        <v>-1.1574</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.053215132863021</v>
+        <v>-1.1574</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.053215132863021</v>
+        <v>-1.1574</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.270209205462939</v>
+        <v>-1.1574</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>180</v>
+        <v>121</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.2702</v>
+        <v>-1.1574</v>
       </c>
       <c r="N32" t="n">
-        <v>180</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>nicx</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.52</v>
+        <v>-1.2398</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.416</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.09916648608369148</v>
+        <v>-0.9222</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.2359</v>
+        <v>-1.2398</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.235871990241638</v>
+        <v>-1.2398</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.235871990241638</v>
+        <v>-1.2398</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.341448994433135</v>
+        <v>-1.2398</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.3414</v>
+        <v>-1.2398</v>
       </c>
       <c r="N33" t="n">
-        <v>162</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0476</v>
+        <v>-1.4085</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.8380800000000002</v>
+        <v>-0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2098118813575737</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.6148</v>
+        <v>-1.4085</v>
       </c>
       <c r="F34" t="n">
-        <v>-2.614801004150642</v>
+        <v>-1.4085</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-2.614801004150642</v>
+        <v>-1.4085</v>
       </c>
       <c r="I34" t="n">
-        <v>-3.153528849226904</v>
+        <v>-1.4085</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-3.1535</v>
+        <v>-1.4085</v>
       </c>
       <c r="N34" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>nicx</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0531</v>
+        <v>-1.6</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.84248</v>
+        <v>-0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2110395401933464</v>
+        <v>-1.0677</v>
       </c>
       <c r="E35" t="n">
-        <v>-2.6301</v>
+        <v>-1.6</v>
       </c>
       <c r="F35" t="n">
-        <v>1.851345169298133</v>
+        <v>-1.6</v>
       </c>
       <c r="G35" t="n">
-        <v>-4.481445991246329</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.851345169298133</v>
+        <v>-1.6</v>
       </c>
       <c r="I35" t="n">
-        <v>2.046713252490398</v>
+        <v>-1.6</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.481445991246329</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="L35" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-2.4347</v>
+        <v>-1.6</v>
       </c>
       <c r="N35" t="n">
-        <v>209</v>
+        <v>162</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2368</v>
+        <v>-1.7381</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.98944</v>
+        <v>-0</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2521594116822989</v>
+        <v>-1.1235</v>
       </c>
       <c r="E36" t="n">
-        <v>-3.1426</v>
+        <v>-1.7381</v>
       </c>
       <c r="F36" t="n">
-        <v>-3.142561224877503</v>
+        <v>-1.7381</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-3.142561224877503</v>
+        <v>-1.7381</v>
       </c>
       <c r="I36" t="n">
-        <v>-2.829562315361299</v>
+        <v>-1.7381</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-2.8296</v>
+        <v>-1.7381</v>
       </c>
       <c r="N36" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.7168</v>
+        <v>-1.8023</v>
       </c>
       <c r="C37" t="n">
-        <v>-1.37344</v>
+        <v>-0</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3663498948747805</v>
+        <v>-1.1495</v>
       </c>
       <c r="E37" t="n">
-        <v>-4.5657</v>
+        <v>-1.8023</v>
       </c>
       <c r="F37" t="n">
-        <v>0.742107355672698</v>
+        <v>-1.8023</v>
       </c>
       <c r="G37" t="n">
-        <v>-5.307778597886546</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.742107355672698</v>
+        <v>-1.8023</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8204201922009726</v>
+        <v>-1.8023</v>
       </c>
       <c r="J37" t="n">
-        <v>-5.307778597886546</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="L37" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-4.4874</v>
+        <v>-1.8023</v>
       </c>
       <c r="N37" t="n">
-        <v>209</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.4522</v>
+        <v>-2.697</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.96176</v>
+        <v>-0</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.5618103673158537</v>
+        <v>-1.5109</v>
       </c>
       <c r="E38" t="n">
-        <v>-7.0016</v>
+        <v>-2.697</v>
       </c>
       <c r="F38" t="n">
-        <v>-5.072425577231138</v>
+        <v>-2.697</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.929190837885702</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-5.072425577231138</v>
+        <v>-2.697</v>
       </c>
       <c r="I38" t="n">
-        <v>-7.307011719294437</v>
+        <v>-2.697</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.929190837885702</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="L38" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-9.2362</v>
+        <v>-2.697</v>
       </c>
       <c r="N38" t="n">
-        <v>264</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-5.0171</v>
+        <v>-2.8405</v>
       </c>
       <c r="C39" t="n">
-        <v>-4.01368</v>
+        <v>-0</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.489807399578128</v>
+        <v>-1.5689</v>
       </c>
       <c r="E39" t="n">
-        <v>-18.5669</v>
+        <v>-2.8405</v>
       </c>
       <c r="F39" t="n">
-        <v>3.933168015197804</v>
+        <v>-1.0985</v>
       </c>
       <c r="G39" t="n">
-        <v>-22.50003781876685</v>
+        <v>-1.742</v>
       </c>
       <c r="H39" t="n">
-        <v>3.933168015197804</v>
+        <v>-1.0985</v>
       </c>
       <c r="I39" t="n">
-        <v>3.170817131942853</v>
+        <v>-0.8904</v>
       </c>
       <c r="J39" t="n">
-        <v>-22.50003781876685</v>
+        <v>-1.742</v>
       </c>
       <c r="K39" t="n">
         <v>97</v>
@@ -2243,7 +2231,7 @@
         <v>156</v>
       </c>
       <c r="M39" t="n">
-        <v>-19.3292</v>
+        <v>-2.6324</v>
       </c>
       <c r="N39" t="n">
         <v>253</v>
@@ -2252,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-5.6609</v>
+        <v>-3.2456</v>
       </c>
       <c r="C40" t="n">
-        <v>-4.52872</v>
+        <v>-0</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.798992041758809</v>
+        <v>-1.7325</v>
       </c>
       <c r="E40" t="n">
-        <v>-22.4201</v>
+        <v>-3.2456</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.140452140923768</v>
+        <v>-2.0796</v>
       </c>
       <c r="G40" t="n">
-        <v>-21.27966137606579</v>
+        <v>-1.166</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.140452140923768</v>
+        <v>-2.0796</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9194026730180571</v>
+        <v>-1.6856</v>
       </c>
       <c r="J40" t="n">
-        <v>-21.27966137606579</v>
+        <v>-1.166</v>
       </c>
       <c r="K40" t="n">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="L40" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="M40" t="n">
-        <v>-22.1991</v>
+        <v>-2.8516</v>
       </c>
       <c r="N40" t="n">
-        <v>253</v>
+        <v>285</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-5.8478</v>
+        <v>-6.0585</v>
       </c>
       <c r="C41" t="n">
-        <v>-4.678240000000001</v>
+        <v>-0</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.89573097713127</v>
+        <v>-2.8689</v>
       </c>
       <c r="E41" t="n">
-        <v>-23.6257</v>
+        <v>-6.0585</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.550812897511294</v>
+        <v>-5.2701</v>
       </c>
       <c r="G41" t="n">
-        <v>-22.07491902257183</v>
+        <v>-0.7884</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.550812897511294</v>
+        <v>-5.2701</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.469449391915805</v>
+        <v>-4.2716</v>
       </c>
       <c r="J41" t="n">
-        <v>-22.07491902257183</v>
+        <v>-0.7884</v>
       </c>
       <c r="K41" t="n">
-        <v>134</v>
+        <v>215</v>
       </c>
       <c r="L41" t="n">
-        <v>151</v>
+        <v>49</v>
       </c>
       <c r="M41" t="n">
-        <v>-23.5444</v>
+        <v>-5.06</v>
       </c>
       <c r="N41" t="n">
-        <v>285</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -2356,52 +2344,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2441,10 +2429,10 @@
         <v>1.38</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3867106200620035</v>
+        <v>0.6621</v>
       </c>
       <c r="J2" t="n">
-        <v>6.187369920992056</v>
+        <v>10.5936</v>
       </c>
     </row>
     <row r="3">
@@ -2481,10 +2469,10 @@
         <v>1.12</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1886933690073678</v>
+        <v>0.3041</v>
       </c>
       <c r="J3" t="n">
-        <v>3.019093904117885</v>
+        <v>4.8656</v>
       </c>
     </row>
     <row r="4">
@@ -2521,10 +2509,10 @@
         <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1040130835384601</v>
+        <v>0.0936</v>
       </c>
       <c r="J4" t="n">
-        <v>1.664209336615361</v>
+        <v>1.4976</v>
       </c>
     </row>
     <row r="5">
@@ -2561,10 +2549,10 @@
         <v>0.65</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.148636778064344</v>
+        <v>-0.5626</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.378188449029504</v>
+        <v>-9.0016</v>
       </c>
     </row>
     <row r="6">
@@ -2601,10 +2589,10 @@
         <v>0.27</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4216292546240976</v>
+        <v>-1.008</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.746068073985562</v>
+        <v>-16.128</v>
       </c>
     </row>
     <row r="7">
@@ -2641,10 +2629,10 @@
         <v>2.54</v>
       </c>
       <c r="I7" t="n">
-        <v>1.867666418885815</v>
+        <v>1.6341</v>
       </c>
       <c r="J7" t="n">
-        <v>29.88266270217303</v>
+        <v>26.1456</v>
       </c>
     </row>
     <row r="8">
@@ -2681,10 +2669,10 @@
         <v>2.25</v>
       </c>
       <c r="I8" t="n">
-        <v>1.48747453722444</v>
+        <v>1.383</v>
       </c>
       <c r="J8" t="n">
-        <v>23.79959259559105</v>
+        <v>22.128</v>
       </c>
     </row>
     <row r="9">
@@ -2721,10 +2709,10 @@
         <v>1.12</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2647817719570135</v>
+        <v>0.1144</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.236508351312216</v>
+        <v>1.8304</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2749,10 @@
         <v>0.82</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7362600658313923</v>
+        <v>-0.4221</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.78016105330228</v>
+        <v>-6.7536</v>
       </c>
     </row>
     <row r="11">
@@ -2801,10 +2789,10 @@
         <v>0.6</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.064123799598084</v>
+        <v>-0.6889</v>
       </c>
       <c r="J11" t="n">
-        <v>-17.02598079356935</v>
+        <v>-11.0224</v>
       </c>
     </row>
     <row r="12">
@@ -2841,10 +2829,10 @@
         <v>2.21</v>
       </c>
       <c r="I12" t="n">
-        <v>1.635667408221408</v>
+        <v>2.2528</v>
       </c>
       <c r="J12" t="n">
-        <v>35.98468298087096</v>
+        <v>49.5616</v>
       </c>
     </row>
     <row r="13">
@@ -2881,10 +2869,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01943927477611922</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4276640450746227</v>
+        <v>1.9118</v>
       </c>
     </row>
     <row r="14">
@@ -2921,10 +2909,10 @@
         <v>0.86</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2541058309190971</v>
+        <v>-0.5589</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.590328280220136</v>
+        <v>-12.2958</v>
       </c>
     </row>
     <row r="15">
@@ -2961,10 +2949,10 @@
         <v>0.85</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2696422605249495</v>
+        <v>-0.5849</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.932129731548889</v>
+        <v>-12.8678</v>
       </c>
     </row>
     <row r="16">
@@ -3001,10 +2989,10 @@
         <v>0.65</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5740728802471031</v>
+        <v>-1.0462</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.62960336543627</v>
+        <v>-23.0164</v>
       </c>
     </row>
     <row r="17">
@@ -3041,10 +3029,10 @@
         <v>1.45</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4118213476592908</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>9.060069648504397</v>
+        <v>15.136</v>
       </c>
     </row>
     <row r="18">
@@ -3081,10 +3069,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1700690873039348</v>
+        <v>0.3048</v>
       </c>
       <c r="J18" t="n">
-        <v>3.741519920686566</v>
+        <v>6.7056</v>
       </c>
     </row>
     <row r="19">
@@ -3121,10 +3109,10 @@
         <v>0.99</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0518060630777391</v>
+        <v>-0.0654</v>
       </c>
       <c r="J19" t="n">
-        <v>1.13973338771026</v>
+        <v>-1.4388</v>
       </c>
     </row>
     <row r="20">
@@ -3161,10 +3149,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>0.02788577594298519</v>
+        <v>-0.1343</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6134870707456742</v>
+        <v>-2.9546</v>
       </c>
     </row>
     <row r="21">
@@ -3201,10 +3189,10 @@
         <v>0.71</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1813493701444921</v>
+        <v>-0.5165</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.989686143178826</v>
+        <v>-11.363</v>
       </c>
     </row>
     <row r="22">
@@ -3241,10 +3229,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5416564797818578</v>
+        <v>1.0467</v>
       </c>
       <c r="J22" t="n">
-        <v>18.41632031258317</v>
+        <v>35.5878</v>
       </c>
     </row>
     <row r="23">
@@ -3281,10 +3269,10 @@
         <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4951862602666288</v>
+        <v>0.9821</v>
       </c>
       <c r="J23" t="n">
-        <v>16.83633284906538</v>
+        <v>33.3914</v>
       </c>
     </row>
     <row r="24">
@@ -3321,10 +3309,10 @@
         <v>1.09</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1049758929492808</v>
+        <v>0.272</v>
       </c>
       <c r="J24" t="n">
-        <v>3.569180360275546</v>
+        <v>9.247999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -3361,10 +3349,10 @@
         <v>0.86</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2279731880710383</v>
+        <v>-0.5514</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.751088394415302</v>
+        <v>-18.7476</v>
       </c>
     </row>
     <row r="26">
@@ -3401,10 +3389,10 @@
         <v>0.8</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3211485799233138</v>
+        <v>-0.7026</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.91905171739267</v>
+        <v>-23.8884</v>
       </c>
     </row>
     <row r="27">
@@ -3441,10 +3429,10 @@
         <v>1.19</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1951191168676159</v>
+        <v>0.3488</v>
       </c>
       <c r="J27" t="n">
-        <v>6.63404997349894</v>
+        <v>11.8592</v>
       </c>
     </row>
     <row r="28">
@@ -3481,10 +3469,10 @@
         <v>1.12</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1397181948056725</v>
+        <v>0.2388</v>
       </c>
       <c r="J28" t="n">
-        <v>4.750418623392864</v>
+        <v>8.119199999999999</v>
       </c>
     </row>
     <row r="29">
@@ -3521,10 +3509,10 @@
         <v>1.09</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1190457309284837</v>
+        <v>0.1858</v>
       </c>
       <c r="J29" t="n">
-        <v>4.047554851568447</v>
+        <v>6.3172</v>
       </c>
     </row>
     <row r="30">
@@ -3561,10 +3549,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1062020996740811</v>
+        <v>0.1466</v>
       </c>
       <c r="J30" t="n">
-        <v>3.610871388918757</v>
+        <v>4.9844</v>
       </c>
     </row>
     <row r="31">
@@ -3601,10 +3589,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.08825460568278649</v>
+        <v>-0.3674</v>
       </c>
       <c r="J31" t="n">
-        <v>-3.000656593214741</v>
+        <v>-12.4916</v>
       </c>
     </row>
     <row r="32">
@@ -3641,10 +3629,10 @@
         <v>1.32</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3873879277707231</v>
+        <v>0.8607</v>
       </c>
       <c r="J32" t="n">
-        <v>13.55857747197531</v>
+        <v>30.1245</v>
       </c>
     </row>
     <row r="33">
@@ -3681,10 +3669,10 @@
         <v>1.25</v>
       </c>
       <c r="I33" t="n">
-        <v>0.280868461538737</v>
+        <v>0.6954</v>
       </c>
       <c r="J33" t="n">
-        <v>9.830396153855796</v>
+        <v>24.339</v>
       </c>
     </row>
     <row r="34">
@@ -3721,10 +3709,10 @@
         <v>1.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2088786557428621</v>
+        <v>0.5666</v>
       </c>
       <c r="J34" t="n">
-        <v>7.310752951000175</v>
+        <v>19.831</v>
       </c>
     </row>
     <row r="35">
@@ -3761,10 +3749,10 @@
         <v>1.03</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.01934290336132012</v>
+        <v>0.0319</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.6770016176462043</v>
+        <v>1.1165</v>
       </c>
     </row>
     <row r="36">
@@ -3801,10 +3789,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.06441864223214168</v>
+        <v>-0.1076</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.254652478124959</v>
+        <v>-3.766</v>
       </c>
     </row>
     <row r="37">
@@ -3841,10 +3829,10 @@
         <v>1.32</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3571531260746507</v>
+        <v>0.5584</v>
       </c>
       <c r="J37" t="n">
-        <v>12.50035941261277</v>
+        <v>19.544</v>
       </c>
     </row>
     <row r="38">
@@ -3881,10 +3869,10 @@
         <v>1.16</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2255304400322044</v>
+        <v>0.3373</v>
       </c>
       <c r="J38" t="n">
-        <v>7.893565401127154</v>
+        <v>11.8055</v>
       </c>
     </row>
     <row r="39">
@@ -3921,10 +3909,10 @@
         <v>0.97</v>
       </c>
       <c r="I39" t="n">
-        <v>0.07792205380168321</v>
+        <v>-0.065</v>
       </c>
       <c r="J39" t="n">
-        <v>2.727271883058912</v>
+        <v>-2.275</v>
       </c>
     </row>
     <row r="40">
@@ -3961,10 +3949,10 @@
         <v>0.74</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.101999094102949</v>
+        <v>-0.4596</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.569968293603214</v>
+        <v>-16.086</v>
       </c>
     </row>
     <row r="41">
@@ -4001,10 +3989,10 @@
         <v>0.63</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.193588828396606</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>-6.775608993881209</v>
+        <v>-21.1155</v>
       </c>
     </row>
     <row r="42">
@@ -4041,10 +4029,10 @@
         <v>1.63</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7721488794636772</v>
+        <v>1.5174</v>
       </c>
       <c r="J42" t="n">
-        <v>22.39231750444664</v>
+        <v>44.0046</v>
       </c>
     </row>
     <row r="43">
@@ -4081,10 +4069,10 @@
         <v>1.24</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2670431464962663</v>
+        <v>0.6985</v>
       </c>
       <c r="J43" t="n">
-        <v>7.744251248391722</v>
+        <v>20.2565</v>
       </c>
     </row>
     <row r="44">
@@ -4121,10 +4109,10 @@
         <v>1.21</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2281129383407773</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>6.615275211882543</v>
+        <v>18.0815</v>
       </c>
     </row>
     <row r="45">
@@ -4161,10 +4149,10 @@
         <v>0.78</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2995214878009888</v>
+        <v>-0.7546</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.686123146228674</v>
+        <v>-21.8834</v>
       </c>
     </row>
     <row r="46">
@@ -4201,10 +4189,10 @@
         <v>0.71</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3911643721507509</v>
+        <v>-0.9145</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.34376679237178</v>
+        <v>-26.5205</v>
       </c>
     </row>
     <row r="47">
@@ -4241,10 +4229,10 @@
         <v>1.14</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1588920874830576</v>
+        <v>0.3161</v>
       </c>
       <c r="J47" t="n">
-        <v>4.607870537008669</v>
+        <v>9.1669</v>
       </c>
     </row>
     <row r="48">
@@ -4281,10 +4269,10 @@
         <v>1.08</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1277694369352592</v>
+        <v>0.2171</v>
       </c>
       <c r="J48" t="n">
-        <v>3.705313671122518</v>
+        <v>6.2959</v>
       </c>
     </row>
     <row r="49">
@@ -4321,10 +4309,10 @@
         <v>0.95</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0617981144627426</v>
+        <v>-0.0944</v>
       </c>
       <c r="J49" t="n">
-        <v>1.792145319419535</v>
+        <v>-2.7376</v>
       </c>
     </row>
     <row r="50">
@@ -4361,10 +4349,10 @@
         <v>0.85</v>
       </c>
       <c r="I50" t="n">
-        <v>0.01546944164798296</v>
+        <v>-0.2902</v>
       </c>
       <c r="J50" t="n">
-        <v>0.4486138077915058</v>
+        <v>-8.415800000000001</v>
       </c>
     </row>
     <row r="51">
@@ -4401,10 +4389,10 @@
         <v>0.67</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.08330379192240596</v>
+        <v>-0.5475</v>
       </c>
       <c r="J51" t="n">
-        <v>-2.415809965749773</v>
+        <v>-15.8775</v>
       </c>
     </row>
     <row r="52">
@@ -4441,10 +4429,10 @@
         <v>1.47</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5126728319703433</v>
+        <v>1.1777</v>
       </c>
       <c r="J52" t="n">
-        <v>10.25345663940687</v>
+        <v>23.554</v>
       </c>
     </row>
     <row r="53">
@@ -4481,10 +4469,10 @@
         <v>1.42</v>
       </c>
       <c r="I53" t="n">
-        <v>0.447007111649087</v>
+        <v>1.0744</v>
       </c>
       <c r="J53" t="n">
-        <v>8.940142232981739</v>
+        <v>21.488</v>
       </c>
     </row>
     <row r="54">
@@ -4521,10 +4509,10 @@
         <v>1.02</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.04704370609201326</v>
+        <v>-0.0097</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.9408741218402652</v>
+        <v>-0.194</v>
       </c>
     </row>
     <row r="55">
@@ -4561,10 +4549,10 @@
         <v>1.02</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.04704370609201326</v>
+        <v>-0.0097</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.9408741218402652</v>
+        <v>-0.194</v>
       </c>
     </row>
     <row r="56">
@@ -4601,10 +4589,10 @@
         <v>0.91</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1869784074867832</v>
+        <v>-0.4382</v>
       </c>
       <c r="J56" t="n">
-        <v>-3.739568149735665</v>
+        <v>-8.763999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4641,10 +4629,10 @@
         <v>1.68</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4367366404738849</v>
+        <v>0.984</v>
       </c>
       <c r="J57" t="n">
-        <v>8.734732809477698</v>
+        <v>19.68</v>
       </c>
     </row>
     <row r="58">
@@ -4681,10 +4669,10 @@
         <v>1.05</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1052675626360123</v>
+        <v>0.1605</v>
       </c>
       <c r="J58" t="n">
-        <v>2.105351252720246</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="59">
@@ -4721,10 +4709,10 @@
         <v>0.88</v>
       </c>
       <c r="I59" t="n">
-        <v>0.02433095639320353</v>
+        <v>-0.2409</v>
       </c>
       <c r="J59" t="n">
-        <v>0.4866191278640707</v>
+        <v>-4.818</v>
       </c>
     </row>
     <row r="60">
@@ -4761,10 +4749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.07890387152674606</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.578077430534921</v>
+        <v>-10.434</v>
       </c>
     </row>
     <row r="61">
@@ -4801,10 +4789,10 @@
         <v>0.4</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2327049460445678</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>-4.654098920891355</v>
+        <v>-17.41</v>
       </c>
     </row>
     <row r="62">
@@ -4841,10 +4829,10 @@
         <v>2.18</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6602307274122062</v>
+        <v>2.054</v>
       </c>
       <c r="J62" t="n">
-        <v>10.5636916385953</v>
+        <v>32.864</v>
       </c>
     </row>
     <row r="63">
@@ -4881,10 +4869,10 @@
         <v>1.8</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4243005643301487</v>
+        <v>1.6888</v>
       </c>
       <c r="J63" t="n">
-        <v>6.78880902928238</v>
+        <v>27.0208</v>
       </c>
     </row>
     <row r="64">
@@ -4921,10 +4909,10 @@
         <v>1.25</v>
       </c>
       <c r="I64" t="n">
-        <v>0.06494927664780543</v>
+        <v>0.536</v>
       </c>
       <c r="J64" t="n">
-        <v>1.039188426364887</v>
+        <v>8.576000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -4961,10 +4949,10 @@
         <v>0.9</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1795426378224902</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.872682205159843</v>
+        <v>-8.379200000000001</v>
       </c>
     </row>
     <row r="66">
@@ -5001,10 +4989,10 @@
         <v>0.85</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2128008811009751</v>
+        <v>-0.6512</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.404814097615602</v>
+        <v>-10.4192</v>
       </c>
     </row>
     <row r="67">
@@ -5041,10 +5029,10 @@
         <v>1.49</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4041494402003446</v>
+        <v>0.8368</v>
       </c>
       <c r="J67" t="n">
-        <v>6.466391043205514</v>
+        <v>13.3888</v>
       </c>
     </row>
     <row r="68">
@@ -5081,10 +5069,10 @@
         <v>0.98</v>
       </c>
       <c r="I68" t="n">
-        <v>0.113319897491593</v>
+        <v>0.0423</v>
       </c>
       <c r="J68" t="n">
-        <v>1.813118359865488</v>
+        <v>0.6768</v>
       </c>
     </row>
     <row r="69">
@@ -5121,10 +5109,10 @@
         <v>0.67</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.05396681853729961</v>
+        <v>-0.5073</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.8634690965967937</v>
+        <v>-8.1168</v>
       </c>
     </row>
     <row r="70">
@@ -5161,10 +5149,10 @@
         <v>0.51</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1470129320407654</v>
+        <v>-0.719</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.352206912652247</v>
+        <v>-11.504</v>
       </c>
     </row>
     <row r="71">
@@ -5201,10 +5189,10 @@
         <v>0.27</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2819523814392196</v>
+        <v>-0.9998</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.511238103027513</v>
+        <v>-15.9968</v>
       </c>
     </row>
     <row r="72">
@@ -5241,10 +5229,10 @@
         <v>2.05</v>
       </c>
       <c r="I72" t="n">
-        <v>0.638228618887125</v>
+        <v>1.9763</v>
       </c>
       <c r="J72" t="n">
-        <v>17.8704013288395</v>
+        <v>55.3364</v>
       </c>
     </row>
     <row r="73">
@@ -5281,10 +5269,10 @@
         <v>1.2</v>
       </c>
       <c r="I73" t="n">
-        <v>0.08700653187999044</v>
+        <v>0.4852</v>
       </c>
       <c r="J73" t="n">
-        <v>2.436182892639732</v>
+        <v>13.5856</v>
       </c>
     </row>
     <row r="74">
@@ -5321,10 +5309,10 @@
         <v>1.15</v>
       </c>
       <c r="I74" t="n">
-        <v>0.05376508297393737</v>
+        <v>0.3526</v>
       </c>
       <c r="J74" t="n">
-        <v>1.505422323270246</v>
+        <v>9.8728</v>
       </c>
     </row>
     <row r="75">
@@ -5361,10 +5349,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.05110858821020313</v>
+        <v>-0.1393</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.431040469885688</v>
+        <v>-3.9004</v>
       </c>
     </row>
     <row r="76">
@@ -5401,10 +5389,10 @@
         <v>0.83</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1666221209569084</v>
+        <v>-0.6689000000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>-4.665419386793436</v>
+        <v>-18.7292</v>
       </c>
     </row>
     <row r="77">
@@ -5441,10 +5429,10 @@
         <v>1.57</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3896543648160767</v>
+        <v>0.8561</v>
       </c>
       <c r="J77" t="n">
-        <v>10.91032221485015</v>
+        <v>23.9708</v>
       </c>
     </row>
     <row r="78">
@@ -5481,10 +5469,10 @@
         <v>0.96</v>
       </c>
       <c r="I78" t="n">
-        <v>0.04223035465671154</v>
+        <v>-0.0921</v>
       </c>
       <c r="J78" t="n">
-        <v>1.182449930387923</v>
+        <v>-2.5788</v>
       </c>
     </row>
     <row r="79">
@@ -5521,10 +5509,10 @@
         <v>0.92</v>
       </c>
       <c r="I79" t="n">
-        <v>0.02308611224093925</v>
+        <v>-0.178</v>
       </c>
       <c r="J79" t="n">
-        <v>0.6464111427462989</v>
+        <v>-4.984</v>
       </c>
     </row>
     <row r="80">
@@ -5561,10 +5549,10 @@
         <v>0.7</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1055561316155107</v>
+        <v>-0.513</v>
       </c>
       <c r="J80" t="n">
-        <v>-2.9555716852343</v>
+        <v>-14.364</v>
       </c>
     </row>
     <row r="81">
@@ -5601,10 +5589,10 @@
         <v>0.66</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.1292134605231977</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="J81" t="n">
-        <v>-3.617976894649536</v>
+        <v>-15.82</v>
       </c>
     </row>
     <row r="82">
@@ -5641,10 +5629,10 @@
         <v>1.32</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0832479670977601</v>
+        <v>0.4915</v>
       </c>
       <c r="J82" t="n">
-        <v>1.997951210346242</v>
+        <v>11.796</v>
       </c>
     </row>
     <row r="83">
@@ -5681,10 +5669,10 @@
         <v>1.31</v>
       </c>
       <c r="I83" t="n">
-        <v>0.08011949511361102</v>
+        <v>0.4783</v>
       </c>
       <c r="J83" t="n">
-        <v>1.922867882726665</v>
+        <v>11.4792</v>
       </c>
     </row>
     <row r="84">
@@ -5721,10 +5709,10 @@
         <v>1.23</v>
       </c>
       <c r="I84" t="n">
-        <v>0.05571866366247941</v>
+        <v>0.3671</v>
       </c>
       <c r="J84" t="n">
-        <v>1.337247927899506</v>
+        <v>8.8104</v>
       </c>
     </row>
     <row r="85">
@@ -5761,10 +5749,10 @@
         <v>1.03</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.000202763905149405</v>
+        <v>0.0158</v>
       </c>
       <c r="J85" t="n">
-        <v>-0.00486633372358572</v>
+        <v>0.3792</v>
       </c>
     </row>
     <row r="86">
@@ -5801,10 +5789,10 @@
         <v>0.96</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.02252153527010474</v>
+        <v>-0.1639</v>
       </c>
       <c r="J86" t="n">
-        <v>-0.5405168464825139</v>
+        <v>-3.9336</v>
       </c>
     </row>
     <row r="87">
@@ -5841,10 +5829,10 @@
         <v>1.07</v>
       </c>
       <c r="I87" t="n">
-        <v>0.03811921000398913</v>
+        <v>0.2516</v>
       </c>
       <c r="J87" t="n">
-        <v>0.9148610400957391</v>
+        <v>6.0384</v>
       </c>
     </row>
     <row r="88">
@@ -5881,10 +5869,10 @@
         <v>0.85</v>
       </c>
       <c r="I88" t="n">
-        <v>0.01414093948126385</v>
+        <v>-0.2116</v>
       </c>
       <c r="J88" t="n">
-        <v>0.3393825475503324</v>
+        <v>-5.0784</v>
       </c>
     </row>
     <row r="89">
@@ -5921,10 +5909,10 @@
         <v>0.78</v>
       </c>
       <c r="I89" t="n">
-        <v>0.008181365814497464</v>
+        <v>-0.3473</v>
       </c>
       <c r="J89" t="n">
-        <v>0.1963527795479391</v>
+        <v>-8.3352</v>
       </c>
     </row>
     <row r="90">
@@ -5961,10 +5949,10 @@
         <v>0.67</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.003212507979279574</v>
+        <v>-0.5145</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.07710019150270978</v>
+        <v>-12.348</v>
       </c>
     </row>
     <row r="91">
@@ -6001,10 +5989,10 @@
         <v>0.66</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.004301485288565266</v>
+        <v>-0.5285</v>
       </c>
       <c r="J91" t="n">
-        <v>-0.1032356469255664</v>
+        <v>-12.684</v>
       </c>
     </row>
     <row r="92">
@@ -6041,10 +6029,10 @@
         <v>1.33</v>
       </c>
       <c r="I92" t="n">
-        <v>0.06453183357980762</v>
+        <v>0.5616</v>
       </c>
       <c r="J92" t="n">
-        <v>2.258614175293267</v>
+        <v>19.656</v>
       </c>
     </row>
     <row r="93">
@@ -6081,10 +6069,10 @@
         <v>1.24</v>
       </c>
       <c r="I93" t="n">
-        <v>0.05024158572053931</v>
+        <v>0.4427</v>
       </c>
       <c r="J93" t="n">
-        <v>1.758455500218876</v>
+        <v>15.4945</v>
       </c>
     </row>
     <row r="94">
@@ -6121,10 +6109,10 @@
         <v>1.13</v>
       </c>
       <c r="I94" t="n">
-        <v>0.03331895443413101</v>
+        <v>0.2805</v>
       </c>
       <c r="J94" t="n">
-        <v>1.166163405194585</v>
+        <v>9.817500000000001</v>
       </c>
     </row>
     <row r="95">
@@ -6161,10 +6149,10 @@
         <v>0.67</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.03519380585528847</v>
+        <v>-0.5575</v>
       </c>
       <c r="J95" t="n">
-        <v>-1.231783204935097</v>
+        <v>-19.5125</v>
       </c>
     </row>
     <row r="96">
@@ -6201,10 +6189,10 @@
         <v>0.59</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.04762012579671922</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="J96" t="n">
-        <v>-1.666704402885173</v>
+        <v>-22.988</v>
       </c>
     </row>
     <row r="97">
@@ -6241,10 +6229,10 @@
         <v>1.41</v>
       </c>
       <c r="I97" t="n">
-        <v>0.08115017137993656</v>
+        <v>1.069</v>
       </c>
       <c r="J97" t="n">
-        <v>2.84025599829778</v>
+        <v>37.415</v>
       </c>
     </row>
     <row r="98">
@@ -6281,10 +6269,10 @@
         <v>1.33</v>
       </c>
       <c r="I98" t="n">
-        <v>0.06339083192101</v>
+        <v>0.8953</v>
       </c>
       <c r="J98" t="n">
-        <v>2.21867911723535</v>
+        <v>31.3355</v>
       </c>
     </row>
     <row r="99">
@@ -6321,10 +6309,10 @@
         <v>1.24</v>
       </c>
       <c r="I99" t="n">
-        <v>0.04356728472691559</v>
+        <v>0.6841</v>
       </c>
       <c r="J99" t="n">
-        <v>1.524854965442046</v>
+        <v>23.9435</v>
       </c>
     </row>
     <row r="100">
@@ -6361,10 +6349,10 @@
         <v>1.04</v>
       </c>
       <c r="I100" t="n">
-        <v>0.004991896562234545</v>
+        <v>0.0784</v>
       </c>
       <c r="J100" t="n">
-        <v>0.174716379678209</v>
+        <v>2.744</v>
       </c>
     </row>
     <row r="101">
@@ -6401,10 +6389,10 @@
         <v>0.67</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.0751049221329904</v>
+        <v>-1.007</v>
       </c>
       <c r="J101" t="n">
-        <v>-2.628672274654664</v>
+        <v>-35.245</v>
       </c>
     </row>
     <row r="102">
@@ -6441,10 +6429,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.06564931681506668</v>
+        <v>0.5396</v>
       </c>
       <c r="J102" t="n">
-        <v>1.903830187636934</v>
+        <v>15.6484</v>
       </c>
     </row>
     <row r="103">
@@ -6481,10 +6469,10 @@
         <v>1.11</v>
       </c>
       <c r="I103" t="n">
-        <v>0.03624261815464425</v>
+        <v>0.2659</v>
       </c>
       <c r="J103" t="n">
-        <v>1.051035926484683</v>
+        <v>7.7111</v>
       </c>
     </row>
     <row r="104">
@@ -6521,10 +6509,10 @@
         <v>0.93</v>
       </c>
       <c r="I104" t="n">
-        <v>0.01065004539781262</v>
+        <v>-0.1488</v>
       </c>
       <c r="J104" t="n">
-        <v>0.3088513165365659</v>
+        <v>-4.3152</v>
       </c>
     </row>
     <row r="105">
@@ -6561,10 +6549,10 @@
         <v>0.83</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.003928921194619839</v>
+        <v>-0.3238</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.1139387146439753</v>
+        <v>-9.3902</v>
       </c>
     </row>
     <row r="106">
@@ -6601,10 +6589,10 @@
         <v>0.55</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.04797567729631277</v>
+        <v>-0.698</v>
       </c>
       <c r="J106" t="n">
-        <v>-1.39129464159307</v>
+        <v>-20.242</v>
       </c>
     </row>
     <row r="107">
@@ -6641,10 +6629,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1272744438423634</v>
+        <v>1.483</v>
       </c>
       <c r="J107" t="n">
-        <v>3.690958871428539</v>
+        <v>43.007</v>
       </c>
     </row>
     <row r="108">
@@ -6681,10 +6669,10 @@
         <v>1.16</v>
       </c>
       <c r="I108" t="n">
-        <v>0.02859044692170896</v>
+        <v>0.4654</v>
       </c>
       <c r="J108" t="n">
-        <v>0.8291229607295599</v>
+        <v>13.4966</v>
       </c>
     </row>
     <row r="109">
@@ -6721,10 +6709,10 @@
         <v>1.09</v>
       </c>
       <c r="I109" t="n">
-        <v>0.01641615846831774</v>
+        <v>0.2374</v>
       </c>
       <c r="J109" t="n">
-        <v>0.4760685955812145</v>
+        <v>6.8846</v>
       </c>
     </row>
     <row r="110">
@@ -6761,10 +6749,10 @@
         <v>1.03</v>
       </c>
       <c r="I110" t="n">
-        <v>0.003787281888176314</v>
+        <v>0.0394</v>
       </c>
       <c r="J110" t="n">
-        <v>0.1098311747571131</v>
+        <v>1.1426</v>
       </c>
     </row>
     <row r="111">
@@ -6801,10 +6789,10 @@
         <v>0.82</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.04139021741942166</v>
+        <v>-0.6669</v>
       </c>
       <c r="J111" t="n">
-        <v>-1.200316305163228</v>
+        <v>-19.3401</v>
       </c>
     </row>
     <row r="112">
@@ -6841,10 +6829,10 @@
         <v>1.06</v>
       </c>
       <c r="I112" t="n">
-        <v>0.03095955345123717</v>
+        <v>0.2401</v>
       </c>
       <c r="J112" t="n">
-        <v>0.5263124086710318</v>
+        <v>4.0817</v>
       </c>
     </row>
     <row r="113">
@@ -6881,10 +6869,10 @@
         <v>0.9</v>
       </c>
       <c r="I113" t="n">
-        <v>0.01741956771436287</v>
+        <v>-0.1165</v>
       </c>
       <c r="J113" t="n">
-        <v>0.2961326511441689</v>
+        <v>-1.9805</v>
       </c>
     </row>
     <row r="114">
@@ -6921,10 +6909,10 @@
         <v>0.88</v>
       </c>
       <c r="I114" t="n">
-        <v>0.01578391353234723</v>
+        <v>-0.1515</v>
       </c>
       <c r="J114" t="n">
-        <v>0.2683265300499028</v>
+        <v>-2.5755</v>
       </c>
     </row>
     <row r="115">
@@ -6961,10 +6949,10 @@
         <v>0.66</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0004447991433498485</v>
+        <v>-0.5234</v>
       </c>
       <c r="J115" t="n">
-        <v>-0.007561585436947425</v>
+        <v>-8.8978</v>
       </c>
     </row>
     <row r="116">
@@ -7001,10 +6989,10 @@
         <v>0.45</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.01776563521655085</v>
+        <v>-0.7934</v>
       </c>
       <c r="J116" t="n">
-        <v>-0.3020157986813645</v>
+        <v>-13.4878</v>
       </c>
     </row>
     <row r="117">
@@ -7041,10 +7029,10 @@
         <v>1.51</v>
       </c>
       <c r="I117" t="n">
-        <v>0.05590227312408126</v>
+        <v>1.1803</v>
       </c>
       <c r="J117" t="n">
-        <v>0.9503386431093814</v>
+        <v>20.0651</v>
       </c>
     </row>
     <row r="118">
@@ -7081,10 +7069,10 @@
         <v>1.46</v>
       </c>
       <c r="I118" t="n">
-        <v>0.04901496461516791</v>
+        <v>1.0772</v>
       </c>
       <c r="J118" t="n">
-        <v>0.8332543984578544</v>
+        <v>18.3124</v>
       </c>
     </row>
     <row r="119">
@@ -7121,10 +7109,10 @@
         <v>1.41</v>
       </c>
       <c r="I119" t="n">
-        <v>0.04226548758053121</v>
+        <v>0.9695</v>
       </c>
       <c r="J119" t="n">
-        <v>0.7185132888690305</v>
+        <v>16.4815</v>
       </c>
     </row>
     <row r="120">
@@ -7161,10 +7149,10 @@
         <v>1.18</v>
       </c>
       <c r="I120" t="n">
-        <v>0.01368689373833804</v>
+        <v>0.394</v>
       </c>
       <c r="J120" t="n">
-        <v>0.2326771935517467</v>
+        <v>6.698</v>
       </c>
     </row>
     <row r="121">
@@ -7201,10 +7189,10 @@
         <v>1.08</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.0004743604942283736</v>
+        <v>0.1288</v>
       </c>
       <c r="J121" t="n">
-        <v>-0.008064128401882351</v>
+        <v>2.1896</v>
       </c>
     </row>
     <row r="122">
@@ -7241,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.04425247858159514</v>
+        <v>0.4994</v>
       </c>
       <c r="J122" t="n">
-        <v>0.8850495716319029</v>
+        <v>9.988</v>
       </c>
     </row>
     <row r="123">
@@ -7281,10 +7269,10 @@
         <v>1.15</v>
       </c>
       <c r="I123" t="n">
-        <v>0.03704384692375756</v>
+        <v>0.3697</v>
       </c>
       <c r="J123" t="n">
-        <v>0.7408769384751512</v>
+        <v>7.394</v>
       </c>
     </row>
     <row r="124">
@@ -7321,10 +7309,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0003860277635989624</v>
+        <v>-0.4964</v>
       </c>
       <c r="J124" t="n">
-        <v>0.007720555271979249</v>
+        <v>-9.928000000000001</v>
       </c>
     </row>
     <row r="125">
@@ -7361,10 +7349,10 @@
         <v>0.65</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.002960006643901503</v>
+        <v>-0.5511</v>
       </c>
       <c r="J125" t="n">
-        <v>-0.05920013287803005</v>
+        <v>-11.022</v>
       </c>
     </row>
     <row r="126">
@@ -7401,10 +7389,10 @@
         <v>0.46</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.01871012531273113</v>
+        <v>-0.7892</v>
       </c>
       <c r="J126" t="n">
-        <v>-0.3742025062546226</v>
+        <v>-15.784</v>
       </c>
     </row>
     <row r="127">
@@ -7441,10 +7429,10 @@
         <v>1.35</v>
       </c>
       <c r="I127" t="n">
-        <v>0.04403448228495774</v>
+        <v>0.8922</v>
       </c>
       <c r="J127" t="n">
-        <v>0.8806896456991548</v>
+        <v>17.844</v>
       </c>
     </row>
     <row r="128">
@@ -7481,10 +7469,10 @@
         <v>1.33</v>
       </c>
       <c r="I128" t="n">
-        <v>0.04129258240076011</v>
+        <v>0.8467</v>
       </c>
       <c r="J128" t="n">
-        <v>0.8258516480152023</v>
+        <v>16.934</v>
       </c>
     </row>
     <row r="129">
@@ -7521,10 +7509,10 @@
         <v>1.22</v>
       </c>
       <c r="I129" t="n">
-        <v>0.02798284006068071</v>
+        <v>0.5567</v>
       </c>
       <c r="J129" t="n">
-        <v>0.5596568012136142</v>
+        <v>11.134</v>
       </c>
     </row>
     <row r="130">
@@ -7561,10 +7549,10 @@
         <v>1.16</v>
       </c>
       <c r="I130" t="n">
-        <v>0.02075112181828576</v>
+        <v>0.39</v>
       </c>
       <c r="J130" t="n">
-        <v>0.4150224363657151</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="131">
@@ -7601,10 +7589,10 @@
         <v>1.07</v>
       </c>
       <c r="I131" t="n">
-        <v>0.008337073996945631</v>
+        <v>0.1357</v>
       </c>
       <c r="J131" t="n">
-        <v>0.1667414799389126</v>
+        <v>2.714</v>
       </c>
     </row>
     <row r="132">
@@ -7641,10 +7629,10 @@
         <v>1.1</v>
       </c>
       <c r="I132" t="n">
-        <v>0.03204934670489894</v>
+        <v>0.355</v>
       </c>
       <c r="J132" t="n">
-        <v>0.7691843209175745</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="133">
@@ -7681,10 +7669,10 @@
         <v>1.1</v>
       </c>
       <c r="I133" t="n">
-        <v>0.03204934670489894</v>
+        <v>0.355</v>
       </c>
       <c r="J133" t="n">
-        <v>0.7691843209175745</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="134">
@@ -7721,10 +7709,10 @@
         <v>1.1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.03204934670489894</v>
+        <v>0.355</v>
       </c>
       <c r="J134" t="n">
-        <v>0.7691843209175745</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="135">
@@ -7761,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.02199722172533511</v>
+        <v>0.2159</v>
       </c>
       <c r="J135" t="n">
-        <v>0.5279333214080426</v>
+        <v>5.1816</v>
       </c>
     </row>
     <row r="136">
@@ -7801,10 +7789,10 @@
         <v>0.93</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.01313613978244451</v>
+        <v>-0.3352</v>
       </c>
       <c r="J136" t="n">
-        <v>-0.3152673547786682</v>
+        <v>-8.0448</v>
       </c>
     </row>
     <row r="137">
@@ -7841,10 +7829,10 @@
         <v>1.32</v>
       </c>
       <c r="I137" t="n">
-        <v>0.06167153849422019</v>
+        <v>0.5508</v>
       </c>
       <c r="J137" t="n">
-        <v>1.480116923861285</v>
+        <v>13.2192</v>
       </c>
     </row>
     <row r="138">
@@ -7881,10 +7869,10 @@
         <v>1.19</v>
       </c>
       <c r="I138" t="n">
-        <v>0.04291433527966437</v>
+        <v>0.374</v>
       </c>
       <c r="J138" t="n">
-        <v>1.029944046711945</v>
+        <v>8.976000000000001</v>
       </c>
     </row>
     <row r="139">
@@ -7921,10 +7909,10 @@
         <v>1</v>
       </c>
       <c r="I139" t="n">
-        <v>0.01767127765476408</v>
+        <v>0.0121</v>
       </c>
       <c r="J139" t="n">
-        <v>0.4241106637143379</v>
+        <v>0.2904</v>
       </c>
     </row>
     <row r="140">
@@ -7961,10 +7949,10 @@
         <v>0.75</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.01570357069425684</v>
+        <v>-0.4507</v>
       </c>
       <c r="J140" t="n">
-        <v>-0.3768856966621642</v>
+        <v>-10.8168</v>
       </c>
     </row>
     <row r="141">
@@ -8001,10 +7989,10 @@
         <v>0.67</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.02721375955850492</v>
+        <v>-0.5565</v>
       </c>
       <c r="J141" t="n">
-        <v>-0.6531302294041181</v>
+        <v>-13.356</v>
       </c>
     </row>
     <row r="142">
@@ -8041,10 +8029,10 @@
         <v>1.36</v>
       </c>
       <c r="I142" t="n">
-        <v>0.06653126830365304</v>
+        <v>0.5861</v>
       </c>
       <c r="J142" t="n">
-        <v>1.929406780805938</v>
+        <v>16.9969</v>
       </c>
     </row>
     <row r="143">
@@ -8081,10 +8069,10 @@
         <v>1.09</v>
       </c>
       <c r="I143" t="n">
-        <v>0.024214842381631</v>
+        <v>0.1975</v>
       </c>
       <c r="J143" t="n">
-        <v>0.7022304290672992</v>
+        <v>5.7275</v>
       </c>
     </row>
     <row r="144">
@@ -8121,10 +8109,10 @@
         <v>1.07</v>
       </c>
       <c r="I144" t="n">
-        <v>0.02153699390369213</v>
+        <v>0.1603</v>
       </c>
       <c r="J144" t="n">
-        <v>0.6245728232070717</v>
+        <v>4.6487</v>
       </c>
     </row>
     <row r="145">
@@ -8161,10 +8149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>0.004769663877046266</v>
+        <v>-0.1665</v>
       </c>
       <c r="J145" t="n">
-        <v>0.1383202524343417</v>
+        <v>-4.8285</v>
       </c>
     </row>
     <row r="146">
@@ -8201,10 +8189,10 @@
         <v>0.7</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.03331071159004743</v>
+        <v>-0.5258</v>
       </c>
       <c r="J146" t="n">
-        <v>-0.9660106361113756</v>
+        <v>-15.2482</v>
       </c>
     </row>
     <row r="147">
@@ -8241,10 +8229,10 @@
         <v>1.31</v>
       </c>
       <c r="I147" t="n">
-        <v>0.08553405196875281</v>
+        <v>0.5115</v>
       </c>
       <c r="J147" t="n">
-        <v>2.480487507093831</v>
+        <v>14.8335</v>
       </c>
     </row>
     <row r="148">
@@ -8281,10 +8269,10 @@
         <v>1.23</v>
       </c>
       <c r="I148" t="n">
-        <v>0.06237648077822137</v>
+        <v>0.4036</v>
       </c>
       <c r="J148" t="n">
-        <v>1.80891794256842</v>
+        <v>11.7044</v>
       </c>
     </row>
     <row r="149">
@@ -8321,10 +8309,10 @@
         <v>1.03</v>
       </c>
       <c r="I149" t="n">
-        <v>0.01204892352095353</v>
+        <v>0.0491</v>
       </c>
       <c r="J149" t="n">
-        <v>0.3494187821076524</v>
+        <v>1.4239</v>
       </c>
     </row>
     <row r="150">
@@ -8361,10 +8349,10 @@
         <v>0.98</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0005886899921988681</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J150" t="n">
-        <v>-0.01707200977376717</v>
+        <v>-2.7463</v>
       </c>
     </row>
     <row r="151">
@@ -8401,10 +8389,10 @@
         <v>0.78</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.05774360216482009</v>
+        <v>-0.4254</v>
       </c>
       <c r="J151" t="n">
-        <v>-1.674564462779783</v>
+        <v>-12.3366</v>
       </c>
     </row>
     <row r="152">
@@ -8441,10 +8429,10 @@
         <v>1.47</v>
       </c>
       <c r="I152" t="n">
-        <v>0.1235263032667897</v>
+        <v>1.1747</v>
       </c>
       <c r="J152" t="n">
-        <v>2.223473458802216</v>
+        <v>21.1446</v>
       </c>
     </row>
     <row r="153">
@@ -8481,10 +8469,10 @@
         <v>1.22</v>
       </c>
       <c r="I153" t="n">
-        <v>0.04566417438948724</v>
+        <v>0.61</v>
       </c>
       <c r="J153" t="n">
-        <v>0.8219551390107702</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="154">
@@ -8521,10 +8509,10 @@
         <v>1.15</v>
       </c>
       <c r="I154" t="n">
-        <v>0.02845400019130833</v>
+        <v>0.3961</v>
       </c>
       <c r="J154" t="n">
-        <v>0.5121720034435499</v>
+        <v>7.1298</v>
       </c>
     </row>
     <row r="155">
@@ -8561,10 +8549,10 @@
         <v>1.07</v>
       </c>
       <c r="I155" t="n">
-        <v>0.004949416079673122</v>
+        <v>0.159</v>
       </c>
       <c r="J155" t="n">
-        <v>0.0890894894341162</v>
+        <v>2.862</v>
       </c>
     </row>
     <row r="156">
@@ -8601,10 +8589,10 @@
         <v>0.96</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.02966017093358875</v>
+        <v>-0.2866</v>
       </c>
       <c r="J156" t="n">
-        <v>-0.5338830768045976</v>
+        <v>-5.1588</v>
       </c>
     </row>
     <row r="157">
@@ -8641,10 +8629,10 @@
         <v>1.31</v>
       </c>
       <c r="I157" t="n">
-        <v>0.06595794523153441</v>
+        <v>0.5663</v>
       </c>
       <c r="J157" t="n">
-        <v>1.187243014167619</v>
+        <v>10.1934</v>
       </c>
     </row>
     <row r="158">
@@ -8681,10 +8669,10 @@
         <v>0.96</v>
       </c>
       <c r="I158" t="n">
-        <v>0.01706525620048692</v>
+        <v>-0.0553</v>
       </c>
       <c r="J158" t="n">
-        <v>0.3071746116087645</v>
+        <v>-0.9954</v>
       </c>
     </row>
     <row r="159">
@@ -8721,10 +8709,10 @@
         <v>0.87</v>
       </c>
       <c r="I159" t="n">
-        <v>0.006758979023178005</v>
+        <v>-0.2435</v>
       </c>
       <c r="J159" t="n">
-        <v>0.1216616224172041</v>
+        <v>-4.383</v>
       </c>
     </row>
     <row r="160">
@@ -8761,10 +8749,10 @@
         <v>0.75</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.009733261491545589</v>
+        <v>-0.4313</v>
       </c>
       <c r="J160" t="n">
-        <v>-0.1751987068478206</v>
+        <v>-7.7634</v>
       </c>
     </row>
     <row r="161">
@@ -8801,10 +8789,10 @@
         <v>0.64</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.02547427562690011</v>
+        <v>-0.5798</v>
       </c>
       <c r="J161" t="n">
-        <v>-0.458536961284202</v>
+        <v>-10.4364</v>
       </c>
     </row>
     <row r="162">
@@ -8841,10 +8829,10 @@
         <v>1.58</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0809720494194531</v>
+        <v>1.3722</v>
       </c>
       <c r="J162" t="n">
-        <v>1.619440988389062</v>
+        <v>27.444</v>
       </c>
     </row>
     <row r="163">
@@ -8881,10 +8869,10 @@
         <v>1.56</v>
       </c>
       <c r="I163" t="n">
-        <v>0.07801178223807399</v>
+        <v>1.3336</v>
       </c>
       <c r="J163" t="n">
-        <v>1.56023564476148</v>
+        <v>26.672</v>
       </c>
     </row>
     <row r="164">
@@ -8921,10 +8909,10 @@
         <v>1.22</v>
       </c>
       <c r="I164" t="n">
-        <v>0.02817018789415149</v>
+        <v>0.5763</v>
       </c>
       <c r="J164" t="n">
-        <v>0.5634037578830298</v>
+        <v>11.526</v>
       </c>
     </row>
     <row r="165">
@@ -8961,10 +8949,10 @@
         <v>1.02</v>
       </c>
       <c r="I165" t="n">
-        <v>-8.491814632718281e-05</v>
+        <v>-0.0281</v>
       </c>
       <c r="J165" t="n">
-        <v>-0.001698362926543656</v>
+        <v>-0.5620000000000001</v>
       </c>
     </row>
     <row r="166">
@@ -9001,10 +8989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.04887457677387512</v>
+        <v>-0.9796</v>
       </c>
       <c r="J166" t="n">
-        <v>-0.9774915354775024</v>
+        <v>-19.592</v>
       </c>
     </row>
     <row r="167">
@@ -9041,10 +9029,10 @@
         <v>1.43</v>
       </c>
       <c r="I167" t="n">
-        <v>0.05680767153350995</v>
+        <v>0.7236</v>
       </c>
       <c r="J167" t="n">
-        <v>1.136153430670199</v>
+        <v>14.472</v>
       </c>
     </row>
     <row r="168">
@@ -9081,10 +9069,10 @@
         <v>0.97</v>
       </c>
       <c r="I168" t="n">
-        <v>0.01894363260095268</v>
+        <v>-0.0235</v>
       </c>
       <c r="J168" t="n">
-        <v>0.3788726520190536</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="169">
@@ -9121,10 +9109,10 @@
         <v>0.77</v>
       </c>
       <c r="I169" t="n">
-        <v>0.004142167218497179</v>
+        <v>-0.3957</v>
       </c>
       <c r="J169" t="n">
-        <v>0.08284334436994359</v>
+        <v>-7.914</v>
       </c>
     </row>
     <row r="170">
@@ -9161,10 +9149,10 @@
         <v>0.65</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.005915187403554154</v>
+        <v>-0.5622</v>
       </c>
       <c r="J170" t="n">
-        <v>-0.1183037480710831</v>
+        <v>-11.244</v>
       </c>
     </row>
     <row r="171">
@@ -9201,10 +9189,10 @@
         <v>0.6</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.01010213515277513</v>
+        <v>-0.6264</v>
       </c>
       <c r="J171" t="n">
-        <v>-0.2020427030555025</v>
+        <v>-12.528</v>
       </c>
     </row>
     <row r="172">
@@ -9241,10 +9229,10 @@
         <v>1.42</v>
       </c>
       <c r="I172" t="n">
-        <v>0.0450415873141312</v>
+        <v>0.662</v>
       </c>
       <c r="J172" t="n">
-        <v>0.9909149209108864</v>
+        <v>14.564</v>
       </c>
     </row>
     <row r="173">
@@ -9281,10 +9269,10 @@
         <v>1.17</v>
       </c>
       <c r="I173" t="n">
-        <v>0.02607813542212881</v>
+        <v>0.331</v>
       </c>
       <c r="J173" t="n">
-        <v>0.5737189792868339</v>
+        <v>7.282</v>
       </c>
     </row>
     <row r="174">
@@ -9321,10 +9309,10 @@
         <v>0.9</v>
       </c>
       <c r="I174" t="n">
-        <v>0.007761839671508095</v>
+        <v>-0.2351</v>
       </c>
       <c r="J174" t="n">
-        <v>0.1707604727731781</v>
+        <v>-5.1722</v>
       </c>
     </row>
     <row r="175">
@@ -9361,10 +9349,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>0.006242717766240326</v>
+        <v>-0.2681</v>
       </c>
       <c r="J175" t="n">
-        <v>0.1373397908572872</v>
+        <v>-5.8982</v>
       </c>
     </row>
     <row r="176">
@@ -9401,10 +9389,10 @@
         <v>0.75</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.003727273501773008</v>
+        <v>-0.4584</v>
       </c>
       <c r="J176" t="n">
-        <v>-0.08200001703900618</v>
+        <v>-10.0848</v>
       </c>
     </row>
     <row r="177">
@@ -9441,10 +9429,10 @@
         <v>1.45</v>
       </c>
       <c r="I177" t="n">
-        <v>0.06985015399526673</v>
+        <v>0.6574</v>
       </c>
       <c r="J177" t="n">
-        <v>1.536703387895868</v>
+        <v>14.4628</v>
       </c>
     </row>
     <row r="178">
@@ -9481,10 +9469,10 @@
         <v>1.39</v>
       </c>
       <c r="I178" t="n">
-        <v>0.05968574717486032</v>
+        <v>0.5851</v>
       </c>
       <c r="J178" t="n">
-        <v>1.313086437846927</v>
+        <v>12.8722</v>
       </c>
     </row>
     <row r="179">
@@ -9521,10 +9509,10 @@
         <v>1.17</v>
       </c>
       <c r="I179" t="n">
-        <v>0.02372164257376377</v>
+        <v>0.2795</v>
       </c>
       <c r="J179" t="n">
-        <v>0.5218761366228029</v>
+        <v>6.149</v>
       </c>
     </row>
     <row r="180">
@@ -9561,10 +9549,10 @@
         <v>1.1</v>
       </c>
       <c r="I180" t="n">
-        <v>0.01448170243528373</v>
+        <v>0.1504</v>
       </c>
       <c r="J180" t="n">
-        <v>0.3185974535762421</v>
+        <v>3.3088</v>
       </c>
     </row>
     <row r="181">
@@ -9601,10 +9589,10 @@
         <v>0.66</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.05801157868527469</v>
+        <v>-0.5929</v>
       </c>
       <c r="J181" t="n">
-        <v>-1.276254731076043</v>
+        <v>-13.0438</v>
       </c>
     </row>
     <row r="182">
@@ -9641,10 +9629,10 @@
         <v>1.69</v>
       </c>
       <c r="I182" t="n">
-        <v>0.1026449360287835</v>
+        <v>1.6183</v>
       </c>
       <c r="J182" t="n">
-        <v>2.360833528662019</v>
+        <v>37.2209</v>
       </c>
     </row>
     <row r="183">
@@ -9681,10 +9669,10 @@
         <v>1.15</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0228008454704633</v>
+        <v>0.4443</v>
       </c>
       <c r="J183" t="n">
-        <v>0.5244194458206559</v>
+        <v>10.2189</v>
       </c>
     </row>
     <row r="184">
@@ -9721,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.02076800319271396</v>
+        <v>0.3721</v>
       </c>
       <c r="J184" t="n">
-        <v>0.4776640734324211</v>
+        <v>8.558299999999999</v>
       </c>
     </row>
     <row r="185">
@@ -9761,10 +9749,10 @@
         <v>1.09</v>
       </c>
       <c r="I185" t="n">
-        <v>0.01584576518317023</v>
+        <v>0.244</v>
       </c>
       <c r="J185" t="n">
-        <v>0.3644525992129154</v>
+        <v>5.612</v>
       </c>
     </row>
     <row r="186">
@@ -9801,10 +9789,10 @@
         <v>0.61</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.05534371181944142</v>
+        <v>-1.132</v>
       </c>
       <c r="J186" t="n">
-        <v>-1.272905371847153</v>
+        <v>-26.036</v>
       </c>
     </row>
     <row r="187">
@@ -9841,10 +9829,10 @@
         <v>1.43</v>
       </c>
       <c r="I187" t="n">
-        <v>0.04965337153258141</v>
+        <v>0.6766</v>
       </c>
       <c r="J187" t="n">
-        <v>1.142027545249372</v>
+        <v>15.5618</v>
       </c>
     </row>
     <row r="188">
@@ -9881,10 +9869,10 @@
         <v>1.18</v>
       </c>
       <c r="I188" t="n">
-        <v>0.02858070230971003</v>
+        <v>0.3488</v>
       </c>
       <c r="J188" t="n">
-        <v>0.6573561531233308</v>
+        <v>8.022399999999999</v>
       </c>
     </row>
     <row r="189">
@@ -9921,10 +9909,10 @@
         <v>1.14</v>
       </c>
       <c r="I189" t="n">
-        <v>0.0253565838473597</v>
+        <v>0.2875</v>
       </c>
       <c r="J189" t="n">
-        <v>0.583201428489273</v>
+        <v>6.6125</v>
       </c>
     </row>
     <row r="190">
@@ -9961,10 +9949,10 @@
         <v>0.79</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.001790932092578343</v>
+        <v>-0.4015</v>
       </c>
       <c r="J190" t="n">
-        <v>-0.04119143812930189</v>
+        <v>-9.234500000000001</v>
       </c>
     </row>
     <row r="191">
@@ -10001,10 +9989,10 @@
         <v>0.54</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.02255614259482576</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="J191" t="n">
-        <v>-0.5187912796809924</v>
+        <v>-16.5439</v>
       </c>
     </row>
     <row r="192">
@@ -10041,10 +10029,10 @@
         <v>1.23</v>
       </c>
       <c r="I192" t="n">
-        <v>0.04110859564654763</v>
+        <v>0.4179</v>
       </c>
       <c r="J192" t="n">
-        <v>0.9866062955171432</v>
+        <v>10.0296</v>
       </c>
     </row>
     <row r="193">
@@ -10081,10 +10069,10 @@
         <v>1.17</v>
       </c>
       <c r="I193" t="n">
-        <v>0.03320200885627944</v>
+        <v>0.331</v>
       </c>
       <c r="J193" t="n">
-        <v>0.7968482125507066</v>
+        <v>7.944</v>
       </c>
     </row>
     <row r="194">
@@ -10121,10 +10109,10 @@
         <v>1.03</v>
       </c>
       <c r="I194" t="n">
-        <v>0.01684180230567769</v>
+        <v>0.078</v>
       </c>
       <c r="J194" t="n">
-        <v>0.4042032553362647</v>
+        <v>1.872</v>
       </c>
     </row>
     <row r="195">
@@ -10161,10 +10149,10 @@
         <v>0.92</v>
       </c>
       <c r="I195" t="n">
-        <v>0.004324444216393657</v>
+        <v>-0.2005</v>
       </c>
       <c r="J195" t="n">
-        <v>0.1037866611934478</v>
+        <v>-4.812</v>
       </c>
     </row>
     <row r="196">
@@ -10201,10 +10189,10 @@
         <v>0.77</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.01554419829830557</v>
+        <v>-0.4311</v>
       </c>
       <c r="J196" t="n">
-        <v>-0.3730607591593338</v>
+        <v>-10.3464</v>
       </c>
     </row>
     <row r="197">
@@ -10241,10 +10229,10 @@
         <v>1.43</v>
       </c>
       <c r="I197" t="n">
-        <v>0.06449224500989473</v>
+        <v>1.1309</v>
       </c>
       <c r="J197" t="n">
-        <v>1.547813880237473</v>
+        <v>27.1416</v>
       </c>
     </row>
     <row r="198">
@@ -10281,10 +10269,10 @@
         <v>1.2</v>
       </c>
       <c r="I198" t="n">
-        <v>0.03203658952159187</v>
+        <v>0.6066</v>
       </c>
       <c r="J198" t="n">
-        <v>0.7688781485182049</v>
+        <v>14.5584</v>
       </c>
     </row>
     <row r="199">
@@ -10321,10 +10309,10 @@
         <v>1.11</v>
       </c>
       <c r="I199" t="n">
-        <v>0.02063678338565846</v>
+        <v>0.3497</v>
       </c>
       <c r="J199" t="n">
-        <v>0.4952828012558029</v>
+        <v>8.392799999999999</v>
       </c>
     </row>
     <row r="200">
@@ -10361,10 +10349,10 @@
         <v>0.93</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.001565866013137896</v>
+        <v>-0.354</v>
       </c>
       <c r="J200" t="n">
-        <v>-0.03758078431530951</v>
+        <v>-8.496</v>
       </c>
     </row>
     <row r="201">
@@ -10401,10 +10389,10 @@
         <v>0.83</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.01574137168992957</v>
+        <v>-0.6286</v>
       </c>
       <c r="J201" t="n">
-        <v>-0.3777929205583097</v>
+        <v>-15.0864</v>
       </c>
     </row>
     <row r="202">
@@ -10441,10 +10429,10 @@
         <v>1.44</v>
       </c>
       <c r="I202" t="n">
-        <v>0.06305389994884923</v>
+        <v>0.6717</v>
       </c>
       <c r="J202" t="n">
-        <v>1.450239698823532</v>
+        <v>15.4491</v>
       </c>
     </row>
     <row r="203">
@@ -10481,10 +10469,10 @@
         <v>1.24</v>
       </c>
       <c r="I203" t="n">
-        <v>0.03655551876597384</v>
+        <v>0.417</v>
       </c>
       <c r="J203" t="n">
-        <v>0.8407769316173984</v>
+        <v>9.590999999999999</v>
       </c>
     </row>
     <row r="204">
@@ -10521,10 +10509,10 @@
         <v>1.03</v>
       </c>
       <c r="I204" t="n">
-        <v>0.01245652348247174</v>
+        <v>0.0483</v>
       </c>
       <c r="J204" t="n">
-        <v>0.2865000400968501</v>
+        <v>1.1109</v>
       </c>
     </row>
     <row r="205">
@@ -10561,10 +10549,10 @@
         <v>0.9</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.004142388062533035</v>
+        <v>-0.2468</v>
       </c>
       <c r="J205" t="n">
-        <v>-0.0952749254382598</v>
+        <v>-5.6764</v>
       </c>
     </row>
     <row r="206">
@@ -10601,10 +10589,10 @@
         <v>0.73</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.02668581819510354</v>
+        <v>-0.4928</v>
       </c>
       <c r="J206" t="n">
-        <v>-0.6137738184873814</v>
+        <v>-11.3344</v>
       </c>
     </row>
     <row r="207">
@@ -10641,10 +10629,10 @@
         <v>1.86</v>
       </c>
       <c r="I207" t="n">
-        <v>0.1151324809877862</v>
+        <v>1.9055</v>
       </c>
       <c r="J207" t="n">
-        <v>2.648047062719082</v>
+        <v>43.8265</v>
       </c>
     </row>
     <row r="208">
@@ -10681,10 +10669,10 @@
         <v>1.27</v>
       </c>
       <c r="I208" t="n">
-        <v>0.03542072371168451</v>
+        <v>0.7522</v>
       </c>
       <c r="J208" t="n">
-        <v>0.8146766453687437</v>
+        <v>17.3006</v>
       </c>
     </row>
     <row r="209">
@@ -10721,10 +10709,10 @@
         <v>0.96</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.003763989829543322</v>
+        <v>-0.276</v>
       </c>
       <c r="J209" t="n">
-        <v>-0.0865717660794964</v>
+        <v>-6.348</v>
       </c>
     </row>
     <row r="210">
@@ -10761,10 +10749,10 @@
         <v>0.91</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.01085306423039833</v>
+        <v>-0.4308</v>
       </c>
       <c r="J210" t="n">
-        <v>-0.2496204772991616</v>
+        <v>-9.9084</v>
       </c>
     </row>
     <row r="211">
@@ -10801,10 +10789,10 @@
         <v>0.73</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.03615784989734472</v>
+        <v>-0.8777</v>
       </c>
       <c r="J211" t="n">
-        <v>-0.8316305476389285</v>
+        <v>-20.1871</v>
       </c>
     </row>
     <row r="212">
@@ -10841,10 +10829,10 @@
         <v>1.3</v>
       </c>
       <c r="I212" t="n">
-        <v>0.05437423861032645</v>
+        <v>0.5655</v>
       </c>
       <c r="J212" t="n">
-        <v>1.033110533596203</v>
+        <v>10.7445</v>
       </c>
     </row>
     <row r="213">
@@ -10881,10 +10869,10 @@
         <v>0.88</v>
       </c>
       <c r="I213" t="n">
-        <v>0.00965276130163866</v>
+        <v>-0.1982</v>
       </c>
       <c r="J213" t="n">
-        <v>0.1834024647311345</v>
+        <v>-3.7658</v>
       </c>
     </row>
     <row r="214">
@@ -10921,10 +10909,10 @@
         <v>0.78</v>
       </c>
       <c r="I214" t="n">
-        <v>0.0002974928393757389</v>
+        <v>-0.3773</v>
       </c>
       <c r="J214" t="n">
-        <v>0.00565236394813904</v>
+        <v>-7.1687</v>
       </c>
     </row>
     <row r="215">
@@ -10961,10 +10949,10 @@
         <v>0.76</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.001835805988176311</v>
+        <v>-0.4072</v>
       </c>
       <c r="J215" t="n">
-        <v>-0.03488031377534991</v>
+        <v>-7.7368</v>
       </c>
     </row>
     <row r="216">
@@ -11001,10 +10989,10 @@
         <v>0.65</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.01381582623073239</v>
+        <v>-0.5599</v>
       </c>
       <c r="J216" t="n">
-        <v>-0.2625006983839154</v>
+        <v>-10.6381</v>
       </c>
     </row>
     <row r="217">
@@ -11041,10 +11029,10 @@
         <v>1.88</v>
       </c>
       <c r="I217" t="n">
-        <v>0.1664026305516605</v>
+        <v>1.8771</v>
       </c>
       <c r="J217" t="n">
-        <v>3.16164998048155</v>
+        <v>35.6649</v>
       </c>
     </row>
     <row r="218">
@@ -11081,10 +11069,10 @@
         <v>1.55</v>
       </c>
       <c r="I218" t="n">
-        <v>0.0941321688432913</v>
+        <v>1.2798</v>
       </c>
       <c r="J218" t="n">
-        <v>1.788511208022535</v>
+        <v>24.3162</v>
       </c>
     </row>
     <row r="219">
@@ -11121,10 +11109,10 @@
         <v>1.07</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.01087903059093518</v>
+        <v>0.1132</v>
       </c>
       <c r="J219" t="n">
-        <v>-0.2067015812277685</v>
+        <v>2.1508</v>
       </c>
     </row>
     <row r="220">
@@ -11161,10 +11149,10 @@
         <v>1.03</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0202660510656555</v>
+        <v>-0.0155</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.3850549702474545</v>
+        <v>-0.2945</v>
       </c>
     </row>
     <row r="221">
@@ -11201,10 +11189,10 @@
         <v>0.9</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.05007293938401909</v>
+        <v>-0.4994</v>
       </c>
       <c r="J221" t="n">
-        <v>-0.9513858482963627</v>
+        <v>-9.4886</v>
       </c>
     </row>
     <row r="222">
@@ -11241,10 +11229,10 @@
         <v>1.24</v>
       </c>
       <c r="I222" t="n">
-        <v>0.04628472336246425</v>
+        <v>0.4645</v>
       </c>
       <c r="J222" t="n">
-        <v>1.064548637336678</v>
+        <v>10.6835</v>
       </c>
     </row>
     <row r="223">
@@ -11281,10 +11269,10 @@
         <v>1.03</v>
       </c>
       <c r="I223" t="n">
-        <v>0.02373210701264465</v>
+        <v>0.1233</v>
       </c>
       <c r="J223" t="n">
-        <v>0.545838461290827</v>
+        <v>2.8359</v>
       </c>
     </row>
     <row r="224">
@@ -11321,10 +11309,10 @@
         <v>0.98</v>
       </c>
       <c r="I224" t="n">
-        <v>0.01852072218006795</v>
+        <v>-0.0212</v>
       </c>
       <c r="J224" t="n">
-        <v>0.4259766101415629</v>
+        <v>-0.4876</v>
       </c>
     </row>
     <row r="225">
@@ -11361,10 +11349,10 @@
         <v>0.75</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.004413710164195058</v>
+        <v>-0.4377</v>
       </c>
       <c r="J225" t="n">
-        <v>-0.1015153337764863</v>
+        <v>-10.0671</v>
       </c>
     </row>
     <row r="226">
@@ -11401,10 +11389,10 @@
         <v>0.65</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.01548065770088889</v>
+        <v>-0.5718</v>
       </c>
       <c r="J226" t="n">
-        <v>-0.3560551271204444</v>
+        <v>-13.1514</v>
       </c>
     </row>
     <row r="227">
@@ -11441,10 +11429,10 @@
         <v>1.6</v>
       </c>
       <c r="I227" t="n">
-        <v>0.1327270181281708</v>
+        <v>1.4554</v>
       </c>
       <c r="J227" t="n">
-        <v>3.052721416947927</v>
+        <v>33.4742</v>
       </c>
     </row>
     <row r="228">
@@ -11481,10 +11469,10 @@
         <v>1.23</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0480576993894579</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="J228" t="n">
-        <v>1.105327085957532</v>
+        <v>15.3594</v>
       </c>
     </row>
     <row r="229">
@@ -11521,10 +11509,10 @@
         <v>1</v>
       </c>
       <c r="I229" t="n">
-        <v>0.0005169687165564145</v>
+        <v>-0.0916</v>
       </c>
       <c r="J229" t="n">
-        <v>0.01189028048079753</v>
+        <v>-2.1068</v>
       </c>
     </row>
     <row r="230">
@@ -11561,10 +11549,10 @@
         <v>0.97</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.006282119292859517</v>
+        <v>-0.2317</v>
       </c>
       <c r="J230" t="n">
-        <v>-0.1444887437357689</v>
+        <v>-5.3291</v>
       </c>
     </row>
     <row r="231">
@@ -11601,10 +11589,10 @@
         <v>0.82</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.04013043222269128</v>
+        <v>-0.661</v>
       </c>
       <c r="J231" t="n">
-        <v>-0.9229999411218993</v>
+        <v>-15.203</v>
       </c>
     </row>
     <row r="232">
@@ -11641,10 +11629,10 @@
         <v>1.81</v>
       </c>
       <c r="I232" t="n">
-        <v>0.08509946003178276</v>
+        <v>1.6781</v>
       </c>
       <c r="J232" t="n">
-        <v>1.276491900476741</v>
+        <v>25.1715</v>
       </c>
     </row>
     <row r="233">
@@ -11681,10 +11669,10 @@
         <v>1.69</v>
       </c>
       <c r="I233" t="n">
-        <v>0.06741858157347458</v>
+        <v>1.461</v>
       </c>
       <c r="J233" t="n">
-        <v>1.011278723602119</v>
+        <v>21.915</v>
       </c>
     </row>
     <row r="234">
@@ -11721,10 +11709,10 @@
         <v>1.45</v>
       </c>
       <c r="I234" t="n">
-        <v>0.03483611999534764</v>
+        <v>0.95</v>
       </c>
       <c r="J234" t="n">
-        <v>0.5225417999302145</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="235">
@@ -11761,10 +11749,10 @@
         <v>1.29</v>
       </c>
       <c r="I235" t="n">
-        <v>0.01166213392769087</v>
+        <v>0.5972</v>
       </c>
       <c r="J235" t="n">
-        <v>0.1749320089153631</v>
+        <v>8.958</v>
       </c>
     </row>
     <row r="236">
@@ -11801,10 +11789,10 @@
         <v>1.15</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.009693080412688067</v>
+        <v>0.2719</v>
       </c>
       <c r="J236" t="n">
-        <v>-0.145396206190321</v>
+        <v>4.0785</v>
       </c>
     </row>
     <row r="237">
@@ -11841,10 +11829,10 @@
         <v>1.26</v>
       </c>
       <c r="I237" t="n">
-        <v>0.06888942756388658</v>
+        <v>0.5466</v>
       </c>
       <c r="J237" t="n">
-        <v>1.033341413458299</v>
+        <v>8.199</v>
       </c>
     </row>
     <row r="238">
@@ -11881,10 +11869,10 @@
         <v>1.18</v>
       </c>
       <c r="I238" t="n">
-        <v>0.05649584987983521</v>
+        <v>0.4343</v>
       </c>
       <c r="J238" t="n">
-        <v>0.847437748197528</v>
+        <v>6.5145</v>
       </c>
     </row>
     <row r="239">
@@ -11921,10 +11909,10 @@
         <v>0.6</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.02992732823932704</v>
+        <v>-0.6051</v>
       </c>
       <c r="J239" t="n">
-        <v>-0.4489099235899056</v>
+        <v>-9.076499999999999</v>
       </c>
     </row>
     <row r="240">
@@ -11961,10 +11949,10 @@
         <v>0.51</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.04376973025167138</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="J240" t="n">
-        <v>-0.6565459537750707</v>
+        <v>-10.8045</v>
       </c>
     </row>
     <row r="241">
@@ -12001,10 +11989,10 @@
         <v>0.4</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.0603840206450847</v>
+        <v>-0.8526</v>
       </c>
       <c r="J241" t="n">
-        <v>-0.9057603096762705</v>
+        <v>-12.789</v>
       </c>
     </row>
     <row r="242">
@@ -12041,10 +12029,10 @@
         <v>1.11</v>
       </c>
       <c r="I242" t="n">
-        <v>0.03214931313898074</v>
+        <v>0.3299</v>
       </c>
       <c r="J242" t="n">
-        <v>0.5465383233626726</v>
+        <v>5.6083</v>
       </c>
     </row>
     <row r="243">
@@ -12081,10 +12069,10 @@
         <v>0.97</v>
       </c>
       <c r="I243" t="n">
-        <v>0.02145930938344442</v>
+        <v>0.0206</v>
       </c>
       <c r="J243" t="n">
-        <v>0.3648082595185551</v>
+        <v>0.3502</v>
       </c>
     </row>
     <row r="244">
@@ -12121,10 +12109,10 @@
         <v>0.86</v>
       </c>
       <c r="I244" t="n">
-        <v>0.013262390456126</v>
+        <v>-0.1819</v>
       </c>
       <c r="J244" t="n">
-        <v>0.2254606377541421</v>
+        <v>-3.0923</v>
       </c>
     </row>
     <row r="245">
@@ -12161,10 +12149,10 @@
         <v>0.51</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.01090545400248223</v>
+        <v>-0.7186</v>
       </c>
       <c r="J245" t="n">
-        <v>-0.1853927180421979</v>
+        <v>-12.2162</v>
       </c>
     </row>
     <row r="246">
@@ -12201,10 +12189,10 @@
         <v>0.46</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.01457911037776766</v>
+        <v>-0.78</v>
       </c>
       <c r="J246" t="n">
-        <v>-0.2478448764220502</v>
+        <v>-13.26</v>
       </c>
     </row>
     <row r="247">
@@ -12241,10 +12229,10 @@
         <v>1.82</v>
       </c>
       <c r="I247" t="n">
-        <v>0.1678100170746999</v>
+        <v>0.9811</v>
       </c>
       <c r="J247" t="n">
-        <v>2.852770290269897</v>
+        <v>16.6787</v>
       </c>
     </row>
     <row r="248">
@@ -12281,10 +12269,10 @@
         <v>1.78</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1557545618408858</v>
+        <v>0.9405</v>
       </c>
       <c r="J248" t="n">
-        <v>2.647827551295059</v>
+        <v>15.9885</v>
       </c>
     </row>
     <row r="249">
@@ -12321,10 +12309,10 @@
         <v>1.37</v>
       </c>
       <c r="I249" t="n">
-        <v>0.03708447228513111</v>
+        <v>0.4513</v>
       </c>
       <c r="J249" t="n">
-        <v>0.6304360288472288</v>
+        <v>7.6721</v>
       </c>
     </row>
     <row r="250">
@@ -12361,10 +12349,10 @@
         <v>1.37</v>
       </c>
       <c r="I250" t="n">
-        <v>0.03708447228513111</v>
+        <v>0.4513</v>
       </c>
       <c r="J250" t="n">
-        <v>0.6304360288472288</v>
+        <v>7.6721</v>
       </c>
     </row>
     <row r="251">
@@ -12401,10 +12389,10 @@
         <v>0.91</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.1063086393999676</v>
+        <v>-0.2914</v>
       </c>
       <c r="J251" t="n">
-        <v>-1.807246869799448</v>
+        <v>-4.9538</v>
       </c>
     </row>
     <row r="252">
@@ -12441,10 +12429,10 @@
         <v>1.68</v>
       </c>
       <c r="I252" t="n">
-        <v>0.09821247587193209</v>
+        <v>1.5797</v>
       </c>
       <c r="J252" t="n">
-        <v>2.35709942092637</v>
+        <v>37.9128</v>
       </c>
     </row>
     <row r="253">
@@ -12481,10 +12469,10 @@
         <v>1.38</v>
       </c>
       <c r="I253" t="n">
-        <v>0.05360620543960441</v>
+        <v>0.9861</v>
       </c>
       <c r="J253" t="n">
-        <v>1.286548930550506</v>
+        <v>23.6664</v>
       </c>
     </row>
     <row r="254">
@@ -12521,10 +12509,10 @@
         <v>1.11</v>
       </c>
       <c r="I254" t="n">
-        <v>0.01598029132523592</v>
+        <v>0.2793</v>
       </c>
       <c r="J254" t="n">
-        <v>0.3835269918056621</v>
+        <v>6.7032</v>
       </c>
     </row>
     <row r="255">
@@ -12561,10 +12549,10 @@
         <v>0.86</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.02103285276373924</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="J255" t="n">
-        <v>-0.5047884663297417</v>
+        <v>-13.8024</v>
       </c>
     </row>
     <row r="256">
@@ -12601,10 +12589,10 @@
         <v>0.84</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.02406479670247929</v>
+        <v>-0.6258</v>
       </c>
       <c r="J256" t="n">
-        <v>-0.5775551208595029</v>
+        <v>-15.0192</v>
       </c>
     </row>
     <row r="257">
@@ -12641,10 +12629,10 @@
         <v>1.08</v>
       </c>
       <c r="I257" t="n">
-        <v>0.02895007978217804</v>
+        <v>0.2093</v>
       </c>
       <c r="J257" t="n">
-        <v>0.694801914772273</v>
+        <v>5.0232</v>
       </c>
     </row>
     <row r="258">
@@ -12681,10 +12669,10 @@
         <v>1.03</v>
       </c>
       <c r="I258" t="n">
-        <v>0.02128938808942203</v>
+        <v>0.1116</v>
       </c>
       <c r="J258" t="n">
-        <v>0.5109453141461286</v>
+        <v>2.6784</v>
       </c>
     </row>
     <row r="259">
@@ -12721,10 +12709,10 @@
         <v>1.01</v>
       </c>
       <c r="I259" t="n">
-        <v>0.01833824752765208</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="J259" t="n">
-        <v>0.44011794066365</v>
+        <v>1.5048</v>
       </c>
     </row>
     <row r="260">
@@ -12761,10 +12749,10 @@
         <v>0.88</v>
       </c>
       <c r="I260" t="n">
-        <v>0.001100945536332533</v>
+        <v>-0.2477</v>
       </c>
       <c r="J260" t="n">
-        <v>0.02642269287198079</v>
+        <v>-5.9448</v>
       </c>
     </row>
     <row r="261">
@@ -12801,10 +12789,10 @@
         <v>0.79</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.01293975921087346</v>
+        <v>-0.3878</v>
       </c>
       <c r="J261" t="n">
-        <v>-0.3105542210609631</v>
+        <v>-9.3072</v>
       </c>
     </row>
     <row r="262">
@@ -12841,10 +12829,10 @@
         <v>1.09</v>
       </c>
       <c r="I262" t="n">
-        <v>0.03265944329214315</v>
+        <v>0.2915</v>
       </c>
       <c r="J262" t="n">
-        <v>0.6531888658428631</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="263">
@@ -12881,10 +12869,10 @@
         <v>0.98</v>
       </c>
       <c r="I263" t="n">
-        <v>0.02330151991411903</v>
+        <v>0.0379</v>
       </c>
       <c r="J263" t="n">
-        <v>0.4660303982823807</v>
+        <v>0.758</v>
       </c>
     </row>
     <row r="264">
@@ -12921,10 +12909,10 @@
         <v>0.8</v>
       </c>
       <c r="I264" t="n">
-        <v>0.009099313193062642</v>
+        <v>-0.2951</v>
       </c>
       <c r="J264" t="n">
-        <v>0.1819862638612528</v>
+        <v>-5.902</v>
       </c>
     </row>
     <row r="265">
@@ -12961,10 +12949,10 @@
         <v>0.57</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.008662597732529548</v>
+        <v>-0.6453</v>
       </c>
       <c r="J265" t="n">
-        <v>-0.173251954650591</v>
+        <v>-12.906</v>
       </c>
     </row>
     <row r="266">
@@ -13001,10 +12989,10 @@
         <v>0.53</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.01196728627154251</v>
+        <v>-0.6961000000000001</v>
       </c>
       <c r="J266" t="n">
-        <v>-0.2393457254308502</v>
+        <v>-13.922</v>
       </c>
     </row>
     <row r="267">
@@ -13041,10 +13029,10 @@
         <v>1.7</v>
       </c>
       <c r="I267" t="n">
-        <v>0.1402129530136389</v>
+        <v>0.879</v>
       </c>
       <c r="J267" t="n">
-        <v>2.804259060272778</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="268">
@@ -13081,10 +13069,10 @@
         <v>1.69</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1374574449117469</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="J268" t="n">
-        <v>2.749148898234939</v>
+        <v>17.368</v>
       </c>
     </row>
     <row r="269">
@@ -13121,10 +13109,10 @@
         <v>1.38</v>
       </c>
       <c r="I269" t="n">
-        <v>0.05276795788676279</v>
+        <v>0.5046</v>
       </c>
       <c r="J269" t="n">
-        <v>1.055359157735256</v>
+        <v>10.092</v>
       </c>
     </row>
     <row r="270">
@@ -13161,10 +13149,10 @@
         <v>1.1</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.02192946744536671</v>
+        <v>0.1002</v>
       </c>
       <c r="J270" t="n">
-        <v>-0.4385893489073343</v>
+        <v>2.004</v>
       </c>
     </row>
     <row r="271">
@@ -13201,10 +13189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.06761552778654585</v>
+        <v>-0.232</v>
       </c>
       <c r="J271" t="n">
-        <v>-1.352310555730917</v>
+        <v>-4.64</v>
       </c>
     </row>
     <row r="272">
@@ -13241,10 +13229,10 @@
         <v>1.98</v>
       </c>
       <c r="I272" t="n">
-        <v>0.1233179592691693</v>
+        <v>1.9568</v>
       </c>
       <c r="J272" t="n">
-        <v>2.343041226114217</v>
+        <v>37.1792</v>
       </c>
     </row>
     <row r="273">
@@ -13281,10 +13269,10 @@
         <v>1.94</v>
       </c>
       <c r="I273" t="n">
-        <v>0.1172064491021207</v>
+        <v>1.9086</v>
       </c>
       <c r="J273" t="n">
-        <v>2.226922532940293</v>
+        <v>36.2634</v>
       </c>
     </row>
     <row r="274">
@@ -13321,10 +13309,10 @@
         <v>1.52</v>
       </c>
       <c r="I274" t="n">
-        <v>0.04937936115760864</v>
+        <v>1.1472</v>
       </c>
       <c r="J274" t="n">
-        <v>0.9382078619945643</v>
+        <v>21.7968</v>
       </c>
     </row>
     <row r="275">
@@ -13361,10 +13349,10 @@
         <v>0.98</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.03691543620206217</v>
+        <v>-0.2876</v>
       </c>
       <c r="J275" t="n">
-        <v>-0.7013932878391812</v>
+        <v>-5.4644</v>
       </c>
     </row>
     <row r="276">
@@ -13401,10 +13389,10 @@
         <v>0.76</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.07089618209210104</v>
+        <v>-0.8653999999999999</v>
       </c>
       <c r="J276" t="n">
-        <v>-1.34702745974992</v>
+        <v>-16.4426</v>
       </c>
     </row>
     <row r="277">
@@ -13441,10 +13429,10 @@
         <v>1.06</v>
       </c>
       <c r="I277" t="n">
-        <v>0.03179855835109908</v>
+        <v>0.2218</v>
       </c>
       <c r="J277" t="n">
-        <v>0.6041726086708826</v>
+        <v>4.2142</v>
       </c>
     </row>
     <row r="278">
@@ -13481,10 +13469,10 @@
         <v>0.98</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0203214838206787</v>
+        <v>0.0208</v>
       </c>
       <c r="J278" t="n">
-        <v>0.3861081925928954</v>
+        <v>0.3952</v>
       </c>
     </row>
     <row r="279">
@@ -13521,10 +13509,10 @@
         <v>0.93</v>
       </c>
       <c r="I279" t="n">
-        <v>0.01331254864955903</v>
+        <v>-0.082</v>
       </c>
       <c r="J279" t="n">
-        <v>0.2529384243416216</v>
+        <v>-1.558</v>
       </c>
     </row>
     <row r="280">
@@ -13561,10 +13549,10 @@
         <v>0.74</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.009967092629720068</v>
+        <v>-0.4231</v>
       </c>
       <c r="J280" t="n">
-        <v>-0.1893747599646813</v>
+        <v>-8.0389</v>
       </c>
     </row>
     <row r="281">
@@ -13601,10 +13589,10 @@
         <v>0.46</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.0488197203544823</v>
+        <v>-0.7886</v>
       </c>
       <c r="J281" t="n">
-        <v>-0.9275746867351637</v>
+        <v>-14.9834</v>
       </c>
     </row>
     <row r="282">
@@ -13641,10 +13629,10 @@
         <v>1.54</v>
       </c>
       <c r="I282" t="n">
-        <v>0.07946834412197147</v>
+        <v>1.2878</v>
       </c>
       <c r="J282" t="n">
-        <v>1.907240258927315</v>
+        <v>30.9072</v>
       </c>
     </row>
     <row r="283">
@@ -13681,10 +13669,10 @@
         <v>1.41</v>
       </c>
       <c r="I283" t="n">
-        <v>0.05771734645783821</v>
+        <v>1.0225</v>
       </c>
       <c r="J283" t="n">
-        <v>1.385216314988117</v>
+        <v>24.54</v>
       </c>
     </row>
     <row r="284">
@@ -13721,10 +13709,10 @@
         <v>1.3</v>
       </c>
       <c r="I284" t="n">
-        <v>0.03954684591772938</v>
+        <v>0.7752</v>
       </c>
       <c r="J284" t="n">
-        <v>0.949124302025505</v>
+        <v>18.6048</v>
       </c>
     </row>
     <row r="285">
@@ -13761,10 +13749,10 @@
         <v>1.24</v>
       </c>
       <c r="I285" t="n">
-        <v>0.0306695473906254</v>
+        <v>0.6212</v>
       </c>
       <c r="J285" t="n">
-        <v>0.7360691373750096</v>
+        <v>14.9088</v>
       </c>
     </row>
     <row r="286">
@@ -13801,10 +13789,10 @@
         <v>0.65</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.06404165072242521</v>
+        <v>-1.0664</v>
       </c>
       <c r="J286" t="n">
-        <v>-1.536999617338205</v>
+        <v>-25.5936</v>
       </c>
     </row>
     <row r="287">
@@ -13841,10 +13829,10 @@
         <v>1.08</v>
       </c>
       <c r="I287" t="n">
-        <v>0.03557586736484014</v>
+        <v>0.2403</v>
       </c>
       <c r="J287" t="n">
-        <v>0.8538208167561634</v>
+        <v>5.7672</v>
       </c>
     </row>
     <row r="288">
@@ -13881,10 +13869,10 @@
         <v>1.04</v>
       </c>
       <c r="I288" t="n">
-        <v>0.02980042760867363</v>
+        <v>0.1654</v>
       </c>
       <c r="J288" t="n">
-        <v>0.715210262608167</v>
+        <v>3.9696</v>
       </c>
     </row>
     <row r="289">
@@ -13921,10 +13909,10 @@
         <v>0.87</v>
       </c>
       <c r="I289" t="n">
-        <v>0.007674491421675764</v>
+        <v>-0.227</v>
       </c>
       <c r="J289" t="n">
-        <v>0.1841877941202184</v>
+        <v>-5.448</v>
       </c>
     </row>
     <row r="290">
@@ -13961,10 +13949,10 @@
         <v>0.7</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.01511885865361965</v>
+        <v>-0.4937</v>
       </c>
       <c r="J290" t="n">
-        <v>-0.3628526076868717</v>
+        <v>-11.8488</v>
       </c>
     </row>
     <row r="291">
@@ -14001,10 +13989,10 @@
         <v>0.7</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.01511885865361965</v>
+        <v>-0.4937</v>
       </c>
       <c r="J291" t="n">
-        <v>-0.3628526076868717</v>
+        <v>-11.8488</v>
       </c>
     </row>
     <row r="292">
@@ -14041,10 +14029,10 @@
         <v>1.28</v>
       </c>
       <c r="I292" t="n">
-        <v>0.05408716392012489</v>
+        <v>0.5056</v>
       </c>
       <c r="J292" t="n">
-        <v>1.568527753683622</v>
+        <v>14.6624</v>
       </c>
     </row>
     <row r="293">
@@ -14081,10 +14069,10 @@
         <v>1.07</v>
       </c>
       <c r="I293" t="n">
-        <v>0.02692327925269889</v>
+        <v>0.1881</v>
       </c>
       <c r="J293" t="n">
-        <v>0.7807750983282679</v>
+        <v>5.4549</v>
       </c>
     </row>
     <row r="294">
@@ -14121,10 +14109,10 @@
         <v>0.89</v>
       </c>
       <c r="I294" t="n">
-        <v>0.006514536312493777</v>
+        <v>-0.2335</v>
       </c>
       <c r="J294" t="n">
-        <v>0.1889215530623195</v>
+        <v>-6.7715</v>
       </c>
     </row>
     <row r="295">
@@ -14161,10 +14149,10 @@
         <v>0.87</v>
       </c>
       <c r="I295" t="n">
-        <v>0.003968747177372924</v>
+        <v>-0.2671</v>
       </c>
       <c r="J295" t="n">
-        <v>0.1150936681438148</v>
+        <v>-7.7459</v>
       </c>
     </row>
     <row r="296">
@@ -14201,10 +14189,10 @@
         <v>0.72</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.01584299498466628</v>
+        <v>-0.4872</v>
       </c>
       <c r="J296" t="n">
-        <v>-0.4594468545553222</v>
+        <v>-14.1288</v>
       </c>
     </row>
     <row r="297">
@@ -14241,10 +14229,10 @@
         <v>1.4</v>
       </c>
       <c r="I297" t="n">
-        <v>0.08787351680645047</v>
+        <v>1.0712</v>
       </c>
       <c r="J297" t="n">
-        <v>2.548331987387064</v>
+        <v>31.0648</v>
       </c>
     </row>
     <row r="298">
@@ -14281,10 +14269,10 @@
         <v>1.28</v>
       </c>
       <c r="I298" t="n">
-        <v>0.06126318878856181</v>
+        <v>0.8055</v>
       </c>
       <c r="J298" t="n">
-        <v>1.776632474868292</v>
+        <v>23.3595</v>
       </c>
     </row>
     <row r="299">
@@ -14321,10 +14309,10 @@
         <v>1.16</v>
       </c>
       <c r="I299" t="n">
-        <v>0.03512104782764711</v>
+        <v>0.504</v>
       </c>
       <c r="J299" t="n">
-        <v>1.018510387001766</v>
+        <v>14.616</v>
       </c>
     </row>
     <row r="300">
@@ -14361,10 +14349,10 @@
         <v>0.83</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.03127269915778151</v>
+        <v>-0.6266</v>
       </c>
       <c r="J300" t="n">
-        <v>-0.9069082755756638</v>
+        <v>-18.1714</v>
       </c>
     </row>
     <row r="301">
@@ -14401,10 +14389,10 @@
         <v>0.8</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.03793254086386844</v>
+        <v>-0.7008</v>
       </c>
       <c r="J301" t="n">
-        <v>-1.100043685052185</v>
+        <v>-20.3232</v>
       </c>
     </row>
     <row r="302">
@@ -14441,10 +14429,10 @@
         <v>1.13</v>
       </c>
       <c r="I302" t="n">
-        <v>0.04241842211995391</v>
+        <v>0.323</v>
       </c>
       <c r="J302" t="n">
-        <v>0.890786864519032</v>
+        <v>6.783</v>
       </c>
     </row>
     <row r="303">
@@ -14481,10 +14469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I303" t="n">
-        <v>0.01769110349653657</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J303" t="n">
-        <v>0.3715131734272679</v>
+        <v>-1.7451</v>
       </c>
     </row>
     <row r="304">
@@ -14521,10 +14509,10 @@
         <v>0.83</v>
       </c>
       <c r="I304" t="n">
-        <v>0.00581298924951365</v>
+        <v>-0.2994</v>
       </c>
       <c r="J304" t="n">
-        <v>0.1220727742397867</v>
+        <v>-6.2874</v>
       </c>
     </row>
     <row r="305">
@@ -14561,10 +14549,10 @@
         <v>0.75</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.004289010942833026</v>
+        <v>-0.4231</v>
       </c>
       <c r="J305" t="n">
-        <v>-0.09006922979949356</v>
+        <v>-8.8851</v>
       </c>
     </row>
     <row r="306">
@@ -14601,10 +14589,10 @@
         <v>0.74</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.005594112360395431</v>
+        <v>-0.4376</v>
       </c>
       <c r="J306" t="n">
-        <v>-0.117476359568304</v>
+        <v>-9.1896</v>
       </c>
     </row>
     <row r="307">
@@ -14641,10 +14629,10 @@
         <v>1.72</v>
       </c>
       <c r="I307" t="n">
-        <v>0.1472728508193641</v>
+        <v>1.6587</v>
       </c>
       <c r="J307" t="n">
-        <v>3.092729867206646</v>
+        <v>34.8327</v>
       </c>
     </row>
     <row r="308">
@@ -14681,10 +14669,10 @@
         <v>1.41</v>
       </c>
       <c r="I308" t="n">
-        <v>0.08168681048241205</v>
+        <v>1.0565</v>
       </c>
       <c r="J308" t="n">
-        <v>1.715423020130653</v>
+        <v>22.1865</v>
       </c>
     </row>
     <row r="309">
@@ -14721,10 +14709,10 @@
         <v>1</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.003096252948691137</v>
+        <v>-0.1085</v>
       </c>
       <c r="J309" t="n">
-        <v>-0.06502131192251387</v>
+        <v>-2.2785</v>
       </c>
     </row>
     <row r="310">
@@ -14761,10 +14749,10 @@
         <v>0.87</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.03114478611338603</v>
+        <v>-0.5455</v>
       </c>
       <c r="J310" t="n">
-        <v>-0.6540405083811067</v>
+        <v>-11.4555</v>
       </c>
     </row>
     <row r="311">
@@ -14801,10 +14789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.04393447765798641</v>
+        <v>-0.6963</v>
       </c>
       <c r="J311" t="n">
-        <v>-0.9226240308177147</v>
+        <v>-14.6223</v>
       </c>
     </row>
     <row r="312">
@@ -14841,10 +14829,10 @@
         <v>1.57</v>
       </c>
       <c r="I312" t="n">
-        <v>0.08877963748928427</v>
+        <v>0.825</v>
       </c>
       <c r="J312" t="n">
-        <v>2.663389124678528</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="313">
@@ -14881,10 +14869,10 @@
         <v>0.97</v>
       </c>
       <c r="I313" t="n">
-        <v>0.009183053851029407</v>
+        <v>-0.1133</v>
       </c>
       <c r="J313" t="n">
-        <v>0.2754916155308822</v>
+        <v>-3.399</v>
       </c>
     </row>
     <row r="314">
@@ -14921,10 +14909,10 @@
         <v>0.95</v>
       </c>
       <c r="I314" t="n">
-        <v>0.0065059825904613</v>
+        <v>-0.1542</v>
       </c>
       <c r="J314" t="n">
-        <v>0.195179477713839</v>
+        <v>-4.626</v>
       </c>
     </row>
     <row r="315">
@@ -14961,10 +14949,10 @@
         <v>0.91</v>
       </c>
       <c r="I315" t="n">
-        <v>0.0009871373278603213</v>
+        <v>-0.2265</v>
       </c>
       <c r="J315" t="n">
-        <v>0.02961411983580964</v>
+        <v>-6.795</v>
       </c>
     </row>
     <row r="316">
@@ -15001,10 +14989,10 @@
         <v>0.87</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.004650562375485535</v>
+        <v>-0.2915</v>
       </c>
       <c r="J316" t="n">
-        <v>-0.1395168712645661</v>
+        <v>-8.744999999999999</v>
       </c>
     </row>
     <row r="317">
@@ -15041,10 +15029,10 @@
         <v>1.34</v>
       </c>
       <c r="I317" t="n">
-        <v>0.05284617609398688</v>
+        <v>0.5656</v>
       </c>
       <c r="J317" t="n">
-        <v>1.585385282819606</v>
+        <v>16.968</v>
       </c>
     </row>
     <row r="318">
@@ -15081,10 +15069,10 @@
         <v>0.97</v>
       </c>
       <c r="I318" t="n">
-        <v>0.01303542173185691</v>
+        <v>-0.1002</v>
       </c>
       <c r="J318" t="n">
-        <v>0.3910626519557074</v>
+        <v>-3.006</v>
       </c>
     </row>
     <row r="319">
@@ -15121,10 +15109,10 @@
         <v>0.95</v>
       </c>
       <c r="I319" t="n">
-        <v>0.01090525792473022</v>
+        <v>-0.1423</v>
       </c>
       <c r="J319" t="n">
-        <v>0.3271577377419066</v>
+        <v>-4.269</v>
       </c>
     </row>
     <row r="320">
@@ -15161,10 +15149,10 @@
         <v>0.92</v>
       </c>
       <c r="I320" t="n">
-        <v>0.007576527927978216</v>
+        <v>-0.1987</v>
       </c>
       <c r="J320" t="n">
-        <v>0.2272958378393465</v>
+        <v>-5.961</v>
       </c>
     </row>
     <row r="321">
@@ -15201,10 +15189,10 @@
         <v>0.91</v>
       </c>
       <c r="I321" t="n">
-        <v>0.006442846565811306</v>
+        <v>-0.2163</v>
       </c>
       <c r="J321" t="n">
-        <v>0.1932853969743392</v>
+        <v>-6.489</v>
       </c>
     </row>
     <row r="322">
@@ -15241,10 +15229,10 @@
         <v>1.03</v>
       </c>
       <c r="I322" t="n">
-        <v>0.02195703001021213</v>
+        <v>0.1266</v>
       </c>
       <c r="J322" t="n">
-        <v>0.5269687202450911</v>
+        <v>3.0384</v>
       </c>
     </row>
     <row r="323">
@@ -15281,10 +15269,10 @@
         <v>1.02</v>
       </c>
       <c r="I323" t="n">
-        <v>0.02127262047877928</v>
+        <v>0.1039</v>
       </c>
       <c r="J323" t="n">
-        <v>0.5105428914907026</v>
+        <v>2.4936</v>
       </c>
     </row>
     <row r="324">
@@ -15321,10 +15309,10 @@
         <v>0.98</v>
       </c>
       <c r="I324" t="n">
-        <v>0.01859555256912927</v>
+        <v>-0.0175</v>
       </c>
       <c r="J324" t="n">
-        <v>0.4462932616591024</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="325">
@@ -15361,10 +15349,10 @@
         <v>0.8</v>
       </c>
       <c r="I325" t="n">
-        <v>0.007529648327809045</v>
+        <v>-0.3628</v>
       </c>
       <c r="J325" t="n">
-        <v>0.1807115598674171</v>
+        <v>-8.7072</v>
       </c>
     </row>
     <row r="326">
@@ -15401,10 +15389,10 @@
         <v>0.78</v>
       </c>
       <c r="I326" t="n">
-        <v>0.006132753475448963</v>
+        <v>-0.3925</v>
       </c>
       <c r="J326" t="n">
-        <v>0.1471860834107751</v>
+        <v>-9.42</v>
       </c>
     </row>
     <row r="327">
@@ -15441,10 +15429,10 @@
         <v>1.32</v>
       </c>
       <c r="I327" t="n">
-        <v>0.06738722601465628</v>
+        <v>0.875</v>
       </c>
       <c r="J327" t="n">
-        <v>1.617293424351751</v>
+        <v>21</v>
       </c>
     </row>
     <row r="328">
@@ -15481,10 +15469,10 @@
         <v>1.24</v>
       </c>
       <c r="I328" t="n">
-        <v>0.04889539299025322</v>
+        <v>0.6865</v>
       </c>
       <c r="J328" t="n">
-        <v>1.173489431766077</v>
+        <v>16.476</v>
       </c>
     </row>
     <row r="329">
@@ -15521,10 +15509,10 @@
         <v>1.18</v>
       </c>
       <c r="I329" t="n">
-        <v>0.0356707338655371</v>
+        <v>0.5309</v>
       </c>
       <c r="J329" t="n">
-        <v>0.8560976127728903</v>
+        <v>12.7416</v>
       </c>
     </row>
     <row r="330">
@@ -15561,10 +15549,10 @@
         <v>1.13</v>
       </c>
       <c r="I330" t="n">
-        <v>0.026588095831237</v>
+        <v>0.3721</v>
       </c>
       <c r="J330" t="n">
-        <v>0.638114299949688</v>
+        <v>8.930400000000001</v>
       </c>
     </row>
     <row r="331">
@@ -15601,10 +15589,10 @@
         <v>0.8</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.04625091287046812</v>
+        <v>-0.7126</v>
       </c>
       <c r="J331" t="n">
-        <v>-1.110021908891235</v>
+        <v>-17.1024</v>
       </c>
     </row>
     <row r="332">
@@ -15641,10 +15629,10 @@
         <v>1.27</v>
       </c>
       <c r="I332" t="n">
-        <v>0.02656743137428075</v>
+        <v>0.4403</v>
       </c>
       <c r="J332" t="n">
-        <v>0.6376183529827379</v>
+        <v>10.5672</v>
       </c>
     </row>
     <row r="333">
@@ -15681,10 +15669,10 @@
         <v>1.23</v>
       </c>
       <c r="I333" t="n">
-        <v>0.02381187508691861</v>
+        <v>0.3845</v>
       </c>
       <c r="J333" t="n">
-        <v>0.5714850020860467</v>
+        <v>9.228</v>
       </c>
     </row>
     <row r="334">
@@ -15721,10 +15709,10 @@
         <v>1.15</v>
       </c>
       <c r="I334" t="n">
-        <v>0.01885318848571737</v>
+        <v>0.2614</v>
       </c>
       <c r="J334" t="n">
-        <v>0.4524765236572169</v>
+        <v>6.2736</v>
       </c>
     </row>
     <row r="335">
@@ -15761,10 +15749,10 @@
         <v>0.99</v>
       </c>
       <c r="I335" t="n">
-        <v>0.009099726337376587</v>
+        <v>-0.0862</v>
       </c>
       <c r="J335" t="n">
-        <v>0.2183934320970381</v>
+        <v>-2.0688</v>
       </c>
     </row>
     <row r="336">
@@ -15801,10 +15789,10 @@
         <v>0.97</v>
       </c>
       <c r="I336" t="n">
-        <v>0.007692782887635519</v>
+        <v>-0.1327</v>
       </c>
       <c r="J336" t="n">
-        <v>0.1846267893032525</v>
+        <v>-3.1848</v>
       </c>
     </row>
     <row r="337">
@@ -15841,10 +15829,10 @@
         <v>1.64</v>
       </c>
       <c r="I337" t="n">
-        <v>0.1244634507340311</v>
+        <v>1.5055</v>
       </c>
       <c r="J337" t="n">
-        <v>2.987122817616745</v>
+        <v>36.132</v>
       </c>
     </row>
     <row r="338">
@@ -15881,10 +15869,10 @@
         <v>1.51</v>
       </c>
       <c r="I338" t="n">
-        <v>0.09500379975967072</v>
+        <v>1.2551</v>
       </c>
       <c r="J338" t="n">
-        <v>2.280091194232097</v>
+        <v>30.1224</v>
       </c>
     </row>
     <row r="339">
@@ -15921,10 +15909,10 @@
         <v>1.31</v>
       </c>
       <c r="I339" t="n">
-        <v>0.04829656840749857</v>
+        <v>0.83</v>
       </c>
       <c r="J339" t="n">
-        <v>1.159117641779966</v>
+        <v>19.92</v>
       </c>
     </row>
     <row r="340">
@@ -15961,10 +15949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.06066461647310691</v>
+        <v>-0.6995</v>
       </c>
       <c r="J340" t="n">
-        <v>-1.455950795354566</v>
+        <v>-16.788</v>
       </c>
     </row>
     <row r="341">
@@ -16001,10 +15989,10 @@
         <v>0.6</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.1075496290220777</v>
+        <v>-1.1597</v>
       </c>
       <c r="J341" t="n">
-        <v>-2.581191096529865</v>
+        <v>-27.8328</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7908/event_7908_evp_summary.xlsx
+++ b/database/event/7908/event_7908_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>9.0244</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3.6697</v>
       </c>
       <c r="D2" t="n">
         <v>3.2243</v>
@@ -545,7 +545,7 @@
         <v>6.7257</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2.7349</v>
       </c>
       <c r="D3" t="n">
         <v>2.2957</v>
@@ -591,7 +591,7 @@
         <v>6.4669</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.6297</v>
       </c>
       <c r="D4" t="n">
         <v>2.1911</v>
@@ -637,7 +637,7 @@
         <v>5.7281</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.3293</v>
       </c>
       <c r="D5" t="n">
         <v>1.8927</v>
@@ -683,7 +683,7 @@
         <v>5.2476</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.1339</v>
       </c>
       <c r="D6" t="n">
         <v>1.6986</v>
@@ -729,7 +729,7 @@
         <v>4.9586</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.0164</v>
       </c>
       <c r="D7" t="n">
         <v>1.5818</v>
@@ -775,7 +775,7 @@
         <v>3.2238</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1.3109</v>
       </c>
       <c r="D8" t="n">
         <v>0.881</v>
@@ -821,7 +821,7 @@
         <v>3.0029</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="D9" t="n">
         <v>0.7917</v>
@@ -867,7 +867,7 @@
         <v>2.9487</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1.1991</v>
       </c>
       <c r="D10" t="n">
         <v>0.7698</v>
@@ -913,7 +913,7 @@
         <v>2.7605</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.1225</v>
       </c>
       <c r="D11" t="n">
         <v>0.6938</v>
@@ -959,7 +959,7 @@
         <v>2.4159</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="D12" t="n">
         <v>0.5546</v>
@@ -1005,7 +1005,7 @@
         <v>2.2413</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.9114</v>
       </c>
       <c r="D13" t="n">
         <v>0.4841</v>
@@ -1051,7 +1051,7 @@
         <v>2.0494</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.8334</v>
       </c>
       <c r="D14" t="n">
         <v>0.4065</v>
@@ -1097,7 +1097,7 @@
         <v>2.0431</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.8308</v>
       </c>
       <c r="D15" t="n">
         <v>0.404</v>
@@ -1143,7 +1143,7 @@
         <v>1.8709</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.7608</v>
       </c>
       <c r="D16" t="n">
         <v>0.3344</v>
@@ -1189,7 +1189,7 @@
         <v>1.6669</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.6778</v>
       </c>
       <c r="D17" t="n">
         <v>0.252</v>
@@ -1235,7 +1235,7 @@
         <v>1.6126</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="D18" t="n">
         <v>0.2301</v>
@@ -1281,7 +1281,7 @@
         <v>1.3642</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.5547</v>
       </c>
       <c r="D19" t="n">
         <v>0.1297</v>
@@ -1327,7 +1327,7 @@
         <v>1.0816</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.4398</v>
       </c>
       <c r="D20" t="n">
         <v>0.0156</v>
@@ -1373,7 +1373,7 @@
         <v>1.0439</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.4245</v>
       </c>
       <c r="D21" t="n">
         <v>0.0004</v>
@@ -1419,7 +1419,7 @@
         <v>0.9709</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.3948</v>
       </c>
       <c r="D22" t="n">
         <v>-0.0291</v>
@@ -1465,7 +1465,7 @@
         <v>0.803</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.3265</v>
       </c>
       <c r="D23" t="n">
         <v>-0.097</v>
@@ -1511,7 +1511,7 @@
         <v>0.7015</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.2853</v>
       </c>
       <c r="D24" t="n">
         <v>-0.138</v>
@@ -1557,7 +1557,7 @@
         <v>0.6704</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.2726</v>
       </c>
       <c r="D25" t="n">
         <v>-0.1505</v>
@@ -1603,7 +1603,7 @@
         <v>0.3872</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.1575</v>
       </c>
       <c r="D26" t="n">
         <v>-0.2649</v>
@@ -1649,7 +1649,7 @@
         <v>0.3015</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.1226</v>
       </c>
       <c r="D27" t="n">
         <v>-0.2996</v>
@@ -1695,7 +1695,7 @@
         <v>0.1261</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.0513</v>
       </c>
       <c r="D28" t="n">
         <v>-0.3704</v>
@@ -1741,7 +1741,7 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.0269</v>
       </c>
       <c r="D29" t="n">
         <v>-0.3947</v>
@@ -1787,7 +1787,7 @@
         <v>0.0565</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="D30" t="n">
         <v>-0.3985</v>
@@ -1833,7 +1833,7 @@
         <v>-0.0285</v>
       </c>
       <c r="C31" t="n">
-        <v>-0</v>
+        <v>-0.0116</v>
       </c>
       <c r="D31" t="n">
         <v>-0.4329</v>
@@ -1879,7 +1879,7 @@
         <v>-1.1574</v>
       </c>
       <c r="C32" t="n">
-        <v>-0</v>
+        <v>-0.4706</v>
       </c>
       <c r="D32" t="n">
         <v>-0.8889</v>
@@ -1925,7 +1925,7 @@
         <v>-1.2398</v>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>-0.5042</v>
       </c>
       <c r="D33" t="n">
         <v>-0.9222</v>
@@ -1971,7 +1971,7 @@
         <v>-1.4085</v>
       </c>
       <c r="C34" t="n">
-        <v>-0</v>
+        <v>-0.5728</v>
       </c>
       <c r="D34" t="n">
         <v>-0.9903999999999999</v>
@@ -2017,7 +2017,7 @@
         <v>-1.6</v>
       </c>
       <c r="C35" t="n">
-        <v>-0</v>
+        <v>-0.6506</v>
       </c>
       <c r="D35" t="n">
         <v>-1.0677</v>
@@ -2063,7 +2063,7 @@
         <v>-1.7381</v>
       </c>
       <c r="C36" t="n">
-        <v>-0</v>
+        <v>-0.7068</v>
       </c>
       <c r="D36" t="n">
         <v>-1.1235</v>
@@ -2109,7 +2109,7 @@
         <v>-1.8023</v>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>-0.7329</v>
       </c>
       <c r="D37" t="n">
         <v>-1.1495</v>
@@ -2155,7 +2155,7 @@
         <v>-2.697</v>
       </c>
       <c r="C38" t="n">
-        <v>-0</v>
+        <v>-1.0967</v>
       </c>
       <c r="D38" t="n">
         <v>-1.5109</v>
@@ -2201,7 +2201,7 @@
         <v>-2.8405</v>
       </c>
       <c r="C39" t="n">
-        <v>-0</v>
+        <v>-1.1551</v>
       </c>
       <c r="D39" t="n">
         <v>-1.5689</v>
@@ -2247,7 +2247,7 @@
         <v>-3.2456</v>
       </c>
       <c r="C40" t="n">
-        <v>-0</v>
+        <v>-1.3198</v>
       </c>
       <c r="D40" t="n">
         <v>-1.7325</v>
@@ -2293,7 +2293,7 @@
         <v>-6.0585</v>
       </c>
       <c r="C41" t="n">
-        <v>-0</v>
+        <v>-2.4636</v>
       </c>
       <c r="D41" t="n">
         <v>-2.8689</v>

--- a/database/event/7908/event_7908_evp_summary.xlsx
+++ b/database/event/7908/event_7908_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>3.6697</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2243</v>
+        <v>3.1514</v>
       </c>
       <c r="E2" t="n">
         <v>9.0244</v>
@@ -548,7 +548,7 @@
         <v>2.7349</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2957</v>
+        <v>2.2356</v>
       </c>
       <c r="E3" t="n">
         <v>6.7257</v>
@@ -594,7 +594,7 @@
         <v>2.6297</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1911</v>
+        <v>2.1325</v>
       </c>
       <c r="E4" t="n">
         <v>6.4669</v>
@@ -640,7 +640,7 @@
         <v>2.3293</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8927</v>
+        <v>1.8382</v>
       </c>
       <c r="E5" t="n">
         <v>5.7281</v>
@@ -686,7 +686,7 @@
         <v>2.1339</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6986</v>
+        <v>1.6467</v>
       </c>
       <c r="E6" t="n">
         <v>5.2476</v>
@@ -732,7 +732,7 @@
         <v>2.0164</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5818</v>
+        <v>1.5316</v>
       </c>
       <c r="E7" t="n">
         <v>4.9586</v>
@@ -778,7 +778,7 @@
         <v>1.3109</v>
       </c>
       <c r="D8" t="n">
-        <v>0.881</v>
+        <v>0.8405</v>
       </c>
       <c r="E8" t="n">
         <v>3.2238</v>
@@ -824,7 +824,7 @@
         <v>1.2211</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7917</v>
+        <v>0.7524</v>
       </c>
       <c r="E9" t="n">
         <v>3.0029</v>
@@ -870,7 +870,7 @@
         <v>1.1991</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7698</v>
+        <v>0.7309</v>
       </c>
       <c r="E10" t="n">
         <v>2.9487</v>
@@ -916,7 +916,7 @@
         <v>1.1225</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6938</v>
+        <v>0.6559</v>
       </c>
       <c r="E11" t="n">
         <v>2.7605</v>
@@ -962,7 +962,7 @@
         <v>0.9824000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5546</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="E12" t="n">
         <v>2.4159</v>
@@ -1008,7 +1008,7 @@
         <v>0.9114</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4841</v>
+        <v>0.449</v>
       </c>
       <c r="E13" t="n">
         <v>2.2413</v>
@@ -1054,7 +1054,7 @@
         <v>0.8334</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4065</v>
+        <v>0.3726</v>
       </c>
       <c r="E14" t="n">
         <v>2.0494</v>
@@ -1100,7 +1100,7 @@
         <v>0.8308</v>
       </c>
       <c r="D15" t="n">
-        <v>0.404</v>
+        <v>0.3701</v>
       </c>
       <c r="E15" t="n">
         <v>2.0431</v>
@@ -1146,7 +1146,7 @@
         <v>0.7608</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3344</v>
+        <v>0.3015</v>
       </c>
       <c r="E16" t="n">
         <v>1.8709</v>
@@ -1192,7 +1192,7 @@
         <v>0.6778</v>
       </c>
       <c r="D17" t="n">
-        <v>0.252</v>
+        <v>0.2202</v>
       </c>
       <c r="E17" t="n">
         <v>1.6669</v>
@@ -1238,7 +1238,7 @@
         <v>0.6556999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2301</v>
+        <v>0.1985</v>
       </c>
       <c r="E18" t="n">
         <v>1.6126</v>
@@ -1284,7 +1284,7 @@
         <v>0.5547</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1297</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="E19" t="n">
         <v>1.3642</v>
@@ -1330,7 +1330,7 @@
         <v>0.4398</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0156</v>
+        <v>-0.013</v>
       </c>
       <c r="E20" t="n">
         <v>1.0816</v>
@@ -1376,7 +1376,7 @@
         <v>0.4245</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0004</v>
+        <v>-0.028</v>
       </c>
       <c r="E21" t="n">
         <v>1.0439</v>
@@ -1422,7 +1422,7 @@
         <v>0.3948</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0291</v>
+        <v>-0.0571</v>
       </c>
       <c r="E22" t="n">
         <v>0.9709</v>
@@ -1468,7 +1468,7 @@
         <v>0.3265</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.097</v>
+        <v>-0.124</v>
       </c>
       <c r="E23" t="n">
         <v>0.803</v>
@@ -1514,7 +1514,7 @@
         <v>0.2853</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.138</v>
+        <v>-0.1644</v>
       </c>
       <c r="E24" t="n">
         <v>0.7015</v>
@@ -1560,7 +1560,7 @@
         <v>0.2726</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1505</v>
+        <v>-0.1768</v>
       </c>
       <c r="E25" t="n">
         <v>0.6704</v>
@@ -1606,7 +1606,7 @@
         <v>0.1575</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2649</v>
+        <v>-0.2896</v>
       </c>
       <c r="E26" t="n">
         <v>0.3872</v>
@@ -1652,7 +1652,7 @@
         <v>0.1226</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2996</v>
+        <v>-0.3238</v>
       </c>
       <c r="E27" t="n">
         <v>0.3015</v>
@@ -1698,7 +1698,7 @@
         <v>0.0513</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3704</v>
+        <v>-0.3937</v>
       </c>
       <c r="E28" t="n">
         <v>0.1261</v>
@@ -1744,7 +1744,7 @@
         <v>0.0269</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3947</v>
+        <v>-0.4176</v>
       </c>
       <c r="E29" t="n">
         <v>0.06610000000000001</v>
@@ -1790,7 +1790,7 @@
         <v>0.023</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3985</v>
+        <v>-0.4214</v>
       </c>
       <c r="E30" t="n">
         <v>0.0565</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0116</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4329</v>
+        <v>-0.4553</v>
       </c>
       <c r="E31" t="n">
         <v>-0.0285</v>
@@ -1882,7 +1882,7 @@
         <v>-0.4706</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8889</v>
+        <v>-0.905</v>
       </c>
       <c r="E32" t="n">
         <v>-1.1574</v>
@@ -1928,7 +1928,7 @@
         <v>-0.5042</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9222</v>
+        <v>-0.9378</v>
       </c>
       <c r="E33" t="n">
         <v>-1.2398</v>
@@ -1974,7 +1974,7 @@
         <v>-0.5728</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9903999999999999</v>
+        <v>-1.0051</v>
       </c>
       <c r="E34" t="n">
         <v>-1.4085</v>
@@ -2020,7 +2020,7 @@
         <v>-0.6506</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0677</v>
+        <v>-1.0814</v>
       </c>
       <c r="E35" t="n">
         <v>-1.6</v>
@@ -2066,7 +2066,7 @@
         <v>-0.7068</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1235</v>
+        <v>-1.1364</v>
       </c>
       <c r="E36" t="n">
         <v>-1.7381</v>
@@ -2112,7 +2112,7 @@
         <v>-0.7329</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1495</v>
+        <v>-1.1619</v>
       </c>
       <c r="E37" t="n">
         <v>-1.8023</v>
@@ -2158,7 +2158,7 @@
         <v>-1.0967</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.5109</v>
+        <v>-1.5184</v>
       </c>
       <c r="E38" t="n">
         <v>-2.697</v>
@@ -2204,7 +2204,7 @@
         <v>-1.1551</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.5689</v>
+        <v>-1.5756</v>
       </c>
       <c r="E39" t="n">
         <v>-2.8405</v>
@@ -2250,7 +2250,7 @@
         <v>-1.3198</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.7325</v>
+        <v>-1.737</v>
       </c>
       <c r="E40" t="n">
         <v>-3.2456</v>
@@ -2296,7 +2296,7 @@
         <v>-2.4636</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.8689</v>
+        <v>-2.8576</v>
       </c>
       <c r="E41" t="n">
         <v>-6.0585</v>

--- a/database/event/7908/event_7908_evp_summary.xlsx
+++ b/database/event/7908/event_7908_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.0244</v>
+        <v>8.0421</v>
       </c>
       <c r="C2" t="n">
-        <v>3.6697</v>
+        <v>3.2703</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1514</v>
+        <v>2.9926</v>
       </c>
       <c r="E2" t="n">
-        <v>9.0244</v>
+        <v>8.0421</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4</v>
+        <v>3.9608</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6243</v>
+        <v>4.0813</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1419</v>
+        <v>8.468999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>4.1677</v>
+        <v>4.4035</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6243</v>
+        <v>4.0813</v>
       </c>
       <c r="K2" t="n">
         <v>97</v>
@@ -529,7 +529,7 @@
         <v>156</v>
       </c>
       <c r="M2" t="n">
-        <v>8.792</v>
+        <v>8.4848</v>
       </c>
       <c r="N2" t="n">
         <v>253</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.7257</v>
+        <v>6.0167</v>
       </c>
       <c r="C3" t="n">
-        <v>2.7349</v>
+        <v>2.4466</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2356</v>
+        <v>2.0782</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7257</v>
+        <v>6.0167</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8343</v>
+        <v>3.2796</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8914</v>
+        <v>2.7371</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8343</v>
+        <v>6.0688</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1078</v>
+        <v>3.1555</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8914</v>
+        <v>2.7371</v>
       </c>
       <c r="K3" t="n">
         <v>134</v>
@@ -575,7 +575,7 @@
         <v>151</v>
       </c>
       <c r="M3" t="n">
-        <v>5.9992</v>
+        <v>5.8926</v>
       </c>
       <c r="N3" t="n">
         <v>285</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4669</v>
+        <v>5.6625</v>
       </c>
       <c r="C4" t="n">
-        <v>2.6297</v>
+        <v>2.3026</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1325</v>
+        <v>1.9183</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4669</v>
+        <v>5.6625</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9425</v>
+        <v>2.9644</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5244</v>
+        <v>2.6981</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9425</v>
+        <v>4.9585</v>
       </c>
       <c r="I4" t="n">
-        <v>2.385</v>
+        <v>2.5782</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5244</v>
+        <v>2.6981</v>
       </c>
       <c r="K4" t="n">
         <v>134</v>
@@ -621,7 +621,7 @@
         <v>151</v>
       </c>
       <c r="M4" t="n">
-        <v>5.9094</v>
+        <v>5.2763</v>
       </c>
       <c r="N4" t="n">
         <v>285</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7281</v>
+        <v>5.3451</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3293</v>
+        <v>2.1735</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8382</v>
+        <v>1.775</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7281</v>
+        <v>5.3451</v>
       </c>
       <c r="F5" t="n">
-        <v>4.428</v>
+        <v>4.1139</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3001</v>
+        <v>1.2312</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2543</v>
+        <v>9.0085</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2587</v>
+        <v>4.684</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3001</v>
+        <v>1.2312</v>
       </c>
       <c r="K5" t="n">
         <v>215</v>
@@ -667,7 +667,7 @@
         <v>49</v>
       </c>
       <c r="M5" t="n">
-        <v>5.5588</v>
+        <v>5.9152</v>
       </c>
       <c r="N5" t="n">
         <v>264</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.2476</v>
+        <v>5.2066</v>
       </c>
       <c r="C6" t="n">
-        <v>2.1339</v>
+        <v>2.1172</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6467</v>
+        <v>1.7125</v>
       </c>
       <c r="E6" t="n">
-        <v>5.2476</v>
+        <v>5.2066</v>
       </c>
       <c r="F6" t="n">
-        <v>3.3636</v>
+        <v>3.2932</v>
       </c>
       <c r="G6" t="n">
-        <v>1.884</v>
+        <v>1.9134</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3636</v>
+        <v>6.1169</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7263</v>
+        <v>3.1805</v>
       </c>
       <c r="J6" t="n">
-        <v>1.884</v>
+        <v>1.9134</v>
       </c>
       <c r="K6" t="n">
         <v>134</v>
@@ -713,7 +713,7 @@
         <v>151</v>
       </c>
       <c r="M6" t="n">
-        <v>4.610300000000001</v>
+        <v>5.0939</v>
       </c>
       <c r="N6" t="n">
         <v>285</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.9586</v>
+        <v>4.7964</v>
       </c>
       <c r="C7" t="n">
-        <v>2.0164</v>
+        <v>1.9504</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5316</v>
+        <v>1.5273</v>
       </c>
       <c r="E7" t="n">
-        <v>4.9586</v>
+        <v>4.7964</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2657</v>
+        <v>3.2418</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6929</v>
+        <v>1.5546</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2657</v>
+        <v>5.9359</v>
       </c>
       <c r="I7" t="n">
-        <v>2.647</v>
+        <v>3.0864</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6929</v>
+        <v>1.5546</v>
       </c>
       <c r="K7" t="n">
         <v>165</v>
@@ -759,7 +759,7 @@
         <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3399</v>
+        <v>4.641</v>
       </c>
       <c r="N7" t="n">
         <v>209</v>
@@ -768,277 +768,277 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2238</v>
+        <v>3.5222</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3109</v>
+        <v>1.4323</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8405</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2238</v>
+        <v>3.5222</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3595</v>
+        <v>3.5222</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1357</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3595</v>
+        <v>4.3743</v>
       </c>
       <c r="I8" t="n">
-        <v>2.723</v>
+        <v>4.3743</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1357</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="L8" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5873</v>
+        <v>4.3743</v>
       </c>
       <c r="N8" t="n">
-        <v>209</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0029</v>
+        <v>3.1743</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2211</v>
+        <v>1.2908</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7524</v>
+        <v>0.795</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0029</v>
+        <v>3.1743</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0029</v>
+        <v>3.1743</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.0029</v>
+        <v>3.6105</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0029</v>
+        <v>3.6105</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>180</v>
+        <v>121</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0029</v>
+        <v>3.6105</v>
       </c>
       <c r="N9" t="n">
-        <v>180</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9487</v>
+        <v>2.9387</v>
       </c>
       <c r="C10" t="n">
-        <v>1.1991</v>
+        <v>1.195</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7309</v>
+        <v>0.6887</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9487</v>
+        <v>2.9387</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9487</v>
+        <v>3.0501</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0.1114</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9487</v>
+        <v>5.2603</v>
       </c>
       <c r="I10" t="n">
-        <v>2.9487</v>
+        <v>2.7351</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.1114</v>
       </c>
       <c r="K10" t="n">
-        <v>121</v>
+        <v>165</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9487</v>
+        <v>2.6237</v>
       </c>
       <c r="N10" t="n">
-        <v>121</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7605</v>
+        <v>2.8325</v>
       </c>
       <c r="C11" t="n">
-        <v>1.1225</v>
+        <v>1.1518</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6559</v>
+        <v>0.6407</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7605</v>
+        <v>2.8325</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7605</v>
+        <v>2.4572</v>
       </c>
       <c r="G11" t="n">
-        <v>-1</v>
+        <v>0.3753</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7605</v>
+        <v>3.1712</v>
       </c>
       <c r="I11" t="n">
-        <v>3.048</v>
+        <v>1.6489</v>
       </c>
       <c r="J11" t="n">
-        <v>-1</v>
+        <v>0.3753</v>
       </c>
       <c r="K11" t="n">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="L11" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M11" t="n">
-        <v>2.048</v>
+        <v>2.0242</v>
       </c>
       <c r="N11" t="n">
-        <v>209</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>kyousuke</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4159</v>
+        <v>2.828</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9824000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.6387</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4159</v>
+        <v>2.828</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2278</v>
+        <v>2.338</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8119</v>
+        <v>0.49</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2278</v>
+        <v>2.7512</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6162</v>
+        <v>1.4305</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8119</v>
+        <v>0.49</v>
       </c>
       <c r="K12" t="n">
-        <v>215</v>
+        <v>97</v>
       </c>
       <c r="L12" t="n">
-        <v>49</v>
+        <v>156</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8043</v>
+        <v>1.9205</v>
       </c>
       <c r="N12" t="n">
-        <v>264</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2413</v>
+        <v>2.7959</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9114</v>
+        <v>1.1369</v>
       </c>
       <c r="D13" t="n">
-        <v>0.449</v>
+        <v>0.6242</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2413</v>
+        <v>2.7959</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2413</v>
+        <v>3.3153</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.5194</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2413</v>
+        <v>6.1948</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2413</v>
+        <v>3.221</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.5194</v>
       </c>
       <c r="K13" t="n">
-        <v>162</v>
+        <v>215</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2413</v>
+        <v>2.7016</v>
       </c>
       <c r="N13" t="n">
-        <v>162</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0494</v>
+        <v>2.7139</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8334</v>
+        <v>1.1036</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3726</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0494</v>
+        <v>2.7139</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0559</v>
+        <v>1.6473</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9935</v>
+        <v>1.0666</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0559</v>
+        <v>1.6473</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8558</v>
+        <v>0.8565</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9935</v>
+        <v>1.0666</v>
       </c>
       <c r="K14" t="n">
         <v>134</v>
@@ -1081,7 +1081,7 @@
         <v>151</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8493</v>
+        <v>1.9231</v>
       </c>
       <c r="N14" t="n">
         <v>285</v>
@@ -1090,139 +1090,139 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0431</v>
+        <v>2.5533</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8308</v>
+        <v>1.0383</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3701</v>
+        <v>0.5147</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0431</v>
+        <v>2.5533</v>
       </c>
       <c r="F15" t="n">
-        <v>3.008</v>
+        <v>3.3184</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9649</v>
+        <v>-0.7651</v>
       </c>
       <c r="H15" t="n">
-        <v>3.008</v>
+        <v>6.2057</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4381</v>
+        <v>3.2267</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9649</v>
+        <v>-0.7651</v>
       </c>
       <c r="K15" t="n">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="L15" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4732</v>
+        <v>2.4616</v>
       </c>
       <c r="N15" t="n">
-        <v>264</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8709</v>
+        <v>2.4521</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7608</v>
+        <v>0.9971</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3015</v>
+        <v>0.469</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8709</v>
+        <v>2.4521</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4933</v>
+        <v>2.4521</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3776</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4933</v>
+        <v>2.4521</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2104</v>
+        <v>2.4521</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3776</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>215</v>
+        <v>162</v>
       </c>
       <c r="L16" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.588</v>
+        <v>2.4521</v>
       </c>
       <c r="N16" t="n">
-        <v>264</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kyousuke</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6669</v>
+        <v>2.3657</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6778</v>
+        <v>0.962</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2202</v>
+        <v>0.43</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6669</v>
+        <v>2.3657</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7033</v>
+        <v>3.0393</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0364</v>
+        <v>-0.6736</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7033</v>
+        <v>5.2224</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3806</v>
+        <v>2.7154</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0364</v>
+        <v>-0.6736</v>
       </c>
       <c r="K17" t="n">
-        <v>97</v>
+        <v>215</v>
       </c>
       <c r="L17" t="n">
-        <v>156</v>
+        <v>49</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3442</v>
+        <v>2.0418</v>
       </c>
       <c r="N17" t="n">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6126</v>
+        <v>1.9713</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.8016</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1985</v>
+        <v>0.2519</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6126</v>
+        <v>1.9713</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6126</v>
+        <v>1.9713</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6126</v>
+        <v>1.9713</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6126</v>
+        <v>1.9713</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6126</v>
+        <v>1.9713</v>
       </c>
       <c r="N18" t="n">
         <v>180</v>
@@ -1274,185 +1274,185 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>controlez</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3642</v>
+        <v>1.7689</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5547</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1606</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3642</v>
+        <v>1.7689</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3642</v>
+        <v>2.4751</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.7062</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3642</v>
+        <v>3.2345</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3642</v>
+        <v>1.6818</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.7062</v>
       </c>
       <c r="K19" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3642</v>
+        <v>0.9755999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>120</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>controlez</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0816</v>
+        <v>1.6756</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4398</v>
+        <v>0.6814</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.013</v>
+        <v>0.1184</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0816</v>
+        <v>1.6756</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0816</v>
+        <v>1.6756</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0816</v>
+        <v>1.6756</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0816</v>
+        <v>1.6756</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0816</v>
+        <v>1.6756</v>
       </c>
       <c r="N20" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0439</v>
+        <v>1.6052</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4245</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.028</v>
+        <v>0.0867</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0439</v>
+        <v>1.6052</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1518</v>
+        <v>1.6052</v>
       </c>
       <c r="G21" t="n">
-        <v>4.1957</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.1518</v>
+        <v>1.6052</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.5546</v>
+        <v>1.6052</v>
       </c>
       <c r="J21" t="n">
-        <v>4.1957</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>97</v>
+        <v>180</v>
       </c>
       <c r="L21" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.6411</v>
+        <v>1.6052</v>
       </c>
       <c r="N21" t="n">
-        <v>253</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9709</v>
+        <v>1.3277</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3948</v>
+        <v>0.5399</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0571</v>
+        <v>-0.0386</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9709</v>
+        <v>1.3277</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9709</v>
+        <v>2.4756</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-1.1479</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9709</v>
+        <v>3.2361</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9709</v>
+        <v>1.6826</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-1.1479</v>
       </c>
       <c r="K22" t="n">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9709</v>
+        <v>0.5347000000000002</v>
       </c>
       <c r="N22" t="n">
-        <v>121</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.803</v>
+        <v>1.2085</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3265</v>
+        <v>0.4914</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.124</v>
+        <v>-0.0924</v>
       </c>
       <c r="E23" t="n">
-        <v>0.803</v>
+        <v>1.2085</v>
       </c>
       <c r="F23" t="n">
-        <v>0.803</v>
+        <v>1.2085</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.803</v>
+        <v>1.2085</v>
       </c>
       <c r="I23" t="n">
-        <v>0.803</v>
+        <v>1.2085</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.803</v>
+        <v>1.2085</v>
       </c>
       <c r="N23" t="n">
         <v>162</v>
@@ -1504,231 +1504,231 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7015</v>
+        <v>1.1945</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2853</v>
+        <v>0.4857</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1644</v>
+        <v>-0.0988</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7015</v>
+        <v>1.1945</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7015</v>
+        <v>1.1945</v>
       </c>
       <c r="G24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.7015</v>
+        <v>1.1945</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3791</v>
+        <v>1.1945</v>
       </c>
       <c r="J24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="L24" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3791</v>
+        <v>1.1945</v>
       </c>
       <c r="N24" t="n">
-        <v>209</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6704</v>
+        <v>1.1765</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2726</v>
+        <v>0.4784</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1768</v>
+        <v>-0.1069</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6704</v>
+        <v>1.1765</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6704</v>
+        <v>1.9944</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.8179</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6704</v>
+        <v>1.9944</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6704</v>
+        <v>1.037</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.8179</v>
       </c>
       <c r="K25" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6704</v>
+        <v>0.2191</v>
       </c>
       <c r="N25" t="n">
-        <v>120</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3872</v>
+        <v>0.8683</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1575</v>
+        <v>0.3531</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2896</v>
+        <v>-0.246</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3872</v>
+        <v>0.8683</v>
       </c>
       <c r="F26" t="n">
-        <v>2.0732</v>
+        <v>0.8683</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.686</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.0732</v>
+        <v>0.8683</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6804</v>
+        <v>0.8683</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.686</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>97</v>
+        <v>162</v>
       </c>
       <c r="L26" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.005600000000000049</v>
+        <v>0.8683</v>
       </c>
       <c r="N26" t="n">
-        <v>253</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3015</v>
+        <v>0.7558</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1226</v>
+        <v>0.3073</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3238</v>
+        <v>-0.2968</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3015</v>
+        <v>0.7558</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3015</v>
+        <v>0.7558</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3015</v>
+        <v>0.7558</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3015</v>
+        <v>0.7558</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3015</v>
+        <v>0.7558</v>
       </c>
       <c r="N27" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1261</v>
+        <v>0.6464</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0513</v>
+        <v>0.2629</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3937</v>
+        <v>-0.3462</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1261</v>
+        <v>0.6464</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1261</v>
+        <v>0.6464</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1261</v>
+        <v>0.6464</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1261</v>
+        <v>0.6464</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1261</v>
+        <v>0.6464</v>
       </c>
       <c r="N28" t="n">
-        <v>162</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.4189</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0269</v>
+        <v>0.1703</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4176</v>
+        <v>-0.4489</v>
       </c>
       <c r="E29" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.4189</v>
       </c>
       <c r="F29" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.4189</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.4189</v>
       </c>
       <c r="I29" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.4189</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.4189</v>
       </c>
       <c r="N29" t="n">
         <v>162</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0565</v>
+        <v>0.3534</v>
       </c>
       <c r="C30" t="n">
-        <v>0.023</v>
+        <v>0.1437</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4214</v>
+        <v>-0.4785</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0565</v>
+        <v>0.3534</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0565</v>
+        <v>0.3534</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0565</v>
+        <v>0.3534</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0565</v>
+        <v>0.3534</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0565</v>
+        <v>0.3534</v>
       </c>
       <c r="N30" t="n">
         <v>120</v>
@@ -1826,47 +1826,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0285</v>
+        <v>-0.5605</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0116</v>
+        <v>-0.2279</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4553</v>
+        <v>-0.8911</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0285</v>
+        <v>-0.5605</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9715</v>
+        <v>-0.5605</v>
       </c>
       <c r="G31" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9715</v>
+        <v>-0.5605</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7874</v>
+        <v>-0.5605</v>
       </c>
       <c r="J31" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="L31" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2126</v>
+        <v>-0.5605</v>
       </c>
       <c r="N31" t="n">
-        <v>209</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.1574</v>
+        <v>-0.5858</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.4706</v>
+        <v>-0.2382</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.905</v>
+        <v>-0.9025</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.1574</v>
+        <v>-0.5858</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.1574</v>
+        <v>-0.5858</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.1574</v>
+        <v>-0.5858</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.1574</v>
+        <v>-0.5858</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.1574</v>
+        <v>-0.5858</v>
       </c>
       <c r="N32" t="n">
         <v>121</v>
@@ -1918,139 +1918,139 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.2398</v>
+        <v>-0.8855</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.5042</v>
+        <v>-0.3601</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9378</v>
+        <v>-1.0378</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.2398</v>
+        <v>-0.8855</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.2398</v>
+        <v>-0.8855</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.2398</v>
+        <v>-0.8855</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.2398</v>
+        <v>-0.8855</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.2398</v>
+        <v>-0.8855</v>
       </c>
       <c r="N33" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.4085</v>
+        <v>-0.9453</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.5728</v>
+        <v>-0.3844</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0051</v>
+        <v>-1.0648</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.4085</v>
+        <v>-0.9453</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.4085</v>
+        <v>-4.4919</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>3.5466</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.4085</v>
+        <v>-4.4919</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.4085</v>
+        <v>-2.3356</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>3.5466</v>
       </c>
       <c r="K34" t="n">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.4085</v>
+        <v>1.211</v>
       </c>
       <c r="N34" t="n">
-        <v>120</v>
+        <v>253</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>nicx</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.6</v>
+        <v>-0.9739</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.6506</v>
+        <v>-0.396</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0814</v>
+        <v>-1.0777</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.6</v>
+        <v>-0.9739</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.6</v>
+        <v>-0.9739</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.6</v>
+        <v>-0.9739</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.6</v>
+        <v>-0.9739</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.6</v>
+        <v>-0.9739</v>
       </c>
       <c r="N35" t="n">
-        <v>162</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.7381</v>
+        <v>-1.0826</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.7068</v>
+        <v>-0.4402</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1364</v>
+        <v>-1.1268</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.7381</v>
+        <v>-1.0826</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.7381</v>
+        <v>-1.0826</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.7381</v>
+        <v>-1.0826</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.7381</v>
+        <v>-1.0826</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.7381</v>
+        <v>-1.0826</v>
       </c>
       <c r="N36" t="n">
         <v>120</v>
@@ -2102,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>nicx</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.8023</v>
+        <v>-1.1121</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.7329</v>
+        <v>-0.4522</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1619</v>
+        <v>-1.1401</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.8023</v>
+        <v>-1.1121</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.8023</v>
+        <v>-1.1121</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.8023</v>
+        <v>-1.1121</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.8023</v>
+        <v>-1.1121</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.8023</v>
+        <v>-1.1121</v>
       </c>
       <c r="N37" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.697</v>
+        <v>-1.9716</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.0967</v>
+        <v>-0.8017</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.5184</v>
+        <v>-1.5281</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.697</v>
+        <v>-1.9716</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.697</v>
+        <v>-1.9716</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-2.697</v>
+        <v>-1.9716</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.697</v>
+        <v>-1.9716</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-2.697</v>
+        <v>-1.9716</v>
       </c>
       <c r="N38" t="n">
         <v>180</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.8405</v>
+        <v>-2.5932</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.1551</v>
+        <v>-1.0545</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.5756</v>
+        <v>-1.8087</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.8405</v>
+        <v>-2.5932</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0985</v>
+        <v>-1.3417</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.742</v>
+        <v>-1.2515</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0985</v>
+        <v>-1.3417</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8904</v>
+        <v>-0.6976</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.742</v>
+        <v>-1.2515</v>
       </c>
       <c r="K39" t="n">
         <v>97</v>
@@ -2231,7 +2231,7 @@
         <v>156</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.6324</v>
+        <v>-1.9491</v>
       </c>
       <c r="N39" t="n">
         <v>253</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.2456</v>
+        <v>-3.4053</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.3198</v>
+        <v>-1.3847</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.737</v>
+        <v>-2.1753</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.2456</v>
+        <v>-3.4053</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.0796</v>
+        <v>-2.2823</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.166</v>
+        <v>-1.123</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.0796</v>
+        <v>-2.2823</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.6856</v>
+        <v>-1.1867</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.166</v>
+        <v>-1.123</v>
       </c>
       <c r="K40" t="n">
         <v>134</v>
@@ -2277,7 +2277,7 @@
         <v>151</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.8516</v>
+        <v>-2.3097</v>
       </c>
       <c r="N40" t="n">
         <v>285</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-6.0585</v>
+        <v>-7.2433</v>
       </c>
       <c r="C41" t="n">
-        <v>-2.4636</v>
+        <v>-2.9454</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.8576</v>
+        <v>-3.908</v>
       </c>
       <c r="E41" t="n">
-        <v>-6.0585</v>
+        <v>-7.2433</v>
       </c>
       <c r="F41" t="n">
-        <v>-5.2701</v>
+        <v>-6.7366</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.7884</v>
+        <v>-0.5067</v>
       </c>
       <c r="H41" t="n">
-        <v>-5.2701</v>
+        <v>-6.7366</v>
       </c>
       <c r="I41" t="n">
-        <v>-4.2716</v>
+        <v>-3.5027</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.7884</v>
+        <v>-0.5067</v>
       </c>
       <c r="K41" t="n">
         <v>215</v>
@@ -2323,7 +2323,7 @@
         <v>49</v>
       </c>
       <c r="M41" t="n">
-        <v>-5.06</v>
+        <v>-4.0094</v>
       </c>
       <c r="N41" t="n">
         <v>264</v>
@@ -2429,10 +2429,10 @@
         <v>1.38</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6621</v>
+        <v>0.6216</v>
       </c>
       <c r="J2" t="n">
-        <v>10.5936</v>
+        <v>9.945600000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.12</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3041</v>
+        <v>0.2483</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8656</v>
+        <v>3.9728</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0936</v>
+        <v>0.0492</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4976</v>
+        <v>0.7872</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.65</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5626</v>
+        <v>-0.3696</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.0016</v>
+        <v>-5.9136</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.27</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.008</v>
+        <v>-0.7128</v>
       </c>
       <c r="J6" t="n">
-        <v>-16.128</v>
+        <v>-11.4048</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>2.54</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6341</v>
+        <v>1.3406</v>
       </c>
       <c r="J7" t="n">
-        <v>26.1456</v>
+        <v>21.4496</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>2.25</v>
       </c>
       <c r="I8" t="n">
-        <v>1.383</v>
+        <v>1.1832</v>
       </c>
       <c r="J8" t="n">
-        <v>22.128</v>
+        <v>18.9312</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.12</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1144</v>
+        <v>0.1501</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8304</v>
+        <v>2.4016</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.82</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4221</v>
+        <v>-0.2608</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.7536</v>
+        <v>-4.1728</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.6</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6889</v>
+        <v>-0.4637</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.0224</v>
+        <v>-7.4192</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>2.21</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2528</v>
+        <v>1.8681</v>
       </c>
       <c r="J12" t="n">
-        <v>49.5616</v>
+        <v>41.0982</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.1386</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9118</v>
+        <v>3.0492</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.86</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5589</v>
+        <v>-0.4959</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.2958</v>
+        <v>-10.9098</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.85</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5849</v>
+        <v>-0.5232</v>
       </c>
       <c r="J15" t="n">
-        <v>-12.8678</v>
+        <v>-11.5104</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.65</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0462</v>
+        <v>-1.027</v>
       </c>
       <c r="J16" t="n">
-        <v>-23.0164</v>
+        <v>-22.594</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.45</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.8475</v>
       </c>
       <c r="J17" t="n">
-        <v>15.136</v>
+        <v>18.645</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3048</v>
+        <v>0.3497</v>
       </c>
       <c r="J18" t="n">
-        <v>6.7056</v>
+        <v>7.6934</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.99</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0654</v>
+        <v>-0.0253</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4388</v>
+        <v>-0.5566</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1343</v>
+        <v>-0.0687</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.9546</v>
+        <v>-1.5114</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.71</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5165</v>
+        <v>-0.3326</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.363</v>
+        <v>-7.3172</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0467</v>
+        <v>1.0182</v>
       </c>
       <c r="J22" t="n">
-        <v>35.5878</v>
+        <v>34.6188</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9821</v>
+        <v>0.9635</v>
       </c>
       <c r="J23" t="n">
-        <v>33.3914</v>
+        <v>32.759</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.09</v>
       </c>
       <c r="I24" t="n">
-        <v>0.272</v>
+        <v>0.2958</v>
       </c>
       <c r="J24" t="n">
-        <v>9.247999999999999</v>
+        <v>10.0572</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.86</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5514</v>
+        <v>-0.4899</v>
       </c>
       <c r="J25" t="n">
-        <v>-18.7476</v>
+        <v>-16.6566</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7026</v>
+        <v>-0.6498</v>
       </c>
       <c r="J26" t="n">
-        <v>-23.8884</v>
+        <v>-22.0932</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.19</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3488</v>
+        <v>0.4038</v>
       </c>
       <c r="J27" t="n">
-        <v>11.8592</v>
+        <v>13.7292</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.12</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2388</v>
+        <v>0.2731</v>
       </c>
       <c r="J28" t="n">
-        <v>8.119199999999999</v>
+        <v>9.285399999999999</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.09</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1858</v>
+        <v>0.214</v>
       </c>
       <c r="J29" t="n">
-        <v>6.3172</v>
+        <v>7.276</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1466</v>
+        <v>0.1731</v>
       </c>
       <c r="J30" t="n">
-        <v>4.9844</v>
+        <v>5.8854</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3674</v>
+        <v>-0.2254</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.4916</v>
+        <v>-7.6636</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.32</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8607</v>
+        <v>0.852</v>
       </c>
       <c r="J32" t="n">
-        <v>30.1245</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.25</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6954</v>
+        <v>0.6876</v>
       </c>
       <c r="J33" t="n">
-        <v>24.339</v>
+        <v>24.066</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5666</v>
+        <v>0.5671</v>
       </c>
       <c r="J34" t="n">
-        <v>19.831</v>
+        <v>19.8485</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.03</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0319</v>
+        <v>0.0945</v>
       </c>
       <c r="J35" t="n">
-        <v>1.1165</v>
+        <v>3.3075</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1076</v>
+        <v>-0.0384</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.766</v>
+        <v>-1.344</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.32</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5584</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>19.544</v>
+        <v>23.338</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.16</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3373</v>
+        <v>0.3753</v>
       </c>
       <c r="J38" t="n">
-        <v>11.8055</v>
+        <v>13.1355</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.97</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.065</v>
+        <v>-0.0475</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.275</v>
+        <v>-1.6625</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.74</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4596</v>
+        <v>-0.2937</v>
       </c>
       <c r="J40" t="n">
-        <v>-16.086</v>
+        <v>-10.2795</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.63</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6032999999999999</v>
+        <v>-0.3977</v>
       </c>
       <c r="J41" t="n">
-        <v>-21.1155</v>
+        <v>-13.9195</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.63</v>
       </c>
       <c r="I42" t="n">
-        <v>1.5174</v>
+        <v>1.0598</v>
       </c>
       <c r="J42" t="n">
-        <v>44.0046</v>
+        <v>30.7342</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.24</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6985</v>
+        <v>0.5364</v>
       </c>
       <c r="J43" t="n">
-        <v>20.2565</v>
+        <v>15.5556</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.21</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.4929</v>
       </c>
       <c r="J44" t="n">
-        <v>18.0815</v>
+        <v>14.2941</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.78</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.7546</v>
+        <v>-0.705</v>
       </c>
       <c r="J45" t="n">
-        <v>-21.8834</v>
+        <v>-20.445</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.71</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9145</v>
+        <v>-0.88</v>
       </c>
       <c r="J46" t="n">
-        <v>-26.5205</v>
+        <v>-25.52</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.14</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3161</v>
+        <v>0.3391</v>
       </c>
       <c r="J47" t="n">
-        <v>9.1669</v>
+        <v>9.8339</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.08</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2171</v>
+        <v>0.2216</v>
       </c>
       <c r="J48" t="n">
-        <v>6.2959</v>
+        <v>6.4264</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.95</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0944</v>
+        <v>-0.0709</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.7376</v>
+        <v>-2.0561</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.85</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2902</v>
+        <v>-0.1807</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.415800000000001</v>
+        <v>-5.2403</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.67</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5475</v>
+        <v>-0.3573</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.8775</v>
+        <v>-10.3617</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.47</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1777</v>
+        <v>0.837</v>
       </c>
       <c r="J52" t="n">
-        <v>23.554</v>
+        <v>16.74</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.42</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0744</v>
+        <v>0.7715</v>
       </c>
       <c r="J53" t="n">
-        <v>21.488</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.02</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0097</v>
+        <v>0.0554</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.194</v>
+        <v>1.108</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.02</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0097</v>
+        <v>0.0554</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.194</v>
+        <v>1.108</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.91</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4382</v>
+        <v>-0.3661</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.763999999999999</v>
+        <v>-7.322</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.68</v>
       </c>
       <c r="I57" t="n">
-        <v>0.984</v>
+        <v>0.8921</v>
       </c>
       <c r="J57" t="n">
-        <v>19.68</v>
+        <v>17.842</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.05</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1605</v>
+        <v>0.1537</v>
       </c>
       <c r="J58" t="n">
-        <v>3.21</v>
+        <v>3.074</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.88</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2409</v>
+        <v>-0.1494</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.818</v>
+        <v>-2.988</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.3387</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.434</v>
+        <v>-6.774</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.4</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-0.6027</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.41</v>
+        <v>-12.054</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.18</v>
       </c>
       <c r="I62" t="n">
-        <v>2.054</v>
+        <v>1.6173</v>
       </c>
       <c r="J62" t="n">
-        <v>32.864</v>
+        <v>25.8768</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.8</v>
       </c>
       <c r="I63" t="n">
-        <v>1.6888</v>
+        <v>1.1861</v>
       </c>
       <c r="J63" t="n">
-        <v>27.0208</v>
+        <v>18.9776</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.25</v>
       </c>
       <c r="I64" t="n">
-        <v>0.536</v>
+        <v>0.5152</v>
       </c>
       <c r="J64" t="n">
-        <v>8.576000000000001</v>
+        <v>8.2432</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.9</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.4475</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.379200000000001</v>
+        <v>-7.16</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.85</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6512</v>
+        <v>-0.5859</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.4192</v>
+        <v>-9.3744</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.49</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8368</v>
+        <v>0.7762</v>
       </c>
       <c r="J67" t="n">
-        <v>13.3888</v>
+        <v>12.4192</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.98</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0423</v>
+        <v>-0.0037</v>
       </c>
       <c r="J68" t="n">
-        <v>0.6768</v>
+        <v>-0.0592</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.67</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5073</v>
+        <v>-0.3366</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.1168</v>
+        <v>-5.3856</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.51</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.719</v>
+        <v>-0.486</v>
       </c>
       <c r="J70" t="n">
-        <v>-11.504</v>
+        <v>-7.776</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.27</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9998</v>
+        <v>-0.705</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.9968</v>
+        <v>-11.28</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>2.05</v>
       </c>
       <c r="I72" t="n">
-        <v>1.9763</v>
+        <v>1.5221</v>
       </c>
       <c r="J72" t="n">
-        <v>55.3364</v>
+        <v>42.6188</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.2</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4852</v>
+        <v>0.4629</v>
       </c>
       <c r="J73" t="n">
-        <v>13.5856</v>
+        <v>12.9612</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.15</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3526</v>
+        <v>0.3889</v>
       </c>
       <c r="J74" t="n">
-        <v>9.8728</v>
+        <v>10.8892</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1393</v>
+        <v>-0.06</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.9004</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.83</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6689000000000001</v>
+        <v>-0.6075</v>
       </c>
       <c r="J76" t="n">
-        <v>-18.7292</v>
+        <v>-17.01</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.57</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8561</v>
+        <v>0.7784</v>
       </c>
       <c r="J77" t="n">
-        <v>23.9708</v>
+        <v>21.7952</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.96</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.0921</v>
+        <v>-0.0601</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.5788</v>
+        <v>-1.6828</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.92</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.178</v>
+        <v>-0.1077</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.984</v>
+        <v>-3.0156</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.7</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.513</v>
+        <v>-0.3319</v>
       </c>
       <c r="J80" t="n">
-        <v>-14.364</v>
+        <v>-9.293200000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.66</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.3696</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.82</v>
+        <v>-10.3488</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.32</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4915</v>
+        <v>0.4268</v>
       </c>
       <c r="J82" t="n">
-        <v>11.796</v>
+        <v>10.2432</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.31</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4783</v>
+        <v>0.4152</v>
       </c>
       <c r="J83" t="n">
-        <v>11.4792</v>
+        <v>9.9648</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.23</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3671</v>
+        <v>0.3204</v>
       </c>
       <c r="J84" t="n">
-        <v>8.8104</v>
+        <v>7.6896</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.03</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0158</v>
+        <v>0.0463</v>
       </c>
       <c r="J85" t="n">
-        <v>0.3792</v>
+        <v>1.1112</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.96</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1639</v>
+        <v>-0.0806</v>
       </c>
       <c r="J86" t="n">
-        <v>-3.9336</v>
+        <v>-1.9344</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.07</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2516</v>
+        <v>0.1923</v>
       </c>
       <c r="J87" t="n">
-        <v>6.0384</v>
+        <v>4.6152</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.85</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2116</v>
+        <v>-0.1669</v>
       </c>
       <c r="J88" t="n">
-        <v>-5.0784</v>
+        <v>-4.0056</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.78</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3473</v>
+        <v>-0.2349</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.3352</v>
+        <v>-5.6376</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.67</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5145</v>
+        <v>-0.3398</v>
       </c>
       <c r="J90" t="n">
-        <v>-12.348</v>
+        <v>-8.155200000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.66</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5285</v>
+        <v>-0.3493</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.684</v>
+        <v>-8.3832</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.33</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5616</v>
+        <v>0.6723</v>
       </c>
       <c r="J92" t="n">
-        <v>19.656</v>
+        <v>23.5305</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.24</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4427</v>
+        <v>0.5141</v>
       </c>
       <c r="J93" t="n">
-        <v>15.4945</v>
+        <v>17.9935</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.13</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2805</v>
+        <v>0.3085</v>
       </c>
       <c r="J94" t="n">
-        <v>9.817500000000001</v>
+        <v>10.7975</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.67</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.5575</v>
+        <v>-0.3636</v>
       </c>
       <c r="J95" t="n">
-        <v>-19.5125</v>
+        <v>-12.726</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.59</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.4375</v>
       </c>
       <c r="J96" t="n">
-        <v>-22.988</v>
+        <v>-15.3125</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.41</v>
       </c>
       <c r="I97" t="n">
-        <v>1.069</v>
+        <v>1.0378</v>
       </c>
       <c r="J97" t="n">
-        <v>37.415</v>
+        <v>36.323</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.33</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8953</v>
+        <v>0.8831</v>
       </c>
       <c r="J98" t="n">
-        <v>31.3355</v>
+        <v>30.9085</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.24</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6841</v>
+        <v>0.67</v>
       </c>
       <c r="J99" t="n">
-        <v>23.9435</v>
+        <v>23.45</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.04</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0784</v>
+        <v>0.1346</v>
       </c>
       <c r="J100" t="n">
-        <v>2.744</v>
+        <v>4.711</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.67</v>
       </c>
       <c r="I101" t="n">
-        <v>-1.007</v>
+        <v>-0.9829</v>
       </c>
       <c r="J101" t="n">
-        <v>-35.245</v>
+        <v>-34.4015</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5396</v>
+        <v>0.6405</v>
       </c>
       <c r="J102" t="n">
-        <v>15.6484</v>
+        <v>18.5745</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.11</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2659</v>
+        <v>0.2828</v>
       </c>
       <c r="J103" t="n">
-        <v>7.7111</v>
+        <v>8.2012</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.93</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1488</v>
+        <v>-0.0946</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.3152</v>
+        <v>-2.7434</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.83</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3238</v>
+        <v>-0.202</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.3902</v>
+        <v>-5.858</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.55</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.698</v>
+        <v>-0.4689</v>
       </c>
       <c r="J106" t="n">
-        <v>-20.242</v>
+        <v>-13.5981</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>1.483</v>
+        <v>1.3105</v>
       </c>
       <c r="J107" t="n">
-        <v>43.007</v>
+        <v>38.0045</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.16</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4654</v>
+        <v>0.4715</v>
       </c>
       <c r="J108" t="n">
-        <v>13.4966</v>
+        <v>13.6735</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.09</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2374</v>
+        <v>0.287</v>
       </c>
       <c r="J109" t="n">
-        <v>6.8846</v>
+        <v>8.323</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.03</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0394</v>
+        <v>0.0985</v>
       </c>
       <c r="J110" t="n">
-        <v>1.1426</v>
+        <v>2.8565</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.82</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6669</v>
+        <v>-0.6091</v>
       </c>
       <c r="J111" t="n">
-        <v>-19.3401</v>
+        <v>-17.6639</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.06</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2401</v>
+        <v>0.2358</v>
       </c>
       <c r="J112" t="n">
-        <v>4.0817</v>
+        <v>4.0086</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.9</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1165</v>
+        <v>-0.1094</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.9805</v>
+        <v>-1.8598</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.88</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1515</v>
+        <v>-0.132</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.5755</v>
+        <v>-2.244</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.66</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5234</v>
+        <v>-0.3469</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.8978</v>
+        <v>-5.8973</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.45</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7934</v>
+        <v>-0.542</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.4878</v>
+        <v>-9.214</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.51</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1803</v>
+        <v>1.1274</v>
       </c>
       <c r="J117" t="n">
-        <v>20.0651</v>
+        <v>19.1658</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.46</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0772</v>
+        <v>1.0654</v>
       </c>
       <c r="J118" t="n">
-        <v>18.3124</v>
+        <v>18.1118</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.41</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9695</v>
+        <v>0.9936</v>
       </c>
       <c r="J119" t="n">
-        <v>16.4815</v>
+        <v>16.8912</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.18</v>
       </c>
       <c r="I120" t="n">
-        <v>0.394</v>
+        <v>0.4857</v>
       </c>
       <c r="J120" t="n">
-        <v>6.698</v>
+        <v>8.2569</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.08</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1288</v>
+        <v>0.2146</v>
       </c>
       <c r="J121" t="n">
-        <v>2.1896</v>
+        <v>3.6482</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4994</v>
+        <v>0.5848</v>
       </c>
       <c r="J122" t="n">
-        <v>9.988</v>
+        <v>11.696</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.15</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3697</v>
+        <v>0.408</v>
       </c>
       <c r="J123" t="n">
-        <v>7.394</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.4964</v>
+        <v>-0.3254</v>
       </c>
       <c r="J124" t="n">
-        <v>-9.928000000000001</v>
+        <v>-6.508</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.65</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5511</v>
+        <v>-0.3632</v>
       </c>
       <c r="J125" t="n">
-        <v>-11.022</v>
+        <v>-7.264</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.46</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7892</v>
+        <v>-0.5387</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.784</v>
+        <v>-10.774</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.35</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8922</v>
+        <v>0.8996</v>
       </c>
       <c r="J127" t="n">
-        <v>17.844</v>
+        <v>17.992</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.33</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8467</v>
+        <v>0.8547</v>
       </c>
       <c r="J128" t="n">
-        <v>16.934</v>
+        <v>17.094</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.22</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5567</v>
+        <v>0.6036</v>
       </c>
       <c r="J129" t="n">
-        <v>11.134</v>
+        <v>12.072</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.16</v>
       </c>
       <c r="I130" t="n">
-        <v>0.39</v>
+        <v>0.4573</v>
       </c>
       <c r="J130" t="n">
-        <v>7.8</v>
+        <v>9.146000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.07</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1357</v>
+        <v>0.2086</v>
       </c>
       <c r="J131" t="n">
-        <v>2.714</v>
+        <v>4.172</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.1</v>
       </c>
       <c r="I132" t="n">
-        <v>0.355</v>
+        <v>0.3313</v>
       </c>
       <c r="J132" t="n">
-        <v>8.52</v>
+        <v>7.9512</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.1</v>
       </c>
       <c r="I133" t="n">
-        <v>0.355</v>
+        <v>0.3313</v>
       </c>
       <c r="J133" t="n">
-        <v>8.52</v>
+        <v>7.9512</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.355</v>
+        <v>0.3313</v>
       </c>
       <c r="J134" t="n">
-        <v>8.52</v>
+        <v>7.9512</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2159</v>
+        <v>0.2155</v>
       </c>
       <c r="J135" t="n">
-        <v>5.1816</v>
+        <v>5.172</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.93</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3352</v>
+        <v>-0.2761</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.0448</v>
+        <v>-6.6264</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.32</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5508</v>
+        <v>0.6574</v>
       </c>
       <c r="J137" t="n">
-        <v>13.2192</v>
+        <v>15.7776</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.19</v>
       </c>
       <c r="I138" t="n">
-        <v>0.374</v>
+        <v>0.4248</v>
       </c>
       <c r="J138" t="n">
-        <v>8.976000000000001</v>
+        <v>10.1952</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0121</v>
+        <v>0.0016</v>
       </c>
       <c r="J139" t="n">
-        <v>0.2904</v>
+        <v>0.0384</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.75</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4507</v>
+        <v>-0.2867</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.8168</v>
+        <v>-6.8808</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.67</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5565</v>
+        <v>-0.3629</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.356</v>
+        <v>-8.7096</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.36</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5861</v>
+        <v>0.5413</v>
       </c>
       <c r="J142" t="n">
-        <v>16.9969</v>
+        <v>15.6977</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.09</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1975</v>
+        <v>0.1674</v>
       </c>
       <c r="J143" t="n">
-        <v>5.7275</v>
+        <v>4.8546</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.07</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1603</v>
+        <v>0.1356</v>
       </c>
       <c r="J144" t="n">
-        <v>4.6487</v>
+        <v>3.9324</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1665</v>
+        <v>-0.0915</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.8285</v>
+        <v>-2.6535</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.7</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5258</v>
+        <v>-0.3398</v>
       </c>
       <c r="J146" t="n">
-        <v>-15.2482</v>
+        <v>-9.854200000000001</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.31</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5115</v>
+        <v>0.4352</v>
       </c>
       <c r="J147" t="n">
-        <v>14.8335</v>
+        <v>12.6208</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.23</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4036</v>
+        <v>0.3369</v>
       </c>
       <c r="J148" t="n">
-        <v>11.7044</v>
+        <v>9.770099999999999</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.03</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0491</v>
+        <v>0.0591</v>
       </c>
       <c r="J149" t="n">
-        <v>1.4239</v>
+        <v>1.7139</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.98</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0422</v>
       </c>
       <c r="J150" t="n">
-        <v>-2.7463</v>
+        <v>-1.2238</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.78</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4254</v>
+        <v>-0.2663</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.3366</v>
+        <v>-7.7227</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.47</v>
       </c>
       <c r="I152" t="n">
-        <v>1.1747</v>
+        <v>1.1092</v>
       </c>
       <c r="J152" t="n">
-        <v>21.1446</v>
+        <v>19.9656</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.22</v>
       </c>
       <c r="I153" t="n">
-        <v>0.61</v>
+        <v>0.6123</v>
       </c>
       <c r="J153" t="n">
-        <v>10.98</v>
+        <v>11.0214</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.15</v>
       </c>
       <c r="I154" t="n">
-        <v>0.3961</v>
+        <v>0.4422</v>
       </c>
       <c r="J154" t="n">
-        <v>7.1298</v>
+        <v>7.9596</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.07</v>
       </c>
       <c r="I155" t="n">
-        <v>0.159</v>
+        <v>0.2212</v>
       </c>
       <c r="J155" t="n">
-        <v>2.862</v>
+        <v>3.9816</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.96</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2866</v>
+        <v>-0.2104</v>
       </c>
       <c r="J156" t="n">
-        <v>-5.1588</v>
+        <v>-3.7872</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.31</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5663</v>
+        <v>0.6768</v>
       </c>
       <c r="J157" t="n">
-        <v>10.1934</v>
+        <v>12.1824</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.96</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0553</v>
+        <v>-0.0548</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.9954</v>
+        <v>-0.9864000000000001</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.87</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2435</v>
+        <v>-0.1563</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.383</v>
+        <v>-2.8134</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.75</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4313</v>
+        <v>-0.2768</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.7634</v>
+        <v>-4.9824</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.64</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5798</v>
+        <v>-0.3816</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.4364</v>
+        <v>-6.8688</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.58</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3722</v>
+        <v>1.2393</v>
       </c>
       <c r="J162" t="n">
-        <v>27.444</v>
+        <v>24.786</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.56</v>
       </c>
       <c r="I163" t="n">
-        <v>1.3336</v>
+        <v>1.2141</v>
       </c>
       <c r="J163" t="n">
-        <v>26.672</v>
+        <v>24.282</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.22</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5763</v>
+        <v>0.6048</v>
       </c>
       <c r="J164" t="n">
-        <v>11.526</v>
+        <v>12.096</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.02</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0281</v>
+        <v>0.0439</v>
       </c>
       <c r="J165" t="n">
-        <v>-0.5620000000000001</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.9796</v>
+        <v>-0.9517</v>
       </c>
       <c r="J166" t="n">
-        <v>-19.592</v>
+        <v>-19.034</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.43</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7236</v>
+        <v>0.9009</v>
       </c>
       <c r="J167" t="n">
-        <v>14.472</v>
+        <v>18.018</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.97</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0235</v>
+        <v>-0.0382</v>
       </c>
       <c r="J168" t="n">
-        <v>-0.47</v>
+        <v>-0.764</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.77</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3957</v>
+        <v>-0.2545</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.914</v>
+        <v>-5.09</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.65</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5622</v>
+        <v>-0.3694</v>
       </c>
       <c r="J170" t="n">
-        <v>-11.244</v>
+        <v>-7.388</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.6</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6264</v>
+        <v>-0.416</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.528</v>
+        <v>-8.32</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.42</v>
       </c>
       <c r="I172" t="n">
-        <v>0.662</v>
+        <v>0.6204</v>
       </c>
       <c r="J172" t="n">
-        <v>14.564</v>
+        <v>13.6488</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.17</v>
       </c>
       <c r="I173" t="n">
-        <v>0.331</v>
+        <v>0.2877</v>
       </c>
       <c r="J173" t="n">
-        <v>7.282</v>
+        <v>6.3294</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.9</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2351</v>
+        <v>-0.1369</v>
       </c>
       <c r="J174" t="n">
-        <v>-5.1722</v>
+        <v>-3.0118</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2681</v>
+        <v>-0.1588</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.8982</v>
+        <v>-3.4936</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.75</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4584</v>
+        <v>-0.291</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.0848</v>
+        <v>-6.402</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.45</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6574</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="J177" t="n">
-        <v>14.4628</v>
+        <v>12.7182</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.39</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5851</v>
+        <v>0.5103</v>
       </c>
       <c r="J178" t="n">
-        <v>12.8722</v>
+        <v>11.2266</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.17</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2795</v>
+        <v>0.2487</v>
       </c>
       <c r="J179" t="n">
-        <v>6.149</v>
+        <v>5.4714</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.1</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1504</v>
+        <v>0.1574</v>
       </c>
       <c r="J180" t="n">
-        <v>3.3088</v>
+        <v>3.4628</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.66</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5929</v>
+        <v>-0.3888</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.0438</v>
+        <v>-8.553599999999999</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.69</v>
       </c>
       <c r="I182" t="n">
-        <v>1.6183</v>
+        <v>1.4024</v>
       </c>
       <c r="J182" t="n">
-        <v>37.2209</v>
+        <v>32.2552</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.15</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4443</v>
+        <v>0.4481</v>
       </c>
       <c r="J183" t="n">
-        <v>10.2189</v>
+        <v>10.3063</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3721</v>
+        <v>0.3975</v>
       </c>
       <c r="J184" t="n">
-        <v>8.558299999999999</v>
+        <v>9.1425</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.09</v>
       </c>
       <c r="I185" t="n">
-        <v>0.244</v>
+        <v>0.2892</v>
       </c>
       <c r="J185" t="n">
-        <v>5.612</v>
+        <v>6.6516</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.61</v>
       </c>
       <c r="I186" t="n">
-        <v>-1.132</v>
+        <v>-1.1244</v>
       </c>
       <c r="J186" t="n">
-        <v>-26.036</v>
+        <v>-25.8612</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.43</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6766</v>
+        <v>0.8307</v>
       </c>
       <c r="J187" t="n">
-        <v>15.5618</v>
+        <v>19.1061</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.18</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3488</v>
+        <v>0.3969</v>
       </c>
       <c r="J188" t="n">
-        <v>8.022399999999999</v>
+        <v>9.1287</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.14</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2875</v>
+        <v>0.3214</v>
       </c>
       <c r="J189" t="n">
-        <v>6.6125</v>
+        <v>7.3922</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.79</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4015</v>
+        <v>-0.2508</v>
       </c>
       <c r="J190" t="n">
-        <v>-9.234500000000001</v>
+        <v>-5.7684</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.54</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.7193000000000001</v>
+        <v>-0.4851</v>
       </c>
       <c r="J191" t="n">
-        <v>-16.5439</v>
+        <v>-11.1573</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.23</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4179</v>
+        <v>0.4855</v>
       </c>
       <c r="J192" t="n">
-        <v>10.0296</v>
+        <v>11.652</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.17</v>
       </c>
       <c r="I193" t="n">
-        <v>0.331</v>
+        <v>0.376</v>
       </c>
       <c r="J193" t="n">
-        <v>7.944</v>
+        <v>9.023999999999999</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.03</v>
       </c>
       <c r="I194" t="n">
-        <v>0.078</v>
+        <v>0.0883</v>
       </c>
       <c r="J194" t="n">
-        <v>1.872</v>
+        <v>2.1192</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.92</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2005</v>
+        <v>-0.1142</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.812</v>
+        <v>-2.7408</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.77</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4311</v>
+        <v>-0.2715</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.3464</v>
+        <v>-6.516</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.43</v>
       </c>
       <c r="I197" t="n">
-        <v>1.1309</v>
+        <v>1.0764</v>
       </c>
       <c r="J197" t="n">
-        <v>27.1416</v>
+        <v>25.8336</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.2</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6066</v>
+        <v>0.5831</v>
       </c>
       <c r="J198" t="n">
-        <v>14.5584</v>
+        <v>13.9944</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.11</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3497</v>
+        <v>0.3498</v>
       </c>
       <c r="J199" t="n">
-        <v>8.392799999999999</v>
+        <v>8.395200000000001</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.93</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.354</v>
+        <v>-0.2877</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.496</v>
+        <v>-6.9048</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.83</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6286</v>
+        <v>-0.571</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.0864</v>
+        <v>-13.704</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.44</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6717</v>
+        <v>0.8257</v>
       </c>
       <c r="J202" t="n">
-        <v>15.4491</v>
+        <v>18.9911</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.24</v>
       </c>
       <c r="I203" t="n">
-        <v>0.417</v>
+        <v>0.4902</v>
       </c>
       <c r="J203" t="n">
-        <v>9.590999999999999</v>
+        <v>11.2746</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.03</v>
       </c>
       <c r="I204" t="n">
-        <v>0.0483</v>
+        <v>0.0827</v>
       </c>
       <c r="J204" t="n">
-        <v>1.1109</v>
+        <v>1.9021</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.9</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2468</v>
+        <v>-0.1417</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.6764</v>
+        <v>-3.2591</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.73</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4928</v>
+        <v>-0.315</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.3344</v>
+        <v>-7.245</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.86</v>
       </c>
       <c r="I207" t="n">
-        <v>1.9055</v>
+        <v>1.6088</v>
       </c>
       <c r="J207" t="n">
-        <v>43.8265</v>
+        <v>37.0024</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.27</v>
       </c>
       <c r="I208" t="n">
-        <v>0.7522</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="J208" t="n">
-        <v>17.3006</v>
+        <v>17.0062</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.96</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.276</v>
+        <v>-0.2031</v>
       </c>
       <c r="J209" t="n">
-        <v>-6.348</v>
+        <v>-4.6713</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.91</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4308</v>
+        <v>-0.3604</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.9084</v>
+        <v>-8.289199999999999</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.73</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.8777</v>
+        <v>-0.8387</v>
       </c>
       <c r="J211" t="n">
-        <v>-20.1871</v>
+        <v>-19.2901</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.3</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5655</v>
+        <v>0.676</v>
       </c>
       <c r="J212" t="n">
-        <v>10.7445</v>
+        <v>12.844</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.88</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1982</v>
+        <v>-0.1433</v>
       </c>
       <c r="J213" t="n">
-        <v>-3.7658</v>
+        <v>-2.7227</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.78</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3773</v>
+        <v>-0.2434</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.1687</v>
+        <v>-4.6246</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.76</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4072</v>
+        <v>-0.2629</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.7368</v>
+        <v>-4.9951</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.65</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5599</v>
+        <v>-0.3681</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.6381</v>
+        <v>-6.9939</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.88</v>
       </c>
       <c r="I217" t="n">
-        <v>1.8771</v>
+        <v>1.5826</v>
       </c>
       <c r="J217" t="n">
-        <v>35.6649</v>
+        <v>30.0694</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.55</v>
       </c>
       <c r="I218" t="n">
-        <v>1.2798</v>
+        <v>1.1849</v>
       </c>
       <c r="J218" t="n">
-        <v>24.3162</v>
+        <v>22.5131</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.07</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1132</v>
+        <v>0.1943</v>
       </c>
       <c r="J219" t="n">
-        <v>2.1508</v>
+        <v>3.6917</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.03</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0155</v>
+        <v>0.0636</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.2945</v>
+        <v>1.2084</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.9</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4994</v>
+        <v>-0.424</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.4886</v>
+        <v>-8.055999999999999</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.24</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4645</v>
+        <v>0.5384</v>
       </c>
       <c r="J222" t="n">
-        <v>10.6835</v>
+        <v>12.3832</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.03</v>
       </c>
       <c r="I223" t="n">
-        <v>0.1233</v>
+        <v>0.1076</v>
       </c>
       <c r="J223" t="n">
-        <v>2.8359</v>
+        <v>2.4748</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.98</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0212</v>
+        <v>-0.03</v>
       </c>
       <c r="J224" t="n">
-        <v>-0.4876</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.75</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4377</v>
+        <v>-0.2799</v>
       </c>
       <c r="J225" t="n">
-        <v>-10.0671</v>
+        <v>-6.4377</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.65</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5718</v>
+        <v>-0.3751</v>
       </c>
       <c r="J226" t="n">
-        <v>-13.1514</v>
+        <v>-8.6273</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.6</v>
       </c>
       <c r="I227" t="n">
-        <v>1.4554</v>
+        <v>1.2916</v>
       </c>
       <c r="J227" t="n">
-        <v>33.4742</v>
+        <v>29.7068</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.23</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6499</v>
       </c>
       <c r="J228" t="n">
-        <v>15.3594</v>
+        <v>14.9477</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0916</v>
+        <v>-0.0291</v>
       </c>
       <c r="J229" t="n">
-        <v>-2.1068</v>
+        <v>-0.6693</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.97</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2317</v>
+        <v>-0.1623</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.3291</v>
+        <v>-3.7329</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.82</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.661</v>
+        <v>-0.6039</v>
       </c>
       <c r="J231" t="n">
-        <v>-15.203</v>
+        <v>-13.8897</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.81</v>
       </c>
       <c r="I232" t="n">
-        <v>1.6781</v>
+        <v>1.4544</v>
       </c>
       <c r="J232" t="n">
-        <v>25.1715</v>
+        <v>21.816</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.69</v>
       </c>
       <c r="I233" t="n">
-        <v>1.461</v>
+        <v>1.3169</v>
       </c>
       <c r="J233" t="n">
-        <v>21.915</v>
+        <v>19.7535</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.45</v>
       </c>
       <c r="I234" t="n">
-        <v>0.95</v>
+        <v>1.0357</v>
       </c>
       <c r="J234" t="n">
-        <v>14.25</v>
+        <v>15.5355</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.29</v>
       </c>
       <c r="I235" t="n">
-        <v>0.5972</v>
+        <v>0.7177</v>
       </c>
       <c r="J235" t="n">
-        <v>8.958</v>
+        <v>10.7655</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.15</v>
       </c>
       <c r="I236" t="n">
-        <v>0.2719</v>
+        <v>0.3764</v>
       </c>
       <c r="J236" t="n">
-        <v>4.0785</v>
+        <v>5.646</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.26</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5466</v>
+        <v>0.6539</v>
       </c>
       <c r="J237" t="n">
-        <v>8.199</v>
+        <v>9.8085</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.18</v>
       </c>
       <c r="I238" t="n">
-        <v>0.4343</v>
+        <v>0.4961</v>
       </c>
       <c r="J238" t="n">
-        <v>6.5145</v>
+        <v>7.4415</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.6</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.6051</v>
+        <v>-0.4033</v>
       </c>
       <c r="J239" t="n">
-        <v>-9.076499999999999</v>
+        <v>-6.0495</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.51</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.4869</v>
       </c>
       <c r="J240" t="n">
-        <v>-10.8045</v>
+        <v>-7.3035</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.4</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.8526</v>
+        <v>-0.5877</v>
       </c>
       <c r="J241" t="n">
-        <v>-12.789</v>
+        <v>-8.8155</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.11</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3299</v>
+        <v>0.2709</v>
       </c>
       <c r="J242" t="n">
-        <v>5.6083</v>
+        <v>4.6053</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.97</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0206</v>
+        <v>-0.0183</v>
       </c>
       <c r="J243" t="n">
-        <v>0.3502</v>
+        <v>-0.3111</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.86</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1819</v>
+        <v>-0.1525</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.0923</v>
+        <v>-2.5925</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.51</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.7186</v>
+        <v>-0.4858</v>
       </c>
       <c r="J245" t="n">
-        <v>-12.2162</v>
+        <v>-8.258599999999999</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.46</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.78</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.26</v>
+        <v>-9.0406</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.82</v>
       </c>
       <c r="I247" t="n">
-        <v>0.9811</v>
+        <v>0.905</v>
       </c>
       <c r="J247" t="n">
-        <v>16.6787</v>
+        <v>15.385</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.78</v>
       </c>
       <c r="I248" t="n">
-        <v>0.9405</v>
+        <v>0.8661</v>
       </c>
       <c r="J248" t="n">
-        <v>15.9885</v>
+        <v>14.7237</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.37</v>
       </c>
       <c r="I249" t="n">
-        <v>0.4513</v>
+        <v>0.453</v>
       </c>
       <c r="J249" t="n">
-        <v>7.6721</v>
+        <v>7.701</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.37</v>
       </c>
       <c r="I250" t="n">
-        <v>0.4513</v>
+        <v>0.453</v>
       </c>
       <c r="J250" t="n">
-        <v>7.6721</v>
+        <v>7.701</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.91</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2914</v>
+        <v>-0.1651</v>
       </c>
       <c r="J251" t="n">
-        <v>-4.9538</v>
+        <v>-2.8067</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.68</v>
       </c>
       <c r="I252" t="n">
-        <v>1.5797</v>
+        <v>1.3761</v>
       </c>
       <c r="J252" t="n">
-        <v>37.9128</v>
+        <v>33.0264</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.38</v>
       </c>
       <c r="I253" t="n">
-        <v>0.9861</v>
+        <v>0.9771</v>
       </c>
       <c r="J253" t="n">
-        <v>23.6664</v>
+        <v>23.4504</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.11</v>
       </c>
       <c r="I254" t="n">
-        <v>0.2793</v>
+        <v>0.3363</v>
       </c>
       <c r="J254" t="n">
-        <v>6.7032</v>
+        <v>8.071199999999999</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.86</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.5095</v>
       </c>
       <c r="J255" t="n">
-        <v>-13.8024</v>
+        <v>-12.228</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.84</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6258</v>
+        <v>-0.5636</v>
       </c>
       <c r="J256" t="n">
-        <v>-15.0192</v>
+        <v>-13.5264</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.08</v>
       </c>
       <c r="I257" t="n">
-        <v>0.2093</v>
+        <v>0.2157</v>
       </c>
       <c r="J257" t="n">
-        <v>5.0232</v>
+        <v>5.1768</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.03</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1116</v>
+        <v>0.1005</v>
       </c>
       <c r="J258" t="n">
-        <v>2.6784</v>
+        <v>2.412</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.01</v>
       </c>
       <c r="I259" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0452</v>
       </c>
       <c r="J259" t="n">
-        <v>1.5048</v>
+        <v>1.0848</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.88</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2477</v>
+        <v>-0.1514</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.9448</v>
+        <v>-3.6336</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.79</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3878</v>
+        <v>-0.244</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.3072</v>
+        <v>-5.856</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.09</v>
       </c>
       <c r="I262" t="n">
-        <v>0.2915</v>
+        <v>0.2319</v>
       </c>
       <c r="J262" t="n">
-        <v>5.83</v>
+        <v>4.638</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.98</v>
       </c>
       <c r="I263" t="n">
-        <v>0.0379</v>
+        <v>-0.0061</v>
       </c>
       <c r="J263" t="n">
-        <v>0.758</v>
+        <v>-0.122</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.8</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2951</v>
+        <v>-0.2152</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.902</v>
+        <v>-4.304</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.57</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.6453</v>
+        <v>-0.4318</v>
       </c>
       <c r="J265" t="n">
-        <v>-12.906</v>
+        <v>-8.635999999999999</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.53</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.4689</v>
       </c>
       <c r="J266" t="n">
-        <v>-13.922</v>
+        <v>-9.378</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.7</v>
       </c>
       <c r="I267" t="n">
-        <v>0.879</v>
+        <v>0.8018</v>
       </c>
       <c r="J267" t="n">
-        <v>17.58</v>
+        <v>16.036</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.69</v>
       </c>
       <c r="I268" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.7917</v>
       </c>
       <c r="J268" t="n">
-        <v>17.368</v>
+        <v>15.834</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.38</v>
       </c>
       <c r="I269" t="n">
-        <v>0.5046</v>
+        <v>0.47</v>
       </c>
       <c r="J269" t="n">
-        <v>10.092</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.1</v>
       </c>
       <c r="I270" t="n">
-        <v>0.1002</v>
+        <v>0.1333</v>
       </c>
       <c r="J270" t="n">
-        <v>2.004</v>
+        <v>2.666</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.232</v>
+        <v>-0.1233</v>
       </c>
       <c r="J271" t="n">
-        <v>-4.64</v>
+        <v>-2.466</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.98</v>
       </c>
       <c r="I272" t="n">
-        <v>1.9568</v>
+        <v>1.6559</v>
       </c>
       <c r="J272" t="n">
-        <v>37.1792</v>
+        <v>31.4621</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.94</v>
       </c>
       <c r="I273" t="n">
-        <v>1.9086</v>
+        <v>1.6108</v>
       </c>
       <c r="J273" t="n">
-        <v>36.2634</v>
+        <v>30.6052</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.52</v>
       </c>
       <c r="I274" t="n">
-        <v>1.1472</v>
+        <v>1.1235</v>
       </c>
       <c r="J274" t="n">
-        <v>21.7968</v>
+        <v>21.3465</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.98</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2876</v>
+        <v>-0.1982</v>
       </c>
       <c r="J275" t="n">
-        <v>-5.4644</v>
+        <v>-3.7658</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.76</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.8653999999999999</v>
+        <v>-0.8238</v>
       </c>
       <c r="J276" t="n">
-        <v>-16.4426</v>
+        <v>-15.6522</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.06</v>
       </c>
       <c r="I277" t="n">
-        <v>0.2218</v>
+        <v>0.2149</v>
       </c>
       <c r="J277" t="n">
-        <v>4.2142</v>
+        <v>4.0831</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.98</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0208</v>
+        <v>-0.0148</v>
       </c>
       <c r="J278" t="n">
-        <v>0.3952</v>
+        <v>-0.2812</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.93</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.082</v>
+        <v>-0.0818</v>
       </c>
       <c r="J279" t="n">
-        <v>-1.558</v>
+        <v>-1.5542</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.74</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4231</v>
+        <v>-0.277</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.0389</v>
+        <v>-5.263</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.46</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.7886</v>
+        <v>-0.5383</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.9834</v>
+        <v>-10.2277</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.54</v>
       </c>
       <c r="I282" t="n">
-        <v>1.2878</v>
+        <v>1.1855</v>
       </c>
       <c r="J282" t="n">
-        <v>30.9072</v>
+        <v>28.452</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.41</v>
       </c>
       <c r="I283" t="n">
-        <v>1.0225</v>
+        <v>1.0145</v>
       </c>
       <c r="J283" t="n">
-        <v>24.54</v>
+        <v>24.348</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.3</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7752</v>
+        <v>0.7862</v>
       </c>
       <c r="J284" t="n">
-        <v>18.6048</v>
+        <v>18.8688</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.24</v>
       </c>
       <c r="I285" t="n">
-        <v>0.6212</v>
+        <v>0.6489</v>
       </c>
       <c r="J285" t="n">
-        <v>14.9088</v>
+        <v>15.5736</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.65</v>
       </c>
       <c r="I286" t="n">
-        <v>-1.0664</v>
+        <v>-1.05</v>
       </c>
       <c r="J286" t="n">
-        <v>-25.5936</v>
+        <v>-25.2</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.08</v>
       </c>
       <c r="I287" t="n">
-        <v>0.2403</v>
+        <v>0.2424</v>
       </c>
       <c r="J287" t="n">
-        <v>5.7672</v>
+        <v>5.8176</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.04</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1654</v>
+        <v>0.1492</v>
       </c>
       <c r="J288" t="n">
-        <v>3.9696</v>
+        <v>3.5808</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.87</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.227</v>
+        <v>-0.1536</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.448</v>
+        <v>-3.6864</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.7</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4937</v>
+        <v>-0.3213</v>
       </c>
       <c r="J290" t="n">
-        <v>-11.8488</v>
+        <v>-7.7112</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.7</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4937</v>
+        <v>-0.3213</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.8488</v>
+        <v>-7.7112</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.28</v>
       </c>
       <c r="I292" t="n">
-        <v>0.5056</v>
+        <v>0.5955</v>
       </c>
       <c r="J292" t="n">
-        <v>14.6624</v>
+        <v>17.2695</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.07</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1881</v>
+        <v>0.1919</v>
       </c>
       <c r="J293" t="n">
-        <v>5.4549</v>
+        <v>5.5651</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.89</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2335</v>
+        <v>-0.1415</v>
       </c>
       <c r="J294" t="n">
-        <v>-6.7715</v>
+        <v>-4.1035</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.87</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2671</v>
+        <v>-0.163</v>
       </c>
       <c r="J295" t="n">
-        <v>-7.7459</v>
+        <v>-4.727</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.72</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4872</v>
+        <v>-0.3132</v>
       </c>
       <c r="J296" t="n">
-        <v>-14.1288</v>
+        <v>-9.082800000000001</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.4</v>
       </c>
       <c r="I297" t="n">
-        <v>1.0712</v>
+        <v>1.036</v>
       </c>
       <c r="J297" t="n">
-        <v>31.0648</v>
+        <v>30.044</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.28</v>
       </c>
       <c r="I298" t="n">
-        <v>0.8055</v>
+        <v>0.7816</v>
       </c>
       <c r="J298" t="n">
-        <v>23.3595</v>
+        <v>22.6664</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.16</v>
       </c>
       <c r="I299" t="n">
-        <v>0.504</v>
+        <v>0.483</v>
       </c>
       <c r="J299" t="n">
-        <v>14.616</v>
+        <v>14.007</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.83</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.6266</v>
+        <v>-0.5693</v>
       </c>
       <c r="J300" t="n">
-        <v>-18.1714</v>
+        <v>-16.5097</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.8</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.7008</v>
+        <v>-0.6481</v>
       </c>
       <c r="J301" t="n">
-        <v>-20.3232</v>
+        <v>-18.7949</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.13</v>
       </c>
       <c r="I302" t="n">
-        <v>0.323</v>
+        <v>0.3484</v>
       </c>
       <c r="J302" t="n">
-        <v>6.783</v>
+        <v>7.3164</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.0764</v>
       </c>
       <c r="J303" t="n">
-        <v>-1.7451</v>
+        <v>-1.6044</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.83</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2994</v>
+        <v>-0.1942</v>
       </c>
       <c r="J304" t="n">
-        <v>-6.2874</v>
+        <v>-4.0782</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.75</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4231</v>
+        <v>-0.2732</v>
       </c>
       <c r="J305" t="n">
-        <v>-8.8851</v>
+        <v>-5.7372</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.74</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4376</v>
+        <v>-0.2829</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.1896</v>
+        <v>-5.9409</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.72</v>
       </c>
       <c r="I307" t="n">
-        <v>1.6587</v>
+        <v>1.43</v>
       </c>
       <c r="J307" t="n">
-        <v>34.8327</v>
+        <v>30.03</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.41</v>
       </c>
       <c r="I308" t="n">
-        <v>1.0565</v>
+        <v>1.0312</v>
       </c>
       <c r="J308" t="n">
-        <v>22.1865</v>
+        <v>21.6552</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1085</v>
+        <v>-0.0389</v>
       </c>
       <c r="J309" t="n">
-        <v>-2.2785</v>
+        <v>-0.8169</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.87</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.5455</v>
+        <v>-0.4788</v>
       </c>
       <c r="J310" t="n">
-        <v>-11.4555</v>
+        <v>-10.0548</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6963</v>
+        <v>-0.6399</v>
       </c>
       <c r="J311" t="n">
-        <v>-14.6223</v>
+        <v>-13.4379</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.57</v>
       </c>
       <c r="I312" t="n">
-        <v>0.825</v>
+        <v>0.7402</v>
       </c>
       <c r="J312" t="n">
-        <v>24.75</v>
+        <v>22.206</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.97</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.1133</v>
+        <v>-0.0553</v>
       </c>
       <c r="J313" t="n">
-        <v>-3.399</v>
+        <v>-1.659</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.95</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.1542</v>
+        <v>-0.0815</v>
       </c>
       <c r="J314" t="n">
-        <v>-4.626</v>
+        <v>-2.445</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.91</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2265</v>
+        <v>-0.129</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.795</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.87</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.2915</v>
+        <v>-0.1729</v>
       </c>
       <c r="J316" t="n">
-        <v>-8.744999999999999</v>
+        <v>-5.187</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.34</v>
       </c>
       <c r="I317" t="n">
-        <v>0.5656</v>
+        <v>0.5196</v>
       </c>
       <c r="J317" t="n">
-        <v>16.968</v>
+        <v>15.588</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.97</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.1002</v>
+        <v>-0.0517</v>
       </c>
       <c r="J318" t="n">
-        <v>-3.006</v>
+        <v>-1.551</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.95</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1423</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.269</v>
+        <v>-2.331</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.92</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1987</v>
+        <v>-0.1136</v>
       </c>
       <c r="J320" t="n">
-        <v>-5.961</v>
+        <v>-3.408</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.91</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2163</v>
+        <v>-0.125</v>
       </c>
       <c r="J321" t="n">
-        <v>-6.489</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.03</v>
       </c>
       <c r="I322" t="n">
-        <v>0.1266</v>
+        <v>0.1099</v>
       </c>
       <c r="J322" t="n">
-        <v>3.0384</v>
+        <v>2.6376</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.02</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1039</v>
+        <v>0.0832</v>
       </c>
       <c r="J323" t="n">
-        <v>2.4936</v>
+        <v>1.9968</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.98</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.0175</v>
+        <v>-0.0291</v>
       </c>
       <c r="J324" t="n">
-        <v>-0.42</v>
+        <v>-0.6984</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.8</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.3628</v>
+        <v>-0.2296</v>
       </c>
       <c r="J325" t="n">
-        <v>-8.7072</v>
+        <v>-5.5104</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.78</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.3925</v>
+        <v>-0.2495</v>
       </c>
       <c r="J326" t="n">
-        <v>-9.42</v>
+        <v>-5.988</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.32</v>
       </c>
       <c r="I327" t="n">
-        <v>0.875</v>
+        <v>0.8613</v>
       </c>
       <c r="J327" t="n">
-        <v>21</v>
+        <v>20.6712</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.24</v>
       </c>
       <c r="I328" t="n">
-        <v>0.6865</v>
+        <v>0.6712</v>
       </c>
       <c r="J328" t="n">
-        <v>16.476</v>
+        <v>16.1088</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.18</v>
       </c>
       <c r="I329" t="n">
-        <v>0.5309</v>
+        <v>0.5236</v>
       </c>
       <c r="J329" t="n">
-        <v>12.7416</v>
+        <v>12.5664</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.13</v>
       </c>
       <c r="I330" t="n">
-        <v>0.3721</v>
+        <v>0.3975</v>
       </c>
       <c r="J330" t="n">
-        <v>8.930400000000001</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.8</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.7126</v>
+        <v>-0.6587</v>
       </c>
       <c r="J331" t="n">
-        <v>-17.1024</v>
+        <v>-15.8088</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.27</v>
       </c>
       <c r="I332" t="n">
-        <v>0.4403</v>
+        <v>0.5278</v>
       </c>
       <c r="J332" t="n">
-        <v>10.5672</v>
+        <v>12.6672</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.23</v>
       </c>
       <c r="I333" t="n">
-        <v>0.3845</v>
+        <v>0.4595</v>
       </c>
       <c r="J333" t="n">
-        <v>9.228</v>
+        <v>11.028</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.15</v>
       </c>
       <c r="I334" t="n">
-        <v>0.2614</v>
+        <v>0.3181</v>
       </c>
       <c r="J334" t="n">
-        <v>6.2736</v>
+        <v>7.6344</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.99</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.0862</v>
+        <v>-0.0321</v>
       </c>
       <c r="J335" t="n">
-        <v>-2.0688</v>
+        <v>-0.7704</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.97</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.1327</v>
+        <v>-0.0623</v>
       </c>
       <c r="J336" t="n">
-        <v>-3.1848</v>
+        <v>-1.4952</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.64</v>
       </c>
       <c r="I337" t="n">
-        <v>1.5055</v>
+        <v>1.3261</v>
       </c>
       <c r="J337" t="n">
-        <v>36.132</v>
+        <v>31.8264</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.51</v>
       </c>
       <c r="I338" t="n">
-        <v>1.2551</v>
+        <v>1.1609</v>
       </c>
       <c r="J338" t="n">
-        <v>30.1224</v>
+        <v>27.8616</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.31</v>
       </c>
       <c r="I339" t="n">
-        <v>0.83</v>
+        <v>0.8243</v>
       </c>
       <c r="J339" t="n">
-        <v>19.92</v>
+        <v>19.7832</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.6995</v>
+        <v>-0.6429</v>
       </c>
       <c r="J340" t="n">
-        <v>-16.788</v>
+        <v>-15.4296</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.6</v>
       </c>
       <c r="I341" t="n">
-        <v>-1.1597</v>
+        <v>-1.1562</v>
       </c>
       <c r="J341" t="n">
-        <v>-27.8328</v>
+        <v>-27.7488</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7908/event_7908_evp_summary.xlsx
+++ b/database/event/7908/event_7908_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.0421</v>
+        <v>8.202400000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.2703</v>
+        <v>3.3354</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9926</v>
+        <v>3.1097</v>
       </c>
       <c r="E2" t="n">
-        <v>8.0421</v>
+        <v>8.202400000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9608</v>
+        <v>3.8972</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0813</v>
+        <v>4.3052</v>
       </c>
       <c r="H2" t="n">
-        <v>8.468999999999999</v>
+        <v>7.964</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4035</v>
+        <v>4.3005</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0813</v>
+        <v>4.3052</v>
       </c>
       <c r="K2" t="n">
         <v>97</v>
@@ -529,7 +529,7 @@
         <v>156</v>
       </c>
       <c r="M2" t="n">
-        <v>8.4848</v>
+        <v>8.605700000000001</v>
       </c>
       <c r="N2" t="n">
         <v>253</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0167</v>
+        <v>6.3552</v>
       </c>
       <c r="C3" t="n">
-        <v>2.4466</v>
+        <v>2.5843</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0782</v>
+        <v>2.2688</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0167</v>
+        <v>6.3552</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2796</v>
+        <v>3.2247</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7371</v>
+        <v>3.1305</v>
       </c>
       <c r="H3" t="n">
-        <v>6.0688</v>
+        <v>5.7453</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1555</v>
+        <v>3.1024</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7371</v>
+        <v>3.1305</v>
       </c>
       <c r="K3" t="n">
         <v>134</v>
@@ -575,7 +575,7 @@
         <v>151</v>
       </c>
       <c r="M3" t="n">
-        <v>5.8926</v>
+        <v>6.2329</v>
       </c>
       <c r="N3" t="n">
         <v>285</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6625</v>
+        <v>5.7098</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3026</v>
+        <v>2.3218</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9183</v>
+        <v>1.975</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6625</v>
+        <v>5.7098</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9644</v>
+        <v>2.8802</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6981</v>
+        <v>2.8296</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9585</v>
+        <v>4.6086</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5782</v>
+        <v>2.4886</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6981</v>
+        <v>2.8296</v>
       </c>
       <c r="K4" t="n">
         <v>134</v>
@@ -621,7 +621,7 @@
         <v>151</v>
       </c>
       <c r="M4" t="n">
-        <v>5.2763</v>
+        <v>5.3182</v>
       </c>
       <c r="N4" t="n">
         <v>285</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3451</v>
+        <v>5.3294</v>
       </c>
       <c r="C5" t="n">
-        <v>2.1735</v>
+        <v>2.1672</v>
       </c>
       <c r="D5" t="n">
-        <v>1.775</v>
+        <v>1.8018</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3451</v>
+        <v>5.3294</v>
       </c>
       <c r="F5" t="n">
-        <v>4.1139</v>
+        <v>3.9991</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2312</v>
+        <v>1.3303</v>
       </c>
       <c r="H5" t="n">
-        <v>9.0085</v>
+        <v>8.3003</v>
       </c>
       <c r="I5" t="n">
-        <v>4.684</v>
+        <v>4.4821</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2312</v>
+        <v>1.3303</v>
       </c>
       <c r="K5" t="n">
         <v>215</v>
@@ -667,7 +667,7 @@
         <v>49</v>
       </c>
       <c r="M5" t="n">
-        <v>5.9152</v>
+        <v>5.8124</v>
       </c>
       <c r="N5" t="n">
         <v>264</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.2066</v>
+        <v>5.1811</v>
       </c>
       <c r="C6" t="n">
-        <v>2.1172</v>
+        <v>2.1068</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7125</v>
+        <v>1.7343</v>
       </c>
       <c r="E6" t="n">
-        <v>5.2066</v>
+        <v>5.1811</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2932</v>
+        <v>3.248</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9134</v>
+        <v>1.9331</v>
       </c>
       <c r="H6" t="n">
-        <v>6.1169</v>
+        <v>5.8223</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1805</v>
+        <v>3.144</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9134</v>
+        <v>1.9331</v>
       </c>
       <c r="K6" t="n">
         <v>134</v>
@@ -713,7 +713,7 @@
         <v>151</v>
       </c>
       <c r="M6" t="n">
-        <v>5.0939</v>
+        <v>5.0771</v>
       </c>
       <c r="N6" t="n">
         <v>285</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.7964</v>
+        <v>4.8438</v>
       </c>
       <c r="C7" t="n">
-        <v>1.9504</v>
+        <v>1.9697</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5273</v>
+        <v>1.5808</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7964</v>
+        <v>4.8438</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2418</v>
+        <v>3.1297</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5546</v>
+        <v>1.7141</v>
       </c>
       <c r="H7" t="n">
-        <v>5.9359</v>
+        <v>5.4318</v>
       </c>
       <c r="I7" t="n">
-        <v>3.0864</v>
+        <v>2.9331</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5546</v>
+        <v>1.7141</v>
       </c>
       <c r="K7" t="n">
         <v>165</v>
@@ -759,7 +759,7 @@
         <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>4.641</v>
+        <v>4.6472</v>
       </c>
       <c r="N7" t="n">
         <v>209</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5222</v>
+        <v>3.2097</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4323</v>
+        <v>1.3052</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.8369</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5222</v>
+        <v>3.2097</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5222</v>
+        <v>3.2097</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3743</v>
+        <v>4.3</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3743</v>
+        <v>4.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3743</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
         <v>180</v>
@@ -814,277 +814,277 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1743</v>
+        <v>2.8814</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2908</v>
+        <v>1.1717</v>
       </c>
       <c r="D9" t="n">
-        <v>0.795</v>
+        <v>0.6875</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1743</v>
+        <v>2.8814</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1743</v>
+        <v>3.0197</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0.1383</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6105</v>
+        <v>5.0688</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6105</v>
+        <v>2.7371</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.1383</v>
       </c>
       <c r="K9" t="n">
-        <v>121</v>
+        <v>165</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6105</v>
+        <v>2.5988</v>
       </c>
       <c r="N9" t="n">
-        <v>121</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9387</v>
+        <v>2.8234</v>
       </c>
       <c r="C10" t="n">
-        <v>1.195</v>
+        <v>1.1481</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6887</v>
+        <v>0.6611</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9387</v>
+        <v>2.8234</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0501</v>
+        <v>2.8234</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1114</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>5.2603</v>
+        <v>3.4547</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7351</v>
+        <v>3.4547</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1114</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="L10" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6237</v>
+        <v>3.4547</v>
       </c>
       <c r="N10" t="n">
-        <v>209</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8325</v>
+        <v>2.7703</v>
       </c>
       <c r="C11" t="n">
-        <v>1.1518</v>
+        <v>1.1265</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6407</v>
+        <v>0.6369</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8325</v>
+        <v>2.7703</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4572</v>
+        <v>1.6452</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3753</v>
+        <v>1.1251</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1712</v>
+        <v>1.6452</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6489</v>
+        <v>0.8884</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3753</v>
+        <v>1.1251</v>
       </c>
       <c r="K11" t="n">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="L11" t="n">
-        <v>49</v>
+        <v>151</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0242</v>
+        <v>2.0135</v>
       </c>
       <c r="N11" t="n">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kyousuke</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.828</v>
+        <v>2.7602</v>
       </c>
       <c r="C12" t="n">
-        <v>1.15</v>
+        <v>1.1224</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6387</v>
+        <v>0.6323</v>
       </c>
       <c r="E12" t="n">
-        <v>2.828</v>
+        <v>2.7602</v>
       </c>
       <c r="F12" t="n">
-        <v>2.338</v>
+        <v>2.3774</v>
       </c>
       <c r="G12" t="n">
-        <v>0.49</v>
+        <v>0.3828</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7512</v>
+        <v>2.9497</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4305</v>
+        <v>1.5928</v>
       </c>
       <c r="J12" t="n">
-        <v>0.49</v>
+        <v>0.3828</v>
       </c>
       <c r="K12" t="n">
-        <v>97</v>
+        <v>215</v>
       </c>
       <c r="L12" t="n">
-        <v>156</v>
+        <v>49</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9205</v>
+        <v>1.9756</v>
       </c>
       <c r="N12" t="n">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>kyousuke</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7959</v>
+        <v>2.7586</v>
       </c>
       <c r="C13" t="n">
-        <v>1.1369</v>
+        <v>1.1218</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6242</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7959</v>
+        <v>2.7586</v>
       </c>
       <c r="F13" t="n">
-        <v>3.3153</v>
+        <v>2.2451</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5194</v>
+        <v>0.5135</v>
       </c>
       <c r="H13" t="n">
-        <v>6.1948</v>
+        <v>2.5132</v>
       </c>
       <c r="I13" t="n">
-        <v>3.221</v>
+        <v>1.3571</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5194</v>
+        <v>0.5135</v>
       </c>
       <c r="K13" t="n">
-        <v>215</v>
+        <v>97</v>
       </c>
       <c r="L13" t="n">
-        <v>49</v>
+        <v>156</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7016</v>
+        <v>1.8706</v>
       </c>
       <c r="N13" t="n">
-        <v>264</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7139</v>
+        <v>2.661</v>
       </c>
       <c r="C14" t="n">
-        <v>1.1036</v>
+        <v>1.0821</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.5871</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7139</v>
+        <v>2.661</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6473</v>
+        <v>3.2082</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0666</v>
+        <v>-0.5472</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6473</v>
+        <v>5.691</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8565</v>
+        <v>3.0731</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0666</v>
+        <v>-0.5472</v>
       </c>
       <c r="K14" t="n">
-        <v>134</v>
+        <v>215</v>
       </c>
       <c r="L14" t="n">
-        <v>151</v>
+        <v>49</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9231</v>
+        <v>2.5259</v>
       </c>
       <c r="N14" t="n">
-        <v>285</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5533</v>
+        <v>2.4834</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0383</v>
+        <v>1.0099</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5147</v>
+        <v>0.5063</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5533</v>
+        <v>2.4834</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3184</v>
+        <v>3.2525</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7651</v>
+        <v>-0.7691</v>
       </c>
       <c r="H15" t="n">
-        <v>6.2057</v>
+        <v>5.8369</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2267</v>
+        <v>3.1519</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7651</v>
+        <v>-0.7691</v>
       </c>
       <c r="K15" t="n">
         <v>165</v>
@@ -1127,7 +1127,7 @@
         <v>44</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4616</v>
+        <v>2.3828</v>
       </c>
       <c r="N15" t="n">
         <v>209</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4521</v>
+        <v>2.3018</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9971</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.469</v>
+        <v>0.4236</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4521</v>
+        <v>2.3018</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4521</v>
+        <v>2.3018</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4521</v>
+        <v>2.313</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4521</v>
+        <v>2.313</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4521</v>
+        <v>2.313</v>
       </c>
       <c r="N16" t="n">
         <v>162</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3657</v>
+        <v>2.2893</v>
       </c>
       <c r="C17" t="n">
-        <v>0.962</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>0.43</v>
+        <v>0.4179</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3657</v>
+        <v>2.2893</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0393</v>
+        <v>2.9736</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6736</v>
+        <v>-0.6843</v>
       </c>
       <c r="H17" t="n">
-        <v>5.2224</v>
+        <v>4.9167</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7154</v>
+        <v>2.655</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6736</v>
+        <v>-0.6843</v>
       </c>
       <c r="K17" t="n">
         <v>215</v>
@@ -1219,7 +1219,7 @@
         <v>49</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0418</v>
+        <v>1.9707</v>
       </c>
       <c r="N17" t="n">
         <v>264</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9713</v>
+        <v>1.9526</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8016</v>
+        <v>0.794</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2519</v>
+        <v>0.2647</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9713</v>
+        <v>1.9526</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9713</v>
+        <v>1.9526</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9713</v>
+        <v>1.9526</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9713</v>
+        <v>1.9526</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9713</v>
+        <v>1.9526</v>
       </c>
       <c r="N18" t="n">
         <v>180</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7689</v>
+        <v>1.6689</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.6786</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1606</v>
+        <v>0.1355</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7689</v>
+        <v>1.6689</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4751</v>
+        <v>2.4028</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7062</v>
+        <v>-0.7339</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2345</v>
+        <v>3.0336</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6818</v>
+        <v>1.6381</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7062</v>
+        <v>-0.7339</v>
       </c>
       <c r="K19" t="n">
         <v>165</v>
@@ -1311,7 +1311,7 @@
         <v>44</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9755999999999999</v>
+        <v>0.9041999999999999</v>
       </c>
       <c r="N19" t="n">
         <v>209</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6756</v>
+        <v>1.6165</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6814</v>
+        <v>0.6573</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1184</v>
+        <v>0.1117</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6756</v>
+        <v>1.6165</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6756</v>
+        <v>1.6165</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6756</v>
+        <v>1.6165</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6756</v>
+        <v>1.6165</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.6756</v>
+        <v>1.6165</v>
       </c>
       <c r="N20" t="n">
         <v>120</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6052</v>
+        <v>1.5319</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.6229</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0867</v>
+        <v>0.0731</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6052</v>
+        <v>1.5319</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6052</v>
+        <v>1.5319</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6052</v>
+        <v>1.5319</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6052</v>
+        <v>1.5319</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.6052</v>
+        <v>1.5319</v>
       </c>
       <c r="N21" t="n">
         <v>180</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3277</v>
+        <v>1.3068</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5399</v>
+        <v>0.5314</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0386</v>
+        <v>-0.0293</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3277</v>
+        <v>1.3068</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4756</v>
+        <v>2.3879</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1479</v>
+        <v>-1.0811</v>
       </c>
       <c r="H22" t="n">
-        <v>3.2361</v>
+        <v>2.9845</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6826</v>
+        <v>1.6116</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1479</v>
+        <v>-1.0811</v>
       </c>
       <c r="K22" t="n">
         <v>97</v>
@@ -1449,7 +1449,7 @@
         <v>156</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5347000000000002</v>
+        <v>0.5305</v>
       </c>
       <c r="N22" t="n">
         <v>253</v>
@@ -1458,139 +1458,139 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kvem</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.2085</v>
+        <v>1.1452</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4914</v>
+        <v>0.4657</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0924</v>
+        <v>-0.1029</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2085</v>
+        <v>1.1452</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2085</v>
+        <v>1.1452</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2085</v>
+        <v>1.1452</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2085</v>
+        <v>1.1452</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2085</v>
+        <v>1.1452</v>
       </c>
       <c r="N23" t="n">
-        <v>162</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1945</v>
+        <v>1.138</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4857</v>
+        <v>0.4628</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0988</v>
+        <v>-0.1062</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1945</v>
+        <v>1.138</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1945</v>
+        <v>1.9774</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.8394</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1945</v>
+        <v>1.9774</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1945</v>
+        <v>1.0678</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.8394</v>
       </c>
       <c r="K24" t="n">
-        <v>121</v>
+        <v>165</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1945</v>
+        <v>0.2284</v>
       </c>
       <c r="N24" t="n">
-        <v>121</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>Kvem</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.1765</v>
+        <v>1.0772</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4784</v>
+        <v>0.438</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1069</v>
+        <v>-0.1338</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1765</v>
+        <v>1.0772</v>
       </c>
       <c r="F25" t="n">
-        <v>1.9944</v>
+        <v>1.0772</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8179</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.9944</v>
+        <v>1.0772</v>
       </c>
       <c r="I25" t="n">
-        <v>1.037</v>
+        <v>1.0772</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8179</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="L25" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2191</v>
+        <v>1.0772</v>
       </c>
       <c r="N25" t="n">
-        <v>209</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8683</v>
+        <v>0.7587</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3531</v>
+        <v>0.3085</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.246</v>
+        <v>-0.2788</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8683</v>
+        <v>0.7587</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8683</v>
+        <v>0.7587</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8683</v>
+        <v>0.7587</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8683</v>
+        <v>0.7587</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8683</v>
+        <v>0.7587</v>
       </c>
       <c r="N26" t="n">
         <v>162</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7558</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3073</v>
+        <v>0.292</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2968</v>
+        <v>-0.2973</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7558</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7558</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7558</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7558</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7558</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>120</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6464</v>
+        <v>0.6273</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2629</v>
+        <v>0.2551</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3462</v>
+        <v>-0.3386</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6464</v>
+        <v>0.6273</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6464</v>
+        <v>0.6273</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6464</v>
+        <v>0.6273</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6464</v>
+        <v>0.6273</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6464</v>
+        <v>0.6273</v>
       </c>
       <c r="N28" t="n">
         <v>121</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4189</v>
+        <v>0.4168</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1703</v>
+        <v>0.1695</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4489</v>
+        <v>-0.4345</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4189</v>
+        <v>0.4168</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4189</v>
+        <v>0.4168</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4189</v>
+        <v>0.4168</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4189</v>
+        <v>0.4168</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4189</v>
+        <v>0.4168</v>
       </c>
       <c r="N29" t="n">
         <v>162</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3534</v>
+        <v>0.3278</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1437</v>
+        <v>0.1333</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4785</v>
+        <v>-0.475</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3534</v>
+        <v>0.3278</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3534</v>
+        <v>0.3278</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3534</v>
+        <v>0.3278</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3534</v>
+        <v>0.3278</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3534</v>
+        <v>0.3278</v>
       </c>
       <c r="N30" t="n">
         <v>120</v>
@@ -1826,47 +1826,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5605</v>
+        <v>-0.1934</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2279</v>
+        <v>-0.0786</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8911</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5605</v>
+        <v>-0.1934</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5605</v>
+        <v>-4.0417</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>3.8483</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5605</v>
+        <v>-4.0417</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5605</v>
+        <v>-2.1825</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>3.8483</v>
       </c>
       <c r="K31" t="n">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5605</v>
+        <v>1.6658</v>
       </c>
       <c r="N31" t="n">
-        <v>180</v>
+        <v>253</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5858</v>
+        <v>-0.5712</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2382</v>
+        <v>-0.2323</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9025</v>
+        <v>-0.8842</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5858</v>
+        <v>-0.5712</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5858</v>
+        <v>-0.5712</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5858</v>
+        <v>-0.5712</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5858</v>
+        <v>-0.5712</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5858</v>
+        <v>-0.5712</v>
       </c>
       <c r="N32" t="n">
         <v>121</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8855</v>
+        <v>-0.5792</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3601</v>
+        <v>-0.2355</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0378</v>
+        <v>-0.8879</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8855</v>
+        <v>-0.5792</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8855</v>
+        <v>-0.5792</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8855</v>
+        <v>-0.5792</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8855</v>
+        <v>-0.5792</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8855</v>
+        <v>-0.5792</v>
       </c>
       <c r="N33" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9453</v>
+        <v>-0.9407</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3844</v>
+        <v>-0.3825</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0648</v>
+        <v>-1.0524</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9453</v>
+        <v>-0.9407</v>
       </c>
       <c r="F34" t="n">
-        <v>-4.4919</v>
+        <v>-0.9407</v>
       </c>
       <c r="G34" t="n">
-        <v>3.5466</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-4.4919</v>
+        <v>-0.9407</v>
       </c>
       <c r="I34" t="n">
-        <v>-2.3356</v>
+        <v>-0.9407</v>
       </c>
       <c r="J34" t="n">
-        <v>3.5466</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="L34" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.211</v>
+        <v>-0.9407</v>
       </c>
       <c r="N34" t="n">
-        <v>253</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9739</v>
+        <v>-0.9915</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.396</v>
+        <v>-0.4032</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0777</v>
+        <v>-1.0756</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9739</v>
+        <v>-0.9915</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9739</v>
+        <v>-0.9915</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9739</v>
+        <v>-0.9915</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9739</v>
+        <v>-0.9915</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9739</v>
+        <v>-0.9915</v>
       </c>
       <c r="N35" t="n">
         <v>121</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>nicx</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0826</v>
+        <v>-1.0103</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4402</v>
+        <v>-0.4108</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1268</v>
+        <v>-1.0841</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0826</v>
+        <v>-1.0103</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.0826</v>
+        <v>-1.0103</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.0826</v>
+        <v>-1.0103</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0826</v>
+        <v>-1.0103</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0826</v>
+        <v>-1.0103</v>
       </c>
       <c r="N36" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>nicx</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1121</v>
+        <v>-1.1397</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4522</v>
+        <v>-0.4634</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1401</v>
+        <v>-1.143</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1121</v>
+        <v>-1.1397</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1121</v>
+        <v>-1.1397</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1121</v>
+        <v>-1.1397</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1121</v>
+        <v>-1.1397</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>162</v>
+        <v>120</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1121</v>
+        <v>-1.1397</v>
       </c>
       <c r="N37" t="n">
-        <v>162</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.9716</v>
+        <v>-1.9452</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.8017</v>
+        <v>-0.791</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.5281</v>
+        <v>-1.5097</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.9716</v>
+        <v>-1.9452</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.9716</v>
+        <v>-1.9452</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.9716</v>
+        <v>-1.9452</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.9716</v>
+        <v>-1.9452</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.9716</v>
+        <v>-1.9452</v>
       </c>
       <c r="N38" t="n">
         <v>180</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.5932</v>
+        <v>-2.3386</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.0545</v>
+        <v>-0.951</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.8087</v>
+        <v>-1.6888</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.5932</v>
+        <v>-2.3386</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.3417</v>
+        <v>-1.1619</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.2515</v>
+        <v>-1.1767</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.3417</v>
+        <v>-1.1619</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6976</v>
+        <v>-0.6274</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.2515</v>
+        <v>-1.1767</v>
       </c>
       <c r="K39" t="n">
         <v>97</v>
@@ -2231,7 +2231,7 @@
         <v>156</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.9491</v>
+        <v>-1.8041</v>
       </c>
       <c r="N39" t="n">
         <v>253</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.4053</v>
+        <v>-3.1019</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.3847</v>
+        <v>-1.2614</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.1753</v>
+        <v>-2.0363</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.4053</v>
+        <v>-3.1019</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.2823</v>
+        <v>-2.0782</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.123</v>
+        <v>-1.0237</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.2823</v>
+        <v>-2.0782</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1867</v>
+        <v>-1.1222</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.123</v>
+        <v>-1.0237</v>
       </c>
       <c r="K40" t="n">
         <v>134</v>
@@ -2277,7 +2277,7 @@
         <v>151</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.3097</v>
+        <v>-2.1459</v>
       </c>
       <c r="N40" t="n">
         <v>285</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-7.2433</v>
+        <v>-6.8138</v>
       </c>
       <c r="C41" t="n">
-        <v>-2.9454</v>
+        <v>-2.7708</v>
       </c>
       <c r="D41" t="n">
-        <v>-3.908</v>
+        <v>-3.726</v>
       </c>
       <c r="E41" t="n">
-        <v>-7.2433</v>
+        <v>-6.8138</v>
       </c>
       <c r="F41" t="n">
-        <v>-6.7366</v>
+        <v>-6.2803</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5067</v>
+        <v>-0.5335</v>
       </c>
       <c r="H41" t="n">
-        <v>-6.7366</v>
+        <v>-6.2803</v>
       </c>
       <c r="I41" t="n">
-        <v>-3.5027</v>
+        <v>-3.3913</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.5067</v>
+        <v>-0.5335</v>
       </c>
       <c r="K41" t="n">
         <v>215</v>
@@ -2323,7 +2323,7 @@
         <v>49</v>
       </c>
       <c r="M41" t="n">
-        <v>-4.0094</v>
+        <v>-3.9248</v>
       </c>
       <c r="N41" t="n">
         <v>264</v>
@@ -2429,10 +2429,10 @@
         <v>1.38</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6216</v>
+        <v>0.5986</v>
       </c>
       <c r="J2" t="n">
-        <v>9.945600000000001</v>
+        <v>9.5776</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.12</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2483</v>
+        <v>0.2496</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9728</v>
+        <v>3.9936</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0492</v>
+        <v>0.049</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7872</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.65</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3696</v>
+        <v>-0.3824</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.9136</v>
+        <v>-6.1184</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.27</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7128</v>
+        <v>-0.705</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.4048</v>
+        <v>-11.28</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>2.54</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3406</v>
+        <v>1.4946</v>
       </c>
       <c r="J7" t="n">
-        <v>21.4496</v>
+        <v>23.9136</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>2.25</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1832</v>
+        <v>1.2611</v>
       </c>
       <c r="J8" t="n">
-        <v>18.9312</v>
+        <v>20.1776</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.12</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1501</v>
+        <v>0.1755</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4016</v>
+        <v>2.808</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.82</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2608</v>
+        <v>-0.2654</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.1728</v>
+        <v>-4.2464</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.6</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4637</v>
+        <v>-0.4645</v>
       </c>
       <c r="J11" t="n">
-        <v>-7.4192</v>
+        <v>-7.432</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>2.21</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8681</v>
+        <v>1.8453</v>
       </c>
       <c r="J12" t="n">
-        <v>41.0982</v>
+        <v>40.5966</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1386</v>
+        <v>0.1512</v>
       </c>
       <c r="J13" t="n">
-        <v>3.0492</v>
+        <v>3.3264</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.86</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4959</v>
+        <v>-0.4686</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.9098</v>
+        <v>-10.3092</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.85</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5232</v>
+        <v>-0.4932</v>
       </c>
       <c r="J15" t="n">
-        <v>-11.5104</v>
+        <v>-10.8504</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.65</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.027</v>
+        <v>-0.9367</v>
       </c>
       <c r="J16" t="n">
-        <v>-22.594</v>
+        <v>-20.6074</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.45</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8475</v>
+        <v>0.8081</v>
       </c>
       <c r="J17" t="n">
-        <v>18.645</v>
+        <v>17.7782</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3497</v>
+        <v>0.3537</v>
       </c>
       <c r="J18" t="n">
-        <v>7.6934</v>
+        <v>7.7814</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.99</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0253</v>
+        <v>-0.0289</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5566</v>
+        <v>-0.6358</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0687</v>
+        <v>-0.0767</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5114</v>
+        <v>-1.6874</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.71</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3326</v>
+        <v>-0.3431</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.3172</v>
+        <v>-7.5482</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0182</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>34.6188</v>
+        <v>32.6128</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9635</v>
+        <v>0.8992</v>
       </c>
       <c r="J23" t="n">
-        <v>32.759</v>
+        <v>30.5728</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.09</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2958</v>
+        <v>0.2988</v>
       </c>
       <c r="J24" t="n">
-        <v>10.0572</v>
+        <v>10.1592</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.86</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4899</v>
+        <v>-0.4644</v>
       </c>
       <c r="J25" t="n">
-        <v>-16.6566</v>
+        <v>-15.7896</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6498</v>
+        <v>-0.6075</v>
       </c>
       <c r="J26" t="n">
-        <v>-22.0932</v>
+        <v>-20.655</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.19</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4038</v>
+        <v>0.4046</v>
       </c>
       <c r="J27" t="n">
-        <v>13.7292</v>
+        <v>13.7564</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.12</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2731</v>
+        <v>0.2812</v>
       </c>
       <c r="J28" t="n">
-        <v>9.285399999999999</v>
+        <v>9.5608</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.09</v>
       </c>
       <c r="I29" t="n">
-        <v>0.214</v>
+        <v>0.2242</v>
       </c>
       <c r="J29" t="n">
-        <v>7.276</v>
+        <v>7.6228</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1731</v>
+        <v>0.1841</v>
       </c>
       <c r="J30" t="n">
-        <v>5.8854</v>
+        <v>6.2594</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2254</v>
+        <v>-0.2375</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.6636</v>
+        <v>-8.074999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.32</v>
       </c>
       <c r="I32" t="n">
-        <v>0.852</v>
+        <v>0.802</v>
       </c>
       <c r="J32" t="n">
-        <v>29.82</v>
+        <v>28.07</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.25</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6876</v>
+        <v>0.6574</v>
       </c>
       <c r="J33" t="n">
-        <v>24.066</v>
+        <v>23.009</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5671</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>19.8485</v>
+        <v>19.2465</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.03</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0945</v>
+        <v>0.1111</v>
       </c>
       <c r="J35" t="n">
-        <v>3.3075</v>
+        <v>3.8885</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0384</v>
+        <v>-0.0265</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.344</v>
+        <v>-0.9275</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.32</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.6399</v>
       </c>
       <c r="J37" t="n">
-        <v>23.338</v>
+        <v>22.3965</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.16</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3753</v>
+        <v>0.3724</v>
       </c>
       <c r="J38" t="n">
-        <v>13.1355</v>
+        <v>13.034</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.97</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0475</v>
+        <v>-0.0563</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.6625</v>
+        <v>-1.9705</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.74</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2937</v>
+        <v>-0.3071</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.2795</v>
+        <v>-10.7485</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.63</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3977</v>
+        <v>-0.4077</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.9195</v>
+        <v>-14.2695</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.63</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0598</v>
+        <v>1.1568</v>
       </c>
       <c r="J42" t="n">
-        <v>30.7342</v>
+        <v>33.5472</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.24</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5364</v>
+        <v>0.5917</v>
       </c>
       <c r="J43" t="n">
-        <v>15.5556</v>
+        <v>17.1593</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.21</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4929</v>
+        <v>0.5433</v>
       </c>
       <c r="J44" t="n">
-        <v>14.2941</v>
+        <v>15.7557</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.78</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.705</v>
+        <v>-0.6558</v>
       </c>
       <c r="J45" t="n">
-        <v>-20.445</v>
+        <v>-19.0182</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.71</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.88</v>
+        <v>-0.8094</v>
       </c>
       <c r="J46" t="n">
-        <v>-25.52</v>
+        <v>-23.4726</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.14</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3391</v>
+        <v>0.3423</v>
       </c>
       <c r="J47" t="n">
-        <v>9.8339</v>
+        <v>9.9267</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.08</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2216</v>
+        <v>0.2245</v>
       </c>
       <c r="J48" t="n">
-        <v>6.4264</v>
+        <v>6.5105</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.95</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0709</v>
+        <v>-0.0823</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.0561</v>
+        <v>-2.3867</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.85</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1807</v>
+        <v>-0.1959</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.2403</v>
+        <v>-5.6811</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.67</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3573</v>
+        <v>-0.3694</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.3617</v>
+        <v>-10.7126</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.47</v>
       </c>
       <c r="I52" t="n">
-        <v>0.837</v>
+        <v>0.9224</v>
       </c>
       <c r="J52" t="n">
-        <v>16.74</v>
+        <v>18.448</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.42</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7715</v>
+        <v>0.8518</v>
       </c>
       <c r="J53" t="n">
-        <v>15.43</v>
+        <v>17.036</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.02</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0554</v>
+        <v>0.0733</v>
       </c>
       <c r="J54" t="n">
-        <v>1.108</v>
+        <v>1.466</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.02</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0554</v>
+        <v>0.0733</v>
       </c>
       <c r="J55" t="n">
-        <v>1.108</v>
+        <v>1.466</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.91</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3661</v>
+        <v>-0.3475</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.322</v>
+        <v>-6.95</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.68</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8921</v>
+        <v>0.988</v>
       </c>
       <c r="J57" t="n">
-        <v>17.842</v>
+        <v>19.76</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.05</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1537</v>
+        <v>0.1583</v>
       </c>
       <c r="J58" t="n">
-        <v>3.074</v>
+        <v>3.166</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.88</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1494</v>
+        <v>-0.1641</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.988</v>
+        <v>-3.282</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3387</v>
+        <v>-0.3513</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.774</v>
+        <v>-7.026</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.4</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6027</v>
+        <v>-0.602</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.054</v>
+        <v>-12.04</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.18</v>
       </c>
       <c r="I62" t="n">
-        <v>1.6173</v>
+        <v>1.7538</v>
       </c>
       <c r="J62" t="n">
-        <v>25.8768</v>
+        <v>28.0608</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.8</v>
       </c>
       <c r="I63" t="n">
-        <v>1.1861</v>
+        <v>1.3038</v>
       </c>
       <c r="J63" t="n">
-        <v>18.9776</v>
+        <v>20.8608</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.25</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5152</v>
+        <v>0.577</v>
       </c>
       <c r="J64" t="n">
-        <v>8.2432</v>
+        <v>9.231999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.9</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4475</v>
+        <v>-0.4111</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.16</v>
+        <v>-6.5776</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.85</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5859</v>
+        <v>-0.5374</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.3744</v>
+        <v>-8.5984</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.49</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7762</v>
+        <v>0.8494</v>
       </c>
       <c r="J67" t="n">
-        <v>12.4192</v>
+        <v>13.5904</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.98</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0037</v>
+        <v>-0.0177</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.0592</v>
+        <v>-0.2832</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.67</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3366</v>
+        <v>-0.3532</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.3856</v>
+        <v>-5.6512</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.51</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.486</v>
+        <v>-0.4952</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.776</v>
+        <v>-7.9232</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.27</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.705</v>
+        <v>-0.6989</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.28</v>
+        <v>-11.1824</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>2.05</v>
       </c>
       <c r="I72" t="n">
-        <v>1.5221</v>
+        <v>1.6477</v>
       </c>
       <c r="J72" t="n">
-        <v>42.6188</v>
+        <v>46.1356</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.2</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4629</v>
+        <v>0.5137</v>
       </c>
       <c r="J73" t="n">
-        <v>12.9612</v>
+        <v>14.3836</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.15</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3889</v>
+        <v>0.4252</v>
       </c>
       <c r="J74" t="n">
-        <v>10.8892</v>
+        <v>11.9056</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.06</v>
+        <v>-0.0415</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.68</v>
+        <v>-1.162</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.83</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6075</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>-17.01</v>
+        <v>-15.764</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.57</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7784</v>
+        <v>0.8647</v>
       </c>
       <c r="J77" t="n">
-        <v>21.7952</v>
+        <v>24.2116</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.96</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.0601</v>
+        <v>-0.0702</v>
       </c>
       <c r="J78" t="n">
-        <v>-1.6828</v>
+        <v>-1.9656</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.92</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1077</v>
+        <v>-0.1206</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.0156</v>
+        <v>-3.3768</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.7</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3319</v>
+        <v>-0.3442</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.293200000000001</v>
+        <v>-9.637600000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.66</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3696</v>
+        <v>-0.3807</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.3488</v>
+        <v>-10.6596</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.32</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4268</v>
+        <v>0.4387</v>
       </c>
       <c r="J82" t="n">
-        <v>10.2432</v>
+        <v>10.5288</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.31</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4152</v>
+        <v>0.4276</v>
       </c>
       <c r="J83" t="n">
-        <v>9.9648</v>
+        <v>10.2624</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.23</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3204</v>
+        <v>0.3364</v>
       </c>
       <c r="J84" t="n">
-        <v>7.6896</v>
+        <v>8.073600000000001</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.03</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0463</v>
+        <v>0.06</v>
       </c>
       <c r="J85" t="n">
-        <v>1.1112</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.96</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.0806</v>
+        <v>-0.0859</v>
       </c>
       <c r="J86" t="n">
-        <v>-1.9344</v>
+        <v>-2.0616</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.07</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1923</v>
+        <v>0.1889</v>
       </c>
       <c r="J87" t="n">
-        <v>4.6152</v>
+        <v>4.5336</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.85</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1669</v>
+        <v>-0.1853</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.0056</v>
+        <v>-4.4472</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.78</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2349</v>
+        <v>-0.2535</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.6376</v>
+        <v>-6.084</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.67</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3398</v>
+        <v>-0.3557</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.155200000000001</v>
+        <v>-8.536799999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.66</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3493</v>
+        <v>-0.3648</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.3832</v>
+        <v>-8.7552</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.33</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6723</v>
+        <v>0.6468</v>
       </c>
       <c r="J92" t="n">
-        <v>23.5305</v>
+        <v>22.638</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.24</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5141</v>
+        <v>0.5028</v>
       </c>
       <c r="J93" t="n">
-        <v>17.9935</v>
+        <v>17.598</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.13</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3085</v>
+        <v>0.3112</v>
       </c>
       <c r="J94" t="n">
-        <v>10.7975</v>
+        <v>10.892</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.67</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3636</v>
+        <v>-0.3743</v>
       </c>
       <c r="J95" t="n">
-        <v>-12.726</v>
+        <v>-13.1005</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.59</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4375</v>
+        <v>-0.4453</v>
       </c>
       <c r="J96" t="n">
-        <v>-15.3125</v>
+        <v>-15.5855</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.41</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0378</v>
+        <v>0.9823</v>
       </c>
       <c r="J97" t="n">
-        <v>36.323</v>
+        <v>34.3805</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.33</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8831</v>
+        <v>0.8277</v>
       </c>
       <c r="J98" t="n">
-        <v>30.9085</v>
+        <v>28.9695</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.24</v>
       </c>
       <c r="I99" t="n">
-        <v>0.67</v>
+        <v>0.6405</v>
       </c>
       <c r="J99" t="n">
-        <v>23.45</v>
+        <v>22.4175</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.04</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1346</v>
+        <v>0.1485</v>
       </c>
       <c r="J100" t="n">
-        <v>4.711</v>
+        <v>5.1975</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.67</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.9829</v>
+        <v>-0.8979</v>
       </c>
       <c r="J101" t="n">
-        <v>-34.4015</v>
+        <v>-31.4265</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6405</v>
+        <v>0.6146</v>
       </c>
       <c r="J102" t="n">
-        <v>18.5745</v>
+        <v>17.8234</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.11</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2828</v>
+        <v>0.2837</v>
       </c>
       <c r="J103" t="n">
-        <v>8.2012</v>
+        <v>8.2273</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.93</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.0946</v>
+        <v>-0.1073</v>
       </c>
       <c r="J104" t="n">
-        <v>-2.7434</v>
+        <v>-3.1117</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.83</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.202</v>
+        <v>-0.217</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.858</v>
+        <v>-6.293</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.55</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4689</v>
+        <v>-0.4759</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.5981</v>
+        <v>-13.8011</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>1.3105</v>
+        <v>1.2815</v>
       </c>
       <c r="J107" t="n">
-        <v>38.0045</v>
+        <v>37.1635</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.16</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4715</v>
+        <v>0.4627</v>
       </c>
       <c r="J108" t="n">
-        <v>13.6735</v>
+        <v>13.4183</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.09</v>
       </c>
       <c r="I109" t="n">
-        <v>0.287</v>
+        <v>0.2928</v>
       </c>
       <c r="J109" t="n">
-        <v>8.323</v>
+        <v>8.491199999999999</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.03</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0985</v>
+        <v>0.1139</v>
       </c>
       <c r="J110" t="n">
-        <v>2.8565</v>
+        <v>3.3031</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.82</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6091</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="J111" t="n">
-        <v>-17.6639</v>
+        <v>-16.5039</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.06</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2358</v>
+        <v>0.2243</v>
       </c>
       <c r="J112" t="n">
-        <v>4.0086</v>
+        <v>3.8131</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.9</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1094</v>
+        <v>-0.1278</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.8598</v>
+        <v>-2.1726</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.88</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.132</v>
+        <v>-0.1508</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.244</v>
+        <v>-2.5636</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.66</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3469</v>
+        <v>-0.3629</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.8973</v>
+        <v>-6.1693</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.45</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.542</v>
+        <v>-0.5476</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.214</v>
+        <v>-9.309200000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.51</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1274</v>
+        <v>1.0943</v>
       </c>
       <c r="J117" t="n">
-        <v>19.1658</v>
+        <v>18.6031</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.46</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0654</v>
+        <v>1.0244</v>
       </c>
       <c r="J118" t="n">
-        <v>18.1118</v>
+        <v>17.4148</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.41</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9936</v>
+        <v>0.9424</v>
       </c>
       <c r="J119" t="n">
-        <v>16.8912</v>
+        <v>16.0208</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.18</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4857</v>
+        <v>0.4836</v>
       </c>
       <c r="J120" t="n">
-        <v>8.2569</v>
+        <v>8.2212</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.08</v>
       </c>
       <c r="I121" t="n">
-        <v>0.2146</v>
+        <v>0.2356</v>
       </c>
       <c r="J121" t="n">
-        <v>3.6482</v>
+        <v>4.0052</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5848</v>
+        <v>0.555</v>
       </c>
       <c r="J122" t="n">
-        <v>11.696</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.15</v>
       </c>
       <c r="I123" t="n">
-        <v>0.408</v>
+        <v>0.3925</v>
       </c>
       <c r="J123" t="n">
-        <v>8.16</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3254</v>
+        <v>-0.3409</v>
       </c>
       <c r="J124" t="n">
-        <v>-6.508</v>
+        <v>-6.818</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.65</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3632</v>
+        <v>-0.3773</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.264</v>
+        <v>-7.546</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.46</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5387</v>
+        <v>-0.5436</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.774</v>
+        <v>-10.872</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.35</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8996</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="J127" t="n">
-        <v>17.992</v>
+        <v>16.946</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.33</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8547</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="J128" t="n">
-        <v>17.094</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.22</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6036</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="J129" t="n">
-        <v>12.072</v>
+        <v>11.704</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.16</v>
       </c>
       <c r="I130" t="n">
-        <v>0.4573</v>
+        <v>0.4531</v>
       </c>
       <c r="J130" t="n">
-        <v>9.146000000000001</v>
+        <v>9.061999999999999</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.07</v>
       </c>
       <c r="I131" t="n">
-        <v>0.2086</v>
+        <v>0.2243</v>
       </c>
       <c r="J131" t="n">
-        <v>4.172</v>
+        <v>4.486</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.1</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3313</v>
+        <v>0.3298</v>
       </c>
       <c r="J132" t="n">
-        <v>7.9512</v>
+        <v>7.9152</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.1</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3313</v>
+        <v>0.3298</v>
       </c>
       <c r="J133" t="n">
-        <v>7.9512</v>
+        <v>7.9152</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3313</v>
+        <v>0.3298</v>
       </c>
       <c r="J134" t="n">
-        <v>7.9512</v>
+        <v>7.9152</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2155</v>
+        <v>0.2212</v>
       </c>
       <c r="J135" t="n">
-        <v>5.172</v>
+        <v>5.3088</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.93</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2761</v>
+        <v>-0.2707</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.6264</v>
+        <v>-6.4968</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.32</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6574</v>
+        <v>0.633</v>
       </c>
       <c r="J137" t="n">
-        <v>15.7776</v>
+        <v>15.192</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.19</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4248</v>
+        <v>0.4199</v>
       </c>
       <c r="J138" t="n">
-        <v>10.1952</v>
+        <v>10.0776</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0016</v>
+        <v>0.0011</v>
       </c>
       <c r="J139" t="n">
-        <v>0.0384</v>
+        <v>0.0264</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.75</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2867</v>
+        <v>-0.2997</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.8808</v>
+        <v>-7.1928</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.67</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3629</v>
+        <v>-0.3738</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.7096</v>
+        <v>-8.9712</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.36</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5413</v>
+        <v>0.5335</v>
       </c>
       <c r="J142" t="n">
-        <v>15.6977</v>
+        <v>15.4715</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.09</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1674</v>
+        <v>0.1783</v>
       </c>
       <c r="J143" t="n">
-        <v>4.8546</v>
+        <v>5.1707</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.07</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1356</v>
+        <v>0.1465</v>
       </c>
       <c r="J144" t="n">
-        <v>3.9324</v>
+        <v>4.2485</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0915</v>
+        <v>-0.1016</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.6535</v>
+        <v>-2.9464</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.7</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3398</v>
+        <v>-0.3504</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.854200000000001</v>
+        <v>-10.1616</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.31</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4352</v>
+        <v>0.4429</v>
       </c>
       <c r="J147" t="n">
-        <v>12.6208</v>
+        <v>12.8441</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.23</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3369</v>
+        <v>0.3488</v>
       </c>
       <c r="J148" t="n">
-        <v>9.770099999999999</v>
+        <v>10.1152</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.03</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0591</v>
+        <v>0.0697</v>
       </c>
       <c r="J149" t="n">
-        <v>1.7139</v>
+        <v>2.0213</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.98</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0422</v>
+        <v>-0.0475</v>
       </c>
       <c r="J150" t="n">
-        <v>-1.2238</v>
+        <v>-1.3775</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.78</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2663</v>
+        <v>-0.2779</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.7227</v>
+        <v>-8.059100000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.47</v>
       </c>
       <c r="I152" t="n">
-        <v>1.1092</v>
+        <v>1.0681</v>
       </c>
       <c r="J152" t="n">
-        <v>19.9656</v>
+        <v>19.2258</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.22</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6123</v>
+        <v>0.5911</v>
       </c>
       <c r="J153" t="n">
-        <v>11.0214</v>
+        <v>10.6398</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.15</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4422</v>
+        <v>0.4371</v>
       </c>
       <c r="J154" t="n">
-        <v>7.9596</v>
+        <v>7.8678</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.07</v>
       </c>
       <c r="I155" t="n">
-        <v>0.2212</v>
+        <v>0.233</v>
       </c>
       <c r="J155" t="n">
-        <v>3.9816</v>
+        <v>4.194</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.96</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2104</v>
+        <v>-0.2007</v>
       </c>
       <c r="J156" t="n">
-        <v>-3.7872</v>
+        <v>-3.6126</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.31</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6768</v>
+        <v>0.6444</v>
       </c>
       <c r="J157" t="n">
-        <v>12.1824</v>
+        <v>11.5992</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.96</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0548</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.9864000000000001</v>
+        <v>-1.1898</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.87</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1563</v>
+        <v>-0.172</v>
       </c>
       <c r="J159" t="n">
-        <v>-2.8134</v>
+        <v>-3.096</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.75</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2768</v>
+        <v>-0.292</v>
       </c>
       <c r="J160" t="n">
-        <v>-4.9824</v>
+        <v>-5.256</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.64</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3816</v>
+        <v>-0.3934</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.8688</v>
+        <v>-7.0812</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.58</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2393</v>
+        <v>1.2095</v>
       </c>
       <c r="J162" t="n">
-        <v>24.786</v>
+        <v>24.19</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.56</v>
       </c>
       <c r="I163" t="n">
-        <v>1.2141</v>
+        <v>1.1827</v>
       </c>
       <c r="J163" t="n">
-        <v>24.282</v>
+        <v>23.654</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.22</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6048</v>
+        <v>0.586</v>
       </c>
       <c r="J164" t="n">
-        <v>12.096</v>
+        <v>11.72</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.02</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0439</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="J165" t="n">
-        <v>0.878</v>
+        <v>1.304</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.9517</v>
+        <v>-0.8681</v>
       </c>
       <c r="J166" t="n">
-        <v>-19.034</v>
+        <v>-17.362</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.43</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9009</v>
+        <v>0.8429</v>
       </c>
       <c r="J167" t="n">
-        <v>18.018</v>
+        <v>16.858</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.97</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0382</v>
+        <v>-0.0492</v>
       </c>
       <c r="J168" t="n">
-        <v>-0.764</v>
+        <v>-0.984</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.77</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2545</v>
+        <v>-0.2706</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.09</v>
+        <v>-5.412</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.65</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3694</v>
+        <v>-0.3822</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.388</v>
+        <v>-7.644</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.6</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.416</v>
+        <v>-0.4268</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.32</v>
+        <v>-8.536</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.42</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6204</v>
+        <v>0.6057</v>
       </c>
       <c r="J172" t="n">
-        <v>13.6488</v>
+        <v>13.3254</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.17</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2877</v>
+        <v>0.2951</v>
       </c>
       <c r="J173" t="n">
-        <v>6.3294</v>
+        <v>6.4922</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.9</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1369</v>
+        <v>-0.149</v>
       </c>
       <c r="J174" t="n">
-        <v>-3.0118</v>
+        <v>-3.278</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1588</v>
+        <v>-0.1714</v>
       </c>
       <c r="J175" t="n">
-        <v>-3.4936</v>
+        <v>-3.7708</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.75</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.291</v>
+        <v>-0.3031</v>
       </c>
       <c r="J176" t="n">
-        <v>-6.402</v>
+        <v>-6.6682</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.45</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.581</v>
       </c>
       <c r="J177" t="n">
-        <v>12.7182</v>
+        <v>12.782</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.39</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5103</v>
+        <v>0.5173</v>
       </c>
       <c r="J178" t="n">
-        <v>11.2266</v>
+        <v>11.3806</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.17</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2487</v>
+        <v>0.2656</v>
       </c>
       <c r="J179" t="n">
-        <v>5.4714</v>
+        <v>5.8432</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.1</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1574</v>
+        <v>0.1742</v>
       </c>
       <c r="J180" t="n">
-        <v>3.4628</v>
+        <v>3.8324</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.66</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3888</v>
+        <v>-0.3959</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.553599999999999</v>
+        <v>-8.7098</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.69</v>
       </c>
       <c r="I182" t="n">
-        <v>1.4024</v>
+        <v>1.378</v>
       </c>
       <c r="J182" t="n">
-        <v>32.2552</v>
+        <v>31.694</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.15</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4481</v>
+        <v>0.441</v>
       </c>
       <c r="J183" t="n">
-        <v>10.3063</v>
+        <v>10.143</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3975</v>
+        <v>0.3945</v>
       </c>
       <c r="J184" t="n">
-        <v>9.1425</v>
+        <v>9.073499999999999</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.09</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2892</v>
+        <v>0.2943</v>
       </c>
       <c r="J185" t="n">
-        <v>6.6516</v>
+        <v>6.7689</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.61</v>
       </c>
       <c r="I186" t="n">
-        <v>-1.1244</v>
+        <v>-1.0202</v>
       </c>
       <c r="J186" t="n">
-        <v>-25.8612</v>
+        <v>-23.4646</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.43</v>
       </c>
       <c r="I187" t="n">
-        <v>0.8307</v>
+        <v>0.7907</v>
       </c>
       <c r="J187" t="n">
-        <v>19.1061</v>
+        <v>18.1861</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.18</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3969</v>
+        <v>0.3958</v>
       </c>
       <c r="J188" t="n">
-        <v>9.1287</v>
+        <v>9.103400000000001</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.14</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3214</v>
+        <v>0.3249</v>
       </c>
       <c r="J189" t="n">
-        <v>7.3922</v>
+        <v>7.4727</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.79</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2508</v>
+        <v>-0.2637</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.7684</v>
+        <v>-6.0651</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.54</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4851</v>
+        <v>-0.4902</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.1573</v>
+        <v>-11.2746</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.23</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4855</v>
+        <v>0.4784</v>
       </c>
       <c r="J192" t="n">
-        <v>11.652</v>
+        <v>11.4816</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.17</v>
       </c>
       <c r="I193" t="n">
-        <v>0.376</v>
+        <v>0.3768</v>
       </c>
       <c r="J193" t="n">
-        <v>9.023999999999999</v>
+        <v>9.043200000000001</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.03</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0883</v>
+        <v>0.0975</v>
       </c>
       <c r="J194" t="n">
-        <v>2.1192</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.92</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1142</v>
+        <v>-0.1256</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.7408</v>
+        <v>-3.0144</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.77</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2715</v>
+        <v>-0.2839</v>
       </c>
       <c r="J196" t="n">
-        <v>-6.516</v>
+        <v>-6.8136</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.43</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0764</v>
+        <v>1.0264</v>
       </c>
       <c r="J197" t="n">
-        <v>25.8336</v>
+        <v>24.6336</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.2</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5831</v>
+        <v>0.5609</v>
       </c>
       <c r="J198" t="n">
-        <v>13.9944</v>
+        <v>13.4616</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.11</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3498</v>
+        <v>0.3492</v>
       </c>
       <c r="J199" t="n">
-        <v>8.395200000000001</v>
+        <v>8.380800000000001</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.93</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2877</v>
+        <v>-0.2787</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.9048</v>
+        <v>-6.6888</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.83</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.571</v>
+        <v>-0.5373</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.704</v>
+        <v>-12.8952</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.44</v>
       </c>
       <c r="I202" t="n">
-        <v>0.8257</v>
+        <v>0.7895</v>
       </c>
       <c r="J202" t="n">
-        <v>18.9911</v>
+        <v>18.1585</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.24</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4902</v>
+        <v>0.4853</v>
       </c>
       <c r="J203" t="n">
-        <v>11.2746</v>
+        <v>11.1619</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.03</v>
       </c>
       <c r="I204" t="n">
-        <v>0.0827</v>
+        <v>0.0935</v>
       </c>
       <c r="J204" t="n">
-        <v>1.9021</v>
+        <v>2.1505</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.9</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1417</v>
+        <v>-0.1528</v>
       </c>
       <c r="J205" t="n">
-        <v>-3.2591</v>
+        <v>-3.5144</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.73</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.315</v>
+        <v>-0.3257</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.245</v>
+        <v>-7.4911</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.86</v>
       </c>
       <c r="I207" t="n">
-        <v>1.6088</v>
+        <v>1.5949</v>
       </c>
       <c r="J207" t="n">
-        <v>37.0024</v>
+        <v>36.6827</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.27</v>
       </c>
       <c r="I208" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7023</v>
       </c>
       <c r="J208" t="n">
-        <v>17.0062</v>
+        <v>16.1529</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.96</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2031</v>
+        <v>-0.1956</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.6713</v>
+        <v>-4.4988</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.91</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3604</v>
+        <v>-0.3434</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.289199999999999</v>
+        <v>-7.8982</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.73</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.8387</v>
+        <v>-0.772</v>
       </c>
       <c r="J211" t="n">
-        <v>-19.2901</v>
+        <v>-17.756</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.3</v>
       </c>
       <c r="I212" t="n">
-        <v>0.676</v>
+        <v>0.6409</v>
       </c>
       <c r="J212" t="n">
-        <v>12.844</v>
+        <v>12.1771</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.88</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1433</v>
+        <v>-0.1595</v>
       </c>
       <c r="J213" t="n">
-        <v>-2.7227</v>
+        <v>-3.0305</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.78</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2434</v>
+        <v>-0.26</v>
       </c>
       <c r="J214" t="n">
-        <v>-4.6246</v>
+        <v>-4.94</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.76</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2629</v>
+        <v>-0.2792</v>
       </c>
       <c r="J215" t="n">
-        <v>-4.9951</v>
+        <v>-5.3048</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.65</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3681</v>
+        <v>-0.3812</v>
       </c>
       <c r="J216" t="n">
-        <v>-6.9939</v>
+        <v>-7.2428</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.88</v>
       </c>
       <c r="I217" t="n">
-        <v>1.5826</v>
+        <v>1.5751</v>
       </c>
       <c r="J217" t="n">
-        <v>30.0694</v>
+        <v>29.9269</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.55</v>
       </c>
       <c r="I218" t="n">
-        <v>1.1849</v>
+        <v>1.1545</v>
       </c>
       <c r="J218" t="n">
-        <v>22.5131</v>
+        <v>21.9355</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.07</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1943</v>
+        <v>0.2143</v>
       </c>
       <c r="J219" t="n">
-        <v>3.6917</v>
+        <v>4.0717</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.03</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0636</v>
+        <v>0.0896</v>
       </c>
       <c r="J220" t="n">
-        <v>1.2084</v>
+        <v>1.7024</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.9</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.424</v>
+        <v>-0.3945</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.055999999999999</v>
+        <v>-7.4955</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.24</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5384</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="J222" t="n">
-        <v>12.3832</v>
+        <v>11.9761</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.03</v>
       </c>
       <c r="I223" t="n">
-        <v>0.1076</v>
+        <v>0.1114</v>
       </c>
       <c r="J223" t="n">
-        <v>2.4748</v>
+        <v>2.5622</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.98</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.03</v>
+        <v>-0.0382</v>
       </c>
       <c r="J224" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.8786</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.75</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2799</v>
+        <v>-0.2944</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.4377</v>
+        <v>-6.7712</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.65</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3751</v>
+        <v>-0.3867</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.6273</v>
+        <v>-8.8941</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.6</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2916</v>
+        <v>1.2603</v>
       </c>
       <c r="J227" t="n">
-        <v>29.7068</v>
+        <v>28.9869</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.23</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6499</v>
+        <v>0.6219</v>
       </c>
       <c r="J228" t="n">
-        <v>14.9477</v>
+        <v>14.3037</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0291</v>
+        <v>-0.02</v>
       </c>
       <c r="J229" t="n">
-        <v>-0.6693</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.97</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1623</v>
+        <v>-0.1578</v>
       </c>
       <c r="J230" t="n">
-        <v>-3.7329</v>
+        <v>-3.6294</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.82</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6039</v>
+        <v>-0.5655</v>
       </c>
       <c r="J231" t="n">
-        <v>-13.8897</v>
+        <v>-13.0065</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.81</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4544</v>
+        <v>1.4482</v>
       </c>
       <c r="J232" t="n">
-        <v>21.816</v>
+        <v>21.723</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.69</v>
       </c>
       <c r="I233" t="n">
-        <v>1.3169</v>
+        <v>1.3024</v>
       </c>
       <c r="J233" t="n">
-        <v>19.7535</v>
+        <v>19.536</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.45</v>
       </c>
       <c r="I234" t="n">
-        <v>1.0357</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="J234" t="n">
-        <v>15.5355</v>
+        <v>14.901</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.29</v>
       </c>
       <c r="I235" t="n">
-        <v>0.7177</v>
+        <v>0.6965</v>
       </c>
       <c r="J235" t="n">
-        <v>10.7655</v>
+        <v>10.4475</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.15</v>
       </c>
       <c r="I236" t="n">
-        <v>0.3764</v>
+        <v>0.3914</v>
       </c>
       <c r="J236" t="n">
-        <v>5.646</v>
+        <v>5.871</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.26</v>
       </c>
       <c r="I237" t="n">
-        <v>0.6539</v>
+        <v>0.6125</v>
       </c>
       <c r="J237" t="n">
-        <v>9.8085</v>
+        <v>9.1875</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.18</v>
       </c>
       <c r="I238" t="n">
-        <v>0.4961</v>
+        <v>0.4689</v>
       </c>
       <c r="J238" t="n">
-        <v>7.4415</v>
+        <v>7.0335</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.6</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4033</v>
+        <v>-0.4168</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.0495</v>
+        <v>-6.252</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.51</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4869</v>
+        <v>-0.4958</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.3035</v>
+        <v>-7.437</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.4</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5877</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.8155</v>
+        <v>-8.853</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.11</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2709</v>
+        <v>0.2633</v>
       </c>
       <c r="J242" t="n">
-        <v>4.6053</v>
+        <v>4.4761</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.97</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0183</v>
+        <v>-0.0337</v>
       </c>
       <c r="J243" t="n">
-        <v>-0.3111</v>
+        <v>-0.5729</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.86</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1525</v>
+        <v>-0.1718</v>
       </c>
       <c r="J244" t="n">
-        <v>-2.5925</v>
+        <v>-2.9206</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.51</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4858</v>
+        <v>-0.495</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.258599999999999</v>
+        <v>-8.414999999999999</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.46</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5318000000000001</v>
+        <v>-0.5382</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.0406</v>
+        <v>-9.1494</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.82</v>
       </c>
       <c r="I247" t="n">
-        <v>0.905</v>
+        <v>0.8928</v>
       </c>
       <c r="J247" t="n">
-        <v>15.385</v>
+        <v>15.1776</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.78</v>
       </c>
       <c r="I248" t="n">
-        <v>0.8661</v>
+        <v>0.8569</v>
       </c>
       <c r="J248" t="n">
-        <v>14.7237</v>
+        <v>14.5673</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.37</v>
       </c>
       <c r="I249" t="n">
-        <v>0.453</v>
+        <v>0.4698</v>
       </c>
       <c r="J249" t="n">
-        <v>7.701</v>
+        <v>7.9866</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.37</v>
       </c>
       <c r="I250" t="n">
-        <v>0.453</v>
+        <v>0.4698</v>
       </c>
       <c r="J250" t="n">
-        <v>7.701</v>
+        <v>7.9866</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.91</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.1651</v>
+        <v>-0.1683</v>
       </c>
       <c r="J251" t="n">
-        <v>-2.8067</v>
+        <v>-2.8611</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.68</v>
       </c>
       <c r="I252" t="n">
-        <v>1.3761</v>
+        <v>1.3525</v>
       </c>
       <c r="J252" t="n">
-        <v>33.0264</v>
+        <v>32.46</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.38</v>
       </c>
       <c r="I253" t="n">
-        <v>0.9771</v>
+        <v>0.9177</v>
       </c>
       <c r="J253" t="n">
-        <v>23.4504</v>
+        <v>22.0248</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.11</v>
       </c>
       <c r="I254" t="n">
-        <v>0.3363</v>
+        <v>0.3401</v>
       </c>
       <c r="J254" t="n">
-        <v>8.071199999999999</v>
+        <v>8.1624</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.86</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.5095</v>
+        <v>-0.4781</v>
       </c>
       <c r="J255" t="n">
-        <v>-12.228</v>
+        <v>-11.4744</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.84</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5636</v>
+        <v>-0.5269</v>
       </c>
       <c r="J256" t="n">
-        <v>-13.5264</v>
+        <v>-12.6456</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.08</v>
       </c>
       <c r="I257" t="n">
-        <v>0.2157</v>
+        <v>0.2202</v>
       </c>
       <c r="J257" t="n">
-        <v>5.1768</v>
+        <v>5.2848</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.03</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1005</v>
+        <v>0.1062</v>
       </c>
       <c r="J258" t="n">
-        <v>2.412</v>
+        <v>2.5488</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.01</v>
       </c>
       <c r="I259" t="n">
-        <v>0.0452</v>
+        <v>0.0487</v>
       </c>
       <c r="J259" t="n">
-        <v>1.0848</v>
+        <v>1.1688</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.88</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1514</v>
+        <v>-0.1656</v>
       </c>
       <c r="J260" t="n">
-        <v>-3.6336</v>
+        <v>-3.9744</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.79</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.244</v>
+        <v>-0.2584</v>
       </c>
       <c r="J261" t="n">
-        <v>-5.856</v>
+        <v>-6.2016</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.09</v>
       </c>
       <c r="I262" t="n">
-        <v>0.2319</v>
+        <v>0.2266</v>
       </c>
       <c r="J262" t="n">
-        <v>4.638</v>
+        <v>4.532</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.98</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.0061</v>
+        <v>-0.0196</v>
       </c>
       <c r="J263" t="n">
-        <v>-0.122</v>
+        <v>-0.392</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.8</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2152</v>
+        <v>-0.234</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.304</v>
+        <v>-4.68</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.57</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4318</v>
+        <v>-0.4438</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.635999999999999</v>
+        <v>-8.875999999999999</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.53</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4689</v>
+        <v>-0.4789</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.378</v>
+        <v>-9.577999999999999</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.7</v>
       </c>
       <c r="I267" t="n">
-        <v>0.8018</v>
+        <v>0.7954</v>
       </c>
       <c r="J267" t="n">
-        <v>16.036</v>
+        <v>15.908</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.69</v>
       </c>
       <c r="I268" t="n">
-        <v>0.7917</v>
+        <v>0.7861</v>
       </c>
       <c r="J268" t="n">
-        <v>15.834</v>
+        <v>15.722</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.38</v>
       </c>
       <c r="I269" t="n">
-        <v>0.47</v>
+        <v>0.4847</v>
       </c>
       <c r="J269" t="n">
-        <v>9.4</v>
+        <v>9.694000000000001</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.1</v>
       </c>
       <c r="I270" t="n">
-        <v>0.1333</v>
+        <v>0.1559</v>
       </c>
       <c r="J270" t="n">
-        <v>2.666</v>
+        <v>3.118</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.1233</v>
+        <v>-0.1264</v>
       </c>
       <c r="J271" t="n">
-        <v>-2.466</v>
+        <v>-2.528</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.98</v>
       </c>
       <c r="I272" t="n">
-        <v>1.6559</v>
+        <v>1.6583</v>
       </c>
       <c r="J272" t="n">
-        <v>31.4621</v>
+        <v>31.5077</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.94</v>
       </c>
       <c r="I273" t="n">
-        <v>1.6108</v>
+        <v>1.6112</v>
       </c>
       <c r="J273" t="n">
-        <v>30.6052</v>
+        <v>30.6128</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.52</v>
       </c>
       <c r="I274" t="n">
-        <v>1.1235</v>
+        <v>1.0935</v>
       </c>
       <c r="J274" t="n">
-        <v>21.3465</v>
+        <v>20.7765</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.98</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1982</v>
+        <v>-0.1724</v>
       </c>
       <c r="J275" t="n">
-        <v>-3.7658</v>
+        <v>-3.2756</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.76</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.8238</v>
+        <v>-0.7487</v>
       </c>
       <c r="J276" t="n">
-        <v>-15.6522</v>
+        <v>-14.2253</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.06</v>
       </c>
       <c r="I277" t="n">
-        <v>0.2149</v>
+        <v>0.2089</v>
       </c>
       <c r="J277" t="n">
-        <v>4.0831</v>
+        <v>3.9691</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.98</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.0148</v>
+        <v>-0.0264</v>
       </c>
       <c r="J278" t="n">
-        <v>-0.2812</v>
+        <v>-0.5016</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.93</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0818</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="J279" t="n">
-        <v>-1.5542</v>
+        <v>-1.8544</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.74</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.277</v>
+        <v>-0.294</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.263</v>
+        <v>-5.586</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.46</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5383</v>
+        <v>-0.5433</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.2277</v>
+        <v>-10.3227</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.54</v>
       </c>
       <c r="I282" t="n">
-        <v>1.1855</v>
+        <v>1.1527</v>
       </c>
       <c r="J282" t="n">
-        <v>28.452</v>
+        <v>27.6648</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.41</v>
       </c>
       <c r="I283" t="n">
-        <v>1.0145</v>
+        <v>0.9606</v>
       </c>
       <c r="J283" t="n">
-        <v>24.348</v>
+        <v>23.0544</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.3</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7862</v>
+        <v>0.7479</v>
       </c>
       <c r="J284" t="n">
-        <v>18.8688</v>
+        <v>17.9496</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.24</v>
       </c>
       <c r="I285" t="n">
-        <v>0.6489</v>
+        <v>0.626</v>
       </c>
       <c r="J285" t="n">
-        <v>15.5736</v>
+        <v>15.024</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.65</v>
       </c>
       <c r="I286" t="n">
-        <v>-1.05</v>
+        <v>-0.953</v>
       </c>
       <c r="J286" t="n">
-        <v>-25.2</v>
+        <v>-22.872</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.08</v>
       </c>
       <c r="I287" t="n">
-        <v>0.2424</v>
+        <v>0.2397</v>
       </c>
       <c r="J287" t="n">
-        <v>5.8176</v>
+        <v>5.7528</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.04</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1492</v>
+        <v>0.1486</v>
       </c>
       <c r="J288" t="n">
-        <v>3.5808</v>
+        <v>3.5664</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.87</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1536</v>
+        <v>-0.17</v>
       </c>
       <c r="J289" t="n">
-        <v>-3.6864</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.7</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3213</v>
+        <v>-0.336</v>
       </c>
       <c r="J290" t="n">
-        <v>-7.7112</v>
+        <v>-8.064</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.7</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3213</v>
+        <v>-0.336</v>
       </c>
       <c r="J291" t="n">
-        <v>-7.7112</v>
+        <v>-8.064</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.28</v>
       </c>
       <c r="I292" t="n">
-        <v>0.5955</v>
+        <v>0.5754</v>
       </c>
       <c r="J292" t="n">
-        <v>17.2695</v>
+        <v>16.6866</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.07</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1919</v>
+        <v>0.1976</v>
       </c>
       <c r="J293" t="n">
-        <v>5.5651</v>
+        <v>5.7304</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.89</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1415</v>
+        <v>-0.1553</v>
       </c>
       <c r="J294" t="n">
-        <v>-4.1035</v>
+        <v>-4.5037</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.87</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.163</v>
+        <v>-0.1772</v>
       </c>
       <c r="J295" t="n">
-        <v>-4.727</v>
+        <v>-5.1388</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.72</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3132</v>
+        <v>-0.3261</v>
       </c>
       <c r="J296" t="n">
-        <v>-9.082800000000001</v>
+        <v>-9.456899999999999</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.4</v>
       </c>
       <c r="I297" t="n">
-        <v>1.036</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="J297" t="n">
-        <v>30.044</v>
+        <v>28.3417</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.28</v>
       </c>
       <c r="I298" t="n">
-        <v>0.7816</v>
+        <v>0.7361</v>
       </c>
       <c r="J298" t="n">
-        <v>22.6664</v>
+        <v>21.3469</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.16</v>
       </c>
       <c r="I299" t="n">
-        <v>0.483</v>
+        <v>0.4706</v>
       </c>
       <c r="J299" t="n">
-        <v>14.007</v>
+        <v>13.6474</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.83</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5693</v>
+        <v>-0.5361</v>
       </c>
       <c r="J300" t="n">
-        <v>-16.5097</v>
+        <v>-15.5469</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.8</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6481</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="J301" t="n">
-        <v>-18.7949</v>
+        <v>-17.5856</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.13</v>
       </c>
       <c r="I302" t="n">
-        <v>0.3484</v>
+        <v>0.3405</v>
       </c>
       <c r="J302" t="n">
-        <v>7.3164</v>
+        <v>7.1505</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0764</v>
+        <v>-0.0901</v>
       </c>
       <c r="J303" t="n">
-        <v>-1.6044</v>
+        <v>-1.8921</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.83</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1942</v>
+        <v>-0.211</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.0782</v>
+        <v>-4.431</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.75</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2732</v>
+        <v>-0.2891</v>
       </c>
       <c r="J305" t="n">
-        <v>-5.7372</v>
+        <v>-6.0711</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.74</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2829</v>
+        <v>-0.2986</v>
       </c>
       <c r="J306" t="n">
-        <v>-5.9409</v>
+        <v>-6.2706</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.72</v>
       </c>
       <c r="I307" t="n">
-        <v>1.43</v>
+        <v>1.4086</v>
       </c>
       <c r="J307" t="n">
-        <v>30.03</v>
+        <v>29.5806</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.41</v>
       </c>
       <c r="I308" t="n">
-        <v>1.0312</v>
+        <v>0.976</v>
       </c>
       <c r="J308" t="n">
-        <v>21.6552</v>
+        <v>20.496</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0389</v>
+        <v>-0.0268</v>
       </c>
       <c r="J309" t="n">
-        <v>-0.8169</v>
+        <v>-0.5628</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.87</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4788</v>
+        <v>-0.451</v>
       </c>
       <c r="J310" t="n">
-        <v>-10.0548</v>
+        <v>-9.471</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6399</v>
+        <v>-0.5957</v>
       </c>
       <c r="J311" t="n">
-        <v>-13.4379</v>
+        <v>-12.5097</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.57</v>
       </c>
       <c r="I312" t="n">
-        <v>0.7402</v>
+        <v>0.7271</v>
       </c>
       <c r="J312" t="n">
-        <v>22.206</v>
+        <v>21.813</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.97</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.0553</v>
+        <v>-0.0622</v>
       </c>
       <c r="J313" t="n">
-        <v>-1.659</v>
+        <v>-1.866</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.95</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.0815</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J314" t="n">
-        <v>-2.445</v>
+        <v>-2.709</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.91</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.129</v>
+        <v>-0.14</v>
       </c>
       <c r="J315" t="n">
-        <v>-3.87</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.87</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.1729</v>
+        <v>-0.1849</v>
       </c>
       <c r="J316" t="n">
-        <v>-5.187</v>
+        <v>-5.547</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.34</v>
       </c>
       <c r="I317" t="n">
-        <v>0.5196</v>
+        <v>0.5127</v>
       </c>
       <c r="J317" t="n">
-        <v>15.588</v>
+        <v>15.381</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.97</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.0517</v>
+        <v>-0.0595</v>
       </c>
       <c r="J318" t="n">
-        <v>-1.551</v>
+        <v>-1.785</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.95</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.331</v>
+        <v>-2.625</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.92</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1136</v>
+        <v>-0.1251</v>
       </c>
       <c r="J320" t="n">
-        <v>-3.408</v>
+        <v>-3.753</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.91</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.125</v>
+        <v>-0.1369</v>
       </c>
       <c r="J321" t="n">
-        <v>-3.75</v>
+        <v>-4.107</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.03</v>
       </c>
       <c r="I322" t="n">
-        <v>0.1099</v>
+        <v>0.113</v>
       </c>
       <c r="J322" t="n">
-        <v>2.6376</v>
+        <v>2.712</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.02</v>
       </c>
       <c r="I323" t="n">
-        <v>0.0832</v>
+        <v>0.0857</v>
       </c>
       <c r="J323" t="n">
-        <v>1.9968</v>
+        <v>2.0568</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.98</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.0291</v>
+        <v>-0.0375</v>
       </c>
       <c r="J324" t="n">
-        <v>-0.6984</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.8</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2296</v>
+        <v>-0.2451</v>
       </c>
       <c r="J325" t="n">
-        <v>-5.5104</v>
+        <v>-5.8824</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.78</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2495</v>
+        <v>-0.2647</v>
       </c>
       <c r="J326" t="n">
-        <v>-5.988</v>
+        <v>-6.3528</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.32</v>
       </c>
       <c r="I327" t="n">
-        <v>0.8613</v>
+        <v>0.8084</v>
       </c>
       <c r="J327" t="n">
-        <v>20.6712</v>
+        <v>19.4016</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.24</v>
       </c>
       <c r="I328" t="n">
-        <v>0.6712</v>
+        <v>0.6413</v>
       </c>
       <c r="J328" t="n">
-        <v>16.1088</v>
+        <v>15.3912</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.18</v>
       </c>
       <c r="I329" t="n">
-        <v>0.5236</v>
+        <v>0.5095</v>
       </c>
       <c r="J329" t="n">
-        <v>12.5664</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.13</v>
       </c>
       <c r="I330" t="n">
-        <v>0.3975</v>
+        <v>0.3945</v>
       </c>
       <c r="J330" t="n">
-        <v>9.539999999999999</v>
+        <v>9.468</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.8</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6587</v>
+        <v>-0.6138</v>
       </c>
       <c r="J331" t="n">
-        <v>-15.8088</v>
+        <v>-14.7312</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.27</v>
       </c>
       <c r="I332" t="n">
-        <v>0.5278</v>
+        <v>0.5226</v>
       </c>
       <c r="J332" t="n">
-        <v>12.6672</v>
+        <v>12.5424</v>
       </c>
     </row>
     <row r="333">
@@ -15709,10 +15709,10 @@
         <v>1.15</v>
       </c>
       <c r="I334" t="n">
-        <v>0.3181</v>
+        <v>0.3268</v>
       </c>
       <c r="J334" t="n">
-        <v>7.6344</v>
+        <v>7.8432</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.99</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.0321</v>
+        <v>-0.0341</v>
       </c>
       <c r="J335" t="n">
-        <v>-0.7704</v>
+        <v>-0.8184</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.97</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.0623</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="J336" t="n">
-        <v>-1.4952</v>
+        <v>-1.6224</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.64</v>
       </c>
       <c r="I337" t="n">
-        <v>1.3261</v>
+        <v>1.2996</v>
       </c>
       <c r="J337" t="n">
-        <v>31.8264</v>
+        <v>31.1904</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.51</v>
       </c>
       <c r="I338" t="n">
-        <v>1.1609</v>
+        <v>1.1239</v>
       </c>
       <c r="J338" t="n">
-        <v>27.8616</v>
+        <v>26.9736</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.31</v>
       </c>
       <c r="I339" t="n">
-        <v>0.8243</v>
+        <v>0.7785</v>
       </c>
       <c r="J339" t="n">
-        <v>19.7832</v>
+        <v>18.684</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.6429</v>
+        <v>-0.5978</v>
       </c>
       <c r="J340" t="n">
-        <v>-15.4296</v>
+        <v>-14.3472</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.6</v>
       </c>
       <c r="I341" t="n">
-        <v>-1.1562</v>
+        <v>-1.0463</v>
       </c>
       <c r="J341" t="n">
-        <v>-27.7488</v>
+        <v>-25.1112</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7908/event_7908_evp_summary.xlsx
+++ b/database/event/7908/event_7908_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.202400000000001</v>
+        <v>8.5649</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3354</v>
+        <v>3.4828</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1097</v>
+        <v>3.2119</v>
       </c>
       <c r="E2" t="n">
-        <v>8.202400000000001</v>
+        <v>8.5649</v>
       </c>
       <c r="F2" t="n">
         <v>3.8972</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3052</v>
+        <v>4.3042</v>
       </c>
       <c r="H2" t="n">
         <v>7.964</v>
@@ -520,7 +520,7 @@
         <v>4.3005</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3052</v>
+        <v>4.3042</v>
       </c>
       <c r="K2" t="n">
         <v>97</v>
@@ -529,7 +529,7 @@
         <v>156</v>
       </c>
       <c r="M2" t="n">
-        <v>8.605700000000001</v>
+        <v>8.604700000000001</v>
       </c>
       <c r="N2" t="n">
         <v>253</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.3552</v>
+        <v>6.5003</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5843</v>
+        <v>2.6433</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2688</v>
+        <v>2.2897</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3552</v>
+        <v>6.5003</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2247</v>
+        <v>3.2248</v>
       </c>
       <c r="G3" t="n">
         <v>3.1305</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7453</v>
+        <v>5.7456</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1024</v>
+        <v>3.1026</v>
       </c>
       <c r="J3" t="n">
         <v>3.1305</v>
@@ -575,7 +575,7 @@
         <v>151</v>
       </c>
       <c r="M3" t="n">
-        <v>6.2329</v>
+        <v>6.2331</v>
       </c>
       <c r="N3" t="n">
         <v>285</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7098</v>
+        <v>5.937</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3218</v>
+        <v>2.4142</v>
       </c>
       <c r="D4" t="n">
-        <v>1.975</v>
+        <v>2.0381</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7098</v>
+        <v>5.937</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8802</v>
+        <v>2.8801</v>
       </c>
       <c r="G4" t="n">
         <v>2.8296</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6086</v>
+        <v>4.6082</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4886</v>
+        <v>2.4884</v>
       </c>
       <c r="J4" t="n">
         <v>2.8296</v>
@@ -621,7 +621,7 @@
         <v>151</v>
       </c>
       <c r="M4" t="n">
-        <v>5.3182</v>
+        <v>5.318</v>
       </c>
       <c r="N4" t="n">
         <v>285</v>
@@ -634,40 +634,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3294</v>
+        <v>5.6626</v>
       </c>
       <c r="C5" t="n">
-        <v>2.1672</v>
+        <v>2.3026</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8018</v>
+        <v>1.9155</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3294</v>
+        <v>5.6626</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9991</v>
+        <v>2.3412</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3303</v>
+        <v>3.0549</v>
       </c>
       <c r="H5" t="n">
-        <v>8.3003</v>
+        <v>2.3992</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4821</v>
+        <v>2.461</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3303</v>
+        <v>3.0549</v>
       </c>
       <c r="K5" t="n">
-        <v>215</v>
+        <v>127</v>
       </c>
       <c r="L5" t="n">
-        <v>49</v>
+        <v>137</v>
       </c>
       <c r="M5" t="n">
-        <v>5.8124</v>
+        <v>5.5159</v>
       </c>
       <c r="N5" t="n">
         <v>264</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.1811</v>
+        <v>5.0596</v>
       </c>
       <c r="C6" t="n">
-        <v>2.1068</v>
+        <v>2.0574</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7343</v>
+        <v>1.6462</v>
       </c>
       <c r="E6" t="n">
-        <v>5.1811</v>
+        <v>5.0596</v>
       </c>
       <c r="F6" t="n">
-        <v>3.248</v>
+        <v>3.2413</v>
       </c>
       <c r="G6" t="n">
         <v>1.9331</v>
       </c>
       <c r="H6" t="n">
-        <v>5.8223</v>
+        <v>5.8001</v>
       </c>
       <c r="I6" t="n">
-        <v>3.144</v>
+        <v>3.132</v>
       </c>
       <c r="J6" t="n">
         <v>1.9331</v>
@@ -713,7 +713,7 @@
         <v>151</v>
       </c>
       <c r="M6" t="n">
-        <v>5.0771</v>
+        <v>5.0651</v>
       </c>
       <c r="N6" t="n">
         <v>285</v>
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.8438</v>
+        <v>4.4326</v>
       </c>
       <c r="C7" t="n">
-        <v>1.9697</v>
+        <v>1.8025</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5808</v>
+        <v>1.3661</v>
       </c>
       <c r="E7" t="n">
-        <v>4.8438</v>
+        <v>4.4326</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1297</v>
+        <v>1.1609</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7141</v>
+        <v>3.2379</v>
       </c>
       <c r="H7" t="n">
-        <v>5.4318</v>
+        <v>1.1609</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9331</v>
+        <v>1.1908</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7141</v>
+        <v>3.2379</v>
       </c>
       <c r="K7" t="n">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6472</v>
+        <v>4.4287</v>
       </c>
       <c r="N7" t="n">
         <v>209</v>
@@ -772,40 +772,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2097</v>
+        <v>4.3189</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3052</v>
+        <v>1.7562</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8369</v>
+        <v>1.3153</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2097</v>
+        <v>4.3189</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2097</v>
+        <v>2.4987</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1.4907</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3</v>
+        <v>2.7439</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3</v>
+        <v>2.7439</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.4907</v>
       </c>
       <c r="K8" t="n">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>4.2346</v>
       </c>
       <c r="N8" t="n">
         <v>180</v>
@@ -814,369 +814,369 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8814</v>
+        <v>3.2216</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1717</v>
+        <v>1.31</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6875</v>
+        <v>0.8252</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8814</v>
+        <v>3.2216</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0197</v>
+        <v>2.8233</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1383</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>5.0688</v>
+        <v>3.4543</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7371</v>
+        <v>3.4543</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1383</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="L9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5988</v>
+        <v>3.4543</v>
       </c>
       <c r="N9" t="n">
-        <v>209</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8234</v>
+        <v>3.007</v>
       </c>
       <c r="C10" t="n">
-        <v>1.1481</v>
+        <v>1.2228</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6611</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8234</v>
+        <v>3.007</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8234</v>
+        <v>1.7039</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1.1251</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4547</v>
+        <v>1.7039</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4547</v>
+        <v>0.9201</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.1251</v>
       </c>
       <c r="K10" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4547</v>
+        <v>2.0452</v>
       </c>
       <c r="N10" t="n">
-        <v>121</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>kyousuke</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7703</v>
+        <v>2.8935</v>
       </c>
       <c r="C11" t="n">
-        <v>1.1265</v>
+        <v>1.1766</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6369</v>
+        <v>0.6786</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7703</v>
+        <v>2.8935</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6452</v>
+        <v>2.2451</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1251</v>
+        <v>0.5265</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6452</v>
+        <v>2.5132</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8884</v>
+        <v>1.3571</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1251</v>
+        <v>0.5265</v>
       </c>
       <c r="K11" t="n">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="L11" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0135</v>
+        <v>1.8836</v>
       </c>
       <c r="N11" t="n">
-        <v>285</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7602</v>
+        <v>2.5908</v>
       </c>
       <c r="C12" t="n">
-        <v>1.1224</v>
+        <v>1.0535</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6323</v>
+        <v>0.5434</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7602</v>
+        <v>2.5908</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3774</v>
+        <v>2.0713</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3828</v>
+        <v>0.2416</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9497</v>
+        <v>2.0713</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5928</v>
+        <v>2.0713</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3828</v>
+        <v>0.2416</v>
       </c>
       <c r="K12" t="n">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="L12" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9756</v>
+        <v>2.3129</v>
       </c>
       <c r="N12" t="n">
-        <v>264</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kyousuke</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7586</v>
+        <v>2.5334</v>
       </c>
       <c r="C13" t="n">
-        <v>1.1218</v>
+        <v>1.0302</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.5178</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7586</v>
+        <v>2.5334</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2451</v>
+        <v>1.4104</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5135</v>
+        <v>1.0744</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5132</v>
+        <v>1.4104</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3571</v>
+        <v>1.4467</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5135</v>
+        <v>1.0744</v>
       </c>
       <c r="K13" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="L13" t="n">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8706</v>
+        <v>2.5211</v>
       </c>
       <c r="N13" t="n">
-        <v>253</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.661</v>
+        <v>2.4472</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0821</v>
+        <v>0.9951</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5871</v>
+        <v>0.4793</v>
       </c>
       <c r="E14" t="n">
-        <v>2.661</v>
+        <v>2.4472</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2082</v>
+        <v>1.7862</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5472</v>
+        <v>0.4022</v>
       </c>
       <c r="H14" t="n">
-        <v>5.691</v>
+        <v>1.7862</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0731</v>
+        <v>1.8322</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5472</v>
+        <v>0.4022</v>
       </c>
       <c r="K14" t="n">
-        <v>215</v>
+        <v>128</v>
       </c>
       <c r="L14" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5259</v>
+        <v>2.2344</v>
       </c>
       <c r="N14" t="n">
-        <v>264</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4834</v>
+        <v>2.2967</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0099</v>
+        <v>0.9339</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5063</v>
+        <v>0.4121</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4834</v>
+        <v>2.2967</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2525</v>
+        <v>1.9188</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7691</v>
+        <v>0.4495</v>
       </c>
       <c r="H15" t="n">
-        <v>5.8369</v>
+        <v>1.9188</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1519</v>
+        <v>1.9682</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7691</v>
+        <v>0.4495</v>
       </c>
       <c r="K15" t="n">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="L15" t="n">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3828</v>
+        <v>2.4177</v>
       </c>
       <c r="N15" t="n">
-        <v>209</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3018</v>
+        <v>2.1521</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.8751</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4236</v>
+        <v>0.3475</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3018</v>
+        <v>2.1521</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3018</v>
+        <v>0.9855</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.9112</v>
       </c>
       <c r="H16" t="n">
-        <v>2.313</v>
+        <v>0.9855</v>
       </c>
       <c r="I16" t="n">
-        <v>2.313</v>
+        <v>0.9855</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.9112</v>
       </c>
       <c r="K16" t="n">
-        <v>162</v>
+        <v>92</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M16" t="n">
-        <v>2.313</v>
+        <v>1.8967</v>
       </c>
       <c r="N16" t="n">
-        <v>162</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17">
@@ -1186,40 +1186,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2893</v>
+        <v>1.9208</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.7811</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4179</v>
+        <v>0.2442</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2893</v>
+        <v>1.9208</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9736</v>
+        <v>2.1589</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6843</v>
+        <v>-0.2144</v>
       </c>
       <c r="H17" t="n">
-        <v>4.9167</v>
+        <v>2.1589</v>
       </c>
       <c r="I17" t="n">
-        <v>2.655</v>
+        <v>2.2145</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6843</v>
+        <v>-0.2144</v>
       </c>
       <c r="K17" t="n">
-        <v>215</v>
+        <v>127</v>
       </c>
       <c r="L17" t="n">
-        <v>49</v>
+        <v>137</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9707</v>
+        <v>2.0001</v>
       </c>
       <c r="N17" t="n">
         <v>264</v>
@@ -1228,231 +1228,231 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9526</v>
+        <v>1.8811</v>
       </c>
       <c r="C18" t="n">
-        <v>0.794</v>
+        <v>0.7649</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2647</v>
+        <v>0.2264</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9526</v>
+        <v>1.8811</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9526</v>
+        <v>1.013</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.8989</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9526</v>
+        <v>1.013</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9526</v>
+        <v>1.0391</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.8989</v>
       </c>
       <c r="K18" t="n">
-        <v>180</v>
+        <v>127</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9526</v>
+        <v>1.938</v>
       </c>
       <c r="N18" t="n">
-        <v>180</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>controlez</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6689</v>
+        <v>1.6517</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6786</v>
+        <v>0.6716</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1355</v>
+        <v>0.124</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6689</v>
+        <v>1.6517</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4028</v>
+        <v>1.6165</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7339</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.0336</v>
+        <v>1.6165</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6381</v>
+        <v>1.6165</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7339</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="L19" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9041999999999999</v>
+        <v>1.6165</v>
       </c>
       <c r="N19" t="n">
-        <v>209</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>controlez</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6165</v>
+        <v>1.534</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6573</v>
+        <v>0.6238</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1117</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6165</v>
+        <v>1.534</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6165</v>
+        <v>1.3602</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.1717</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6165</v>
+        <v>1.3602</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6165</v>
+        <v>1.3602</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.1717</v>
       </c>
       <c r="K20" t="n">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M20" t="n">
-        <v>1.6165</v>
+        <v>1.5319</v>
       </c>
       <c r="N20" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.5319</v>
+        <v>1.1138</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6229</v>
+        <v>0.4529</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0731</v>
+        <v>-0.1163</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5319</v>
+        <v>1.1138</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5319</v>
+        <v>2.3879</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-1.0816</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5319</v>
+        <v>2.9845</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5319</v>
+        <v>1.6116</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-1.0816</v>
       </c>
       <c r="K21" t="n">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M21" t="n">
-        <v>1.5319</v>
+        <v>0.53</v>
       </c>
       <c r="N21" t="n">
-        <v>180</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Kvem</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3068</v>
+        <v>1.0081</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5314</v>
+        <v>0.4099</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0293</v>
+        <v>-0.1635</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3068</v>
+        <v>1.0081</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3879</v>
+        <v>2.0021</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0811</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>2.9845</v>
+        <v>2.0021</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6116</v>
+        <v>2.0021</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0811</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="L22" t="n">
-        <v>156</v>
+        <v>37</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5305</v>
+        <v>1.0772</v>
       </c>
       <c r="N22" t="n">
-        <v>253</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1452</v>
+        <v>1.0003</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4657</v>
+        <v>0.4068</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1029</v>
+        <v>-0.167</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1452</v>
+        <v>1.0003</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1452</v>
+        <v>1.1624</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1452</v>
+        <v>1.1624</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1452</v>
+        <v>1.1624</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1452</v>
+        <v>1.1624</v>
       </c>
       <c r="N23" t="n">
         <v>121</v>
@@ -1504,44 +1504,44 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.138</v>
+        <v>0.8733</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4628</v>
+        <v>0.3551</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1062</v>
+        <v>-0.2237</v>
       </c>
       <c r="E24" t="n">
-        <v>1.138</v>
+        <v>0.8733</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9774</v>
+        <v>0.8933</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8394</v>
+        <v>0.0487</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9774</v>
+        <v>0.8933</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0678</v>
+        <v>0.9163</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8394</v>
+        <v>0.0487</v>
       </c>
       <c r="K24" t="n">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="L24" t="n">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2284</v>
+        <v>0.965</v>
       </c>
       <c r="N24" t="n">
         <v>209</v>
@@ -1550,277 +1550,277 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kvem</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0772</v>
+        <v>0.7986</v>
       </c>
       <c r="C25" t="n">
-        <v>0.438</v>
+        <v>0.3247</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1338</v>
+        <v>-0.2571</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0772</v>
+        <v>0.7986</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0772</v>
+        <v>0.6373</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0772</v>
+        <v>0.6373</v>
       </c>
       <c r="I25" t="n">
-        <v>1.0772</v>
+        <v>0.6373</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0772</v>
+        <v>0.6373</v>
       </c>
       <c r="N25" t="n">
-        <v>162</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7587</v>
+        <v>0.7288</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3085</v>
+        <v>0.2964</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2788</v>
+        <v>-0.2883</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7587</v>
+        <v>0.7288</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7587</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7587</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7587</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>162</v>
+        <v>120</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7587</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>162</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.6615</v>
       </c>
       <c r="C27" t="n">
-        <v>0.292</v>
+        <v>0.269</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2973</v>
+        <v>-0.3183</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.6615</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7181999999999999</v>
+        <v>1.4301</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.6714</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7181999999999999</v>
+        <v>1.4301</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7181999999999999</v>
+        <v>1.4301</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.6714</v>
       </c>
       <c r="K27" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.7586999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6273</v>
+        <v>0.2717</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2551</v>
+        <v>0.1105</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3386</v>
+        <v>-0.4925</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6273</v>
+        <v>0.2717</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6273</v>
+        <v>0.5334</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.1166</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6273</v>
+        <v>0.5334</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6273</v>
+        <v>0.5334</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.1166</v>
       </c>
       <c r="K28" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6273</v>
+        <v>0.4168</v>
       </c>
       <c r="N28" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4168</v>
+        <v>0.2434</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1695</v>
+        <v>0.099</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4345</v>
+        <v>-0.5051</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4168</v>
+        <v>0.2434</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4168</v>
+        <v>0.3278</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4168</v>
+        <v>0.3278</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4168</v>
+        <v>0.3278</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>162</v>
+        <v>120</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4168</v>
+        <v>0.3278</v>
       </c>
       <c r="N29" t="n">
-        <v>162</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3278</v>
+        <v>-0.0281</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1333</v>
+        <v>-0.0114</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.475</v>
+        <v>-0.6264</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3278</v>
+        <v>-0.0281</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3278</v>
+        <v>-0.4009</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.4887</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3278</v>
+        <v>-0.4009</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3278</v>
+        <v>-0.4112</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.4887</v>
       </c>
       <c r="K30" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3278</v>
+        <v>0.07750000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>120</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31">
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1934</v>
+        <v>-0.2229</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0786</v>
+        <v>-0.0906</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7122000000000001</v>
+        <v>-0.7134</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1934</v>
+        <v>-0.2229</v>
       </c>
       <c r="F31" t="n">
         <v>-4.0417</v>
       </c>
       <c r="G31" t="n">
-        <v>3.8483</v>
+        <v>3.8824</v>
       </c>
       <c r="H31" t="n">
         <v>-4.0417</v>
@@ -1854,7 +1854,7 @@
         <v>-2.1825</v>
       </c>
       <c r="J31" t="n">
-        <v>3.8483</v>
+        <v>3.8824</v>
       </c>
       <c r="K31" t="n">
         <v>97</v>
@@ -1863,7 +1863,7 @@
         <v>156</v>
       </c>
       <c r="M31" t="n">
-        <v>1.6658</v>
+        <v>1.6999</v>
       </c>
       <c r="N31" t="n">
         <v>253</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5712</v>
+        <v>-0.7131</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2323</v>
+        <v>-0.29</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8842</v>
+        <v>-0.9323</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5712</v>
+        <v>-0.7131</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5712</v>
+        <v>-0.3317</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.2475</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5712</v>
+        <v>-0.3317</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5712</v>
+        <v>-0.3317</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.2475</v>
       </c>
       <c r="K32" t="n">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5712</v>
+        <v>-0.5791999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>121</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5792</v>
+        <v>-0.7325</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2355</v>
+        <v>-0.2979</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8879</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5792</v>
+        <v>-0.7325</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5792</v>
+        <v>-0.5838</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5792</v>
+        <v>-0.5838</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5792</v>
+        <v>-0.5838</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>180</v>
+        <v>121</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5792</v>
+        <v>-0.5838</v>
       </c>
       <c r="N33" t="n">
-        <v>180</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34">
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9407</v>
+        <v>-0.9315</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3825</v>
+        <v>-0.3788</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0524</v>
+        <v>-1.0299</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9407</v>
+        <v>-0.9315</v>
       </c>
       <c r="F34" t="n">
         <v>-0.9407</v>
@@ -2010,47 +2010,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9915</v>
+        <v>-1.1177</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4032</v>
+        <v>-0.4545</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0756</v>
+        <v>-1.1131</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9915</v>
+        <v>-1.1177</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9915</v>
+        <v>-1.1397</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9915</v>
+        <v>-1.1397</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9915</v>
+        <v>-1.1397</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9915</v>
+        <v>-1.1397</v>
       </c>
       <c r="N35" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36">
@@ -2060,40 +2060,40 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0103</v>
+        <v>-1.214</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4108</v>
+        <v>-0.4937</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0841</v>
+        <v>-1.1561</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0103</v>
+        <v>-1.214</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.0103</v>
+        <v>-1.2024</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.1617</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.0103</v>
+        <v>-1.2024</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0103</v>
+        <v>-1.2024</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.1617</v>
       </c>
       <c r="K36" t="n">
-        <v>162</v>
+        <v>125</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0103</v>
+        <v>-1.0407</v>
       </c>
       <c r="N36" t="n">
         <v>162</v>
@@ -2102,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1397</v>
+        <v>-1.4259</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4634</v>
+        <v>-0.5798</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.143</v>
+        <v>-1.2507</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1397</v>
+        <v>-1.4259</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1397</v>
+        <v>-0.9917</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1397</v>
+        <v>-0.9917</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1397</v>
+        <v>-0.9917</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1397</v>
+        <v>-0.9917</v>
       </c>
       <c r="N37" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38">
@@ -2152,37 +2152,37 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.9452</v>
+        <v>-2.2496</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.791</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.5097</v>
+        <v>-1.6187</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.9452</v>
+        <v>-2.2496</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.9452</v>
+        <v>-1.4139</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.5313</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.9452</v>
+        <v>-1.4139</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.9452</v>
+        <v>-1.4139</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.5313</v>
       </c>
       <c r="K38" t="n">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M38" t="n">
         <v>-1.9452</v>
@@ -2198,22 +2198,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.3386</v>
+        <v>-2.472</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.951</v>
+        <v>-1.0052</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.6888</v>
+        <v>-1.718</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.3386</v>
+        <v>-2.472</v>
       </c>
       <c r="F39" t="n">
         <v>-1.1619</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.1767</v>
+        <v>-1.1771</v>
       </c>
       <c r="H39" t="n">
         <v>-1.1619</v>
@@ -2222,7 +2222,7 @@
         <v>-0.6274</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.1767</v>
+        <v>-1.1771</v>
       </c>
       <c r="K39" t="n">
         <v>97</v>
@@ -2231,7 +2231,7 @@
         <v>156</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.8041</v>
+        <v>-1.8045</v>
       </c>
       <c r="N39" t="n">
         <v>253</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.1019</v>
+        <v>-3.3557</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.2614</v>
+        <v>-1.3646</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.0363</v>
+        <v>-2.1127</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.1019</v>
+        <v>-3.3557</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.0782</v>
+        <v>-2.0786</v>
       </c>
       <c r="G40" t="n">
         <v>-1.0237</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.0782</v>
+        <v>-2.0786</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1222</v>
+        <v>-1.1224</v>
       </c>
       <c r="J40" t="n">
         <v>-1.0237</v>
@@ -2277,7 +2277,7 @@
         <v>151</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.1459</v>
+        <v>-2.1461</v>
       </c>
       <c r="N40" t="n">
         <v>285</v>
@@ -2290,40 +2290,40 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-6.8138</v>
+        <v>-3.3872</v>
       </c>
       <c r="C41" t="n">
-        <v>-2.7708</v>
+        <v>-1.3774</v>
       </c>
       <c r="D41" t="n">
-        <v>-3.726</v>
+        <v>-2.1268</v>
       </c>
       <c r="E41" t="n">
-        <v>-6.8138</v>
+        <v>-3.3872</v>
       </c>
       <c r="F41" t="n">
-        <v>-6.2803</v>
+        <v>-1.5294</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5335</v>
+        <v>-1.5333</v>
       </c>
       <c r="H41" t="n">
-        <v>-6.2803</v>
+        <v>-1.5294</v>
       </c>
       <c r="I41" t="n">
-        <v>-3.3913</v>
+        <v>-1.5688</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.5335</v>
+        <v>-1.5333</v>
       </c>
       <c r="K41" t="n">
-        <v>215</v>
+        <v>127</v>
       </c>
       <c r="L41" t="n">
-        <v>49</v>
+        <v>137</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.9248</v>
+        <v>-3.1021</v>
       </c>
       <c r="N41" t="n">
         <v>264</v>
@@ -3026,13 +3026,13 @@
         <v>22</v>
       </c>
       <c r="H17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8081</v>
+        <v>0.8213</v>
       </c>
       <c r="J17" t="n">
-        <v>17.7782</v>
+        <v>18.0686</v>
       </c>
     </row>
     <row r="18">
@@ -3066,13 +3066,13 @@
         <v>22</v>
       </c>
       <c r="H18" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3537</v>
+        <v>0.3704</v>
       </c>
       <c r="J18" t="n">
-        <v>7.7814</v>
+        <v>8.1488</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.99</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0289</v>
+        <v>-0.0292</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6358</v>
+        <v>-0.6424</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0767</v>
+        <v>-0.077</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.6874</v>
+        <v>-1.694</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.71</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3431</v>
+        <v>-0.3434</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.5482</v>
+        <v>-7.5548</v>
       </c>
     </row>
     <row r="22">
@@ -3829,10 +3829,10 @@
         <v>1.32</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6399</v>
+        <v>0.6392</v>
       </c>
       <c r="J37" t="n">
-        <v>22.3965</v>
+        <v>22.372</v>
       </c>
     </row>
     <row r="38">
@@ -3866,13 +3866,13 @@
         <v>35</v>
       </c>
       <c r="H38" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3724</v>
+        <v>0.3898</v>
       </c>
       <c r="J38" t="n">
-        <v>13.034</v>
+        <v>13.643</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.97</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0563</v>
+        <v>-0.0564</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.9705</v>
+        <v>-1.974</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.74</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3071</v>
+        <v>-0.3073</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.7485</v>
+        <v>-10.7555</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.63</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4077</v>
+        <v>-0.4079</v>
       </c>
       <c r="J41" t="n">
-        <v>-14.2695</v>
+        <v>-14.2765</v>
       </c>
     </row>
     <row r="42">
@@ -4229,10 +4229,10 @@
         <v>1.14</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3423</v>
+        <v>0.3428</v>
       </c>
       <c r="J47" t="n">
-        <v>9.9267</v>
+        <v>9.9412</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.08</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2245</v>
+        <v>0.225</v>
       </c>
       <c r="J48" t="n">
-        <v>6.5105</v>
+        <v>6.525</v>
       </c>
     </row>
     <row r="49">
@@ -4306,13 +4306,13 @@
         <v>29</v>
       </c>
       <c r="H49" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0823</v>
+        <v>-0.0949</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.3867</v>
+        <v>-2.7521</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.85</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1959</v>
+        <v>-0.1957</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.6811</v>
+        <v>-5.6753</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.67</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3694</v>
+        <v>-0.3692</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.7126</v>
+        <v>-10.7068</v>
       </c>
     </row>
     <row r="52">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -5629,10 +5629,10 @@
         <v>1.32</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4387</v>
+        <v>0.4359</v>
       </c>
       <c r="J82" t="n">
-        <v>10.5288</v>
+        <v>10.4616</v>
       </c>
     </row>
     <row r="83">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -5669,10 +5669,10 @@
         <v>1.31</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4276</v>
+        <v>0.426</v>
       </c>
       <c r="J83" t="n">
-        <v>10.2624</v>
+        <v>10.224</v>
       </c>
     </row>
     <row r="84">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -6029,10 +6029,10 @@
         <v>1.33</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6468</v>
+        <v>0.5925</v>
       </c>
       <c r="J92" t="n">
-        <v>22.638</v>
+        <v>20.7375</v>
       </c>
     </row>
     <row r="93">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -6069,10 +6069,10 @@
         <v>1.24</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5028</v>
+        <v>0.486</v>
       </c>
       <c r="J93" t="n">
-        <v>17.598</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="94">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -6229,10 +6229,10 @@
         <v>1.41</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9823</v>
+        <v>0.8434</v>
       </c>
       <c r="J97" t="n">
-        <v>34.3805</v>
+        <v>29.519</v>
       </c>
     </row>
     <row r="98">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -6269,10 +6269,10 @@
         <v>1.33</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8277</v>
+        <v>0.726</v>
       </c>
       <c r="J98" t="n">
-        <v>28.9695</v>
+        <v>25.41</v>
       </c>
     </row>
     <row r="99">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6309,10 +6309,10 @@
         <v>1.24</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6405</v>
+        <v>0.5876</v>
       </c>
       <c r="J99" t="n">
-        <v>22.4175</v>
+        <v>20.566</v>
       </c>
     </row>
     <row r="100">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -6346,13 +6346,13 @@
         <v>35</v>
       </c>
       <c r="H100" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1485</v>
+        <v>0.1797</v>
       </c>
       <c r="J100" t="n">
-        <v>5.1975</v>
+        <v>6.2895</v>
       </c>
     </row>
     <row r="101">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -6389,10 +6389,10 @@
         <v>0.67</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8979</v>
+        <v>-0.8983</v>
       </c>
       <c r="J101" t="n">
-        <v>-31.4265</v>
+        <v>-31.4405</v>
       </c>
     </row>
     <row r="102">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -6429,10 +6429,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6146</v>
+        <v>0.5688</v>
       </c>
       <c r="J102" t="n">
-        <v>17.8234</v>
+        <v>16.4952</v>
       </c>
     </row>
     <row r="103">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -6629,10 +6629,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>1.2815</v>
+        <v>1.1342</v>
       </c>
       <c r="J107" t="n">
-        <v>37.1635</v>
+        <v>32.8918</v>
       </c>
     </row>
     <row r="108">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -6669,10 +6669,10 @@
         <v>1.16</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4627</v>
+        <v>0.4558</v>
       </c>
       <c r="J108" t="n">
-        <v>13.4183</v>
+        <v>13.2182</v>
       </c>
     </row>
     <row r="109">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -7029,10 +7029,10 @@
         <v>1.51</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0943</v>
+        <v>0.947</v>
       </c>
       <c r="J117" t="n">
-        <v>18.6031</v>
+        <v>16.099</v>
       </c>
     </row>
     <row r="118">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -7069,10 +7069,10 @@
         <v>1.46</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0244</v>
+        <v>0.88</v>
       </c>
       <c r="J118" t="n">
-        <v>17.4148</v>
+        <v>14.96</v>
       </c>
     </row>
     <row r="119">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -7109,10 +7109,10 @@
         <v>1.41</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9424</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="J119" t="n">
-        <v>16.0208</v>
+        <v>13.804</v>
       </c>
     </row>
     <row r="120">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -7149,10 +7149,10 @@
         <v>1.18</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4836</v>
+        <v>0.4718</v>
       </c>
       <c r="J120" t="n">
-        <v>8.2212</v>
+        <v>8.0206</v>
       </c>
     </row>
     <row r="121">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.555</v>
+        <v>0.5246</v>
       </c>
       <c r="J122" t="n">
-        <v>11.1</v>
+        <v>10.492</v>
       </c>
     </row>
     <row r="123">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -7269,10 +7269,10 @@
         <v>1.15</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3925</v>
+        <v>0.3924</v>
       </c>
       <c r="J123" t="n">
-        <v>7.85</v>
+        <v>7.848</v>
       </c>
     </row>
     <row r="124">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -7429,10 +7429,10 @@
         <v>1.35</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.7409</v>
       </c>
       <c r="J127" t="n">
-        <v>16.946</v>
+        <v>14.818</v>
       </c>
     </row>
     <row r="128">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -7469,10 +7469,10 @@
         <v>1.33</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.7118</v>
       </c>
       <c r="J128" t="n">
-        <v>16.16</v>
+        <v>14.236</v>
       </c>
     </row>
     <row r="129">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -7509,10 +7509,10 @@
         <v>1.22</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.547</v>
       </c>
       <c r="J129" t="n">
-        <v>11.704</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="130">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -7549,10 +7549,10 @@
         <v>1.16</v>
       </c>
       <c r="I130" t="n">
-        <v>0.4531</v>
+        <v>0.4481</v>
       </c>
       <c r="J130" t="n">
-        <v>9.061999999999999</v>
+        <v>8.962</v>
       </c>
     </row>
     <row r="131">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -8626,13 +8626,13 @@
         <v>18</v>
       </c>
       <c r="H157" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6444</v>
+        <v>0.659</v>
       </c>
       <c r="J157" t="n">
-        <v>11.5992</v>
+        <v>11.862</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.96</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.0665</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.1898</v>
+        <v>-1.197</v>
       </c>
     </row>
     <row r="159">
@@ -8706,13 +8706,13 @@
         <v>18</v>
       </c>
       <c r="H159" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.172</v>
+        <v>-0.1616</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.096</v>
+        <v>-2.9088</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.75</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.292</v>
+        <v>-0.2924</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.256</v>
+        <v>-5.2632</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.64</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3934</v>
+        <v>-0.3938</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.0812</v>
+        <v>-7.0884</v>
       </c>
     </row>
     <row r="162">
@@ -9429,10 +9429,10 @@
         <v>1.45</v>
       </c>
       <c r="I177" t="n">
-        <v>0.581</v>
+        <v>0.5813</v>
       </c>
       <c r="J177" t="n">
-        <v>12.782</v>
+        <v>12.7886</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.39</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5173</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J178" t="n">
-        <v>11.3806</v>
+        <v>11.3872</v>
       </c>
     </row>
     <row r="179">
@@ -9506,13 +9506,13 @@
         <v>22</v>
       </c>
       <c r="H179" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2656</v>
+        <v>0.2534</v>
       </c>
       <c r="J179" t="n">
-        <v>5.8432</v>
+        <v>5.5748</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.1</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1742</v>
+        <v>0.1743</v>
       </c>
       <c r="J180" t="n">
-        <v>3.8324</v>
+        <v>3.8346</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.66</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3959</v>
+        <v>-0.3957</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.7098</v>
+        <v>-8.705399999999999</v>
       </c>
     </row>
     <row r="182">
@@ -12029,10 +12029,10 @@
         <v>1.11</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2633</v>
+        <v>0.2639</v>
       </c>
       <c r="J242" t="n">
-        <v>4.4761</v>
+        <v>4.4863</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.97</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0337</v>
+        <v>-0.0333</v>
       </c>
       <c r="J243" t="n">
-        <v>-0.5729</v>
+        <v>-0.5661</v>
       </c>
     </row>
     <row r="244">
@@ -12106,13 +12106,13 @@
         <v>17</v>
       </c>
       <c r="H244" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1718</v>
+        <v>-0.1822</v>
       </c>
       <c r="J244" t="n">
-        <v>-2.9206</v>
+        <v>-3.0974</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.51</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.495</v>
+        <v>-0.4948</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.414999999999999</v>
+        <v>-8.4116</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.46</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5382</v>
+        <v>-0.538</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.1494</v>
+        <v>-9.146000000000001</v>
       </c>
     </row>
     <row r="247">
@@ -12226,13 +12226,13 @@
         <v>17</v>
       </c>
       <c r="H247" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="I247" t="n">
-        <v>0.8928</v>
+        <v>0.9097</v>
       </c>
       <c r="J247" t="n">
-        <v>15.1776</v>
+        <v>15.4649</v>
       </c>
     </row>
     <row r="248">
@@ -12269,16 +12269,16 @@
         <v>1.78</v>
       </c>
       <c r="I248" t="n">
-        <v>0.8569</v>
+        <v>0.8562</v>
       </c>
       <c r="J248" t="n">
-        <v>14.5673</v>
+        <v>14.5554</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -12306,19 +12306,19 @@
         <v>17</v>
       </c>
       <c r="H249" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="I249" t="n">
-        <v>0.4698</v>
+        <v>0.4797</v>
       </c>
       <c r="J249" t="n">
-        <v>7.9866</v>
+        <v>8.1549</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -12349,10 +12349,10 @@
         <v>1.37</v>
       </c>
       <c r="I250" t="n">
-        <v>0.4698</v>
+        <v>0.4694</v>
       </c>
       <c r="J250" t="n">
-        <v>7.9866</v>
+        <v>7.9798</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.91</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.1683</v>
+        <v>-0.1687</v>
       </c>
       <c r="J251" t="n">
-        <v>-2.8611</v>
+        <v>-2.8679</v>
       </c>
     </row>
     <row r="252">
@@ -12826,13 +12826,13 @@
         <v>20</v>
       </c>
       <c r="H262" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I262" t="n">
-        <v>0.2266</v>
+        <v>0.258</v>
       </c>
       <c r="J262" t="n">
-        <v>4.532</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.98</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.0196</v>
+        <v>-0.0203</v>
       </c>
       <c r="J263" t="n">
-        <v>-0.392</v>
+        <v>-0.406</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.8</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.234</v>
+        <v>-0.2342</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.68</v>
+        <v>-4.684</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.57</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4438</v>
+        <v>-0.4442</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.875999999999999</v>
+        <v>-8.884</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.53</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4789</v>
+        <v>-0.4793</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.577999999999999</v>
+        <v>-9.586</v>
       </c>
     </row>
     <row r="267">
@@ -13226,13 +13226,13 @@
         <v>19</v>
       </c>
       <c r="H272" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="I272" t="n">
-        <v>1.6583</v>
+        <v>1.647</v>
       </c>
       <c r="J272" t="n">
-        <v>31.5077</v>
+        <v>31.293</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.94</v>
       </c>
       <c r="I273" t="n">
-        <v>1.6112</v>
+        <v>1.6116</v>
       </c>
       <c r="J273" t="n">
-        <v>30.6128</v>
+        <v>30.6204</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.52</v>
       </c>
       <c r="I274" t="n">
-        <v>1.0935</v>
+        <v>1.0937</v>
       </c>
       <c r="J274" t="n">
-        <v>20.7765</v>
+        <v>20.7803</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.98</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1724</v>
+        <v>-0.1722</v>
       </c>
       <c r="J275" t="n">
-        <v>-3.2756</v>
+        <v>-3.2718</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.76</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.7487</v>
+        <v>-0.7484</v>
       </c>
       <c r="J276" t="n">
-        <v>-14.2253</v>
+        <v>-14.2196</v>
       </c>
     </row>
     <row r="277">
@@ -13426,13 +13426,13 @@
         <v>19</v>
       </c>
       <c r="H277" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="I277" t="n">
-        <v>0.2089</v>
+        <v>0.2494</v>
       </c>
       <c r="J277" t="n">
-        <v>3.9691</v>
+        <v>4.7386</v>
       </c>
     </row>
     <row r="278">
@@ -13466,13 +13466,13 @@
         <v>19</v>
       </c>
       <c r="H278" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.0264</v>
+        <v>0.0726</v>
       </c>
       <c r="J278" t="n">
-        <v>-0.5016</v>
+        <v>1.3794</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.93</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="J279" t="n">
-        <v>-1.8544</v>
+        <v>-1.8829</v>
       </c>
     </row>
     <row r="280">
@@ -13546,13 +13546,13 @@
         <v>19</v>
       </c>
       <c r="H280" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.294</v>
+        <v>-0.2859</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.586</v>
+        <v>-5.4321</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.46</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5433</v>
+        <v>-0.5444</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.3227</v>
+        <v>-10.3436</v>
       </c>
     </row>
     <row r="282">

--- a/database/event/7908/event_7908_evp_summary.xlsx
+++ b/database/event/7908/event_7908_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.5649</v>
+        <v>8.267300000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4828</v>
+        <v>3.3618</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2119</v>
+        <v>3.1604</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5649</v>
+        <v>8.267300000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8972</v>
+        <v>3.7604</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3042</v>
+        <v>4.1434</v>
       </c>
       <c r="H2" t="n">
-        <v>7.964</v>
+        <v>7.6756</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3005</v>
+        <v>4.3096</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3042</v>
+        <v>4.1434</v>
       </c>
       <c r="K2" t="n">
         <v>97</v>
@@ -529,7 +529,7 @@
         <v>156</v>
       </c>
       <c r="M2" t="n">
-        <v>8.604700000000001</v>
+        <v>8.452999999999999</v>
       </c>
       <c r="N2" t="n">
         <v>253</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.5003</v>
+        <v>6.4072</v>
       </c>
       <c r="C3" t="n">
-        <v>2.6433</v>
+        <v>2.6054</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2897</v>
+        <v>2.313</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5003</v>
+        <v>6.4072</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2248</v>
+        <v>3.1577</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1305</v>
+        <v>3.1047</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7456</v>
+        <v>5.4126</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1026</v>
+        <v>3.039</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1305</v>
+        <v>3.1047</v>
       </c>
       <c r="K3" t="n">
         <v>134</v>
@@ -575,7 +575,7 @@
         <v>151</v>
       </c>
       <c r="M3" t="n">
-        <v>6.2331</v>
+        <v>6.1437</v>
       </c>
       <c r="N3" t="n">
         <v>285</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.937</v>
+        <v>6.091</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4142</v>
+        <v>2.4769</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0381</v>
+        <v>2.169</v>
       </c>
       <c r="E4" t="n">
-        <v>5.937</v>
+        <v>6.091</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8801</v>
+        <v>2.8577</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8296</v>
+        <v>3.006</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6082</v>
+        <v>4.2864</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4884</v>
+        <v>2.4067</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8296</v>
+        <v>3.006</v>
       </c>
       <c r="K4" t="n">
         <v>134</v>
@@ -621,7 +621,7 @@
         <v>151</v>
       </c>
       <c r="M4" t="n">
-        <v>5.318</v>
+        <v>5.412699999999999</v>
       </c>
       <c r="N4" t="n">
         <v>285</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6626</v>
+        <v>5.5444</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3026</v>
+        <v>2.2546</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9155</v>
+        <v>1.92</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6626</v>
+        <v>5.5444</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3412</v>
+        <v>2.3136</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0549</v>
+        <v>2.9643</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3992</v>
+        <v>2.3519</v>
       </c>
       <c r="I5" t="n">
-        <v>2.461</v>
+        <v>2.4147</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0549</v>
+        <v>2.9643</v>
       </c>
       <c r="K5" t="n">
         <v>127</v>
@@ -667,7 +667,7 @@
         <v>137</v>
       </c>
       <c r="M5" t="n">
-        <v>5.5159</v>
+        <v>5.379</v>
       </c>
       <c r="N5" t="n">
         <v>264</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.0596</v>
+        <v>5.0132</v>
       </c>
       <c r="C6" t="n">
-        <v>2.0574</v>
+        <v>2.0386</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6462</v>
+        <v>1.678</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0596</v>
+        <v>5.0132</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2413</v>
+        <v>3.2102</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9331</v>
+        <v>1.9178</v>
       </c>
       <c r="H6" t="n">
-        <v>5.8001</v>
+        <v>5.6098</v>
       </c>
       <c r="I6" t="n">
-        <v>3.132</v>
+        <v>3.1497</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9331</v>
+        <v>1.9178</v>
       </c>
       <c r="K6" t="n">
         <v>134</v>
@@ -713,7 +713,7 @@
         <v>151</v>
       </c>
       <c r="M6" t="n">
-        <v>5.0651</v>
+        <v>5.0675</v>
       </c>
       <c r="N6" t="n">
         <v>285</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.4326</v>
+        <v>4.3206</v>
       </c>
       <c r="C7" t="n">
-        <v>1.8025</v>
+        <v>1.7569</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3661</v>
+        <v>1.3625</v>
       </c>
       <c r="E7" t="n">
-        <v>4.4326</v>
+        <v>4.3206</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1609</v>
+        <v>1.1311</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2379</v>
+        <v>3.1558</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1609</v>
+        <v>1.1311</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1908</v>
+        <v>1.1613</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2379</v>
+        <v>3.1558</v>
       </c>
       <c r="K7" t="n">
         <v>128</v>
@@ -759,7 +759,7 @@
         <v>81</v>
       </c>
       <c r="M7" t="n">
-        <v>4.4287</v>
+        <v>4.3171</v>
       </c>
       <c r="N7" t="n">
         <v>209</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3189</v>
+        <v>4.1829</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7562</v>
+        <v>1.7009</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3153</v>
+        <v>1.2997</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3189</v>
+        <v>4.1829</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4987</v>
+        <v>2.5009</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4907</v>
+        <v>1.3525</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7439</v>
+        <v>2.7812</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7439</v>
+        <v>2.7812</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4907</v>
+        <v>1.3525</v>
       </c>
       <c r="K8" t="n">
         <v>92</v>
@@ -805,7 +805,7 @@
         <v>88</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2346</v>
+        <v>4.1337</v>
       </c>
       <c r="N8" t="n">
         <v>180</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2216</v>
+        <v>3.0725</v>
       </c>
       <c r="C9" t="n">
-        <v>1.31</v>
+        <v>1.2494</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8252</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2216</v>
+        <v>3.0725</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8233</v>
+        <v>2.6742</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4543</v>
+        <v>3.1784</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4543</v>
+        <v>3.1784</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4543</v>
+        <v>3.1784</v>
       </c>
       <c r="N9" t="n">
         <v>121</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>kyousuke</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.007</v>
+        <v>2.9872</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2228</v>
+        <v>1.2147</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="E10" t="n">
-        <v>3.007</v>
+        <v>2.9872</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7039</v>
+        <v>2.3937</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1251</v>
+        <v>0.4716</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7039</v>
+        <v>2.5442</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9201</v>
+        <v>1.4285</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1251</v>
+        <v>0.4716</v>
       </c>
       <c r="K10" t="n">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="L10" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="M10" t="n">
-        <v>2.0452</v>
+        <v>1.9001</v>
       </c>
       <c r="N10" t="n">
-        <v>285</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kyousuke</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8935</v>
+        <v>2.9204</v>
       </c>
       <c r="C11" t="n">
-        <v>1.1766</v>
+        <v>1.1876</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6786</v>
+        <v>0.7246</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8935</v>
+        <v>2.9204</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2451</v>
+        <v>1.6263</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5265</v>
+        <v>1.1161</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5132</v>
+        <v>1.6263</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3571</v>
+        <v>0.9131</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5265</v>
+        <v>1.1161</v>
       </c>
       <c r="K11" t="n">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="L11" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8836</v>
+        <v>2.0292</v>
       </c>
       <c r="N11" t="n">
-        <v>253</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5908</v>
+        <v>2.4329</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0535</v>
+        <v>0.9893</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5434</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5908</v>
+        <v>2.4329</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0713</v>
+        <v>1.9501</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2416</v>
+        <v>0.2049</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0713</v>
+        <v>1.9501</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0713</v>
+        <v>1.9501</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2416</v>
+        <v>0.2049</v>
       </c>
       <c r="K12" t="n">
         <v>125</v>
@@ -989,7 +989,7 @@
         <v>37</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3129</v>
+        <v>2.155</v>
       </c>
       <c r="N12" t="n">
         <v>162</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5334</v>
+        <v>2.3525</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0302</v>
+        <v>0.9566</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5178</v>
+        <v>0.4659</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5334</v>
+        <v>2.3525</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4104</v>
+        <v>1.2369</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0744</v>
+        <v>1.067</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4104</v>
+        <v>1.2369</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4467</v>
+        <v>1.27</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0744</v>
+        <v>1.067</v>
       </c>
       <c r="K13" t="n">
         <v>128</v>
@@ -1035,7 +1035,7 @@
         <v>81</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5211</v>
+        <v>2.337</v>
       </c>
       <c r="N13" t="n">
         <v>209</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4472</v>
+        <v>2.2713</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9951</v>
+        <v>0.9236</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4793</v>
+        <v>0.4289</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4472</v>
+        <v>2.2713</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7862</v>
+        <v>1.6722</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4022</v>
+        <v>0.3403</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7862</v>
+        <v>1.6722</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8322</v>
+        <v>1.7169</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4022</v>
+        <v>0.3403</v>
       </c>
       <c r="K14" t="n">
         <v>128</v>
@@ -1081,7 +1081,7 @@
         <v>81</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2344</v>
+        <v>2.0572</v>
       </c>
       <c r="N14" t="n">
         <v>209</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2967</v>
+        <v>2.2707</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9339</v>
+        <v>0.9234</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4121</v>
+        <v>0.4286</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2967</v>
+        <v>2.2707</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9188</v>
+        <v>1.8871</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4495</v>
+        <v>0.4552</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9188</v>
+        <v>1.8871</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9682</v>
+        <v>1.9375</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4495</v>
+        <v>0.4552</v>
       </c>
       <c r="K15" t="n">
         <v>127</v>
@@ -1127,7 +1127,7 @@
         <v>137</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4177</v>
+        <v>2.3927</v>
       </c>
       <c r="N15" t="n">
         <v>264</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1521</v>
+        <v>1.9421</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8751</v>
+        <v>0.7897</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3475</v>
+        <v>0.2789</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1521</v>
+        <v>1.9421</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9855</v>
+        <v>0.8546</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9112</v>
+        <v>0.8321</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9855</v>
+        <v>0.8546</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9855</v>
+        <v>0.8546</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9112</v>
+        <v>0.8321</v>
       </c>
       <c r="K16" t="n">
         <v>92</v>
@@ -1173,7 +1173,7 @@
         <v>88</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8967</v>
+        <v>1.6867</v>
       </c>
       <c r="N16" t="n">
         <v>180</v>
@@ -1182,35 +1182,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9208</v>
+        <v>1.7895</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7811</v>
+        <v>0.7277</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2442</v>
+        <v>0.2094</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9208</v>
+        <v>1.7895</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1589</v>
+        <v>1.0347</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2144</v>
+        <v>0.7856</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1589</v>
+        <v>1.0347</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2145</v>
+        <v>1.0624</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2144</v>
+        <v>0.7856</v>
       </c>
       <c r="K17" t="n">
         <v>127</v>
@@ -1219,7 +1219,7 @@
         <v>137</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0001</v>
+        <v>1.848</v>
       </c>
       <c r="N17" t="n">
         <v>264</v>
@@ -1228,35 +1228,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8811</v>
+        <v>1.7303</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7649</v>
+        <v>0.7036</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2264</v>
+        <v>0.1824</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8811</v>
+        <v>1.7303</v>
       </c>
       <c r="F18" t="n">
-        <v>1.013</v>
+        <v>2.0312</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8989</v>
+        <v>-0.2772</v>
       </c>
       <c r="H18" t="n">
-        <v>1.013</v>
+        <v>2.0312</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0391</v>
+        <v>2.0855</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8989</v>
+        <v>-0.2772</v>
       </c>
       <c r="K18" t="n">
         <v>127</v>
@@ -1265,7 +1265,7 @@
         <v>137</v>
       </c>
       <c r="M18" t="n">
-        <v>1.938</v>
+        <v>1.8083</v>
       </c>
       <c r="N18" t="n">
         <v>264</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6517</v>
+        <v>1.4685</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6716</v>
+        <v>0.5972</v>
       </c>
       <c r="D19" t="n">
-        <v>0.124</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6517</v>
+        <v>1.4685</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6165</v>
+        <v>1.4333</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6165</v>
+        <v>1.4333</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6165</v>
+        <v>1.4333</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6165</v>
+        <v>1.4333</v>
       </c>
       <c r="N19" t="n">
         <v>120</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.534</v>
+        <v>1.4349</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6238</v>
+        <v>0.5835</v>
       </c>
       <c r="D20" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0479</v>
       </c>
       <c r="E20" t="n">
-        <v>1.534</v>
+        <v>1.4349</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3602</v>
+        <v>1.3679</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1717</v>
+        <v>0.0649</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3602</v>
+        <v>1.3679</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3602</v>
+        <v>1.3679</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1717</v>
+        <v>0.0649</v>
       </c>
       <c r="K20" t="n">
         <v>92</v>
@@ -1357,7 +1357,7 @@
         <v>88</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5319</v>
+        <v>1.4328</v>
       </c>
       <c r="N20" t="n">
         <v>180</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1138</v>
+        <v>1.2069</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4529</v>
+        <v>0.4908</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1163</v>
+        <v>-0.056</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1138</v>
+        <v>1.2069</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3879</v>
+        <v>2.462</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0816</v>
+        <v>-1.0626</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9845</v>
+        <v>2.8007</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6116</v>
+        <v>1.5725</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0816</v>
+        <v>-1.0626</v>
       </c>
       <c r="K21" t="n">
         <v>97</v>
@@ -1403,7 +1403,7 @@
         <v>156</v>
       </c>
       <c r="M21" t="n">
-        <v>0.53</v>
+        <v>0.5099</v>
       </c>
       <c r="N21" t="n">
         <v>253</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0081</v>
+        <v>0.9701</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4099</v>
+        <v>0.3945</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1635</v>
+        <v>-0.1639</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0081</v>
+        <v>0.9701</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0021</v>
+        <v>1.9565</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.9173</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0021</v>
+        <v>1.9565</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0021</v>
+        <v>1.9565</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.9173</v>
       </c>
       <c r="K22" t="n">
         <v>125</v>
@@ -1449,7 +1449,7 @@
         <v>37</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0772</v>
+        <v>1.0392</v>
       </c>
       <c r="N22" t="n">
         <v>162</v>
@@ -1458,231 +1458,231 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0003</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4068</v>
+        <v>0.3687</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.167</v>
+        <v>-0.1927</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0003</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1624</v>
+        <v>0.9363</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.0392</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1624</v>
+        <v>0.9363</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1624</v>
+        <v>0.9613</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.0392</v>
       </c>
       <c r="K23" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1624</v>
+        <v>1.0005</v>
       </c>
       <c r="N23" t="n">
-        <v>121</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8733</v>
+        <v>0.8369</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3551</v>
+        <v>0.3403</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2237</v>
+        <v>-0.2245</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8733</v>
+        <v>0.8369</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8933</v>
+        <v>0.999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0487</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8933</v>
+        <v>0.999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9163</v>
+        <v>0.999</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0487</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="L24" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.965</v>
+        <v>0.999</v>
       </c>
       <c r="N24" t="n">
-        <v>209</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7986</v>
+        <v>0.7045</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3247</v>
+        <v>0.2865</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2571</v>
+        <v>-0.2849</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7986</v>
+        <v>0.7045</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6373</v>
+        <v>1.4639</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.6622</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6373</v>
+        <v>1.4639</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6373</v>
+        <v>1.4639</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.6622</v>
       </c>
       <c r="K25" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6373</v>
+        <v>0.8017</v>
       </c>
       <c r="N25" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7288</v>
+        <v>0.6688</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2964</v>
+        <v>0.272</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2883</v>
+        <v>-0.3011</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7288</v>
+        <v>0.6688</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.5075</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.5075</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.5075</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.5075</v>
       </c>
       <c r="N26" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6615</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>0.269</v>
+        <v>0.2605</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3183</v>
+        <v>-0.314</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6615</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4301</v>
+        <v>0.63</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.6714</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.4301</v>
+        <v>0.63</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4301</v>
+        <v>0.63</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.6714</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="L27" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7586999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="N27" t="n">
-        <v>162</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28">
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2717</v>
+        <v>0.2231</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1105</v>
+        <v>0.0907</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4925</v>
+        <v>-0.5042</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2717</v>
+        <v>0.2231</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5334</v>
+        <v>0.5072</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.1166</v>
+        <v>-0.139</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5334</v>
+        <v>0.5072</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5334</v>
+        <v>0.5072</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.1166</v>
+        <v>-0.139</v>
       </c>
       <c r="K28" t="n">
         <v>125</v>
@@ -1725,7 +1725,7 @@
         <v>37</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4168</v>
+        <v>0.3682</v>
       </c>
       <c r="N28" t="n">
         <v>162</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2434</v>
+        <v>0.1614</v>
       </c>
       <c r="C29" t="n">
-        <v>0.099</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5051</v>
+        <v>-0.5323</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2434</v>
+        <v>0.1614</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3278</v>
+        <v>0.2458</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3278</v>
+        <v>0.2458</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3278</v>
+        <v>0.2458</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3278</v>
+        <v>0.2458</v>
       </c>
       <c r="N29" t="n">
         <v>120</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0281</v>
+        <v>-0.0227</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0114</v>
+        <v>-0.0092</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6264</v>
+        <v>-0.6161</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0281</v>
+        <v>-0.0227</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4009</v>
+        <v>-3.6351</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4887</v>
+        <v>3.676</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4009</v>
+        <v>-3.6351</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4112</v>
+        <v>-2.041</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4887</v>
+        <v>3.676</v>
       </c>
       <c r="K30" t="n">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="L30" t="n">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07750000000000001</v>
+        <v>1.635</v>
       </c>
       <c r="N30" t="n">
-        <v>209</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2229</v>
+        <v>-0.0925</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0906</v>
+        <v>-0.0376</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7134</v>
+        <v>-0.6479</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2229</v>
+        <v>-0.0925</v>
       </c>
       <c r="F31" t="n">
-        <v>-4.0417</v>
+        <v>-0.4406</v>
       </c>
       <c r="G31" t="n">
-        <v>3.8824</v>
+        <v>0.464</v>
       </c>
       <c r="H31" t="n">
-        <v>-4.0417</v>
+        <v>-0.4406</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.1825</v>
+        <v>-0.4524</v>
       </c>
       <c r="J31" t="n">
-        <v>3.8824</v>
+        <v>0.464</v>
       </c>
       <c r="K31" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="L31" t="n">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="M31" t="n">
-        <v>1.6999</v>
+        <v>0.0116</v>
       </c>
       <c r="N31" t="n">
-        <v>253</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7131</v>
+        <v>-0.6995</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.29</v>
+        <v>-0.2844</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9323</v>
+        <v>-0.9244</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7131</v>
+        <v>-0.6995</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3317</v>
+        <v>-0.2897</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.2475</v>
+        <v>-0.2759</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3317</v>
+        <v>-0.2897</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3317</v>
+        <v>-0.2897</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2475</v>
+        <v>-0.2759</v>
       </c>
       <c r="K32" t="n">
         <v>92</v>
@@ -1909,7 +1909,7 @@
         <v>88</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5791999999999999</v>
+        <v>-0.5656</v>
       </c>
       <c r="N32" t="n">
         <v>180</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7325</v>
+        <v>-0.8544</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2979</v>
+        <v>-0.3474</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-0.995</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7325</v>
+        <v>-0.8544</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5838</v>
+        <v>-0.8636</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5838</v>
+        <v>-0.8636</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5838</v>
+        <v>-0.8636</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5838</v>
+        <v>-0.8636</v>
       </c>
       <c r="N33" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9315</v>
+        <v>-0.8603</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3788</v>
+        <v>-0.3498</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0299</v>
+        <v>-0.9977</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9315</v>
+        <v>-0.8603</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9407</v>
+        <v>-0.7116</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9407</v>
+        <v>-0.7116</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9407</v>
+        <v>-0.7116</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9407</v>
+        <v>-0.7116</v>
       </c>
       <c r="N34" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1177</v>
+        <v>-1.0366</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4545</v>
+        <v>-0.4215</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1131</v>
+        <v>-1.078</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1177</v>
+        <v>-1.0366</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1397</v>
+        <v>-1.0586</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.1397</v>
+        <v>-1.0586</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.1397</v>
+        <v>-1.0586</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1397</v>
+        <v>-1.0586</v>
       </c>
       <c r="N35" t="n">
         <v>120</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.214</v>
+        <v>-1.2634</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4937</v>
+        <v>-0.5138</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1561</v>
+        <v>-1.1813</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.214</v>
+        <v>-1.2634</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2024</v>
+        <v>-1.2421</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1617</v>
+        <v>0.152</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2024</v>
+        <v>-1.2421</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.2024</v>
+        <v>-1.2421</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1617</v>
+        <v>0.152</v>
       </c>
       <c r="K36" t="n">
         <v>125</v>
@@ -2093,7 +2093,7 @@
         <v>37</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0407</v>
+        <v>-1.0901</v>
       </c>
       <c r="N36" t="n">
         <v>162</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4259</v>
+        <v>-1.4965</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5798</v>
+        <v>-0.6085</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2507</v>
+        <v>-1.2875</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4259</v>
+        <v>-1.4965</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9917</v>
+        <v>-1.0623</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9917</v>
+        <v>-1.0623</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9917</v>
+        <v>-1.0623</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9917</v>
+        <v>-1.0623</v>
       </c>
       <c r="N37" t="n">
         <v>121</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.2496</v>
+        <v>-2.1187</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.9147999999999999</v>
+        <v>-0.8616</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.6187</v>
+        <v>-1.571</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.2496</v>
+        <v>-2.1187</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4139</v>
+        <v>-1.2988</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.5313</v>
+        <v>-0.5155</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.4139</v>
+        <v>-1.2988</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.4139</v>
+        <v>-1.2988</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.5313</v>
+        <v>-0.5155</v>
       </c>
       <c r="K38" t="n">
         <v>92</v>
@@ -2185,7 +2185,7 @@
         <v>88</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.9452</v>
+        <v>-1.8143</v>
       </c>
       <c r="N38" t="n">
         <v>180</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.472</v>
+        <v>-2.3405</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.0052</v>
+        <v>-0.9517</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.718</v>
+        <v>-1.672</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.472</v>
+        <v>-2.3405</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1619</v>
+        <v>-1.0344</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.1771</v>
+        <v>-1.1731</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1619</v>
+        <v>-1.0344</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6274</v>
+        <v>-0.5808</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.1771</v>
+        <v>-1.1731</v>
       </c>
       <c r="K39" t="n">
         <v>97</v>
@@ -2231,7 +2231,7 @@
         <v>156</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.8045</v>
+        <v>-1.7539</v>
       </c>
       <c r="N39" t="n">
         <v>253</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.3557</v>
+        <v>-3.0828</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.3646</v>
+        <v>-1.2536</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.1127</v>
+        <v>-2.0102</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.3557</v>
+        <v>-3.0828</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.0786</v>
+        <v>-1.8297</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.0237</v>
+        <v>-0.9997</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.0786</v>
+        <v>-1.8297</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1224</v>
+        <v>-1.0273</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.0237</v>
+        <v>-0.9997</v>
       </c>
       <c r="K40" t="n">
         <v>134</v>
@@ -2277,7 +2277,7 @@
         <v>151</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.1461</v>
+        <v>-2.027</v>
       </c>
       <c r="N40" t="n">
         <v>285</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.3872</v>
+        <v>-3.3</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.3774</v>
+        <v>-1.3419</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.1268</v>
+        <v>-2.1091</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.3872</v>
+        <v>-3.3</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.5294</v>
+        <v>-1.4753</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.5333</v>
+        <v>-1.5002</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.5294</v>
+        <v>-1.4753</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.5688</v>
+        <v>-1.5147</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.5333</v>
+        <v>-1.5002</v>
       </c>
       <c r="K41" t="n">
         <v>127</v>
@@ -2323,7 +2323,7 @@
         <v>137</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.1021</v>
+        <v>-3.0149</v>
       </c>
       <c r="N41" t="n">
         <v>264</v>
@@ -2429,10 +2429,10 @@
         <v>1.38</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5986</v>
+        <v>0.6322</v>
       </c>
       <c r="J2" t="n">
-        <v>9.5776</v>
+        <v>10.1152</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.12</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2496</v>
+        <v>0.2357</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9936</v>
+        <v>3.7712</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.049</v>
+        <v>0.0385</v>
       </c>
       <c r="J4" t="n">
-        <v>0.784</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.65</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3824</v>
+        <v>-0.3696</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.1184</v>
+        <v>-5.9136</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.27</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.705</v>
+        <v>-0.7409</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.28</v>
+        <v>-11.8544</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>2.54</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4946</v>
+        <v>1.4631</v>
       </c>
       <c r="J7" t="n">
-        <v>23.9136</v>
+        <v>23.4096</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>2.25</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2611</v>
+        <v>1.2119</v>
       </c>
       <c r="J8" t="n">
-        <v>20.1776</v>
+        <v>19.3904</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.12</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1755</v>
+        <v>0.1384</v>
       </c>
       <c r="J9" t="n">
-        <v>2.808</v>
+        <v>2.2144</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.82</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2654</v>
+        <v>-0.2509</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.2464</v>
+        <v>-4.0144</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.6</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4645</v>
+        <v>-0.4675</v>
       </c>
       <c r="J11" t="n">
-        <v>-7.432</v>
+        <v>-7.48</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>2.21</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J12" t="n">
-        <v>40.5966</v>
+        <v>43.6084</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1512</v>
+        <v>0.1261</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3264</v>
+        <v>2.7742</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.86</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4686</v>
+        <v>-0.4267</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.3092</v>
+        <v>-9.3874</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.85</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4932</v>
+        <v>-0.4519</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.8504</v>
+        <v>-9.941800000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.65</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9367</v>
+        <v>-0.9286</v>
       </c>
       <c r="J16" t="n">
-        <v>-20.6074</v>
+        <v>-20.4292</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.46</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8213</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>18.0686</v>
+        <v>16.9092</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.17</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3704</v>
+        <v>0.3161</v>
       </c>
       <c r="J18" t="n">
-        <v>8.1488</v>
+        <v>6.9542</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.99</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0292</v>
+        <v>-0.0207</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6424</v>
+        <v>-0.4554</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.077</v>
+        <v>-0.0617</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.694</v>
+        <v>-1.3574</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.71</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3434</v>
+        <v>-0.3288</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.5548</v>
+        <v>-7.2336</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9469</v>
       </c>
       <c r="J22" t="n">
-        <v>32.6128</v>
+        <v>32.1946</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8992</v>
+        <v>0.8809</v>
       </c>
       <c r="J23" t="n">
-        <v>30.5728</v>
+        <v>29.9506</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.09</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2988</v>
+        <v>0.2628</v>
       </c>
       <c r="J24" t="n">
-        <v>10.1592</v>
+        <v>8.9352</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.86</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4644</v>
+        <v>-0.4221</v>
       </c>
       <c r="J25" t="n">
-        <v>-15.7896</v>
+        <v>-14.3514</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6075</v>
+        <v>-0.5704</v>
       </c>
       <c r="J26" t="n">
-        <v>-20.655</v>
+        <v>-19.3936</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.19</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4046</v>
+        <v>0.3485</v>
       </c>
       <c r="J27" t="n">
-        <v>13.7564</v>
+        <v>11.849</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.12</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2812</v>
+        <v>0.2333</v>
       </c>
       <c r="J28" t="n">
-        <v>9.5608</v>
+        <v>7.9322</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.09</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2242</v>
+        <v>0.182</v>
       </c>
       <c r="J29" t="n">
-        <v>7.6228</v>
+        <v>6.188</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1841</v>
+        <v>0.1469</v>
       </c>
       <c r="J30" t="n">
-        <v>6.2594</v>
+        <v>4.9946</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2375</v>
+        <v>-0.2174</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.074999999999999</v>
+        <v>-7.3916</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.32</v>
       </c>
       <c r="I32" t="n">
-        <v>0.802</v>
+        <v>0.7765</v>
       </c>
       <c r="J32" t="n">
-        <v>28.07</v>
+        <v>27.1775</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.25</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6574</v>
+        <v>0.6241</v>
       </c>
       <c r="J33" t="n">
-        <v>23.009</v>
+        <v>21.8435</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5137</v>
       </c>
       <c r="J34" t="n">
-        <v>19.2465</v>
+        <v>17.9795</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.03</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1111</v>
+        <v>0.0902</v>
       </c>
       <c r="J35" t="n">
-        <v>3.8885</v>
+        <v>3.157</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0265</v>
+        <v>-0.021</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.9275</v>
+        <v>-0.735</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.32</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6392</v>
+        <v>0.5823</v>
       </c>
       <c r="J37" t="n">
-        <v>22.372</v>
+        <v>20.3805</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.17</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3898</v>
+        <v>0.334</v>
       </c>
       <c r="J38" t="n">
-        <v>13.643</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.97</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0564</v>
+        <v>-0.0447</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.974</v>
+        <v>-1.5645</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.74</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3073</v>
+        <v>-0.2896</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.7555</v>
+        <v>-10.136</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.63</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4079</v>
+        <v>-0.3981</v>
       </c>
       <c r="J41" t="n">
-        <v>-14.2765</v>
+        <v>-13.9335</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.63</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1568</v>
+        <v>1.1548</v>
       </c>
       <c r="J42" t="n">
-        <v>33.5472</v>
+        <v>33.4892</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.24</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5917</v>
+        <v>0.5799</v>
       </c>
       <c r="J43" t="n">
-        <v>17.1593</v>
+        <v>16.8171</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.21</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5433</v>
+        <v>0.5329</v>
       </c>
       <c r="J44" t="n">
-        <v>15.7557</v>
+        <v>15.4541</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.78</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.6558</v>
+        <v>-0.6217</v>
       </c>
       <c r="J45" t="n">
-        <v>-19.0182</v>
+        <v>-18.0293</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.71</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8094</v>
+        <v>-0.7876</v>
       </c>
       <c r="J46" t="n">
-        <v>-23.4726</v>
+        <v>-22.8404</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.14</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3428</v>
+        <v>0.2897</v>
       </c>
       <c r="J47" t="n">
-        <v>9.9412</v>
+        <v>8.401300000000001</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.08</v>
       </c>
       <c r="I48" t="n">
-        <v>0.225</v>
+        <v>0.1808</v>
       </c>
       <c r="J48" t="n">
-        <v>6.525</v>
+        <v>5.2432</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0949</v>
+        <v>-0.0796</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.7521</v>
+        <v>-2.3084</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.85</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1957</v>
+        <v>-0.1755</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.6753</v>
+        <v>-5.0895</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.67</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3692</v>
+        <v>-0.3556</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.7068</v>
+        <v>-10.3124</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.47</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9224</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>18.448</v>
+        <v>18.156</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.42</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8518</v>
+        <v>0.836</v>
       </c>
       <c r="J53" t="n">
-        <v>17.036</v>
+        <v>16.72</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.02</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0733</v>
+        <v>0.0569</v>
       </c>
       <c r="J54" t="n">
-        <v>1.466</v>
+        <v>1.138</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.02</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0733</v>
+        <v>0.0569</v>
       </c>
       <c r="J55" t="n">
-        <v>1.466</v>
+        <v>1.138</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.91</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3475</v>
+        <v>-0.3061</v>
       </c>
       <c r="J56" t="n">
-        <v>-6.95</v>
+        <v>-6.122</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.68</v>
       </c>
       <c r="I57" t="n">
-        <v>0.988</v>
+        <v>0.962</v>
       </c>
       <c r="J57" t="n">
-        <v>19.76</v>
+        <v>19.24</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.05</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1583</v>
+        <v>0.122</v>
       </c>
       <c r="J58" t="n">
-        <v>3.166</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.88</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1641</v>
+        <v>-0.1446</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.282</v>
+        <v>-2.892</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3513</v>
+        <v>-0.3364</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.026</v>
+        <v>-6.728</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.4</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.602</v>
+        <v>-0.6188</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.04</v>
+        <v>-12.376</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.18</v>
       </c>
       <c r="I62" t="n">
-        <v>1.7538</v>
+        <v>1.8008</v>
       </c>
       <c r="J62" t="n">
-        <v>28.0608</v>
+        <v>28.8128</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.8</v>
       </c>
       <c r="I63" t="n">
-        <v>1.3038</v>
+        <v>1.3063</v>
       </c>
       <c r="J63" t="n">
-        <v>20.8608</v>
+        <v>20.9008</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.25</v>
       </c>
       <c r="I64" t="n">
-        <v>0.577</v>
+        <v>0.574</v>
       </c>
       <c r="J64" t="n">
-        <v>9.231999999999999</v>
+        <v>9.183999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.9</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4111</v>
+        <v>-0.3758</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.5776</v>
+        <v>-6.0128</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.85</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5374</v>
+        <v>-0.505</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.5984</v>
+        <v>-8.08</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.49</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8494</v>
+        <v>0.8367</v>
       </c>
       <c r="J67" t="n">
-        <v>13.5904</v>
+        <v>13.3872</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.98</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0177</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.2832</v>
+        <v>-0.1584</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.67</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3532</v>
+        <v>-0.3385</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.6512</v>
+        <v>-5.416</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.51</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4952</v>
+        <v>-0.4935</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.9232</v>
+        <v>-7.896</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.27</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6989</v>
+        <v>-0.732</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.1824</v>
+        <v>-11.712</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>2.05</v>
       </c>
       <c r="I72" t="n">
-        <v>1.6477</v>
+        <v>1.6892</v>
       </c>
       <c r="J72" t="n">
-        <v>46.1356</v>
+        <v>47.2976</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.2</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5137</v>
+        <v>0.5053</v>
       </c>
       <c r="J73" t="n">
-        <v>14.3836</v>
+        <v>14.1484</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.15</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4252</v>
+        <v>0.3937</v>
       </c>
       <c r="J74" t="n">
-        <v>11.9056</v>
+        <v>11.0236</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0415</v>
+        <v>-0.0362</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.162</v>
+        <v>-1.0136</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.83</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.5271</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.764</v>
+        <v>-14.7588</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.57</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8647</v>
+        <v>0.833</v>
       </c>
       <c r="J77" t="n">
-        <v>24.2116</v>
+        <v>23.324</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.96</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.0702</v>
+        <v>-0.0569</v>
       </c>
       <c r="J78" t="n">
-        <v>-1.9656</v>
+        <v>-1.5932</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.92</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1206</v>
+        <v>-0.1028</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.3768</v>
+        <v>-2.8784</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.7</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3442</v>
+        <v>-0.3289</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.637600000000001</v>
+        <v>-9.209199999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.66</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3807</v>
+        <v>-0.3683</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.6596</v>
+        <v>-10.3124</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.32</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4359</v>
+        <v>0.3737</v>
       </c>
       <c r="J82" t="n">
-        <v>10.4616</v>
+        <v>8.9688</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.31</v>
       </c>
       <c r="I83" t="n">
-        <v>0.426</v>
+        <v>0.3633</v>
       </c>
       <c r="J83" t="n">
-        <v>10.224</v>
+        <v>8.719200000000001</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.23</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3364</v>
+        <v>0.2793</v>
       </c>
       <c r="J84" t="n">
-        <v>8.073600000000001</v>
+        <v>6.7032</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.03</v>
       </c>
       <c r="I85" t="n">
-        <v>0.06</v>
+        <v>0.0428</v>
       </c>
       <c r="J85" t="n">
-        <v>1.44</v>
+        <v>1.0272</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.96</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.0859</v>
+        <v>-0.0702</v>
       </c>
       <c r="J86" t="n">
-        <v>-2.0616</v>
+        <v>-1.6848</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.07</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1889</v>
+        <v>0.1761</v>
       </c>
       <c r="J87" t="n">
-        <v>4.5336</v>
+        <v>4.2264</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.85</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1853</v>
+        <v>-0.1685</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.4472</v>
+        <v>-4.044</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.78</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2535</v>
+        <v>-0.2357</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.084</v>
+        <v>-5.6568</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.67</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3557</v>
+        <v>-0.341</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.536799999999999</v>
+        <v>-8.183999999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.66</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3648</v>
+        <v>-0.3506</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.7552</v>
+        <v>-8.414400000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.33</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5925</v>
+        <v>0.5655</v>
       </c>
       <c r="J92" t="n">
-        <v>20.7375</v>
+        <v>19.7925</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.24</v>
       </c>
       <c r="I93" t="n">
-        <v>0.486</v>
+        <v>0.4439</v>
       </c>
       <c r="J93" t="n">
-        <v>17.01</v>
+        <v>15.5365</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.13</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3112</v>
+        <v>0.2598</v>
       </c>
       <c r="J94" t="n">
-        <v>10.892</v>
+        <v>9.093</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.67</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3743</v>
+        <v>-0.3616</v>
       </c>
       <c r="J95" t="n">
-        <v>-13.1005</v>
+        <v>-12.656</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.59</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4453</v>
+        <v>-0.4399</v>
       </c>
       <c r="J96" t="n">
-        <v>-15.5855</v>
+        <v>-15.3965</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.41</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8434</v>
+        <v>0.8276</v>
       </c>
       <c r="J97" t="n">
-        <v>29.519</v>
+        <v>28.966</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.33</v>
       </c>
       <c r="I98" t="n">
-        <v>0.726</v>
+        <v>0.7104</v>
       </c>
       <c r="J98" t="n">
-        <v>25.41</v>
+        <v>24.864</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.24</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5876</v>
+        <v>0.5765</v>
       </c>
       <c r="J99" t="n">
-        <v>20.566</v>
+        <v>20.1775</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.05</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1797</v>
+        <v>0.1524</v>
       </c>
       <c r="J100" t="n">
-        <v>6.2895</v>
+        <v>5.334</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.67</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8983</v>
+        <v>-0.8863</v>
       </c>
       <c r="J101" t="n">
-        <v>-31.4405</v>
+        <v>-31.0205</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5688</v>
+        <v>0.5443</v>
       </c>
       <c r="J102" t="n">
-        <v>16.4952</v>
+        <v>15.7847</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.11</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2837</v>
+        <v>0.2342</v>
       </c>
       <c r="J103" t="n">
-        <v>8.2273</v>
+        <v>6.7918</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.93</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1073</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.1117</v>
+        <v>-2.6361</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.83</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.217</v>
+        <v>-0.1967</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.293</v>
+        <v>-5.7043</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.55</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4759</v>
+        <v>-0.4737</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.8011</v>
+        <v>-13.7373</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>1.1342</v>
+        <v>1.1294</v>
       </c>
       <c r="J107" t="n">
-        <v>32.8918</v>
+        <v>32.7526</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.16</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4558</v>
+        <v>0.4252</v>
       </c>
       <c r="J108" t="n">
-        <v>13.2182</v>
+        <v>12.3308</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.09</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2928</v>
+        <v>0.259</v>
       </c>
       <c r="J109" t="n">
-        <v>8.491199999999999</v>
+        <v>7.511</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.03</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1139</v>
+        <v>0.0927</v>
       </c>
       <c r="J110" t="n">
-        <v>3.3031</v>
+        <v>2.6883</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.82</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.531</v>
       </c>
       <c r="J111" t="n">
-        <v>-16.5039</v>
+        <v>-15.399</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.06</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2243</v>
+        <v>0.1862</v>
       </c>
       <c r="J112" t="n">
-        <v>3.8131</v>
+        <v>3.1654</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.9</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1278</v>
+        <v>-0.1128</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.1726</v>
+        <v>-1.9176</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.88</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1508</v>
+        <v>-0.1352</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.5636</v>
+        <v>-2.2984</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.66</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3629</v>
+        <v>-0.3488</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.1693</v>
+        <v>-5.9296</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.45</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5476</v>
+        <v>-0.5533</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.309200000000001</v>
+        <v>-9.4061</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.51</v>
       </c>
       <c r="I117" t="n">
-        <v>0.947</v>
+        <v>0.9343</v>
       </c>
       <c r="J117" t="n">
-        <v>16.099</v>
+        <v>15.8831</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.46</v>
       </c>
       <c r="I118" t="n">
-        <v>0.88</v>
+        <v>0.8669</v>
       </c>
       <c r="J118" t="n">
-        <v>14.96</v>
+        <v>14.7373</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.41</v>
       </c>
       <c r="I119" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.7994</v>
       </c>
       <c r="J119" t="n">
-        <v>13.804</v>
+        <v>13.5898</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.18</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4718</v>
+        <v>0.4531</v>
       </c>
       <c r="J120" t="n">
-        <v>8.0206</v>
+        <v>7.7027</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.08</v>
       </c>
       <c r="I121" t="n">
-        <v>0.2356</v>
+        <v>0.2053</v>
       </c>
       <c r="J121" t="n">
-        <v>4.0052</v>
+        <v>3.4901</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5246</v>
+        <v>0.5019</v>
       </c>
       <c r="J122" t="n">
-        <v>10.492</v>
+        <v>10.038</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.15</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3924</v>
+        <v>0.3415</v>
       </c>
       <c r="J123" t="n">
-        <v>7.848</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3409</v>
+        <v>-0.3252</v>
       </c>
       <c r="J124" t="n">
-        <v>-6.818</v>
+        <v>-6.504</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.65</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3773</v>
+        <v>-0.364</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.546</v>
+        <v>-7.28</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.46</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5436</v>
+        <v>-0.5494</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.872</v>
+        <v>-10.988</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.35</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7409</v>
+        <v>0.7266</v>
       </c>
       <c r="J127" t="n">
-        <v>14.818</v>
+        <v>14.532</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.33</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7118</v>
+        <v>0.6982</v>
       </c>
       <c r="J128" t="n">
-        <v>14.236</v>
+        <v>13.964</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.22</v>
       </c>
       <c r="I129" t="n">
-        <v>0.547</v>
+        <v>0.5407</v>
       </c>
       <c r="J129" t="n">
-        <v>10.94</v>
+        <v>10.814</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.16</v>
       </c>
       <c r="I130" t="n">
-        <v>0.4481</v>
+        <v>0.4195</v>
       </c>
       <c r="J130" t="n">
-        <v>8.962</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.07</v>
       </c>
       <c r="I131" t="n">
-        <v>0.2243</v>
+        <v>0.1949</v>
       </c>
       <c r="J131" t="n">
-        <v>4.486</v>
+        <v>3.898</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.1</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3298</v>
+        <v>0.2904</v>
       </c>
       <c r="J132" t="n">
-        <v>7.9152</v>
+        <v>6.9696</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.1</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3298</v>
+        <v>0.2904</v>
       </c>
       <c r="J133" t="n">
-        <v>7.9152</v>
+        <v>6.9696</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3298</v>
+        <v>0.2904</v>
       </c>
       <c r="J134" t="n">
-        <v>7.9152</v>
+        <v>6.9696</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2212</v>
+        <v>0.1878</v>
       </c>
       <c r="J135" t="n">
-        <v>5.3088</v>
+        <v>4.5072</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.93</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2707</v>
+        <v>-0.2307</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.4968</v>
+        <v>-5.5368</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.32</v>
       </c>
       <c r="I137" t="n">
-        <v>0.633</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="J137" t="n">
-        <v>15.192</v>
+        <v>13.8024</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.19</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4199</v>
+        <v>0.3629</v>
       </c>
       <c r="J138" t="n">
-        <v>10.0776</v>
+        <v>8.7096</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0011</v>
+        <v>0.0005</v>
       </c>
       <c r="J139" t="n">
-        <v>0.0264</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.75</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2997</v>
+        <v>-0.2817</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.1928</v>
+        <v>-6.7608</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.67</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3738</v>
+        <v>-0.361</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.9712</v>
+        <v>-8.664</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.36</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5335</v>
+        <v>0.548</v>
       </c>
       <c r="J142" t="n">
-        <v>15.4715</v>
+        <v>15.892</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.09</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1783</v>
+        <v>0.162</v>
       </c>
       <c r="J143" t="n">
-        <v>5.1707</v>
+        <v>4.698</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.07</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1465</v>
+        <v>0.1305</v>
       </c>
       <c r="J144" t="n">
-        <v>4.2485</v>
+        <v>3.7845</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1016</v>
+        <v>-0.0843</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.9464</v>
+        <v>-2.4447</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.7</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3504</v>
+        <v>-0.3361</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.1616</v>
+        <v>-9.7469</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.31</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4429</v>
+        <v>0.377</v>
       </c>
       <c r="J147" t="n">
-        <v>12.8441</v>
+        <v>10.933</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.23</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3488</v>
+        <v>0.289</v>
       </c>
       <c r="J148" t="n">
-        <v>10.1152</v>
+        <v>8.381</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.03</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0697</v>
+        <v>0.0497</v>
       </c>
       <c r="J149" t="n">
-        <v>2.0213</v>
+        <v>1.4413</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.98</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0475</v>
+        <v>-0.0359</v>
       </c>
       <c r="J150" t="n">
-        <v>-1.3775</v>
+        <v>-1.0411</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.78</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2779</v>
+        <v>-0.2593</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.059100000000001</v>
+        <v>-7.5197</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.47</v>
       </c>
       <c r="I152" t="n">
-        <v>1.0681</v>
+        <v>1.076</v>
       </c>
       <c r="J152" t="n">
-        <v>19.2258</v>
+        <v>19.368</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.22</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5911</v>
+        <v>0.5564</v>
       </c>
       <c r="J153" t="n">
-        <v>10.6398</v>
+        <v>10.0152</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.15</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4371</v>
+        <v>0.4012</v>
       </c>
       <c r="J154" t="n">
-        <v>7.8678</v>
+        <v>7.2216</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.07</v>
       </c>
       <c r="I155" t="n">
-        <v>0.233</v>
+        <v>0.2028</v>
       </c>
       <c r="J155" t="n">
-        <v>4.194</v>
+        <v>3.6504</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.96</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2007</v>
+        <v>-0.1661</v>
       </c>
       <c r="J156" t="n">
-        <v>-3.6126</v>
+        <v>-2.9898</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.32</v>
       </c>
       <c r="I157" t="n">
-        <v>0.659</v>
+        <v>0.6059</v>
       </c>
       <c r="J157" t="n">
-        <v>11.862</v>
+        <v>10.9062</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.96</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0665</v>
+        <v>-0.0547</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.197</v>
+        <v>-0.9846</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.88</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1616</v>
+        <v>-0.1428</v>
       </c>
       <c r="J159" t="n">
-        <v>-2.9088</v>
+        <v>-2.5704</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.75</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2924</v>
+        <v>-0.274</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.2632</v>
+        <v>-4.932</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.64</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3938</v>
+        <v>-0.3821</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.0884</v>
+        <v>-6.8778</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.58</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2095</v>
+        <v>1.2249</v>
       </c>
       <c r="J162" t="n">
-        <v>24.19</v>
+        <v>24.498</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.56</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1827</v>
+        <v>1.197</v>
       </c>
       <c r="J163" t="n">
-        <v>23.654</v>
+        <v>23.94</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.22</v>
       </c>
       <c r="I164" t="n">
-        <v>0.586</v>
+        <v>0.5534</v>
       </c>
       <c r="J164" t="n">
-        <v>11.72</v>
+        <v>11.068</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.02</v>
       </c>
       <c r="I165" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0491</v>
       </c>
       <c r="J165" t="n">
-        <v>1.304</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.8681</v>
+        <v>-0.855</v>
       </c>
       <c r="J166" t="n">
-        <v>-17.362</v>
+        <v>-17.1</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.43</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8429</v>
+        <v>0.8042</v>
       </c>
       <c r="J167" t="n">
-        <v>16.858</v>
+        <v>16.084</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.97</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0492</v>
+        <v>-0.0395</v>
       </c>
       <c r="J168" t="n">
-        <v>-0.984</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.77</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2706</v>
+        <v>-0.2516</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.412</v>
+        <v>-5.032</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.65</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3822</v>
+        <v>-0.3694</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.644</v>
+        <v>-7.388</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.6</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4268</v>
+        <v>-0.4182</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.536</v>
+        <v>-8.364000000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.42</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6057</v>
+        <v>0.6324</v>
       </c>
       <c r="J172" t="n">
-        <v>13.3254</v>
+        <v>13.9128</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.17</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2951</v>
+        <v>0.2828</v>
       </c>
       <c r="J173" t="n">
-        <v>6.4922</v>
+        <v>6.2216</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.9</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.149</v>
+        <v>-0.1292</v>
       </c>
       <c r="J174" t="n">
-        <v>-3.278</v>
+        <v>-2.8424</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1714</v>
+        <v>-0.151</v>
       </c>
       <c r="J175" t="n">
-        <v>-3.7708</v>
+        <v>-3.322</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.75</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3031</v>
+        <v>-0.2855</v>
       </c>
       <c r="J176" t="n">
-        <v>-6.6682</v>
+        <v>-6.281</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.45</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5813</v>
+        <v>0.5105</v>
       </c>
       <c r="J177" t="n">
-        <v>12.7886</v>
+        <v>11.231</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.39</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.4486</v>
       </c>
       <c r="J178" t="n">
-        <v>11.3872</v>
+        <v>9.869199999999999</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.16</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2534</v>
+        <v>0.205</v>
       </c>
       <c r="J179" t="n">
-        <v>5.5748</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.1</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1743</v>
+        <v>0.1368</v>
       </c>
       <c r="J180" t="n">
-        <v>3.8346</v>
+        <v>3.0096</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.66</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3957</v>
+        <v>-0.3869</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.705399999999999</v>
+        <v>-8.511799999999999</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.69</v>
       </c>
       <c r="I182" t="n">
-        <v>1.378</v>
+        <v>1.4064</v>
       </c>
       <c r="J182" t="n">
-        <v>31.694</v>
+        <v>32.3472</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.15</v>
       </c>
       <c r="I183" t="n">
-        <v>0.441</v>
+        <v>0.403</v>
       </c>
       <c r="J183" t="n">
-        <v>10.143</v>
+        <v>9.269</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3945</v>
+        <v>0.3571</v>
       </c>
       <c r="J184" t="n">
-        <v>9.073499999999999</v>
+        <v>8.2133</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.09</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2943</v>
+        <v>0.2601</v>
       </c>
       <c r="J185" t="n">
-        <v>6.7689</v>
+        <v>5.9823</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.61</v>
       </c>
       <c r="I186" t="n">
-        <v>-1.0202</v>
+        <v>-1.0229</v>
       </c>
       <c r="J186" t="n">
-        <v>-23.4646</v>
+        <v>-23.5267</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.43</v>
       </c>
       <c r="I187" t="n">
-        <v>0.7907</v>
+        <v>0.7379</v>
       </c>
       <c r="J187" t="n">
-        <v>18.1861</v>
+        <v>16.9717</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.18</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3958</v>
+        <v>0.3397</v>
       </c>
       <c r="J188" t="n">
-        <v>9.103400000000001</v>
+        <v>7.8131</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.14</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3249</v>
+        <v>0.2727</v>
       </c>
       <c r="J189" t="n">
-        <v>7.4727</v>
+        <v>6.2721</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.79</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2637</v>
+        <v>-0.2443</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.0651</v>
+        <v>-5.6189</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.54</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4902</v>
+        <v>-0.4908</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.2746</v>
+        <v>-11.2884</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.23</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4784</v>
+        <v>0.4196</v>
       </c>
       <c r="J192" t="n">
-        <v>11.4816</v>
+        <v>10.0704</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.17</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3768</v>
+        <v>0.3216</v>
       </c>
       <c r="J193" t="n">
-        <v>9.043200000000001</v>
+        <v>7.7184</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.03</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0975</v>
+        <v>0.0726</v>
       </c>
       <c r="J194" t="n">
-        <v>2.34</v>
+        <v>1.7424</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.92</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1256</v>
+        <v>-0.1068</v>
       </c>
       <c r="J195" t="n">
-        <v>-3.0144</v>
+        <v>-2.5632</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.77</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2839</v>
+        <v>-0.2653</v>
       </c>
       <c r="J196" t="n">
-        <v>-6.8136</v>
+        <v>-6.3672</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.43</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0264</v>
+        <v>1.0285</v>
       </c>
       <c r="J197" t="n">
-        <v>24.6336</v>
+        <v>24.684</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.2</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5609</v>
+        <v>0.5222</v>
       </c>
       <c r="J198" t="n">
-        <v>13.4616</v>
+        <v>12.5328</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.11</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3492</v>
+        <v>0.3112</v>
       </c>
       <c r="J199" t="n">
-        <v>8.380800000000001</v>
+        <v>7.4688</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.93</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2787</v>
+        <v>-0.2384</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.6888</v>
+        <v>-5.7216</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.83</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5373</v>
+        <v>-0.497</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.8952</v>
+        <v>-11.928</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.44</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7895</v>
+        <v>0.7348</v>
       </c>
       <c r="J202" t="n">
-        <v>18.1585</v>
+        <v>16.9004</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.24</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4853</v>
+        <v>0.4265</v>
       </c>
       <c r="J203" t="n">
-        <v>11.1619</v>
+        <v>9.8095</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.03</v>
       </c>
       <c r="I204" t="n">
-        <v>0.0935</v>
+        <v>0.0706</v>
       </c>
       <c r="J204" t="n">
-        <v>2.1505</v>
+        <v>1.6238</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.9</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1528</v>
+        <v>-0.1327</v>
       </c>
       <c r="J205" t="n">
-        <v>-3.5144</v>
+        <v>-3.0521</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.73</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3257</v>
+        <v>-0.3099</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.4911</v>
+        <v>-7.1277</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.86</v>
       </c>
       <c r="I207" t="n">
-        <v>1.5949</v>
+        <v>1.6442</v>
       </c>
       <c r="J207" t="n">
-        <v>36.6827</v>
+        <v>37.8166</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.27</v>
       </c>
       <c r="I208" t="n">
-        <v>0.7023</v>
+        <v>0.6705</v>
       </c>
       <c r="J208" t="n">
-        <v>16.1529</v>
+        <v>15.4215</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.96</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1956</v>
+        <v>-0.1609</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.4988</v>
+        <v>-3.7007</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.91</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3434</v>
+        <v>-0.3017</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.8982</v>
+        <v>-6.9391</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.73</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.772</v>
+        <v>-0.7476</v>
       </c>
       <c r="J211" t="n">
-        <v>-17.756</v>
+        <v>-17.1948</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.3</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6409</v>
+        <v>0.5899</v>
       </c>
       <c r="J212" t="n">
-        <v>12.1771</v>
+        <v>11.2081</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.88</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1595</v>
+        <v>-0.1417</v>
       </c>
       <c r="J213" t="n">
-        <v>-3.0305</v>
+        <v>-2.6923</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.78</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.26</v>
+        <v>-0.2408</v>
       </c>
       <c r="J214" t="n">
-        <v>-4.94</v>
+        <v>-4.5752</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.76</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2792</v>
+        <v>-0.2605</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.3048</v>
+        <v>-4.9495</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.65</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3812</v>
+        <v>-0.3682</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.2428</v>
+        <v>-6.9958</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.88</v>
       </c>
       <c r="I217" t="n">
-        <v>1.5751</v>
+        <v>1.6151</v>
       </c>
       <c r="J217" t="n">
-        <v>29.9269</v>
+        <v>30.6869</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.55</v>
       </c>
       <c r="I218" t="n">
-        <v>1.1545</v>
+        <v>1.168</v>
       </c>
       <c r="J218" t="n">
-        <v>21.9355</v>
+        <v>22.192</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.07</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2143</v>
+        <v>0.1852</v>
       </c>
       <c r="J219" t="n">
-        <v>4.0717</v>
+        <v>3.5188</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.03</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0896</v>
+        <v>0.0688</v>
       </c>
       <c r="J220" t="n">
-        <v>1.7024</v>
+        <v>1.3072</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.9</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3945</v>
+        <v>-0.3558</v>
       </c>
       <c r="J221" t="n">
-        <v>-7.4955</v>
+        <v>-6.7602</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.24</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.4634</v>
       </c>
       <c r="J222" t="n">
-        <v>11.9761</v>
+        <v>10.6582</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.03</v>
       </c>
       <c r="I223" t="n">
-        <v>0.1114</v>
+        <v>0.0823</v>
       </c>
       <c r="J223" t="n">
-        <v>2.5622</v>
+        <v>1.8929</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.98</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0382</v>
+        <v>-0.0298</v>
       </c>
       <c r="J224" t="n">
-        <v>-0.8786</v>
+        <v>-0.6854</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.75</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2944</v>
+        <v>-0.276</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.7712</v>
+        <v>-6.348</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.65</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3867</v>
+        <v>-0.3746</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.8941</v>
+        <v>-8.6158</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.6</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2603</v>
+        <v>1.2805</v>
       </c>
       <c r="J227" t="n">
-        <v>28.9869</v>
+        <v>29.4515</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.23</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6219</v>
+        <v>0.5859</v>
       </c>
       <c r="J228" t="n">
-        <v>14.3037</v>
+        <v>13.4757</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.02</v>
+        <v>-0.0149</v>
       </c>
       <c r="J229" t="n">
-        <v>-0.46</v>
+        <v>-0.3427</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.97</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1578</v>
+        <v>-0.1263</v>
       </c>
       <c r="J230" t="n">
-        <v>-3.6294</v>
+        <v>-2.9049</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.82</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5655</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="J231" t="n">
-        <v>-13.0065</v>
+        <v>-12.1141</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.81</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4482</v>
+        <v>1.4765</v>
       </c>
       <c r="J232" t="n">
-        <v>21.723</v>
+        <v>22.1475</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.69</v>
       </c>
       <c r="I233" t="n">
-        <v>1.3024</v>
+        <v>1.3235</v>
       </c>
       <c r="J233" t="n">
-        <v>19.536</v>
+        <v>19.8525</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.45</v>
       </c>
       <c r="I234" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="J234" t="n">
-        <v>14.901</v>
+        <v>14.994</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.29</v>
       </c>
       <c r="I235" t="n">
-        <v>0.6965</v>
+        <v>0.6776</v>
       </c>
       <c r="J235" t="n">
-        <v>10.4475</v>
+        <v>10.164</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.15</v>
       </c>
       <c r="I236" t="n">
-        <v>0.3914</v>
+        <v>0.3591</v>
       </c>
       <c r="J236" t="n">
-        <v>5.871</v>
+        <v>5.3865</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.26</v>
       </c>
       <c r="I237" t="n">
-        <v>0.6125</v>
+        <v>0.5697</v>
       </c>
       <c r="J237" t="n">
-        <v>9.1875</v>
+        <v>8.545500000000001</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.18</v>
       </c>
       <c r="I238" t="n">
-        <v>0.4689</v>
+        <v>0.4218</v>
       </c>
       <c r="J238" t="n">
-        <v>7.0335</v>
+        <v>6.327</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.6</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4168</v>
+        <v>-0.4067</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.252</v>
+        <v>-6.1005</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.51</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4958</v>
+        <v>-0.4943</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.437</v>
+        <v>-7.4145</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.4</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.6027</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.853</v>
+        <v>-9.0405</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.11</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2639</v>
+        <v>0.2574</v>
       </c>
       <c r="J242" t="n">
-        <v>4.4863</v>
+        <v>4.3758</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.97</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0333</v>
+        <v>-0.0236</v>
       </c>
       <c r="J243" t="n">
-        <v>-0.5661</v>
+        <v>-0.4012</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.85</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1822</v>
+        <v>-0.1661</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.0974</v>
+        <v>-2.8237</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.51</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4948</v>
+        <v>-0.493</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.4116</v>
+        <v>-8.381</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.46</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.538</v>
+        <v>-0.5421</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.146000000000001</v>
+        <v>-9.2157</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.84</v>
       </c>
       <c r="I247" t="n">
-        <v>0.9097</v>
+        <v>0.8407</v>
       </c>
       <c r="J247" t="n">
-        <v>15.4649</v>
+        <v>14.2919</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.78</v>
       </c>
       <c r="I248" t="n">
-        <v>0.8562</v>
+        <v>0.7859</v>
       </c>
       <c r="J248" t="n">
-        <v>14.5554</v>
+        <v>13.3603</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.38</v>
       </c>
       <c r="I249" t="n">
-        <v>0.4797</v>
+        <v>0.4183</v>
       </c>
       <c r="J249" t="n">
-        <v>8.1549</v>
+        <v>7.1111</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.37</v>
       </c>
       <c r="I250" t="n">
-        <v>0.4694</v>
+        <v>0.4086</v>
       </c>
       <c r="J250" t="n">
-        <v>7.9798</v>
+        <v>6.9462</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.91</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.1687</v>
+        <v>-0.1525</v>
       </c>
       <c r="J251" t="n">
-        <v>-2.8679</v>
+        <v>-2.5925</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.68</v>
       </c>
       <c r="I252" t="n">
-        <v>1.3525</v>
+        <v>1.3773</v>
       </c>
       <c r="J252" t="n">
-        <v>32.46</v>
+        <v>33.0552</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.38</v>
       </c>
       <c r="I253" t="n">
-        <v>0.9177</v>
+        <v>0.9019</v>
       </c>
       <c r="J253" t="n">
-        <v>22.0248</v>
+        <v>21.6456</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.11</v>
       </c>
       <c r="I254" t="n">
-        <v>0.3401</v>
+        <v>0.3058</v>
       </c>
       <c r="J254" t="n">
-        <v>8.1624</v>
+        <v>7.3392</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.86</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.4781</v>
+        <v>-0.4374</v>
       </c>
       <c r="J255" t="n">
-        <v>-11.4744</v>
+        <v>-10.4976</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.84</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5269</v>
+        <v>-0.4877</v>
       </c>
       <c r="J256" t="n">
-        <v>-12.6456</v>
+        <v>-11.7048</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.08</v>
       </c>
       <c r="I257" t="n">
-        <v>0.2202</v>
+        <v>0.1765</v>
       </c>
       <c r="J257" t="n">
-        <v>5.2848</v>
+        <v>4.236</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.03</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1062</v>
+        <v>0.0781</v>
       </c>
       <c r="J258" t="n">
-        <v>2.5488</v>
+        <v>1.8744</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.01</v>
       </c>
       <c r="I259" t="n">
-        <v>0.0487</v>
+        <v>0.0325</v>
       </c>
       <c r="J259" t="n">
-        <v>1.1688</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.88</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1656</v>
+        <v>-0.1458</v>
       </c>
       <c r="J260" t="n">
-        <v>-3.9744</v>
+        <v>-3.4992</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.79</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2584</v>
+        <v>-0.2387</v>
       </c>
       <c r="J261" t="n">
-        <v>-6.2016</v>
+        <v>-5.7288</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.11</v>
       </c>
       <c r="I262" t="n">
-        <v>0.258</v>
+        <v>0.2495</v>
       </c>
       <c r="J262" t="n">
-        <v>5.16</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.98</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.0203</v>
+        <v>-0.0128</v>
       </c>
       <c r="J263" t="n">
-        <v>-0.406</v>
+        <v>-0.256</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.8</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2342</v>
+        <v>-0.2168</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.684</v>
+        <v>-4.336</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.57</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4442</v>
+        <v>-0.4368</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.884</v>
+        <v>-8.736000000000001</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.53</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4793</v>
+        <v>-0.4758</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.586</v>
+        <v>-9.516</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.7</v>
       </c>
       <c r="I267" t="n">
-        <v>0.7954</v>
+        <v>0.7238</v>
       </c>
       <c r="J267" t="n">
-        <v>15.908</v>
+        <v>14.476</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.69</v>
       </c>
       <c r="I268" t="n">
-        <v>0.7861</v>
+        <v>0.7144</v>
       </c>
       <c r="J268" t="n">
-        <v>15.722</v>
+        <v>14.288</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.38</v>
       </c>
       <c r="I269" t="n">
-        <v>0.4847</v>
+        <v>0.4209</v>
       </c>
       <c r="J269" t="n">
-        <v>9.694000000000001</v>
+        <v>8.417999999999999</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.1</v>
       </c>
       <c r="I270" t="n">
-        <v>0.1559</v>
+        <v>0.1218</v>
       </c>
       <c r="J270" t="n">
-        <v>3.118</v>
+        <v>2.436</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.1264</v>
+        <v>-0.1102</v>
       </c>
       <c r="J271" t="n">
-        <v>-2.528</v>
+        <v>-2.204</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.97</v>
       </c>
       <c r="I272" t="n">
-        <v>1.647</v>
+        <v>1.6904</v>
       </c>
       <c r="J272" t="n">
-        <v>31.293</v>
+        <v>32.1176</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.94</v>
       </c>
       <c r="I273" t="n">
-        <v>1.6116</v>
+        <v>1.6518</v>
       </c>
       <c r="J273" t="n">
-        <v>30.6204</v>
+        <v>31.3842</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.52</v>
       </c>
       <c r="I274" t="n">
-        <v>1.0937</v>
+        <v>1.1088</v>
       </c>
       <c r="J274" t="n">
-        <v>20.7803</v>
+        <v>21.0672</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.98</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1722</v>
+        <v>-0.1497</v>
       </c>
       <c r="J275" t="n">
-        <v>-3.2718</v>
+        <v>-2.8443</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.76</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.7484</v>
+        <v>-0.7305</v>
       </c>
       <c r="J276" t="n">
-        <v>-14.2196</v>
+        <v>-13.8795</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.08</v>
       </c>
       <c r="I277" t="n">
-        <v>0.2494</v>
+        <v>0.2053</v>
       </c>
       <c r="J277" t="n">
-        <v>4.7386</v>
+        <v>3.9007</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.01</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0726</v>
+        <v>0.0532</v>
       </c>
       <c r="J278" t="n">
-        <v>1.3794</v>
+        <v>1.0108</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.93</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.0852</v>
       </c>
       <c r="J279" t="n">
-        <v>-1.8829</v>
+        <v>-1.6188</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.75</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2859</v>
+        <v>-0.2677</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.4321</v>
+        <v>-5.0863</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.46</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5444</v>
+        <v>-0.5503</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.3436</v>
+        <v>-10.4557</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.54</v>
       </c>
       <c r="I282" t="n">
-        <v>1.1527</v>
+        <v>1.1658</v>
       </c>
       <c r="J282" t="n">
-        <v>27.6648</v>
+        <v>27.9792</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.41</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9606</v>
+        <v>0.9516</v>
       </c>
       <c r="J283" t="n">
-        <v>23.0544</v>
+        <v>22.8384</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.3</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7479</v>
+        <v>0.7218</v>
       </c>
       <c r="J284" t="n">
-        <v>17.9496</v>
+        <v>17.3232</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.24</v>
       </c>
       <c r="I285" t="n">
-        <v>0.626</v>
+        <v>0.5952</v>
       </c>
       <c r="J285" t="n">
-        <v>15.024</v>
+        <v>14.2848</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.65</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.953</v>
+        <v>-0.95</v>
       </c>
       <c r="J286" t="n">
-        <v>-22.872</v>
+        <v>-22.8</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.08</v>
       </c>
       <c r="I287" t="n">
-        <v>0.2397</v>
+        <v>0.1951</v>
       </c>
       <c r="J287" t="n">
-        <v>5.7528</v>
+        <v>4.6824</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.04</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1486</v>
+        <v>0.1144</v>
       </c>
       <c r="J288" t="n">
-        <v>3.5664</v>
+        <v>2.7456</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.87</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.17</v>
+        <v>-0.1517</v>
       </c>
       <c r="J289" t="n">
-        <v>-4.08</v>
+        <v>-3.6408</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.7</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.336</v>
+        <v>-0.3198</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.064</v>
+        <v>-7.6752</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.7</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.336</v>
+        <v>-0.3198</v>
       </c>
       <c r="J291" t="n">
-        <v>-8.064</v>
+        <v>-7.6752</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.28</v>
       </c>
       <c r="I292" t="n">
-        <v>0.5754</v>
+        <v>0.5172</v>
       </c>
       <c r="J292" t="n">
-        <v>16.6866</v>
+        <v>14.9988</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.07</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1976</v>
+        <v>0.1564</v>
       </c>
       <c r="J293" t="n">
-        <v>5.7304</v>
+        <v>4.5356</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.89</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1553</v>
+        <v>-0.1357</v>
       </c>
       <c r="J294" t="n">
-        <v>-4.5037</v>
+        <v>-3.9353</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.87</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1772</v>
+        <v>-0.157</v>
       </c>
       <c r="J295" t="n">
-        <v>-5.1388</v>
+        <v>-4.553</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.72</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3261</v>
+        <v>-0.3095</v>
       </c>
       <c r="J296" t="n">
-        <v>-9.456899999999999</v>
+        <v>-8.9755</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.4</v>
       </c>
       <c r="I297" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9704</v>
       </c>
       <c r="J297" t="n">
-        <v>28.3417</v>
+        <v>28.1416</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.28</v>
       </c>
       <c r="I298" t="n">
-        <v>0.7361</v>
+        <v>0.705</v>
       </c>
       <c r="J298" t="n">
-        <v>21.3469</v>
+        <v>20.445</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.16</v>
       </c>
       <c r="I299" t="n">
-        <v>0.4706</v>
+        <v>0.4305</v>
       </c>
       <c r="J299" t="n">
-        <v>13.6474</v>
+        <v>12.4845</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.83</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5361</v>
+        <v>-0.4957</v>
       </c>
       <c r="J300" t="n">
-        <v>-15.5469</v>
+        <v>-14.3753</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.8</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.569</v>
       </c>
       <c r="J301" t="n">
-        <v>-17.5856</v>
+        <v>-16.501</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.13</v>
       </c>
       <c r="I302" t="n">
-        <v>0.3405</v>
+        <v>0.2891</v>
       </c>
       <c r="J302" t="n">
-        <v>7.1505</v>
+        <v>6.0711</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0901</v>
+        <v>-0.0765</v>
       </c>
       <c r="J303" t="n">
-        <v>-1.8921</v>
+        <v>-1.6065</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.83</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.211</v>
+        <v>-0.1916</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.431</v>
+        <v>-4.0236</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.75</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2891</v>
+        <v>-0.2708</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.0711</v>
+        <v>-5.6868</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.74</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2986</v>
+        <v>-0.2806</v>
       </c>
       <c r="J306" t="n">
-        <v>-6.2706</v>
+        <v>-5.8926</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.72</v>
       </c>
       <c r="I307" t="n">
-        <v>1.4086</v>
+        <v>1.4382</v>
       </c>
       <c r="J307" t="n">
-        <v>29.5806</v>
+        <v>30.2022</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.41</v>
       </c>
       <c r="I308" t="n">
-        <v>0.976</v>
+        <v>0.9685</v>
       </c>
       <c r="J308" t="n">
-        <v>20.496</v>
+        <v>20.3385</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0268</v>
+        <v>-0.0213</v>
       </c>
       <c r="J309" t="n">
-        <v>-0.5628</v>
+        <v>-0.4473</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.87</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.451</v>
+        <v>-0.4095</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.471</v>
+        <v>-8.599500000000001</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5957</v>
+        <v>-0.5593</v>
       </c>
       <c r="J311" t="n">
-        <v>-12.5097</v>
+        <v>-11.7453</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.57</v>
       </c>
       <c r="I312" t="n">
-        <v>0.7271</v>
+        <v>0.659</v>
       </c>
       <c r="J312" t="n">
-        <v>21.813</v>
+        <v>19.77</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.97</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.0622</v>
+        <v>-0.0486</v>
       </c>
       <c r="J313" t="n">
-        <v>-1.866</v>
+        <v>-1.458</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.95</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.0738</v>
       </c>
       <c r="J314" t="n">
-        <v>-2.709</v>
+        <v>-2.214</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.91</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.14</v>
+        <v>-0.1204</v>
       </c>
       <c r="J315" t="n">
-        <v>-4.2</v>
+        <v>-3.612</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.87</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.1849</v>
+        <v>-0.1643</v>
       </c>
       <c r="J316" t="n">
-        <v>-5.547</v>
+        <v>-4.929</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.34</v>
       </c>
       <c r="I317" t="n">
-        <v>0.5127</v>
+        <v>0.5243</v>
       </c>
       <c r="J317" t="n">
-        <v>15.381</v>
+        <v>15.729</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.97</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.0595</v>
+        <v>-0.0465</v>
       </c>
       <c r="J318" t="n">
-        <v>-1.785</v>
+        <v>-1.395</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.95</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.625</v>
+        <v>-2.142</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.92</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1251</v>
+        <v>-0.1064</v>
       </c>
       <c r="J320" t="n">
-        <v>-3.753</v>
+        <v>-3.192</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.91</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.1369</v>
+        <v>-0.1176</v>
       </c>
       <c r="J321" t="n">
-        <v>-4.107</v>
+        <v>-3.528</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.03</v>
       </c>
       <c r="I322" t="n">
-        <v>0.113</v>
+        <v>0.0837</v>
       </c>
       <c r="J322" t="n">
-        <v>2.712</v>
+        <v>2.0088</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.02</v>
       </c>
       <c r="I323" t="n">
-        <v>0.0857</v>
+        <v>0.0614</v>
       </c>
       <c r="J323" t="n">
-        <v>2.0568</v>
+        <v>1.4736</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.98</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.0375</v>
+        <v>-0.0293</v>
       </c>
       <c r="J324" t="n">
-        <v>-0.9</v>
+        <v>-0.7032</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.8</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2451</v>
+        <v>-0.2252</v>
       </c>
       <c r="J325" t="n">
-        <v>-5.8824</v>
+        <v>-5.4048</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.78</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2647</v>
+        <v>-0.2453</v>
       </c>
       <c r="J326" t="n">
-        <v>-6.3528</v>
+        <v>-5.8872</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.32</v>
       </c>
       <c r="I327" t="n">
-        <v>0.8084</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="J327" t="n">
-        <v>19.4016</v>
+        <v>18.7872</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.24</v>
       </c>
       <c r="I328" t="n">
-        <v>0.6413</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="J328" t="n">
-        <v>15.3912</v>
+        <v>14.5536</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.18</v>
       </c>
       <c r="I329" t="n">
-        <v>0.5095</v>
+        <v>0.4715</v>
       </c>
       <c r="J329" t="n">
-        <v>12.228</v>
+        <v>11.316</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.13</v>
       </c>
       <c r="I330" t="n">
-        <v>0.3945</v>
+        <v>0.3571</v>
       </c>
       <c r="J330" t="n">
-        <v>9.468</v>
+        <v>8.570399999999999</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.8</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6138</v>
+        <v>-0.5777</v>
       </c>
       <c r="J331" t="n">
-        <v>-14.7312</v>
+        <v>-13.8648</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.27</v>
       </c>
       <c r="I332" t="n">
-        <v>0.5226</v>
+        <v>0.4637</v>
       </c>
       <c r="J332" t="n">
-        <v>12.5424</v>
+        <v>11.1288</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.23</v>
       </c>
       <c r="I333" t="n">
-        <v>0.4595</v>
+        <v>0.4024</v>
       </c>
       <c r="J333" t="n">
-        <v>11.028</v>
+        <v>9.6576</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.15</v>
       </c>
       <c r="I334" t="n">
-        <v>0.3268</v>
+        <v>0.2772</v>
       </c>
       <c r="J334" t="n">
-        <v>7.8432</v>
+        <v>6.6528</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.99</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.0341</v>
+        <v>-0.0249</v>
       </c>
       <c r="J335" t="n">
-        <v>-0.8184</v>
+        <v>-0.5976</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.97</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0534</v>
       </c>
       <c r="J336" t="n">
-        <v>-1.6224</v>
+        <v>-1.2816</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.64</v>
       </c>
       <c r="I337" t="n">
-        <v>1.2996</v>
+        <v>1.3207</v>
       </c>
       <c r="J337" t="n">
-        <v>31.1904</v>
+        <v>31.6968</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.51</v>
       </c>
       <c r="I338" t="n">
-        <v>1.1239</v>
+        <v>1.1363</v>
       </c>
       <c r="J338" t="n">
-        <v>26.9736</v>
+        <v>27.2712</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.31</v>
       </c>
       <c r="I339" t="n">
-        <v>0.7785</v>
+        <v>0.7519</v>
       </c>
       <c r="J339" t="n">
-        <v>18.684</v>
+        <v>18.0456</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.5978</v>
+        <v>-0.5618</v>
       </c>
       <c r="J340" t="n">
-        <v>-14.3472</v>
+        <v>-13.4832</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.6</v>
       </c>
       <c r="I341" t="n">
-        <v>-1.0463</v>
+        <v>-1.0537</v>
       </c>
       <c r="J341" t="n">
-        <v>-25.1112</v>
+        <v>-25.2888</v>
       </c>
     </row>
   </sheetData>
